--- a/docs/design/ACSMS-SCR-014/【日本農業新聞様】VTIジャパン_クラウド版購読者管理システム_API設計書_購読者明細検索画面_V1.0.xlsx
+++ b/docs/design/ACSMS-SCR-014/【日本農業新聞様】VTIジャパン_クラウド版購読者管理システム_API設計書_購読者明細検索画面_V1.0.xlsx
@@ -1354,7 +1354,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG5"/>
+  <dimension ref="A1:AG7"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="4.25" customWidth="1" min="1" max="1"/>
@@ -1691,19 +1691,146 @@
       <c r="AF5" s="10" t="n"/>
       <c r="AG5" s="11" t="n"/>
     </row>
+    <row r="6" ht="19.5" customHeight="1">
+      <c r="A6" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="11" t="n"/>
+      <c r="C6" s="18" t="inlineStr">
+        <is>
+          <t>2026/07/17</t>
+        </is>
+      </c>
+      <c r="D6" s="10" t="n"/>
+      <c r="E6" s="10" t="n"/>
+      <c r="F6" s="10" t="n"/>
+      <c r="G6" s="11" t="n"/>
+      <c r="H6" s="17" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="I6" s="10" t="n"/>
+      <c r="J6" s="11" t="n"/>
+      <c r="K6" s="17" t="inlineStr">
+        <is>
+          <t>Tran Duc Tuyen</t>
+        </is>
+      </c>
+      <c r="L6" s="10" t="n"/>
+      <c r="M6" s="10" t="n"/>
+      <c r="N6" s="10" t="n"/>
+      <c r="O6" s="10" t="n"/>
+      <c r="P6" s="10" t="n"/>
+      <c r="Q6" s="11" t="n"/>
+      <c r="R6" s="19" t="inlineStr">
+        <is>
+          <t>顧客要件 2026-07 改訂：失効単価参照フィルタ `inactive_tanka_flg`（真偽・失効のみ）を **有効単価フラグ `active_tanka_flg`（トライステート：true=有効単価参照のみ / false=失効単価参照のみ / 省略=両方）** へ変更。UI を単価一覧(SCR-006)と同一のラジオ（有効/無効）に統一。SCR-020 の失効単価エラーからの導線(`?inactive_tanka=1`)は「無効(false)」で初期選択。JOIN の active_flg はパラメータバインド。</t>
+        </is>
+      </c>
+      <c r="S6" s="10" t="n"/>
+      <c r="T6" s="10" t="n"/>
+      <c r="U6" s="10" t="n"/>
+      <c r="V6" s="11" t="n"/>
+      <c r="W6" s="17" t="inlineStr">
+        <is>
+          <t>Nguyen Huy Dat</t>
+        </is>
+      </c>
+      <c r="X6" s="10" t="n"/>
+      <c r="Y6" s="10" t="n"/>
+      <c r="Z6" s="10" t="n"/>
+      <c r="AA6" s="11" t="n"/>
+      <c r="AB6" s="17" t="inlineStr">
+        <is>
+          <t>Nguyen Huy Dat</t>
+        </is>
+      </c>
+      <c r="AC6" s="10" t="n"/>
+      <c r="AD6" s="10" t="n"/>
+      <c r="AE6" s="10" t="n"/>
+      <c r="AF6" s="10" t="n"/>
+      <c r="AG6" s="11" t="n"/>
+    </row>
+    <row r="7" ht="19.5" customHeight="1">
+      <c r="A7" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="11" t="n"/>
+      <c r="C7" s="18" t="inlineStr">
+        <is>
+          <t>2026/07/17</t>
+        </is>
+      </c>
+      <c r="D7" s="10" t="n"/>
+      <c r="E7" s="10" t="n"/>
+      <c r="F7" s="10" t="n"/>
+      <c r="G7" s="11" t="n"/>
+      <c r="H7" s="17" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I7" s="10" t="n"/>
+      <c r="J7" s="11" t="n"/>
+      <c r="K7" s="17" t="inlineStr">
+        <is>
+          <t>Tran Duc Tuyen</t>
+        </is>
+      </c>
+      <c r="L7" s="10" t="n"/>
+      <c r="M7" s="10" t="n"/>
+      <c r="N7" s="10" t="n"/>
+      <c r="O7" s="10" t="n"/>
+      <c r="P7" s="10" t="n"/>
+      <c r="Q7" s="11" t="n"/>
+      <c r="R7" s="19" t="inlineStr">
+        <is>
+          <t>顧客要件 2026-07 改訂：Stop Dokusya（ACSMS-API-014-004）で購読中止日を予約時点に master（t_dokusya.dokusya_chushi_date）へ即時反映する仕様を明記。予約行は未来日で有効行にならないが購読中止日のみ一覧(SCR-014)・詳細(SCR-011)へ直ちに表示。予約行を取消すと購読中止日は自動で null へ戻る（解約フラグ・購読状態の確定は従来どおり到来日バッチ Phase 2）。</t>
+        </is>
+      </c>
+      <c r="S7" s="10" t="n"/>
+      <c r="T7" s="10" t="n"/>
+      <c r="U7" s="10" t="n"/>
+      <c r="V7" s="11" t="n"/>
+      <c r="W7" s="17" t="inlineStr">
+        <is>
+          <t>Nguyen Huy Dat</t>
+        </is>
+      </c>
+      <c r="X7" s="10" t="n"/>
+      <c r="Y7" s="10" t="n"/>
+      <c r="Z7" s="10" t="n"/>
+      <c r="AA7" s="11" t="n"/>
+      <c r="AB7" s="17" t="inlineStr">
+        <is>
+          <t>Nguyen Huy Dat</t>
+        </is>
+      </c>
+      <c r="AC7" s="10" t="n"/>
+      <c r="AD7" s="10" t="n"/>
+      <c r="AE7" s="10" t="n"/>
+      <c r="AF7" s="10" t="n"/>
+      <c r="AG7" s="11" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="35">
+  <mergeCells count="49">
     <mergeCell ref="R1:V1"/>
     <mergeCell ref="AB1:AG1"/>
+    <mergeCell ref="C6:G6"/>
     <mergeCell ref="R5:V5"/>
+    <mergeCell ref="W6:AA6"/>
     <mergeCell ref="C5:G5"/>
+    <mergeCell ref="K7:Q7"/>
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="H2:J2"/>
     <mergeCell ref="W5:AA5"/>
     <mergeCell ref="R4:V4"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="H7:J7"/>
     <mergeCell ref="AB2:AG2"/>
     <mergeCell ref="C4:G4"/>
+    <mergeCell ref="R7:V7"/>
     <mergeCell ref="K4:Q4"/>
+    <mergeCell ref="K6:Q6"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="R6:V6"/>
     <mergeCell ref="C1:G1"/>
     <mergeCell ref="K3:Q3"/>
     <mergeCell ref="W4:AA4"/>
@@ -1711,16 +1838,20 @@
     <mergeCell ref="W3:AA3"/>
     <mergeCell ref="H3:J3"/>
     <mergeCell ref="A3:B3"/>
+    <mergeCell ref="AB7:AG7"/>
     <mergeCell ref="K5:Q5"/>
     <mergeCell ref="A2:B2"/>
+    <mergeCell ref="W7:AA7"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="H5:J5"/>
     <mergeCell ref="A5:B5"/>
     <mergeCell ref="R3:V3"/>
     <mergeCell ref="AB3:AG3"/>
     <mergeCell ref="K1:Q1"/>
+    <mergeCell ref="AB6:AG6"/>
     <mergeCell ref="H1:J1"/>
     <mergeCell ref="A4:B4"/>
+    <mergeCell ref="C7:G7"/>
     <mergeCell ref="AB5:AG5"/>
     <mergeCell ref="W2:AA2"/>
     <mergeCell ref="H4:J4"/>
@@ -1728,6 +1859,7 @@
     <mergeCell ref="AB4:AG4"/>
     <mergeCell ref="K2:Q2"/>
     <mergeCell ref="C3:G3"/>
+    <mergeCell ref="H6:J6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1900,7 +2032,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/07/16</t>
+          <t>2026/07/17</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -2416,7 +2548,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/07/16</t>
+          <t>2026/07/17</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -3402,7 +3534,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/07/16</t>
+          <t>2026/07/17</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -3718,7 +3850,7 @@
       <c r="R9" s="11" t="n"/>
       <c r="S9" s="19" t="inlineStr">
         <is>
-          <t>一覧の「購読を停止する」ボタンから、購読中止日（解約予定日）だけを指定して解約予約行を1件挿入する専用API。実際の解約確定（t_dokusya への反映）は到来日バッチ（Phase 2）が行う。</t>
+          <t>一覧の「購読を停止する」ボタンから、購読中止日（解約予定日）だけを指定して解約予約行を1件挿入する専用API。購読中止日は予約時点で master（t_dokusya.dokusya_chushi_date）へ即時反映し、一覧（SCR-014）・詳細（SCR-011）に直ちに表示する。解約の確定（解約フラグ・購読状態の反映）は到来日バッチ（Phase 2）が行う。予約行を取消すると master の購読中止日は自動で null へ戻る。</t>
         </is>
       </c>
       <c r="T9" s="10" t="n"/>
@@ -3963,7 +4095,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/07/16</t>
+          <t>2026/07/17</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -5971,13 +6103,13 @@
       <c r="AJ44" s="10" t="n"/>
       <c r="AK44" s="11" t="n"/>
     </row>
-    <row r="45" ht="72" customHeight="1">
+    <row r="45" ht="108" customHeight="1">
       <c r="B45" s="31" t="n">
         <v>22.5</v>
       </c>
       <c r="C45" s="19" t="inlineStr">
         <is>
-          <t>inactive_tanka_flg</t>
+          <t>active_tanka_flg</t>
         </is>
       </c>
       <c r="D45" s="10" t="n"/>
@@ -6022,7 +6154,7 @@
       <c r="AE45" s="11" t="n"/>
       <c r="AF45" s="19" t="inlineStr">
         <is>
-          <t>失効単価参照フラグ（SCR-020 error gate 連携・顧客要件2026-07）。`true`/`1` のときのみ有効。参照する購読料単価(tanka_type=1)が `active_flg=FALSE` の購読者だけを抽出（口座振替出力で失効単価参照によりブロックされた購読者を手動で新単価へ移行するための絞込）【詳細検索】</t>
+          <t>有効単価フラグ（SCR-020 error gate 連携・顧客要件2026-07 改訂）。単価一覧(SCR-006)と同一のトライステート: `true`=有効単価(active_flg=TRUE)を参照する購読者のみ、`false`=失効単価(active_flg=FALSE)を参照する購読者のみ、省略=両方。参照する購読料単価は tanka_type=1。口座振替出力(SCR-020)の失効単価エラーからは `false`(無効)で初期選択される【詳細検索】</t>
         </is>
       </c>
       <c r="AG45" s="10" t="n"/>
@@ -8857,10 +8989,10 @@
         </is>
       </c>
     </row>
-    <row r="160" ht="54" customHeight="1">
+    <row r="160" ht="90" customHeight="1">
       <c r="D160" s="41" t="inlineStr">
         <is>
-          <t>inactive_tanka_flg=true 指定時：参照購読料単価が失効している購読者のみ抽出。`tanka_id` は m_tanka の PK のため INNER JOIN で行数は増えない（0/1件）。</t>
+          <t>active_tanka_flg 指定時：`true`=参照購読料単価が有効(active_flg=TRUE)の購読者のみ、`false`=失効(active_flg=FALSE)の購読者のみ抽出（省略時は絞り込まない）。`tanka_id` は m_tanka の PK のため INNER JOIN で行数は増えない（0/1件）。JOIN 条件の active_flg はパラメータ（`:activeTankaFlg`）でバインドする。</t>
         </is>
       </c>
     </row>
@@ -9799,7 +9931,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/07/16</t>
+          <t>2026/07/17</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -11985,7 +12117,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/07/16</t>
+          <t>2026/07/17</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -14597,7 +14729,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/07/16</t>
+          <t>2026/07/17</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -14706,7 +14838,7 @@
       <c r="AJ7" s="10" t="n"/>
       <c r="AK7" s="11" t="n"/>
     </row>
-    <row r="8" ht="18" customHeight="1">
+    <row r="8" ht="54" customHeight="1">
       <c r="B8" s="33" t="inlineStr">
         <is>
           <t>概要</t>
@@ -14721,7 +14853,7 @@
       <c r="I8" s="11" t="n"/>
       <c r="J8" s="19" t="inlineStr">
         <is>
-          <t>一覧の「購読を停止する」ボタンから、購読中止日（解約予定日）だけを指定して解約予約行を1件挿入する専用API。実際の解約確定（t_dokusya への反映）は到来日バッチ（Phase 2）が行う。</t>
+          <t>一覧の「購読を停止する」ボタンから、購読中止日（解約予定日）だけを指定して解約予約行を1件挿入する専用API。購読中止日は予約時点で master（t_dokusya.dokusya_chushi_date）へ即時反映し、一覧（SCR-014）・詳細（SCR-011）に直ちに表示する。解約の確定（解約フラグ・購読状態の反映）は到来日バッチ（Phase 2）が行う。予約行を取消すると master の購読中止日は自動で null へ戻る。</t>
         </is>
       </c>
       <c r="K8" s="10" t="n"/>

--- a/docs/design/ACSMS-SCR-014/【日本農業新聞様】VTIジャパン_クラウド版購読者管理システム_API設計書_購読者明細検索画面_V1.0.xlsx
+++ b/docs/design/ACSMS-SCR-014/【日本農業新聞様】VTIジャパン_クラウド版購読者管理システム_API設計書_購読者明細検索画面_V1.0.xlsx
@@ -1354,7 +1354,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG7"/>
+  <dimension ref="A1:AG10"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="4.25" customWidth="1" min="1" max="1"/>
@@ -1809,21 +1809,204 @@
       <c r="AF7" s="10" t="n"/>
       <c r="AG7" s="11" t="n"/>
     </row>
+    <row r="8" ht="19.5" customHeight="1">
+      <c r="A8" s="17" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="11" t="n"/>
+      <c r="C8" s="18" t="inlineStr">
+        <is>
+          <t>2026/07/24</t>
+        </is>
+      </c>
+      <c r="D8" s="10" t="n"/>
+      <c r="E8" s="10" t="n"/>
+      <c r="F8" s="10" t="n"/>
+      <c r="G8" s="11" t="n"/>
+      <c r="H8" s="17" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="I8" s="10" t="n"/>
+      <c r="J8" s="11" t="n"/>
+      <c r="K8" s="17" t="inlineStr">
+        <is>
+          <t>Tran Duc Tuyen</t>
+        </is>
+      </c>
+      <c r="L8" s="10" t="n"/>
+      <c r="M8" s="10" t="n"/>
+      <c r="N8" s="10" t="n"/>
+      <c r="O8" s="10" t="n"/>
+      <c r="P8" s="10" t="n"/>
+      <c r="Q8" s="11" t="n"/>
+      <c r="R8" s="19" t="inlineStr">
+        <is>
+          <t>顧客要件 2026-07 改訂：&lt;br&gt;1. 検索結果テーブル・一覧レスポンスに `haitatsu_renrakusaki_1`（配送先連絡先１）を「連絡先１」の直後へ追加（16 列）。&lt;br&gt;2. 一覧の停止ボタン名を「購読停止」→「購読中止」に変更。&lt;br&gt;3. 購読停止（解約予約）ポップアップのタイトルを「購読を停止する」→「購読中止」、OK ボタンを「購読を停止する」→「確認」に変更（API 契約・応答メッセージ `購読停止を予約しました。` は不変）。</t>
+        </is>
+      </c>
+      <c r="S8" s="10" t="n"/>
+      <c r="T8" s="10" t="n"/>
+      <c r="U8" s="10" t="n"/>
+      <c r="V8" s="11" t="n"/>
+      <c r="W8" s="17" t="inlineStr">
+        <is>
+          <t>Nguyen Huy Dat</t>
+        </is>
+      </c>
+      <c r="X8" s="10" t="n"/>
+      <c r="Y8" s="10" t="n"/>
+      <c r="Z8" s="10" t="n"/>
+      <c r="AA8" s="11" t="n"/>
+      <c r="AB8" s="17" t="inlineStr">
+        <is>
+          <t>Nguyen Huy Dat</t>
+        </is>
+      </c>
+      <c r="AC8" s="10" t="n"/>
+      <c r="AD8" s="10" t="n"/>
+      <c r="AE8" s="10" t="n"/>
+      <c r="AF8" s="10" t="n"/>
+      <c r="AG8" s="11" t="n"/>
+    </row>
+    <row r="9" ht="19.5" customHeight="1">
+      <c r="A9" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="11" t="n"/>
+      <c r="C9" s="18" t="inlineStr">
+        <is>
+          <t>2026/07/24</t>
+        </is>
+      </c>
+      <c r="D9" s="10" t="n"/>
+      <c r="E9" s="10" t="n"/>
+      <c r="F9" s="10" t="n"/>
+      <c r="G9" s="11" t="n"/>
+      <c r="H9" s="17" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="I9" s="10" t="n"/>
+      <c r="J9" s="11" t="n"/>
+      <c r="K9" s="17" t="inlineStr">
+        <is>
+          <t>Tran Duc Tuyen</t>
+        </is>
+      </c>
+      <c r="L9" s="10" t="n"/>
+      <c r="M9" s="10" t="n"/>
+      <c r="N9" s="10" t="n"/>
+      <c r="O9" s="10" t="n"/>
+      <c r="P9" s="10" t="n"/>
+      <c r="Q9" s="11" t="n"/>
+      <c r="R9" s="19" t="inlineStr">
+        <is>
+          <t>顧客要件 2026-07 改訂：詳細検索エリアの「支払方法」の後に検索条件を3件追加 — `yubin_kubun`（郵送区分・m_code YUBIN_KUBUN 0:空/1:郵送・完全一致）、`tanka_id`（新聞単価・完全一致）、`biko`（備考・部分一致）。</t>
+        </is>
+      </c>
+      <c r="S9" s="10" t="n"/>
+      <c r="T9" s="10" t="n"/>
+      <c r="U9" s="10" t="n"/>
+      <c r="V9" s="11" t="n"/>
+      <c r="W9" s="17" t="inlineStr">
+        <is>
+          <t>Nguyen Huy Dat</t>
+        </is>
+      </c>
+      <c r="X9" s="10" t="n"/>
+      <c r="Y9" s="10" t="n"/>
+      <c r="Z9" s="10" t="n"/>
+      <c r="AA9" s="11" t="n"/>
+      <c r="AB9" s="17" t="inlineStr">
+        <is>
+          <t>Nguyen Huy Dat</t>
+        </is>
+      </c>
+      <c r="AC9" s="10" t="n"/>
+      <c r="AD9" s="10" t="n"/>
+      <c r="AE9" s="10" t="n"/>
+      <c r="AF9" s="10" t="n"/>
+      <c r="AG9" s="11" t="n"/>
+    </row>
+    <row r="10" ht="19.5" customHeight="1">
+      <c r="A10" s="17" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="11" t="n"/>
+      <c r="C10" s="18" t="inlineStr">
+        <is>
+          <t>2026/07/24</t>
+        </is>
+      </c>
+      <c r="D10" s="10" t="n"/>
+      <c r="E10" s="10" t="n"/>
+      <c r="F10" s="10" t="n"/>
+      <c r="G10" s="11" t="n"/>
+      <c r="H10" s="17" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="I10" s="10" t="n"/>
+      <c r="J10" s="11" t="n"/>
+      <c r="K10" s="17" t="inlineStr">
+        <is>
+          <t>Tran Duc Tuyen</t>
+        </is>
+      </c>
+      <c r="L10" s="10" t="n"/>
+      <c r="M10" s="10" t="n"/>
+      <c r="N10" s="10" t="n"/>
+      <c r="O10" s="10" t="n"/>
+      <c r="P10" s="10" t="n"/>
+      <c r="Q10" s="11" t="n"/>
+      <c r="R10" s="19" t="inlineStr">
+        <is>
+          <t>不具合修正：検索結果テーブル・Excel出力の「販売店コード」列が販売店ID（hanbaiten_id）を表示していたため、`m_hanbaiten` を JOIN した実コード `hanbaiten_code` を表示するよう修正。一覧レスポンスに `hanbaiten_code` を追加、ソート許可カラムに `hanbaiten_code` を追加（列クリックのソートも code 基準）。検索条件の「配達販売店」(hanbaiten_id) は不変。</t>
+        </is>
+      </c>
+      <c r="S10" s="10" t="n"/>
+      <c r="T10" s="10" t="n"/>
+      <c r="U10" s="10" t="n"/>
+      <c r="V10" s="11" t="n"/>
+      <c r="W10" s="17" t="inlineStr">
+        <is>
+          <t>Nguyen Huy Dat</t>
+        </is>
+      </c>
+      <c r="X10" s="10" t="n"/>
+      <c r="Y10" s="10" t="n"/>
+      <c r="Z10" s="10" t="n"/>
+      <c r="AA10" s="11" t="n"/>
+      <c r="AB10" s="17" t="inlineStr">
+        <is>
+          <t>Nguyen Huy Dat</t>
+        </is>
+      </c>
+      <c r="AC10" s="10" t="n"/>
+      <c r="AD10" s="10" t="n"/>
+      <c r="AE10" s="10" t="n"/>
+      <c r="AF10" s="10" t="n"/>
+      <c r="AG10" s="11" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="49">
+  <mergeCells count="70">
     <mergeCell ref="R1:V1"/>
+    <mergeCell ref="R8:V8"/>
     <mergeCell ref="AB1:AG1"/>
     <mergeCell ref="C6:G6"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="W10:AA10"/>
     <mergeCell ref="R5:V5"/>
     <mergeCell ref="W6:AA6"/>
+    <mergeCell ref="AB9:AG9"/>
     <mergeCell ref="C5:G5"/>
     <mergeCell ref="K7:Q7"/>
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="H2:J2"/>
     <mergeCell ref="W5:AA5"/>
     <mergeCell ref="R4:V4"/>
+    <mergeCell ref="R10:V10"/>
     <mergeCell ref="A6:B6"/>
     <mergeCell ref="H7:J7"/>
+    <mergeCell ref="K10:Q10"/>
     <mergeCell ref="AB2:AG2"/>
     <mergeCell ref="C4:G4"/>
     <mergeCell ref="R7:V7"/>
@@ -1831,33 +2014,48 @@
     <mergeCell ref="K6:Q6"/>
     <mergeCell ref="A7:B7"/>
     <mergeCell ref="R6:V6"/>
+    <mergeCell ref="C10:G10"/>
     <mergeCell ref="C1:G1"/>
     <mergeCell ref="K3:Q3"/>
     <mergeCell ref="W4:AA4"/>
     <mergeCell ref="W1:AA1"/>
     <mergeCell ref="W3:AA3"/>
     <mergeCell ref="H3:J3"/>
+    <mergeCell ref="AB8:AG8"/>
     <mergeCell ref="A3:B3"/>
+    <mergeCell ref="C9:G9"/>
+    <mergeCell ref="K9:Q9"/>
     <mergeCell ref="AB7:AG7"/>
     <mergeCell ref="K5:Q5"/>
     <mergeCell ref="A2:B2"/>
+    <mergeCell ref="AB10:AG10"/>
     <mergeCell ref="W7:AA7"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="H5:J5"/>
     <mergeCell ref="A5:B5"/>
+    <mergeCell ref="H8:J8"/>
     <mergeCell ref="R3:V3"/>
     <mergeCell ref="AB3:AG3"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="C8:G8"/>
     <mergeCell ref="K1:Q1"/>
     <mergeCell ref="AB6:AG6"/>
     <mergeCell ref="H1:J1"/>
     <mergeCell ref="A4:B4"/>
+    <mergeCell ref="W9:AA9"/>
     <mergeCell ref="C7:G7"/>
+    <mergeCell ref="H10:J10"/>
+    <mergeCell ref="W8:AA8"/>
     <mergeCell ref="AB5:AG5"/>
     <mergeCell ref="W2:AA2"/>
+    <mergeCell ref="A10:B10"/>
     <mergeCell ref="H4:J4"/>
     <mergeCell ref="R2:V2"/>
+    <mergeCell ref="H9:J9"/>
+    <mergeCell ref="K8:Q8"/>
     <mergeCell ref="AB4:AG4"/>
     <mergeCell ref="K2:Q2"/>
+    <mergeCell ref="R9:V9"/>
     <mergeCell ref="C3:G3"/>
     <mergeCell ref="H6:J6"/>
   </mergeCells>
@@ -2024,7 +2222,7 @@
       <c r="Y2" s="22" t="n"/>
       <c r="Z2" s="20" t="inlineStr">
         <is>
-          <t>Nguyen Duyen Manh</t>
+          <t>Tran Duc Tuyen</t>
         </is>
       </c>
       <c r="AA2" s="21" t="n"/>
@@ -2032,7 +2230,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/07/17</t>
+          <t>2026/07/24</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -2040,7 +2238,7 @@
       <c r="AG2" s="22" t="n"/>
       <c r="AH2" s="20" t="inlineStr">
         <is>
-          <t>Nguyen Duyen Manh</t>
+          <t>Tran Duc Tuyen</t>
         </is>
       </c>
       <c r="AI2" s="21" t="n"/>
@@ -2540,7 +2738,7 @@
       <c r="Y2" s="22" t="n"/>
       <c r="Z2" s="20" t="inlineStr">
         <is>
-          <t>Nguyen Duyen Manh</t>
+          <t>Tran Duc Tuyen</t>
         </is>
       </c>
       <c r="AA2" s="21" t="n"/>
@@ -2548,7 +2746,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/07/17</t>
+          <t>2026/07/24</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -2556,7 +2754,7 @@
       <c r="AG2" s="22" t="n"/>
       <c r="AH2" s="20" t="inlineStr">
         <is>
-          <t>Nguyen Duyen Manh</t>
+          <t>Tran Duc Tuyen</t>
         </is>
       </c>
       <c r="AI2" s="21" t="n"/>
@@ -3526,7 +3724,7 @@
       <c r="Y2" s="22" t="n"/>
       <c r="Z2" s="20" t="inlineStr">
         <is>
-          <t>Nguyen Duyen Manh</t>
+          <t>Tran Duc Tuyen</t>
         </is>
       </c>
       <c r="AA2" s="21" t="n"/>
@@ -3534,7 +3732,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/07/17</t>
+          <t>2026/07/24</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -3542,7 +3740,7 @@
       <c r="AG2" s="22" t="n"/>
       <c r="AH2" s="20" t="inlineStr">
         <is>
-          <t>Nguyen Duyen Manh</t>
+          <t>Tran Duc Tuyen</t>
         </is>
       </c>
       <c r="AI2" s="21" t="n"/>
@@ -3850,7 +4048,7 @@
       <c r="R9" s="11" t="n"/>
       <c r="S9" s="19" t="inlineStr">
         <is>
-          <t>一覧の「購読を停止する」ボタンから、購読中止日（解約予定日）だけを指定して解約予約行を1件挿入する専用API。購読中止日は予約時点で master（t_dokusya.dokusya_chushi_date）へ即時反映し、一覧（SCR-014）・詳細（SCR-011）に直ちに表示する。解約の確定（解約フラグ・購読状態の反映）は到来日バッチ（Phase 2）が行う。予約行を取消すると master の購読中止日は自動で null へ戻る。</t>
+          <t>一覧の「購読中止」ボタンから、購読中止日（解約予定日）だけを指定して解約予約行を1件挿入する専用API。購読中止日は予約時点で master（t_dokusya.dokusya_chushi_date）へ即時反映し、一覧（SCR-014）・詳細（SCR-011）に直ちに表示する。解約の確定（解約フラグ・購読状態の反映）は到来日バッチ（Phase 2）が行う。予約行を取消すると master の購読中止日は自動で null へ戻る。</t>
         </is>
       </c>
       <c r="T9" s="10" t="n"/>
@@ -3934,7 +4132,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK175"/>
+  <dimension ref="A1:AK184"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="4.25" customWidth="1" min="1" max="1"/>
@@ -4087,7 +4285,7 @@
       <c r="Y2" s="22" t="n"/>
       <c r="Z2" s="20" t="inlineStr">
         <is>
-          <t>Nguyen Duyen Manh</t>
+          <t>Tran Duc Tuyen</t>
         </is>
       </c>
       <c r="AA2" s="21" t="n"/>
@@ -4095,7 +4293,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/07/17</t>
+          <t>2026/07/24</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -4103,7 +4301,7 @@
       <c r="AG2" s="22" t="n"/>
       <c r="AH2" s="20" t="inlineStr">
         <is>
-          <t>Nguyen Duyen Manh</t>
+          <t>Tran Duc Tuyen</t>
         </is>
       </c>
       <c r="AI2" s="21" t="n"/>
@@ -4953,7 +5151,7 @@
       </c>
       <c r="C26" s="19" t="inlineStr">
         <is>
-          <t>jastem_toriatsukai_tenpo_code</t>
+          <t>bank_branch</t>
         </is>
       </c>
       <c r="D26" s="10" t="n"/>
@@ -4994,13 +5192,13 @@
       <c r="AA26" s="10" t="n"/>
       <c r="AB26" s="11" t="n"/>
       <c r="AC26" s="17" t="n">
-        <v>3</v>
+        <v>100</v>
       </c>
       <c r="AD26" s="10" t="n"/>
       <c r="AE26" s="11" t="n"/>
       <c r="AF26" s="19" t="inlineStr">
         <is>
-          <t>引落元口座支店コード（部分一致）。物理カラムは `bank_branch_code`（レガシー名）【詳細検索】</t>
+          <t>引落元口座支店（部分一致）。コード（`bank_branch_code`）・名称（`bank_branch_name`）を横断して OR 部分一致【詳細検索】</t>
         </is>
       </c>
       <c r="AG26" s="10" t="n"/>
@@ -5009,13 +5207,13 @@
       <c r="AJ26" s="10" t="n"/>
       <c r="AK26" s="11" t="n"/>
     </row>
-    <row r="27" ht="36" customHeight="1">
+    <row r="27" ht="54" customHeight="1">
       <c r="B27" s="31" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C27" s="19" t="inlineStr">
         <is>
-          <t>jastem_tenpo_name</t>
+          <t>full_name</t>
         </is>
       </c>
       <c r="D27" s="10" t="n"/>
@@ -5062,7 +5260,7 @@
       <c r="AE27" s="11" t="n"/>
       <c r="AF27" s="19" t="inlineStr">
         <is>
-          <t>引落元口座支店名（部分一致）。物理カラムは `bank_branch_name`（レガシー名）【詳細検索】</t>
+          <t>氏名（部分一致）。`shimei_sei` / `shimei_mei` / `haitatsu_shimei_sei` / `haitatsu_shimei_mei` のいずれかに部分一致（OR）【常時表示】</t>
         </is>
       </c>
       <c r="AG27" s="10" t="n"/>
@@ -5073,11 +5271,11 @@
     </row>
     <row r="28" ht="54" customHeight="1">
       <c r="B28" s="31" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C28" s="19" t="inlineStr">
         <is>
-          <t>full_name</t>
+          <t>full_name_kana</t>
         </is>
       </c>
       <c r="D28" s="10" t="n"/>
@@ -5124,7 +5322,7 @@
       <c r="AE28" s="11" t="n"/>
       <c r="AF28" s="19" t="inlineStr">
         <is>
-          <t>氏名（部分一致）。`shimei_sei` / `shimei_mei` / `haitatsu_shimei_sei` / `haitatsu_shimei_mei` のいずれかに部分一致（OR）【常時表示】</t>
+          <t>かな氏名（部分一致）。`shimei_kana_sei` / `shimei_kana_mei` / `haitatsu_shimei_kana_sei` / `haitatsu_shimei_kana_mei` のいずれかに部分一致（OR）【常時表示】</t>
         </is>
       </c>
       <c r="AG28" s="10" t="n"/>
@@ -5135,11 +5333,11 @@
     </row>
     <row r="29" ht="54" customHeight="1">
       <c r="B29" s="31" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C29" s="19" t="inlineStr">
         <is>
-          <t>full_name_kana</t>
+          <t>renrakusaki</t>
         </is>
       </c>
       <c r="D29" s="10" t="n"/>
@@ -5180,13 +5378,13 @@
       <c r="AA29" s="10" t="n"/>
       <c r="AB29" s="11" t="n"/>
       <c r="AC29" s="17" t="n">
-        <v>100</v>
+        <v>15</v>
       </c>
       <c r="AD29" s="10" t="n"/>
       <c r="AE29" s="11" t="n"/>
       <c r="AF29" s="19" t="inlineStr">
         <is>
-          <t>かな氏名（部分一致）。`shimei_kana_sei` / `shimei_kana_mei` / `haitatsu_shimei_kana_sei` / `haitatsu_shimei_kana_mei` のいずれかに部分一致（OR）【常時表示】</t>
+          <t>連絡先（部分一致）。`renrakusaki_1` / `haitatsu_renrakusaki_1` / `renrakusaki_2` / `haitatsu_renrakusaki_2` のいずれかに部分一致（OR）【詳細検索】</t>
         </is>
       </c>
       <c r="AG29" s="10" t="n"/>
@@ -5195,13 +5393,13 @@
       <c r="AJ29" s="10" t="n"/>
       <c r="AK29" s="11" t="n"/>
     </row>
-    <row r="30" ht="36" customHeight="1">
+    <row r="30" ht="90" customHeight="1">
       <c r="B30" s="31" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C30" s="19" t="inlineStr">
         <is>
-          <t>renrakusaki_1</t>
+          <t>haitatsu</t>
         </is>
       </c>
       <c r="D30" s="10" t="n"/>
@@ -5242,13 +5440,13 @@
       <c r="AA30" s="10" t="n"/>
       <c r="AB30" s="11" t="n"/>
       <c r="AC30" s="17" t="n">
-        <v>15</v>
+        <v>200</v>
       </c>
       <c r="AD30" s="10" t="n"/>
       <c r="AE30" s="11" t="n"/>
       <c r="AF30" s="19" t="inlineStr">
         <is>
-          <t>連絡先１（部分一致）。`renrakusaki_1` / `haitatsu_renrakusaki_1` のいずれかに部分一致（OR）【詳細検索】</t>
+          <t>配達先住所（部分一致）。配達先住所4項目（`haitatsu_todofuken_code` / `haitatsu_shikuchoson` / `haitatsu_chome_banchi` / `haitatsu_tatemono_mei`）＋購読者住所4項目（`todofuken_code` / `shikuchoson` / `chome_banchi` / `tatemono_mei`）のいずれかに部分一致（OR）【常時表示】</t>
         </is>
       </c>
       <c r="AG30" s="10" t="n"/>
@@ -5257,13 +5455,13 @@
       <c r="AJ30" s="10" t="n"/>
       <c r="AK30" s="11" t="n"/>
     </row>
-    <row r="31" ht="90" customHeight="1">
+    <row r="31" ht="18" customHeight="1">
       <c r="B31" s="31" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C31" s="19" t="inlineStr">
         <is>
-          <t>haitatsu</t>
+          <t>hanbaiten_id</t>
         </is>
       </c>
       <c r="D31" s="10" t="n"/>
@@ -5277,7 +5475,7 @@
       <c r="L31" s="11" t="n"/>
       <c r="M31" s="17" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Number</t>
         </is>
       </c>
       <c r="N31" s="10" t="n"/>
@@ -5303,14 +5501,12 @@
       <c r="Z31" s="10" t="n"/>
       <c r="AA31" s="10" t="n"/>
       <c r="AB31" s="11" t="n"/>
-      <c r="AC31" s="17" t="n">
-        <v>200</v>
-      </c>
+      <c r="AC31" s="17" t="inlineStr"/>
       <c r="AD31" s="10" t="n"/>
       <c r="AE31" s="11" t="n"/>
       <c r="AF31" s="19" t="inlineStr">
         <is>
-          <t>配達先住所（部分一致）。配達先住所4項目（`haitatsu_todofuken_code` / `haitatsu_shikuchoson` / `haitatsu_chome_banchi` / `haitatsu_tatemono_mei`）＋購読者住所4項目（`todofuken_code` / `shikuchoson` / `chome_banchi` / `tatemono_mei`）のいずれかに部分一致（OR）【常時表示】</t>
+          <t>配達販売店ID（プルダウン）【常時表示】</t>
         </is>
       </c>
       <c r="AG31" s="10" t="n"/>
@@ -5321,11 +5517,11 @@
     </row>
     <row r="32" ht="18" customHeight="1">
       <c r="B32" s="31" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C32" s="19" t="inlineStr">
         <is>
-          <t>hanbaiten_id</t>
+          <t>email</t>
         </is>
       </c>
       <c r="D32" s="10" t="n"/>
@@ -5339,7 +5535,7 @@
       <c r="L32" s="11" t="n"/>
       <c r="M32" s="17" t="inlineStr">
         <is>
-          <t>Number</t>
+          <t>String</t>
         </is>
       </c>
       <c r="N32" s="10" t="n"/>
@@ -5365,12 +5561,14 @@
       <c r="Z32" s="10" t="n"/>
       <c r="AA32" s="10" t="n"/>
       <c r="AB32" s="11" t="n"/>
-      <c r="AC32" s="17" t="inlineStr"/>
+      <c r="AC32" s="17" t="n">
+        <v>100</v>
+      </c>
       <c r="AD32" s="10" t="n"/>
       <c r="AE32" s="11" t="n"/>
       <c r="AF32" s="19" t="inlineStr">
         <is>
-          <t>配達販売店ID（プルダウン）【常時表示】</t>
+          <t>メールアドレス（部分一致、メール形式チェック）【詳細検索】</t>
         </is>
       </c>
       <c r="AG32" s="10" t="n"/>
@@ -5379,13 +5577,13 @@
       <c r="AJ32" s="10" t="n"/>
       <c r="AK32" s="11" t="n"/>
     </row>
-    <row r="33" ht="18" customHeight="1">
+    <row r="33" ht="36" customHeight="1">
       <c r="B33" s="31" t="n">
-        <v>11</v>
+        <v>11.1</v>
       </c>
       <c r="C33" s="19" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>yubin_kubun</t>
         </is>
       </c>
       <c r="D33" s="10" t="n"/>
@@ -5425,14 +5623,16 @@
       <c r="Z33" s="10" t="n"/>
       <c r="AA33" s="10" t="n"/>
       <c r="AB33" s="11" t="n"/>
-      <c r="AC33" s="17" t="n">
-        <v>100</v>
+      <c r="AC33" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="AD33" s="10" t="n"/>
       <c r="AE33" s="11" t="n"/>
       <c r="AF33" s="19" t="inlineStr">
         <is>
-          <t>メールアドレス（部分一致、メール形式チェック）【詳細検索】</t>
+          <t>郵送区分（m_code YUBIN_KUBUN: 0:空 / 1:郵送）。完全一致【詳細検索】</t>
         </is>
       </c>
       <c r="AG33" s="10" t="n"/>
@@ -5443,11 +5643,11 @@
     </row>
     <row r="34" ht="18" customHeight="1">
       <c r="B34" s="31" t="n">
-        <v>12</v>
+        <v>11.2</v>
       </c>
       <c r="C34" s="19" t="inlineStr">
         <is>
-          <t>seikyu_kaishi_month</t>
+          <t>tanka_id</t>
         </is>
       </c>
       <c r="D34" s="10" t="n"/>
@@ -5461,7 +5661,7 @@
       <c r="L34" s="11" t="n"/>
       <c r="M34" s="17" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Number</t>
         </is>
       </c>
       <c r="N34" s="10" t="n"/>
@@ -5487,14 +5687,16 @@
       <c r="Z34" s="10" t="n"/>
       <c r="AA34" s="10" t="n"/>
       <c r="AB34" s="11" t="n"/>
-      <c r="AC34" s="17" t="n">
-        <v>6</v>
+      <c r="AC34" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="AD34" s="10" t="n"/>
       <c r="AE34" s="11" t="n"/>
       <c r="AF34" s="19" t="inlineStr">
         <is>
-          <t>請求開始月（YYYYMM、部分一致）【詳細検索】</t>
+          <t>新聞単価ID。完全一致【詳細検索】</t>
         </is>
       </c>
       <c r="AG34" s="10" t="n"/>
@@ -5505,11 +5707,11 @@
     </row>
     <row r="35" ht="18" customHeight="1">
       <c r="B35" s="31" t="n">
-        <v>13</v>
+        <v>11.3</v>
       </c>
       <c r="C35" s="19" t="inlineStr">
         <is>
-          <t>shoki_dokusya_kaishi_date_from</t>
+          <t>biko</t>
         </is>
       </c>
       <c r="D35" s="10" t="n"/>
@@ -5549,12 +5751,14 @@
       <c r="Z35" s="10" t="n"/>
       <c r="AA35" s="10" t="n"/>
       <c r="AB35" s="11" t="n"/>
-      <c r="AC35" s="17" t="inlineStr"/>
+      <c r="AC35" s="17" t="n">
+        <v>500</v>
+      </c>
       <c r="AD35" s="10" t="n"/>
       <c r="AE35" s="11" t="n"/>
       <c r="AF35" s="19" t="inlineStr">
         <is>
-          <t>購読開始日（範囲開始）YYYY/MM/DD【常時表示】</t>
+          <t>備考（部分一致）【詳細検索】</t>
         </is>
       </c>
       <c r="AG35" s="10" t="n"/>
@@ -5565,11 +5769,11 @@
     </row>
     <row r="36" ht="18" customHeight="1">
       <c r="B36" s="31" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C36" s="19" t="inlineStr">
         <is>
-          <t>shoki_dokusya_kaishi_date_to</t>
+          <t>seikyu_kaishi_month_from</t>
         </is>
       </c>
       <c r="D36" s="10" t="n"/>
@@ -5609,12 +5813,14 @@
       <c r="Z36" s="10" t="n"/>
       <c r="AA36" s="10" t="n"/>
       <c r="AB36" s="11" t="n"/>
-      <c r="AC36" s="17" t="inlineStr"/>
+      <c r="AC36" s="17" t="n">
+        <v>6</v>
+      </c>
       <c r="AD36" s="10" t="n"/>
       <c r="AE36" s="11" t="n"/>
       <c r="AF36" s="19" t="inlineStr">
         <is>
-          <t>購読開始日（範囲終了）YYYY/MM/DD ※相関チェック：from ≦ to【常時表示】</t>
+          <t>請求開始月（範囲開始）YYYYMM【詳細検索】</t>
         </is>
       </c>
       <c r="AG36" s="10" t="n"/>
@@ -5625,11 +5831,11 @@
     </row>
     <row r="37" ht="18" customHeight="1">
       <c r="B37" s="31" t="n">
-        <v>15</v>
+        <v>12.5</v>
       </c>
       <c r="C37" s="19" t="inlineStr">
         <is>
-          <t>dokusya_chushi_date_from</t>
+          <t>seikyu_kaishi_month_to</t>
         </is>
       </c>
       <c r="D37" s="10" t="n"/>
@@ -5669,12 +5875,14 @@
       <c r="Z37" s="10" t="n"/>
       <c r="AA37" s="10" t="n"/>
       <c r="AB37" s="11" t="n"/>
-      <c r="AC37" s="17" t="inlineStr"/>
+      <c r="AC37" s="17" t="n">
+        <v>6</v>
+      </c>
       <c r="AD37" s="10" t="n"/>
       <c r="AE37" s="11" t="n"/>
       <c r="AF37" s="19" t="inlineStr">
         <is>
-          <t>購読中止日（範囲開始）YYYY/MM/DD【常時表示】</t>
+          <t>請求開始月（範囲終了）YYYYMM ※相関チェック：from ≦ to【詳細検索】</t>
         </is>
       </c>
       <c r="AG37" s="10" t="n"/>
@@ -5685,11 +5893,11 @@
     </row>
     <row r="38" ht="18" customHeight="1">
       <c r="B38" s="31" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C38" s="19" t="inlineStr">
         <is>
-          <t>dokusya_chushi_date_to</t>
+          <t>shoki_dokusya_kaishi_date_from</t>
         </is>
       </c>
       <c r="D38" s="10" t="n"/>
@@ -5734,7 +5942,7 @@
       <c r="AE38" s="11" t="n"/>
       <c r="AF38" s="19" t="inlineStr">
         <is>
-          <t>購読中止日（範囲終了）YYYY/MM/DD ※相関チェック：from ≦ to【常時表示】</t>
+          <t>購読開始日（範囲開始）YYYY/MM/DD【常時表示】</t>
         </is>
       </c>
       <c r="AG38" s="10" t="n"/>
@@ -5743,13 +5951,13 @@
       <c r="AJ38" s="10" t="n"/>
       <c r="AK38" s="11" t="n"/>
     </row>
-    <row r="39" ht="36" customHeight="1">
+    <row r="39" ht="18" customHeight="1">
       <c r="B39" s="31" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C39" s="19" t="inlineStr">
         <is>
-          <t>dokusya_shubetsu</t>
+          <t>shoki_dokusya_kaishi_date_to</t>
         </is>
       </c>
       <c r="D39" s="10" t="n"/>
@@ -5763,7 +5971,7 @@
       <c r="L39" s="11" t="n"/>
       <c r="M39" s="17" t="inlineStr">
         <is>
-          <t>Number</t>
+          <t>String</t>
         </is>
       </c>
       <c r="N39" s="10" t="n"/>
@@ -5794,7 +6002,7 @@
       <c r="AE39" s="11" t="n"/>
       <c r="AF39" s="19" t="inlineStr">
         <is>
-          <t>購読種別 ※m_code.code_category='DOKUSYA_SHUBETSU'を参照（1:紙版, 2:電子版, 3:併読）【常時表示】</t>
+          <t>購読開始日（範囲終了）YYYY/MM/DD ※相関チェック：from ≦ to【常時表示】</t>
         </is>
       </c>
       <c r="AG39" s="10" t="n"/>
@@ -5803,13 +6011,13 @@
       <c r="AJ39" s="10" t="n"/>
       <c r="AK39" s="11" t="n"/>
     </row>
-    <row r="40" ht="36" customHeight="1">
+    <row r="40" ht="18" customHeight="1">
       <c r="B40" s="31" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C40" s="19" t="inlineStr">
         <is>
-          <t>denshi_shonin_status</t>
+          <t>dokusya_chushi_date_from</t>
         </is>
       </c>
       <c r="D40" s="10" t="n"/>
@@ -5823,7 +6031,7 @@
       <c r="L40" s="11" t="n"/>
       <c r="M40" s="17" t="inlineStr">
         <is>
-          <t>Number</t>
+          <t>String</t>
         </is>
       </c>
       <c r="N40" s="10" t="n"/>
@@ -5854,7 +6062,7 @@
       <c r="AE40" s="11" t="n"/>
       <c r="AF40" s="19" t="inlineStr">
         <is>
-          <t>電子版承認ステータス（NULL=Web申込以外, 0:未承認, 1:承認済み, 2:否認）【常時表示】</t>
+          <t>購読中止日（範囲開始）YYYY/MM/DD【常時表示】</t>
         </is>
       </c>
       <c r="AG40" s="10" t="n"/>
@@ -5863,13 +6071,13 @@
       <c r="AJ40" s="10" t="n"/>
       <c r="AK40" s="11" t="n"/>
     </row>
-    <row r="41" ht="36" customHeight="1">
+    <row r="41" ht="18" customHeight="1">
       <c r="B41" s="31" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C41" s="19" t="inlineStr">
         <is>
-          <t>tetsuzuki_shurui</t>
+          <t>dokusya_chushi_date_to</t>
         </is>
       </c>
       <c r="D41" s="10" t="n"/>
@@ -5883,7 +6091,7 @@
       <c r="L41" s="11" t="n"/>
       <c r="M41" s="17" t="inlineStr">
         <is>
-          <t>Number</t>
+          <t>String</t>
         </is>
       </c>
       <c r="N41" s="10" t="n"/>
@@ -5914,7 +6122,7 @@
       <c r="AE41" s="11" t="n"/>
       <c r="AF41" s="19" t="inlineStr">
         <is>
-          <t>手続種類 ※m_code.code_category='TETSUZUKI_SHURUI'を参照（0:解約, 1:新規）【常時表示】</t>
+          <t>購読中止日（範囲終了）YYYY/MM/DD ※相関チェック：from ≦ to【常時表示】</t>
         </is>
       </c>
       <c r="AG41" s="10" t="n"/>
@@ -5923,13 +6131,13 @@
       <c r="AJ41" s="10" t="n"/>
       <c r="AK41" s="11" t="n"/>
     </row>
-    <row r="42" ht="18" customHeight="1">
+    <row r="42" ht="36" customHeight="1">
       <c r="B42" s="31" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C42" s="19" t="inlineStr">
         <is>
-          <t>joho_henko_tekiyo_date_from</t>
+          <t>dokusya_shubetsu</t>
         </is>
       </c>
       <c r="D42" s="10" t="n"/>
@@ -5943,7 +6151,7 @@
       <c r="L42" s="11" t="n"/>
       <c r="M42" s="17" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Number</t>
         </is>
       </c>
       <c r="N42" s="10" t="n"/>
@@ -5974,7 +6182,7 @@
       <c r="AE42" s="11" t="n"/>
       <c r="AF42" s="19" t="inlineStr">
         <is>
-          <t>適用日（範囲開始）YYYY/MM/DD【詳細検索】</t>
+          <t>購読種別 ※m_code.code_category='DOKUSYA_SHUBETSU'を参照（1:紙版, 2:電子版, 3:併読）【常時表示】</t>
         </is>
       </c>
       <c r="AG42" s="10" t="n"/>
@@ -5985,11 +6193,11 @@
     </row>
     <row r="43" ht="36" customHeight="1">
       <c r="B43" s="31" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C43" s="19" t="inlineStr">
         <is>
-          <t>joho_henko_tekiyo_date_to</t>
+          <t>denshi_shonin_status</t>
         </is>
       </c>
       <c r="D43" s="10" t="n"/>
@@ -6003,7 +6211,7 @@
       <c r="L43" s="11" t="n"/>
       <c r="M43" s="17" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Number</t>
         </is>
       </c>
       <c r="N43" s="10" t="n"/>
@@ -6034,7 +6242,7 @@
       <c r="AE43" s="11" t="n"/>
       <c r="AF43" s="19" t="inlineStr">
         <is>
-          <t>適用日（範囲終了）YYYY/MM/DD ※相関チェック：from ≦ to。両方空欄=最新データフラグ=1、入力時=変更適用日が範囲内の履歴を抽出【詳細検索】</t>
+          <t>電子版承認ステータス（NULL=Web申込以外, 0:未承認, 1:承認済み, 2:否認）【常時表示】</t>
         </is>
       </c>
       <c r="AG43" s="10" t="n"/>
@@ -6043,13 +6251,13 @@
       <c r="AJ43" s="10" t="n"/>
       <c r="AK43" s="11" t="n"/>
     </row>
-    <row r="44" ht="54" customHeight="1">
+    <row r="44" ht="36" customHeight="1">
       <c r="B44" s="31" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C44" s="19" t="inlineStr">
         <is>
-          <t>shiharai_hoho</t>
+          <t>tetsuzuki_shurui</t>
         </is>
       </c>
       <c r="D44" s="10" t="n"/>
@@ -6094,7 +6302,7 @@
       <c r="AE44" s="11" t="n"/>
       <c r="AF44" s="19" t="inlineStr">
         <is>
-          <t>支払方法 ※m_code.code_category='SHIHARAI_HOHO'を参照（1:口座引落, 2:現金集金, 3:振込集金, 4:JA施設等, 5:給与天引き, 6:クレジットカード, 9:その他）【詳細検索】</t>
+          <t>手続種類 ※m_code.code_category='TETSUZUKI_SHURUI'を参照（0:解約, 1:新規）【常時表示】</t>
         </is>
       </c>
       <c r="AG44" s="10" t="n"/>
@@ -6103,13 +6311,13 @@
       <c r="AJ44" s="10" t="n"/>
       <c r="AK44" s="11" t="n"/>
     </row>
-    <row r="45" ht="108" customHeight="1">
+    <row r="45" ht="18" customHeight="1">
       <c r="B45" s="31" t="n">
-        <v>22.5</v>
+        <v>20</v>
       </c>
       <c r="C45" s="19" t="inlineStr">
         <is>
-          <t>active_tanka_flg</t>
+          <t>joho_henko_tekiyo_date_from</t>
         </is>
       </c>
       <c r="D45" s="10" t="n"/>
@@ -6123,7 +6331,7 @@
       <c r="L45" s="11" t="n"/>
       <c r="M45" s="17" t="inlineStr">
         <is>
-          <t>Boolean</t>
+          <t>String</t>
         </is>
       </c>
       <c r="N45" s="10" t="n"/>
@@ -6154,7 +6362,7 @@
       <c r="AE45" s="11" t="n"/>
       <c r="AF45" s="19" t="inlineStr">
         <is>
-          <t>有効単価フラグ（SCR-020 error gate 連携・顧客要件2026-07 改訂）。単価一覧(SCR-006)と同一のトライステート: `true`=有効単価(active_flg=TRUE)を参照する購読者のみ、`false`=失効単価(active_flg=FALSE)を参照する購読者のみ、省略=両方。参照する購読料単価は tanka_type=1。口座振替出力(SCR-020)の失効単価エラーからは `false`(無効)で初期選択される【詳細検索】</t>
+          <t>適用日（範囲開始）YYYY/MM/DD【詳細検索】</t>
         </is>
       </c>
       <c r="AG45" s="10" t="n"/>
@@ -6163,13 +6371,13 @@
       <c r="AJ45" s="10" t="n"/>
       <c r="AK45" s="11" t="n"/>
     </row>
-    <row r="46" ht="18" customHeight="1">
+    <row r="46" ht="36" customHeight="1">
       <c r="B46" s="31" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C46" s="19" t="inlineStr">
         <is>
-          <t>page</t>
+          <t>joho_henko_tekiyo_date_to</t>
         </is>
       </c>
       <c r="D46" s="10" t="n"/>
@@ -6183,7 +6391,7 @@
       <c r="L46" s="11" t="n"/>
       <c r="M46" s="17" t="inlineStr">
         <is>
-          <t>Number</t>
+          <t>String</t>
         </is>
       </c>
       <c r="N46" s="10" t="n"/>
@@ -6214,7 +6422,7 @@
       <c r="AE46" s="11" t="n"/>
       <c r="AF46" s="19" t="inlineStr">
         <is>
-          <t>ページ番号（デフォルト: 1）</t>
+          <t>適用日（範囲終了）YYYY/MM/DD ※相関チェック：from ≦ to。両方空欄=最新データフラグ=1、入力時=変更適用日が範囲内の履歴を抽出【詳細検索】</t>
         </is>
       </c>
       <c r="AG46" s="10" t="n"/>
@@ -6223,13 +6431,13 @@
       <c r="AJ46" s="10" t="n"/>
       <c r="AK46" s="11" t="n"/>
     </row>
-    <row r="47" ht="18" customHeight="1">
+    <row r="47" ht="54" customHeight="1">
       <c r="B47" s="31" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C47" s="19" t="inlineStr">
         <is>
-          <t>per_page</t>
+          <t>shiharai_hoho</t>
         </is>
       </c>
       <c r="D47" s="10" t="n"/>
@@ -6274,7 +6482,7 @@
       <c r="AE47" s="11" t="n"/>
       <c r="AF47" s="19" t="inlineStr">
         <is>
-          <t>1ページの件数（デフォルト: 20、最大: 100）</t>
+          <t>支払方法 ※m_code.code_category='SHIHARAI_HOHO'を参照（1:口座引落, 2:現金集金, 3:振込集金, 4:JA施設等, 5:給与天引き, 6:クレジットカード, 9:その他）【詳細検索】</t>
         </is>
       </c>
       <c r="AG47" s="10" t="n"/>
@@ -6283,13 +6491,13 @@
       <c r="AJ47" s="10" t="n"/>
       <c r="AK47" s="11" t="n"/>
     </row>
-    <row r="48" ht="72" customHeight="1">
+    <row r="48" ht="108" customHeight="1">
       <c r="B48" s="31" t="n">
-        <v>25</v>
+        <v>22.5</v>
       </c>
       <c r="C48" s="19" t="inlineStr">
         <is>
-          <t>sort_by</t>
+          <t>active_tanka_flg</t>
         </is>
       </c>
       <c r="D48" s="10" t="n"/>
@@ -6303,7 +6511,7 @@
       <c r="L48" s="11" t="n"/>
       <c r="M48" s="17" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Boolean</t>
         </is>
       </c>
       <c r="N48" s="10" t="n"/>
@@ -6334,7 +6542,7 @@
       <c r="AE48" s="11" t="n"/>
       <c r="AF48" s="19" t="inlineStr">
         <is>
-          <t>ソートカラム（dokusya_id, kanri_shiten_id, shiten_id, kumiaiin_code, hanbaiten_id, shoki_dokusya_kaishi_date, dokusya_chushi_date）。デフォルト: updated_at</t>
+          <t>有効単価フラグ（SCR-020 error gate 連携・顧客要件2026-07 改訂）。単価一覧(SCR-006)と同一のトライステート: `true`=有効単価(active_flg=TRUE)を参照する購読者のみ、`false`=失効単価(active_flg=FALSE)を参照する購読者のみ、省略=両方。参照する購読料単価は tanka_type=1。口座振替出力(SCR-020)の失効単価エラーからは `false`(無効)で初期選択される【詳細検索】</t>
         </is>
       </c>
       <c r="AG48" s="10" t="n"/>
@@ -6345,11 +6553,11 @@
     </row>
     <row r="49" ht="18" customHeight="1">
       <c r="B49" s="31" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C49" s="19" t="inlineStr">
         <is>
-          <t>sort_order</t>
+          <t>page</t>
         </is>
       </c>
       <c r="D49" s="10" t="n"/>
@@ -6363,7 +6571,7 @@
       <c r="L49" s="11" t="n"/>
       <c r="M49" s="17" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Number</t>
         </is>
       </c>
       <c r="N49" s="10" t="n"/>
@@ -6394,7 +6602,7 @@
       <c r="AE49" s="11" t="n"/>
       <c r="AF49" s="19" t="inlineStr">
         <is>
-          <t>ソート順（asc / desc、デフォルト: desc）</t>
+          <t>ページ番号（デフォルト: 1）</t>
         </is>
       </c>
       <c r="AG49" s="10" t="n"/>
@@ -6403,211 +6611,207 @@
       <c r="AJ49" s="10" t="n"/>
       <c r="AK49" s="11" t="n"/>
     </row>
-    <row r="50" ht="19.5" customHeight="1"/>
-    <row r="51" ht="19.5" customHeight="1">
-      <c r="A51" s="27" t="inlineStr">
+    <row r="50" ht="18" customHeight="1">
+      <c r="B50" s="31" t="n">
+        <v>24</v>
+      </c>
+      <c r="C50" s="19" t="inlineStr">
+        <is>
+          <t>per_page</t>
+        </is>
+      </c>
+      <c r="D50" s="10" t="n"/>
+      <c r="E50" s="10" t="n"/>
+      <c r="F50" s="10" t="n"/>
+      <c r="G50" s="10" t="n"/>
+      <c r="H50" s="10" t="n"/>
+      <c r="I50" s="10" t="n"/>
+      <c r="J50" s="10" t="n"/>
+      <c r="K50" s="10" t="n"/>
+      <c r="L50" s="11" t="n"/>
+      <c r="M50" s="17" t="inlineStr">
+        <is>
+          <t>Number</t>
+        </is>
+      </c>
+      <c r="N50" s="10" t="n"/>
+      <c r="O50" s="10" t="n"/>
+      <c r="P50" s="11" t="n"/>
+      <c r="Q50" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R50" s="10" t="n"/>
+      <c r="S50" s="11" t="n"/>
+      <c r="T50" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U50" s="10" t="n"/>
+      <c r="V50" s="10" t="n"/>
+      <c r="W50" s="10" t="n"/>
+      <c r="X50" s="11" t="n"/>
+      <c r="Y50" s="17" t="inlineStr"/>
+      <c r="Z50" s="10" t="n"/>
+      <c r="AA50" s="10" t="n"/>
+      <c r="AB50" s="11" t="n"/>
+      <c r="AC50" s="17" t="inlineStr"/>
+      <c r="AD50" s="10" t="n"/>
+      <c r="AE50" s="11" t="n"/>
+      <c r="AF50" s="19" t="inlineStr">
+        <is>
+          <t>1ページの件数（デフォルト: 20、最大: 100）</t>
+        </is>
+      </c>
+      <c r="AG50" s="10" t="n"/>
+      <c r="AH50" s="10" t="n"/>
+      <c r="AI50" s="10" t="n"/>
+      <c r="AJ50" s="10" t="n"/>
+      <c r="AK50" s="11" t="n"/>
+    </row>
+    <row r="51" ht="72" customHeight="1">
+      <c r="B51" s="31" t="n">
+        <v>25</v>
+      </c>
+      <c r="C51" s="19" t="inlineStr">
+        <is>
+          <t>sort_by</t>
+        </is>
+      </c>
+      <c r="D51" s="10" t="n"/>
+      <c r="E51" s="10" t="n"/>
+      <c r="F51" s="10" t="n"/>
+      <c r="G51" s="10" t="n"/>
+      <c r="H51" s="10" t="n"/>
+      <c r="I51" s="10" t="n"/>
+      <c r="J51" s="10" t="n"/>
+      <c r="K51" s="10" t="n"/>
+      <c r="L51" s="11" t="n"/>
+      <c r="M51" s="17" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="N51" s="10" t="n"/>
+      <c r="O51" s="10" t="n"/>
+      <c r="P51" s="11" t="n"/>
+      <c r="Q51" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R51" s="10" t="n"/>
+      <c r="S51" s="11" t="n"/>
+      <c r="T51" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U51" s="10" t="n"/>
+      <c r="V51" s="10" t="n"/>
+      <c r="W51" s="10" t="n"/>
+      <c r="X51" s="11" t="n"/>
+      <c r="Y51" s="17" t="inlineStr"/>
+      <c r="Z51" s="10" t="n"/>
+      <c r="AA51" s="10" t="n"/>
+      <c r="AB51" s="11" t="n"/>
+      <c r="AC51" s="17" t="inlineStr"/>
+      <c r="AD51" s="10" t="n"/>
+      <c r="AE51" s="11" t="n"/>
+      <c r="AF51" s="19" t="inlineStr">
+        <is>
+          <t>ソートカラム（dokusya_id, kanri_shiten_id, shiten_id, kumiaiin_code, hanbaiten_id, hanbaiten_code, shoki_dokusya_kaishi_date, dokusya_chushi_date）。デフォルト: updated_at</t>
+        </is>
+      </c>
+      <c r="AG51" s="10" t="n"/>
+      <c r="AH51" s="10" t="n"/>
+      <c r="AI51" s="10" t="n"/>
+      <c r="AJ51" s="10" t="n"/>
+      <c r="AK51" s="11" t="n"/>
+    </row>
+    <row r="52" ht="18" customHeight="1">
+      <c r="B52" s="31" t="n">
+        <v>26</v>
+      </c>
+      <c r="C52" s="19" t="inlineStr">
+        <is>
+          <t>sort_order</t>
+        </is>
+      </c>
+      <c r="D52" s="10" t="n"/>
+      <c r="E52" s="10" t="n"/>
+      <c r="F52" s="10" t="n"/>
+      <c r="G52" s="10" t="n"/>
+      <c r="H52" s="10" t="n"/>
+      <c r="I52" s="10" t="n"/>
+      <c r="J52" s="10" t="n"/>
+      <c r="K52" s="10" t="n"/>
+      <c r="L52" s="11" t="n"/>
+      <c r="M52" s="17" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="N52" s="10" t="n"/>
+      <c r="O52" s="10" t="n"/>
+      <c r="P52" s="11" t="n"/>
+      <c r="Q52" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R52" s="10" t="n"/>
+      <c r="S52" s="11" t="n"/>
+      <c r="T52" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U52" s="10" t="n"/>
+      <c r="V52" s="10" t="n"/>
+      <c r="W52" s="10" t="n"/>
+      <c r="X52" s="11" t="n"/>
+      <c r="Y52" s="17" t="inlineStr"/>
+      <c r="Z52" s="10" t="n"/>
+      <c r="AA52" s="10" t="n"/>
+      <c r="AB52" s="11" t="n"/>
+      <c r="AC52" s="17" t="inlineStr"/>
+      <c r="AD52" s="10" t="n"/>
+      <c r="AE52" s="11" t="n"/>
+      <c r="AF52" s="19" t="inlineStr">
+        <is>
+          <t>ソート順（asc / desc、デフォルト: desc）</t>
+        </is>
+      </c>
+      <c r="AG52" s="10" t="n"/>
+      <c r="AH52" s="10" t="n"/>
+      <c r="AI52" s="10" t="n"/>
+      <c r="AJ52" s="10" t="n"/>
+      <c r="AK52" s="11" t="n"/>
+    </row>
+    <row r="53" ht="19.5" customHeight="1"/>
+    <row r="54" ht="19.5" customHeight="1">
+      <c r="A54" s="27" t="inlineStr">
         <is>
           <t>3.レスポンスデータ</t>
         </is>
       </c>
     </row>
-    <row r="52" ht="19.5" customHeight="1"/>
-    <row r="53" ht="19.5" customHeight="1">
-      <c r="B53" s="30" t="inlineStr">
+    <row r="55" ht="19.5" customHeight="1"/>
+    <row r="56" ht="19.5" customHeight="1">
+      <c r="B56" s="30" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="C53" s="16" t="inlineStr">
+      <c r="C56" s="16" t="inlineStr">
         <is>
           <t>項目ID</t>
         </is>
       </c>
-      <c r="D53" s="10" t="n"/>
-      <c r="E53" s="10" t="n"/>
-      <c r="F53" s="10" t="n"/>
-      <c r="G53" s="10" t="n"/>
-      <c r="H53" s="10" t="n"/>
-      <c r="I53" s="10" t="n"/>
-      <c r="J53" s="10" t="n"/>
-      <c r="K53" s="10" t="n"/>
-      <c r="L53" s="11" t="n"/>
-      <c r="M53" s="16" t="inlineStr">
-        <is>
-          <t>タイプ</t>
-        </is>
-      </c>
-      <c r="N53" s="10" t="n"/>
-      <c r="O53" s="10" t="n"/>
-      <c r="P53" s="11" t="n"/>
-      <c r="Q53" s="16" t="inlineStr">
-        <is>
-          <t>繰り返し</t>
-        </is>
-      </c>
-      <c r="R53" s="10" t="n"/>
-      <c r="S53" s="11" t="n"/>
-      <c r="T53" s="16" t="inlineStr">
-        <is>
-          <t>フォーマット</t>
-        </is>
-      </c>
-      <c r="U53" s="10" t="n"/>
-      <c r="V53" s="10" t="n"/>
-      <c r="W53" s="10" t="n"/>
-      <c r="X53" s="11" t="n"/>
-      <c r="Y53" s="16" t="inlineStr">
-        <is>
-          <t>Nullable</t>
-        </is>
-      </c>
-      <c r="Z53" s="10" t="n"/>
-      <c r="AA53" s="10" t="n"/>
-      <c r="AB53" s="10" t="n"/>
-      <c r="AC53" s="10" t="n"/>
-      <c r="AD53" s="10" t="n"/>
-      <c r="AE53" s="11" t="n"/>
-      <c r="AF53" s="16" t="inlineStr">
-        <is>
-          <t>説明</t>
-        </is>
-      </c>
-      <c r="AG53" s="10" t="n"/>
-      <c r="AH53" s="10" t="n"/>
-      <c r="AI53" s="10" t="n"/>
-      <c r="AJ53" s="10" t="n"/>
-      <c r="AK53" s="11" t="n"/>
-    </row>
-    <row r="54" ht="18" customHeight="1">
-      <c r="B54" s="31" t="n">
-        <v>1</v>
-      </c>
-      <c r="C54" s="19" t="inlineStr">
-        <is>
-          <t>data</t>
-        </is>
-      </c>
-      <c r="D54" s="10" t="n"/>
-      <c r="E54" s="10" t="n"/>
-      <c r="F54" s="10" t="n"/>
-      <c r="G54" s="10" t="n"/>
-      <c r="H54" s="10" t="n"/>
-      <c r="I54" s="10" t="n"/>
-      <c r="J54" s="10" t="n"/>
-      <c r="K54" s="10" t="n"/>
-      <c r="L54" s="11" t="n"/>
-      <c r="M54" s="17" t="inlineStr">
-        <is>
-          <t>Array</t>
-        </is>
-      </c>
-      <c r="N54" s="10" t="n"/>
-      <c r="O54" s="10" t="n"/>
-      <c r="P54" s="11" t="n"/>
-      <c r="Q54" s="17" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="R54" s="10" t="n"/>
-      <c r="S54" s="11" t="n"/>
-      <c r="T54" s="17" t="inlineStr"/>
-      <c r="U54" s="10" t="n"/>
-      <c r="V54" s="10" t="n"/>
-      <c r="W54" s="10" t="n"/>
-      <c r="X54" s="11" t="n"/>
-      <c r="Y54" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Z54" s="10" t="n"/>
-      <c r="AA54" s="10" t="n"/>
-      <c r="AB54" s="10" t="n"/>
-      <c r="AC54" s="10" t="n"/>
-      <c r="AD54" s="10" t="n"/>
-      <c r="AE54" s="11" t="n"/>
-      <c r="AF54" s="19" t="inlineStr">
-        <is>
-          <t>購読者一覧</t>
-        </is>
-      </c>
-      <c r="AG54" s="10" t="n"/>
-      <c r="AH54" s="10" t="n"/>
-      <c r="AI54" s="10" t="n"/>
-      <c r="AJ54" s="10" t="n"/>
-      <c r="AK54" s="11" t="n"/>
-    </row>
-    <row r="55" ht="18" customHeight="1">
-      <c r="B55" s="31" t="n">
-        <v>2</v>
-      </c>
-      <c r="C55" s="37" t="n"/>
-      <c r="D55" s="19" t="inlineStr">
-        <is>
-          <t>dokusya_id</t>
-        </is>
-      </c>
-      <c r="E55" s="10" t="n"/>
-      <c r="F55" s="10" t="n"/>
-      <c r="G55" s="10" t="n"/>
-      <c r="H55" s="10" t="n"/>
-      <c r="I55" s="10" t="n"/>
-      <c r="J55" s="10" t="n"/>
-      <c r="K55" s="10" t="n"/>
-      <c r="L55" s="11" t="n"/>
-      <c r="M55" s="17" t="inlineStr">
-        <is>
-          <t>Number</t>
-        </is>
-      </c>
-      <c r="N55" s="10" t="n"/>
-      <c r="O55" s="10" t="n"/>
-      <c r="P55" s="11" t="n"/>
-      <c r="Q55" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R55" s="10" t="n"/>
-      <c r="S55" s="11" t="n"/>
-      <c r="T55" s="17" t="inlineStr"/>
-      <c r="U55" s="10" t="n"/>
-      <c r="V55" s="10" t="n"/>
-      <c r="W55" s="10" t="n"/>
-      <c r="X55" s="11" t="n"/>
-      <c r="Y55" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Z55" s="10" t="n"/>
-      <c r="AA55" s="10" t="n"/>
-      <c r="AB55" s="10" t="n"/>
-      <c r="AC55" s="10" t="n"/>
-      <c r="AD55" s="10" t="n"/>
-      <c r="AE55" s="11" t="n"/>
-      <c r="AF55" s="19" t="inlineStr">
-        <is>
-          <t>購読者ID</t>
-        </is>
-      </c>
-      <c r="AG55" s="10" t="n"/>
-      <c r="AH55" s="10" t="n"/>
-      <c r="AI55" s="10" t="n"/>
-      <c r="AJ55" s="10" t="n"/>
-      <c r="AK55" s="11" t="n"/>
-    </row>
-    <row r="56" ht="18" customHeight="1">
-      <c r="B56" s="31" t="n">
-        <v>3</v>
-      </c>
-      <c r="C56" s="38" t="n"/>
-      <c r="D56" s="19" t="inlineStr">
-        <is>
-          <t>ja_id</t>
-        </is>
-      </c>
+      <c r="D56" s="10" t="n"/>
       <c r="E56" s="10" t="n"/>
       <c r="F56" s="10" t="n"/>
       <c r="G56" s="10" t="n"/>
@@ -6616,29 +6820,33 @@
       <c r="J56" s="10" t="n"/>
       <c r="K56" s="10" t="n"/>
       <c r="L56" s="11" t="n"/>
-      <c r="M56" s="17" t="inlineStr">
-        <is>
-          <t>Number</t>
+      <c r="M56" s="16" t="inlineStr">
+        <is>
+          <t>タイプ</t>
         </is>
       </c>
       <c r="N56" s="10" t="n"/>
       <c r="O56" s="10" t="n"/>
       <c r="P56" s="11" t="n"/>
-      <c r="Q56" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="Q56" s="16" t="inlineStr">
+        <is>
+          <t>繰り返し</t>
         </is>
       </c>
       <c r="R56" s="10" t="n"/>
       <c r="S56" s="11" t="n"/>
-      <c r="T56" s="17" t="inlineStr"/>
+      <c r="T56" s="16" t="inlineStr">
+        <is>
+          <t>フォーマット</t>
+        </is>
+      </c>
       <c r="U56" s="10" t="n"/>
       <c r="V56" s="10" t="n"/>
       <c r="W56" s="10" t="n"/>
       <c r="X56" s="11" t="n"/>
-      <c r="Y56" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="Y56" s="16" t="inlineStr">
+        <is>
+          <t>Nullable</t>
         </is>
       </c>
       <c r="Z56" s="10" t="n"/>
@@ -6647,9 +6855,9 @@
       <c r="AC56" s="10" t="n"/>
       <c r="AD56" s="10" t="n"/>
       <c r="AE56" s="11" t="n"/>
-      <c r="AF56" s="19" t="inlineStr">
-        <is>
-          <t>JA ID</t>
+      <c r="AF56" s="16" t="inlineStr">
+        <is>
+          <t>説明</t>
         </is>
       </c>
       <c r="AG56" s="10" t="n"/>
@@ -6660,14 +6868,14 @@
     </row>
     <row r="57" ht="18" customHeight="1">
       <c r="B57" s="31" t="n">
-        <v>4</v>
-      </c>
-      <c r="C57" s="38" t="n"/>
-      <c r="D57" s="19" t="inlineStr">
-        <is>
-          <t>kanri_shiten_id</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="C57" s="19" t="inlineStr">
+        <is>
+          <t>data</t>
+        </is>
+      </c>
+      <c r="D57" s="10" t="n"/>
       <c r="E57" s="10" t="n"/>
       <c r="F57" s="10" t="n"/>
       <c r="G57" s="10" t="n"/>
@@ -6678,7 +6886,7 @@
       <c r="L57" s="11" t="n"/>
       <c r="M57" s="17" t="inlineStr">
         <is>
-          <t>Number</t>
+          <t>Array</t>
         </is>
       </c>
       <c r="N57" s="10" t="n"/>
@@ -6686,7 +6894,7 @@
       <c r="P57" s="11" t="n"/>
       <c r="Q57" s="17" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>○</t>
         </is>
       </c>
       <c r="R57" s="10" t="n"/>
@@ -6698,7 +6906,7 @@
       <c r="X57" s="11" t="n"/>
       <c r="Y57" s="17" t="inlineStr">
         <is>
-          <t>〇</t>
+          <t>-</t>
         </is>
       </c>
       <c r="Z57" s="10" t="n"/>
@@ -6709,7 +6917,7 @@
       <c r="AE57" s="11" t="n"/>
       <c r="AF57" s="19" t="inlineStr">
         <is>
-          <t>管理支店ID</t>
+          <t>購読者一覧</t>
         </is>
       </c>
       <c r="AG57" s="10" t="n"/>
@@ -6720,12 +6928,12 @@
     </row>
     <row r="58" ht="18" customHeight="1">
       <c r="B58" s="31" t="n">
-        <v>5</v>
-      </c>
-      <c r="C58" s="38" t="n"/>
+        <v>2</v>
+      </c>
+      <c r="C58" s="37" t="n"/>
       <c r="D58" s="19" t="inlineStr">
         <is>
-          <t>kanri_shiten_name</t>
+          <t>dokusya_id</t>
         </is>
       </c>
       <c r="E58" s="10" t="n"/>
@@ -6738,7 +6946,7 @@
       <c r="L58" s="11" t="n"/>
       <c r="M58" s="17" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Number</t>
         </is>
       </c>
       <c r="N58" s="10" t="n"/>
@@ -6758,7 +6966,7 @@
       <c r="X58" s="11" t="n"/>
       <c r="Y58" s="17" t="inlineStr">
         <is>
-          <t>〇</t>
+          <t>-</t>
         </is>
       </c>
       <c r="Z58" s="10" t="n"/>
@@ -6769,7 +6977,7 @@
       <c r="AE58" s="11" t="n"/>
       <c r="AF58" s="19" t="inlineStr">
         <is>
-          <t>管理支店名</t>
+          <t>購読者ID</t>
         </is>
       </c>
       <c r="AG58" s="10" t="n"/>
@@ -6780,12 +6988,12 @@
     </row>
     <row r="59" ht="18" customHeight="1">
       <c r="B59" s="31" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C59" s="38" t="n"/>
       <c r="D59" s="19" t="inlineStr">
         <is>
-          <t>shiten_id</t>
+          <t>ja_id</t>
         </is>
       </c>
       <c r="E59" s="10" t="n"/>
@@ -6818,7 +7026,7 @@
       <c r="X59" s="11" t="n"/>
       <c r="Y59" s="17" t="inlineStr">
         <is>
-          <t>〇</t>
+          <t>-</t>
         </is>
       </c>
       <c r="Z59" s="10" t="n"/>
@@ -6829,7 +7037,7 @@
       <c r="AE59" s="11" t="n"/>
       <c r="AF59" s="19" t="inlineStr">
         <is>
-          <t>支店ID</t>
+          <t>JA ID</t>
         </is>
       </c>
       <c r="AG59" s="10" t="n"/>
@@ -6840,12 +7048,12 @@
     </row>
     <row r="60" ht="18" customHeight="1">
       <c r="B60" s="31" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C60" s="38" t="n"/>
       <c r="D60" s="19" t="inlineStr">
         <is>
-          <t>shiten_name</t>
+          <t>kanri_shiten_id</t>
         </is>
       </c>
       <c r="E60" s="10" t="n"/>
@@ -6858,7 +7066,7 @@
       <c r="L60" s="11" t="n"/>
       <c r="M60" s="17" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Number</t>
         </is>
       </c>
       <c r="N60" s="10" t="n"/>
@@ -6889,7 +7097,7 @@
       <c r="AE60" s="11" t="n"/>
       <c r="AF60" s="19" t="inlineStr">
         <is>
-          <t>支店名</t>
+          <t>管理支店ID</t>
         </is>
       </c>
       <c r="AG60" s="10" t="n"/>
@@ -6900,12 +7108,12 @@
     </row>
     <row r="61" ht="18" customHeight="1">
       <c r="B61" s="31" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C61" s="38" t="n"/>
       <c r="D61" s="19" t="inlineStr">
         <is>
-          <t>kumiaiin_code</t>
+          <t>kanri_shiten_name</t>
         </is>
       </c>
       <c r="E61" s="10" t="n"/>
@@ -6938,7 +7146,7 @@
       <c r="X61" s="11" t="n"/>
       <c r="Y61" s="17" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>〇</t>
         </is>
       </c>
       <c r="Z61" s="10" t="n"/>
@@ -6949,7 +7157,7 @@
       <c r="AE61" s="11" t="n"/>
       <c r="AF61" s="19" t="inlineStr">
         <is>
-          <t>組合員コード（空文字許容）</t>
+          <t>管理支店名</t>
         </is>
       </c>
       <c r="AG61" s="10" t="n"/>
@@ -6958,14 +7166,14 @@
       <c r="AJ61" s="10" t="n"/>
       <c r="AK61" s="11" t="n"/>
     </row>
-    <row r="62" ht="36" customHeight="1">
+    <row r="62" ht="18" customHeight="1">
       <c r="B62" s="31" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C62" s="38" t="n"/>
       <c r="D62" s="19" t="inlineStr">
         <is>
-          <t>full_name</t>
+          <t>shiten_id</t>
         </is>
       </c>
       <c r="E62" s="10" t="n"/>
@@ -6978,7 +7186,7 @@
       <c r="L62" s="11" t="n"/>
       <c r="M62" s="17" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Number</t>
         </is>
       </c>
       <c r="N62" s="10" t="n"/>
@@ -6998,7 +7206,7 @@
       <c r="X62" s="11" t="n"/>
       <c r="Y62" s="17" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>〇</t>
         </is>
       </c>
       <c r="Z62" s="10" t="n"/>
@@ -7009,7 +7217,7 @@
       <c r="AE62" s="11" t="n"/>
       <c r="AF62" s="19" t="inlineStr">
         <is>
-          <t>氏名（shimei_sei + " " + shimei_mei）</t>
+          <t>支店ID</t>
         </is>
       </c>
       <c r="AG62" s="10" t="n"/>
@@ -7018,14 +7226,14 @@
       <c r="AJ62" s="10" t="n"/>
       <c r="AK62" s="11" t="n"/>
     </row>
-    <row r="63" ht="36" customHeight="1">
+    <row r="63" ht="18" customHeight="1">
       <c r="B63" s="31" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C63" s="38" t="n"/>
       <c r="D63" s="19" t="inlineStr">
         <is>
-          <t>full_name_kana</t>
+          <t>shiten_name</t>
         </is>
       </c>
       <c r="E63" s="10" t="n"/>
@@ -7058,7 +7266,7 @@
       <c r="X63" s="11" t="n"/>
       <c r="Y63" s="17" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>〇</t>
         </is>
       </c>
       <c r="Z63" s="10" t="n"/>
@@ -7069,7 +7277,7 @@
       <c r="AE63" s="11" t="n"/>
       <c r="AF63" s="19" t="inlineStr">
         <is>
-          <t>かな氏名（shimei_kana_sei + " " + shimei_kana_mei）</t>
+          <t>支店名</t>
         </is>
       </c>
       <c r="AG63" s="10" t="n"/>
@@ -7078,14 +7286,14 @@
       <c r="AJ63" s="10" t="n"/>
       <c r="AK63" s="11" t="n"/>
     </row>
-    <row r="64" ht="36" customHeight="1">
+    <row r="64" ht="18" customHeight="1">
       <c r="B64" s="31" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C64" s="38" t="n"/>
       <c r="D64" s="19" t="inlineStr">
         <is>
-          <t>tetsuzuki_shurui</t>
+          <t>kumiaiin_code</t>
         </is>
       </c>
       <c r="E64" s="10" t="n"/>
@@ -7098,7 +7306,7 @@
       <c r="L64" s="11" t="n"/>
       <c r="M64" s="17" t="inlineStr">
         <is>
-          <t>Number</t>
+          <t>String</t>
         </is>
       </c>
       <c r="N64" s="10" t="n"/>
@@ -7129,7 +7337,7 @@
       <c r="AE64" s="11" t="n"/>
       <c r="AF64" s="19" t="inlineStr">
         <is>
-          <t>手続種類 ※m_code.code_category='TETSUZUKI_SHURUI'を参照（0:解約, 1:新規）</t>
+          <t>組合員コード（空文字許容）</t>
         </is>
       </c>
       <c r="AG64" s="10" t="n"/>
@@ -7138,14 +7346,14 @@
       <c r="AJ64" s="10" t="n"/>
       <c r="AK64" s="11" t="n"/>
     </row>
-    <row r="65" ht="18" customHeight="1">
+    <row r="65" ht="36" customHeight="1">
       <c r="B65" s="31" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C65" s="38" t="n"/>
       <c r="D65" s="19" t="inlineStr">
         <is>
-          <t>renrakusaki_1</t>
+          <t>full_name</t>
         </is>
       </c>
       <c r="E65" s="10" t="n"/>
@@ -7189,7 +7397,7 @@
       <c r="AE65" s="11" t="n"/>
       <c r="AF65" s="19" t="inlineStr">
         <is>
-          <t>連絡先１（空文字許容）</t>
+          <t>氏名（shimei_sei + " " + shimei_mei）</t>
         </is>
       </c>
       <c r="AG65" s="10" t="n"/>
@@ -7198,14 +7406,14 @@
       <c r="AJ65" s="10" t="n"/>
       <c r="AK65" s="11" t="n"/>
     </row>
-    <row r="66" ht="18" customHeight="1">
+    <row r="66" ht="36" customHeight="1">
       <c r="B66" s="31" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C66" s="38" t="n"/>
       <c r="D66" s="19" t="inlineStr">
         <is>
-          <t>renrakusaki_2</t>
+          <t>full_name_kana</t>
         </is>
       </c>
       <c r="E66" s="10" t="n"/>
@@ -7249,7 +7457,7 @@
       <c r="AE66" s="11" t="n"/>
       <c r="AF66" s="19" t="inlineStr">
         <is>
-          <t>連絡先２（空文字許容）</t>
+          <t>かな氏名（shimei_kana_sei + " " + shimei_kana_mei）</t>
         </is>
       </c>
       <c r="AG66" s="10" t="n"/>
@@ -7258,14 +7466,14 @@
       <c r="AJ66" s="10" t="n"/>
       <c r="AK66" s="11" t="n"/>
     </row>
-    <row r="67" ht="54" customHeight="1">
+    <row r="67" ht="36" customHeight="1">
       <c r="B67" s="31" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C67" s="38" t="n"/>
       <c r="D67" s="19" t="inlineStr">
         <is>
-          <t>haitatsu_full_name</t>
+          <t>tetsuzuki_shurui</t>
         </is>
       </c>
       <c r="E67" s="10" t="n"/>
@@ -7278,7 +7486,7 @@
       <c r="L67" s="11" t="n"/>
       <c r="M67" s="17" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Number</t>
         </is>
       </c>
       <c r="N67" s="10" t="n"/>
@@ -7309,7 +7517,7 @@
       <c r="AE67" s="11" t="n"/>
       <c r="AF67" s="19" t="inlineStr">
         <is>
-          <t>配達先氏名（haitatsu_shimei_sei + " " + haitatsu_shimei_mei、前後空白トリム）</t>
+          <t>手続種類 ※m_code.code_category='TETSUZUKI_SHURUI'を参照（0:解約, 1:新規）</t>
         </is>
       </c>
       <c r="AG67" s="10" t="n"/>
@@ -7320,12 +7528,12 @@
     </row>
     <row r="68" ht="18" customHeight="1">
       <c r="B68" s="31" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C68" s="38" t="n"/>
       <c r="D68" s="19" t="inlineStr">
         <is>
-          <t>haitatsu_yubin_no</t>
+          <t>renrakusaki_1</t>
         </is>
       </c>
       <c r="E68" s="10" t="n"/>
@@ -7369,7 +7577,7 @@
       <c r="AE68" s="11" t="n"/>
       <c r="AF68" s="19" t="inlineStr">
         <is>
-          <t>配達先郵便番号（空文字許容）</t>
+          <t>連絡先１（空文字許容）</t>
         </is>
       </c>
       <c r="AG68" s="10" t="n"/>
@@ -7378,14 +7586,14 @@
       <c r="AJ68" s="10" t="n"/>
       <c r="AK68" s="11" t="n"/>
     </row>
-    <row r="69" ht="54" customHeight="1">
+    <row r="69" ht="18" customHeight="1">
       <c r="B69" s="31" t="n">
-        <v>16</v>
+        <v>12.5</v>
       </c>
       <c r="C69" s="38" t="n"/>
       <c r="D69" s="19" t="inlineStr">
         <is>
-          <t>haitatsu</t>
+          <t>haitatsu_renrakusaki_1</t>
         </is>
       </c>
       <c r="E69" s="10" t="n"/>
@@ -7429,7 +7637,7 @@
       <c r="AE69" s="11" t="n"/>
       <c r="AF69" s="19" t="inlineStr">
         <is>
-          <t>配達先住所（todofuken_name + shikuchoson + chome_banchi + tatemono_mei）</t>
+          <t>配送先連絡先１（空文字許容）</t>
         </is>
       </c>
       <c r="AG69" s="10" t="n"/>
@@ -7440,12 +7648,12 @@
     </row>
     <row r="70" ht="18" customHeight="1">
       <c r="B70" s="31" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C70" s="38" t="n"/>
       <c r="D70" s="19" t="inlineStr">
         <is>
-          <t>hanbaiten_id</t>
+          <t>renrakusaki_2</t>
         </is>
       </c>
       <c r="E70" s="10" t="n"/>
@@ -7458,7 +7666,7 @@
       <c r="L70" s="11" t="n"/>
       <c r="M70" s="17" t="inlineStr">
         <is>
-          <t>Number</t>
+          <t>String</t>
         </is>
       </c>
       <c r="N70" s="10" t="n"/>
@@ -7489,7 +7697,7 @@
       <c r="AE70" s="11" t="n"/>
       <c r="AF70" s="19" t="inlineStr">
         <is>
-          <t>販売店ID</t>
+          <t>連絡先２（空文字許容）</t>
         </is>
       </c>
       <c r="AG70" s="10" t="n"/>
@@ -7498,14 +7706,14 @@
       <c r="AJ70" s="10" t="n"/>
       <c r="AK70" s="11" t="n"/>
     </row>
-    <row r="71" ht="18" customHeight="1">
+    <row r="71" ht="54" customHeight="1">
       <c r="B71" s="31" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="C71" s="38" t="n"/>
       <c r="D71" s="19" t="inlineStr">
         <is>
-          <t>hanbaiten_name</t>
+          <t>haitatsu_full_name</t>
         </is>
       </c>
       <c r="E71" s="10" t="n"/>
@@ -7549,7 +7757,7 @@
       <c r="AE71" s="11" t="n"/>
       <c r="AF71" s="19" t="inlineStr">
         <is>
-          <t>販売店名</t>
+          <t>配達先氏名（haitatsu_shimei_sei + " " + haitatsu_shimei_mei、前後空白トリム）</t>
         </is>
       </c>
       <c r="AG71" s="10" t="n"/>
@@ -7558,14 +7766,14 @@
       <c r="AJ71" s="10" t="n"/>
       <c r="AK71" s="11" t="n"/>
     </row>
-    <row r="72" ht="54" customHeight="1">
+    <row r="72" ht="18" customHeight="1">
       <c r="B72" s="31" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C72" s="38" t="n"/>
       <c r="D72" s="19" t="inlineStr">
         <is>
-          <t>dokusya_shubetsu</t>
+          <t>haitatsu_yubin_no</t>
         </is>
       </c>
       <c r="E72" s="10" t="n"/>
@@ -7578,7 +7786,7 @@
       <c r="L72" s="11" t="n"/>
       <c r="M72" s="17" t="inlineStr">
         <is>
-          <t>Number</t>
+          <t>String</t>
         </is>
       </c>
       <c r="N72" s="10" t="n"/>
@@ -7609,7 +7817,7 @@
       <c r="AE72" s="11" t="n"/>
       <c r="AF72" s="19" t="inlineStr">
         <is>
-          <t>購読種別 ※m_code.code_category='DOKUSYA_SHUBETSU'を参照（1:紙版, 2:電子版, 3:併読）</t>
+          <t>配達先郵便番号（空文字許容）</t>
         </is>
       </c>
       <c r="AG72" s="10" t="n"/>
@@ -7618,14 +7826,14 @@
       <c r="AJ72" s="10" t="n"/>
       <c r="AK72" s="11" t="n"/>
     </row>
-    <row r="73" ht="36" customHeight="1">
+    <row r="73" ht="54" customHeight="1">
       <c r="B73" s="31" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C73" s="38" t="n"/>
       <c r="D73" s="19" t="inlineStr">
         <is>
-          <t>shiharai_hoho</t>
+          <t>haitatsu</t>
         </is>
       </c>
       <c r="E73" s="10" t="n"/>
@@ -7638,7 +7846,7 @@
       <c r="L73" s="11" t="n"/>
       <c r="M73" s="17" t="inlineStr">
         <is>
-          <t>Number</t>
+          <t>String</t>
         </is>
       </c>
       <c r="N73" s="10" t="n"/>
@@ -7669,7 +7877,7 @@
       <c r="AE73" s="11" t="n"/>
       <c r="AF73" s="19" t="inlineStr">
         <is>
-          <t>支払方法 ※m_code.code_category='SHIHARAI_HOHO'を参照</t>
+          <t>配達先住所（todofuken_name + shikuchoson + chome_banchi + tatemono_mei）</t>
         </is>
       </c>
       <c r="AG73" s="10" t="n"/>
@@ -7678,14 +7886,14 @@
       <c r="AJ73" s="10" t="n"/>
       <c r="AK73" s="11" t="n"/>
     </row>
-    <row r="74" ht="36" customHeight="1">
+    <row r="74" ht="18" customHeight="1">
       <c r="B74" s="31" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="C74" s="38" t="n"/>
       <c r="D74" s="19" t="inlineStr">
         <is>
-          <t>denshi_shonin_status</t>
+          <t>hanbaiten_id</t>
         </is>
       </c>
       <c r="E74" s="10" t="n"/>
@@ -7718,7 +7926,7 @@
       <c r="X74" s="11" t="n"/>
       <c r="Y74" s="17" t="inlineStr">
         <is>
-          <t>〇</t>
+          <t>-</t>
         </is>
       </c>
       <c r="Z74" s="10" t="n"/>
@@ -7729,7 +7937,7 @@
       <c r="AE74" s="11" t="n"/>
       <c r="AF74" s="19" t="inlineStr">
         <is>
-          <t>電子版承認ステータス（NULL=Web申込以外, 0:未承認, 1:承認済み, 2:否認）</t>
+          <t>販売店ID</t>
         </is>
       </c>
       <c r="AG74" s="10" t="n"/>
@@ -7740,12 +7948,12 @@
     </row>
     <row r="75" ht="18" customHeight="1">
       <c r="B75" s="31" t="n">
-        <v>22</v>
+        <v>17.5</v>
       </c>
       <c r="C75" s="38" t="n"/>
       <c r="D75" s="19" t="inlineStr">
         <is>
-          <t>shoki_dokusya_kaishi_date</t>
+          <t>hanbaiten_code</t>
         </is>
       </c>
       <c r="E75" s="10" t="n"/>
@@ -7771,11 +7979,7 @@
       </c>
       <c r="R75" s="10" t="n"/>
       <c r="S75" s="11" t="n"/>
-      <c r="T75" s="17" t="inlineStr">
-        <is>
-          <t>YYYY/MM/DD</t>
-        </is>
-      </c>
+      <c r="T75" s="17" t="inlineStr"/>
       <c r="U75" s="10" t="n"/>
       <c r="V75" s="10" t="n"/>
       <c r="W75" s="10" t="n"/>
@@ -7793,7 +7997,7 @@
       <c r="AE75" s="11" t="n"/>
       <c r="AF75" s="19" t="inlineStr">
         <is>
-          <t>初回購読開始日</t>
+          <t>販売店コード（検索結果テーブルの「販売店コード」列に表示）</t>
         </is>
       </c>
       <c r="AG75" s="10" t="n"/>
@@ -7804,12 +8008,12 @@
     </row>
     <row r="76" ht="18" customHeight="1">
       <c r="B76" s="31" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="C76" s="38" t="n"/>
       <c r="D76" s="19" t="inlineStr">
         <is>
-          <t>dokusya_chushi_date</t>
+          <t>hanbaiten_name</t>
         </is>
       </c>
       <c r="E76" s="10" t="n"/>
@@ -7835,18 +8039,14 @@
       </c>
       <c r="R76" s="10" t="n"/>
       <c r="S76" s="11" t="n"/>
-      <c r="T76" s="17" t="inlineStr">
-        <is>
-          <t>YYYY/MM/DD</t>
-        </is>
-      </c>
+      <c r="T76" s="17" t="inlineStr"/>
       <c r="U76" s="10" t="n"/>
       <c r="V76" s="10" t="n"/>
       <c r="W76" s="10" t="n"/>
       <c r="X76" s="11" t="n"/>
       <c r="Y76" s="17" t="inlineStr">
         <is>
-          <t>〇</t>
+          <t>-</t>
         </is>
       </c>
       <c r="Z76" s="10" t="n"/>
@@ -7857,7 +8057,7 @@
       <c r="AE76" s="11" t="n"/>
       <c r="AF76" s="19" t="inlineStr">
         <is>
-          <t>購読中止日</t>
+          <t>販売店名</t>
         </is>
       </c>
       <c r="AG76" s="10" t="n"/>
@@ -7866,14 +8066,14 @@
       <c r="AJ76" s="10" t="n"/>
       <c r="AK76" s="11" t="n"/>
     </row>
-    <row r="77" ht="36" customHeight="1">
+    <row r="77" ht="54" customHeight="1">
       <c r="B77" s="31" t="n">
-        <v>24</v>
-      </c>
-      <c r="C77" s="39" t="n"/>
+        <v>19</v>
+      </c>
+      <c r="C77" s="38" t="n"/>
       <c r="D77" s="19" t="inlineStr">
         <is>
-          <t>is_read_only</t>
+          <t>dokusya_shubetsu</t>
         </is>
       </c>
       <c r="E77" s="10" t="n"/>
@@ -7886,7 +8086,7 @@
       <c r="L77" s="11" t="n"/>
       <c r="M77" s="17" t="inlineStr">
         <is>
-          <t>Boolean</t>
+          <t>Number</t>
         </is>
       </c>
       <c r="N77" s="10" t="n"/>
@@ -7917,7 +8117,7 @@
       <c r="AE77" s="11" t="n"/>
       <c r="AF77" s="19" t="inlineStr">
         <is>
-          <t>編集・削除不可フラグ（true=電子版クレジットカード決済者または併読者）</t>
+          <t>購読種別 ※m_code.code_category='DOKUSYA_SHUBETSU'を参照（1:紙版, 2:電子版, 3:併読）</t>
         </is>
       </c>
       <c r="AG77" s="10" t="n"/>
@@ -7926,16 +8126,16 @@
       <c r="AJ77" s="10" t="n"/>
       <c r="AK77" s="11" t="n"/>
     </row>
-    <row r="78" ht="18" customHeight="1">
+    <row r="78" ht="36" customHeight="1">
       <c r="B78" s="31" t="n">
-        <v>25</v>
-      </c>
-      <c r="C78" s="19" t="inlineStr">
-        <is>
-          <t>meta</t>
-        </is>
-      </c>
-      <c r="D78" s="10" t="n"/>
+        <v>20</v>
+      </c>
+      <c r="C78" s="38" t="n"/>
+      <c r="D78" s="19" t="inlineStr">
+        <is>
+          <t>shiharai_hoho</t>
+        </is>
+      </c>
       <c r="E78" s="10" t="n"/>
       <c r="F78" s="10" t="n"/>
       <c r="G78" s="10" t="n"/>
@@ -7946,7 +8146,7 @@
       <c r="L78" s="11" t="n"/>
       <c r="M78" s="17" t="inlineStr">
         <is>
-          <t>Object</t>
+          <t>Number</t>
         </is>
       </c>
       <c r="N78" s="10" t="n"/>
@@ -7977,7 +8177,7 @@
       <c r="AE78" s="11" t="n"/>
       <c r="AF78" s="19" t="inlineStr">
         <is>
-          <t>ページネーション情報</t>
+          <t>支払方法 ※m_code.code_category='SHIHARAI_HOHO'を参照</t>
         </is>
       </c>
       <c r="AG78" s="10" t="n"/>
@@ -7986,14 +8186,14 @@
       <c r="AJ78" s="10" t="n"/>
       <c r="AK78" s="11" t="n"/>
     </row>
-    <row r="79" ht="18" customHeight="1">
+    <row r="79" ht="36" customHeight="1">
       <c r="B79" s="31" t="n">
-        <v>26</v>
-      </c>
-      <c r="C79" s="37" t="n"/>
+        <v>21</v>
+      </c>
+      <c r="C79" s="38" t="n"/>
       <c r="D79" s="19" t="inlineStr">
         <is>
-          <t>total</t>
+          <t>denshi_shonin_status</t>
         </is>
       </c>
       <c r="E79" s="10" t="n"/>
@@ -8026,7 +8226,7 @@
       <c r="X79" s="11" t="n"/>
       <c r="Y79" s="17" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>〇</t>
         </is>
       </c>
       <c r="Z79" s="10" t="n"/>
@@ -8037,7 +8237,7 @@
       <c r="AE79" s="11" t="n"/>
       <c r="AF79" s="19" t="inlineStr">
         <is>
-          <t>総件数</t>
+          <t>電子版承認ステータス（NULL=Web申込以外, 0:未承認, 1:承認済み, 2:否認）</t>
         </is>
       </c>
       <c r="AG79" s="10" t="n"/>
@@ -8048,12 +8248,12 @@
     </row>
     <row r="80" ht="18" customHeight="1">
       <c r="B80" s="31" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="C80" s="38" t="n"/>
       <c r="D80" s="19" t="inlineStr">
         <is>
-          <t>page</t>
+          <t>shoki_dokusya_kaishi_date</t>
         </is>
       </c>
       <c r="E80" s="10" t="n"/>
@@ -8066,7 +8266,7 @@
       <c r="L80" s="11" t="n"/>
       <c r="M80" s="17" t="inlineStr">
         <is>
-          <t>Number</t>
+          <t>String</t>
         </is>
       </c>
       <c r="N80" s="10" t="n"/>
@@ -8079,7 +8279,11 @@
       </c>
       <c r="R80" s="10" t="n"/>
       <c r="S80" s="11" t="n"/>
-      <c r="T80" s="17" t="inlineStr"/>
+      <c r="T80" s="17" t="inlineStr">
+        <is>
+          <t>YYYY/MM/DD</t>
+        </is>
+      </c>
       <c r="U80" s="10" t="n"/>
       <c r="V80" s="10" t="n"/>
       <c r="W80" s="10" t="n"/>
@@ -8097,7 +8301,7 @@
       <c r="AE80" s="11" t="n"/>
       <c r="AF80" s="19" t="inlineStr">
         <is>
-          <t>現在ページ番号</t>
+          <t>初回購読開始日</t>
         </is>
       </c>
       <c r="AG80" s="10" t="n"/>
@@ -8108,12 +8312,12 @@
     </row>
     <row r="81" ht="18" customHeight="1">
       <c r="B81" s="31" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C81" s="38" t="n"/>
       <c r="D81" s="19" t="inlineStr">
         <is>
-          <t>per_page</t>
+          <t>dokusya_chushi_date</t>
         </is>
       </c>
       <c r="E81" s="10" t="n"/>
@@ -8126,7 +8330,7 @@
       <c r="L81" s="11" t="n"/>
       <c r="M81" s="17" t="inlineStr">
         <is>
-          <t>Number</t>
+          <t>String</t>
         </is>
       </c>
       <c r="N81" s="10" t="n"/>
@@ -8139,14 +8343,18 @@
       </c>
       <c r="R81" s="10" t="n"/>
       <c r="S81" s="11" t="n"/>
-      <c r="T81" s="17" t="inlineStr"/>
+      <c r="T81" s="17" t="inlineStr">
+        <is>
+          <t>YYYY/MM/DD</t>
+        </is>
+      </c>
       <c r="U81" s="10" t="n"/>
       <c r="V81" s="10" t="n"/>
       <c r="W81" s="10" t="n"/>
       <c r="X81" s="11" t="n"/>
       <c r="Y81" s="17" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>〇</t>
         </is>
       </c>
       <c r="Z81" s="10" t="n"/>
@@ -8157,7 +8365,7 @@
       <c r="AE81" s="11" t="n"/>
       <c r="AF81" s="19" t="inlineStr">
         <is>
-          <t>1ページの件数</t>
+          <t>購読中止日</t>
         </is>
       </c>
       <c r="AG81" s="10" t="n"/>
@@ -8166,14 +8374,14 @@
       <c r="AJ81" s="10" t="n"/>
       <c r="AK81" s="11" t="n"/>
     </row>
-    <row r="82" ht="18" customHeight="1">
+    <row r="82" ht="36" customHeight="1">
       <c r="B82" s="31" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C82" s="39" t="n"/>
       <c r="D82" s="19" t="inlineStr">
         <is>
-          <t>total_pages</t>
+          <t>is_read_only</t>
         </is>
       </c>
       <c r="E82" s="10" t="n"/>
@@ -8186,7 +8394,7 @@
       <c r="L82" s="11" t="n"/>
       <c r="M82" s="17" t="inlineStr">
         <is>
-          <t>Number</t>
+          <t>Boolean</t>
         </is>
       </c>
       <c r="N82" s="10" t="n"/>
@@ -8217,7 +8425,7 @@
       <c r="AE82" s="11" t="n"/>
       <c r="AF82" s="19" t="inlineStr">
         <is>
-          <t>総ページ数</t>
+          <t>編集・削除不可フラグ（true=電子版クレジットカード決済者または併読者）</t>
         </is>
       </c>
       <c r="AG82" s="10" t="n"/>
@@ -8226,21 +8434,136 @@
       <c r="AJ82" s="10" t="n"/>
       <c r="AK82" s="11" t="n"/>
     </row>
-    <row r="83" ht="19.5" customHeight="1"/>
-    <row r="84" ht="19.5" customHeight="1">
-      <c r="B84" s="40" t="inlineStr">
-        <is>
-          <t>リクエスト</t>
-        </is>
-      </c>
+    <row r="83" ht="18" customHeight="1">
+      <c r="B83" s="31" t="n">
+        <v>25</v>
+      </c>
+      <c r="C83" s="19" t="inlineStr">
+        <is>
+          <t>meta</t>
+        </is>
+      </c>
+      <c r="D83" s="10" t="n"/>
+      <c r="E83" s="10" t="n"/>
+      <c r="F83" s="10" t="n"/>
+      <c r="G83" s="10" t="n"/>
+      <c r="H83" s="10" t="n"/>
+      <c r="I83" s="10" t="n"/>
+      <c r="J83" s="10" t="n"/>
+      <c r="K83" s="10" t="n"/>
+      <c r="L83" s="11" t="n"/>
+      <c r="M83" s="17" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="N83" s="10" t="n"/>
+      <c r="O83" s="10" t="n"/>
+      <c r="P83" s="11" t="n"/>
+      <c r="Q83" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R83" s="10" t="n"/>
+      <c r="S83" s="11" t="n"/>
+      <c r="T83" s="17" t="inlineStr"/>
+      <c r="U83" s="10" t="n"/>
+      <c r="V83" s="10" t="n"/>
+      <c r="W83" s="10" t="n"/>
+      <c r="X83" s="11" t="n"/>
+      <c r="Y83" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z83" s="10" t="n"/>
+      <c r="AA83" s="10" t="n"/>
+      <c r="AB83" s="10" t="n"/>
+      <c r="AC83" s="10" t="n"/>
+      <c r="AD83" s="10" t="n"/>
+      <c r="AE83" s="11" t="n"/>
+      <c r="AF83" s="19" t="inlineStr">
+        <is>
+          <t>ページネーション情報</t>
+        </is>
+      </c>
+      <c r="AG83" s="10" t="n"/>
+      <c r="AH83" s="10" t="n"/>
+      <c r="AI83" s="10" t="n"/>
+      <c r="AJ83" s="10" t="n"/>
+      <c r="AK83" s="11" t="n"/>
+    </row>
+    <row r="84" ht="18" customHeight="1">
+      <c r="B84" s="31" t="n">
+        <v>26</v>
+      </c>
+      <c r="C84" s="37" t="n"/>
+      <c r="D84" s="19" t="inlineStr">
+        <is>
+          <t>total</t>
+        </is>
+      </c>
+      <c r="E84" s="10" t="n"/>
+      <c r="F84" s="10" t="n"/>
+      <c r="G84" s="10" t="n"/>
+      <c r="H84" s="10" t="n"/>
+      <c r="I84" s="10" t="n"/>
+      <c r="J84" s="10" t="n"/>
+      <c r="K84" s="10" t="n"/>
+      <c r="L84" s="11" t="n"/>
+      <c r="M84" s="17" t="inlineStr">
+        <is>
+          <t>Number</t>
+        </is>
+      </c>
+      <c r="N84" s="10" t="n"/>
+      <c r="O84" s="10" t="n"/>
+      <c r="P84" s="11" t="n"/>
+      <c r="Q84" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R84" s="10" t="n"/>
+      <c r="S84" s="11" t="n"/>
+      <c r="T84" s="17" t="inlineStr"/>
+      <c r="U84" s="10" t="n"/>
+      <c r="V84" s="10" t="n"/>
+      <c r="W84" s="10" t="n"/>
+      <c r="X84" s="11" t="n"/>
+      <c r="Y84" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z84" s="10" t="n"/>
+      <c r="AA84" s="10" t="n"/>
+      <c r="AB84" s="10" t="n"/>
+      <c r="AC84" s="10" t="n"/>
+      <c r="AD84" s="10" t="n"/>
+      <c r="AE84" s="11" t="n"/>
+      <c r="AF84" s="19" t="inlineStr">
+        <is>
+          <t>総件数</t>
+        </is>
+      </c>
+      <c r="AG84" s="10" t="n"/>
+      <c r="AH84" s="10" t="n"/>
+      <c r="AI84" s="10" t="n"/>
+      <c r="AJ84" s="10" t="n"/>
+      <c r="AK84" s="11" t="n"/>
     </row>
     <row r="85" ht="18" customHeight="1">
-      <c r="C85" s="19" t="inlineStr">
-        <is>
-          <t>GET /api/v1/dokusya?kanri_shiten_id=10&amp;shiten_id=21&amp;dokusya_shubetsu=1&amp;shoki_dokusya_kaishi_date_from=2024/01/01&amp;shoki_dokusya_kaishi_date_to=2024/12/31&amp;page=1&amp;per_page=20&amp;sort_by=updated_at&amp;sort_order=desc</t>
-        </is>
-      </c>
-      <c r="D85" s="10" t="n"/>
+      <c r="B85" s="31" t="n">
+        <v>27</v>
+      </c>
+      <c r="C85" s="38" t="n"/>
+      <c r="D85" s="19" t="inlineStr">
+        <is>
+          <t>page</t>
+        </is>
+      </c>
       <c r="E85" s="10" t="n"/>
       <c r="F85" s="10" t="n"/>
       <c r="G85" s="10" t="n"/>
@@ -8248,42 +8571,227 @@
       <c r="I85" s="10" t="n"/>
       <c r="J85" s="10" t="n"/>
       <c r="K85" s="10" t="n"/>
-      <c r="L85" s="10" t="n"/>
-      <c r="M85" s="10" t="n"/>
+      <c r="L85" s="11" t="n"/>
+      <c r="M85" s="17" t="inlineStr">
+        <is>
+          <t>Number</t>
+        </is>
+      </c>
       <c r="N85" s="10" t="n"/>
       <c r="O85" s="10" t="n"/>
-      <c r="P85" s="10" t="n"/>
-      <c r="Q85" s="10" t="n"/>
+      <c r="P85" s="11" t="n"/>
+      <c r="Q85" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="R85" s="10" t="n"/>
-      <c r="S85" s="10" t="n"/>
-      <c r="T85" s="10" t="n"/>
+      <c r="S85" s="11" t="n"/>
+      <c r="T85" s="17" t="inlineStr"/>
       <c r="U85" s="10" t="n"/>
       <c r="V85" s="10" t="n"/>
       <c r="W85" s="10" t="n"/>
-      <c r="X85" s="10" t="n"/>
-      <c r="Y85" s="10" t="n"/>
+      <c r="X85" s="11" t="n"/>
+      <c r="Y85" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="Z85" s="10" t="n"/>
       <c r="AA85" s="10" t="n"/>
       <c r="AB85" s="10" t="n"/>
       <c r="AC85" s="10" t="n"/>
       <c r="AD85" s="10" t="n"/>
-      <c r="AE85" s="10" t="n"/>
-      <c r="AF85" s="10" t="n"/>
+      <c r="AE85" s="11" t="n"/>
+      <c r="AF85" s="19" t="inlineStr">
+        <is>
+          <t>現在ページ番号</t>
+        </is>
+      </c>
       <c r="AG85" s="10" t="n"/>
       <c r="AH85" s="10" t="n"/>
       <c r="AI85" s="10" t="n"/>
       <c r="AJ85" s="10" t="n"/>
       <c r="AK85" s="11" t="n"/>
     </row>
-    <row r="87" ht="19.5" customHeight="1">
-      <c r="B87" s="40" t="inlineStr">
+    <row r="86" ht="18" customHeight="1">
+      <c r="B86" s="31" t="n">
+        <v>28</v>
+      </c>
+      <c r="C86" s="38" t="n"/>
+      <c r="D86" s="19" t="inlineStr">
+        <is>
+          <t>per_page</t>
+        </is>
+      </c>
+      <c r="E86" s="10" t="n"/>
+      <c r="F86" s="10" t="n"/>
+      <c r="G86" s="10" t="n"/>
+      <c r="H86" s="10" t="n"/>
+      <c r="I86" s="10" t="n"/>
+      <c r="J86" s="10" t="n"/>
+      <c r="K86" s="10" t="n"/>
+      <c r="L86" s="11" t="n"/>
+      <c r="M86" s="17" t="inlineStr">
+        <is>
+          <t>Number</t>
+        </is>
+      </c>
+      <c r="N86" s="10" t="n"/>
+      <c r="O86" s="10" t="n"/>
+      <c r="P86" s="11" t="n"/>
+      <c r="Q86" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R86" s="10" t="n"/>
+      <c r="S86" s="11" t="n"/>
+      <c r="T86" s="17" t="inlineStr"/>
+      <c r="U86" s="10" t="n"/>
+      <c r="V86" s="10" t="n"/>
+      <c r="W86" s="10" t="n"/>
+      <c r="X86" s="11" t="n"/>
+      <c r="Y86" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z86" s="10" t="n"/>
+      <c r="AA86" s="10" t="n"/>
+      <c r="AB86" s="10" t="n"/>
+      <c r="AC86" s="10" t="n"/>
+      <c r="AD86" s="10" t="n"/>
+      <c r="AE86" s="11" t="n"/>
+      <c r="AF86" s="19" t="inlineStr">
+        <is>
+          <t>1ページの件数</t>
+        </is>
+      </c>
+      <c r="AG86" s="10" t="n"/>
+      <c r="AH86" s="10" t="n"/>
+      <c r="AI86" s="10" t="n"/>
+      <c r="AJ86" s="10" t="n"/>
+      <c r="AK86" s="11" t="n"/>
+    </row>
+    <row r="87" ht="18" customHeight="1">
+      <c r="B87" s="31" t="n">
+        <v>29</v>
+      </c>
+      <c r="C87" s="39" t="n"/>
+      <c r="D87" s="19" t="inlineStr">
+        <is>
+          <t>total_pages</t>
+        </is>
+      </c>
+      <c r="E87" s="10" t="n"/>
+      <c r="F87" s="10" t="n"/>
+      <c r="G87" s="10" t="n"/>
+      <c r="H87" s="10" t="n"/>
+      <c r="I87" s="10" t="n"/>
+      <c r="J87" s="10" t="n"/>
+      <c r="K87" s="10" t="n"/>
+      <c r="L87" s="11" t="n"/>
+      <c r="M87" s="17" t="inlineStr">
+        <is>
+          <t>Number</t>
+        </is>
+      </c>
+      <c r="N87" s="10" t="n"/>
+      <c r="O87" s="10" t="n"/>
+      <c r="P87" s="11" t="n"/>
+      <c r="Q87" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R87" s="10" t="n"/>
+      <c r="S87" s="11" t="n"/>
+      <c r="T87" s="17" t="inlineStr"/>
+      <c r="U87" s="10" t="n"/>
+      <c r="V87" s="10" t="n"/>
+      <c r="W87" s="10" t="n"/>
+      <c r="X87" s="11" t="n"/>
+      <c r="Y87" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z87" s="10" t="n"/>
+      <c r="AA87" s="10" t="n"/>
+      <c r="AB87" s="10" t="n"/>
+      <c r="AC87" s="10" t="n"/>
+      <c r="AD87" s="10" t="n"/>
+      <c r="AE87" s="11" t="n"/>
+      <c r="AF87" s="19" t="inlineStr">
+        <is>
+          <t>総ページ数</t>
+        </is>
+      </c>
+      <c r="AG87" s="10" t="n"/>
+      <c r="AH87" s="10" t="n"/>
+      <c r="AI87" s="10" t="n"/>
+      <c r="AJ87" s="10" t="n"/>
+      <c r="AK87" s="11" t="n"/>
+    </row>
+    <row r="88" ht="19.5" customHeight="1"/>
+    <row r="89" ht="19.5" customHeight="1">
+      <c r="B89" s="40" t="inlineStr">
+        <is>
+          <t>リクエスト</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="18" customHeight="1">
+      <c r="C90" s="19" t="inlineStr">
+        <is>
+          <t>GET /api/v1/dokusya?kanri_shiten_id=10&amp;shiten_id=21&amp;dokusya_shubetsu=1&amp;shoki_dokusya_kaishi_date_from=2024/01/01&amp;shoki_dokusya_kaishi_date_to=2024/12/31&amp;page=1&amp;per_page=20&amp;sort_by=updated_at&amp;sort_order=desc</t>
+        </is>
+      </c>
+      <c r="D90" s="10" t="n"/>
+      <c r="E90" s="10" t="n"/>
+      <c r="F90" s="10" t="n"/>
+      <c r="G90" s="10" t="n"/>
+      <c r="H90" s="10" t="n"/>
+      <c r="I90" s="10" t="n"/>
+      <c r="J90" s="10" t="n"/>
+      <c r="K90" s="10" t="n"/>
+      <c r="L90" s="10" t="n"/>
+      <c r="M90" s="10" t="n"/>
+      <c r="N90" s="10" t="n"/>
+      <c r="O90" s="10" t="n"/>
+      <c r="P90" s="10" t="n"/>
+      <c r="Q90" s="10" t="n"/>
+      <c r="R90" s="10" t="n"/>
+      <c r="S90" s="10" t="n"/>
+      <c r="T90" s="10" t="n"/>
+      <c r="U90" s="10" t="n"/>
+      <c r="V90" s="10" t="n"/>
+      <c r="W90" s="10" t="n"/>
+      <c r="X90" s="10" t="n"/>
+      <c r="Y90" s="10" t="n"/>
+      <c r="Z90" s="10" t="n"/>
+      <c r="AA90" s="10" t="n"/>
+      <c r="AB90" s="10" t="n"/>
+      <c r="AC90" s="10" t="n"/>
+      <c r="AD90" s="10" t="n"/>
+      <c r="AE90" s="10" t="n"/>
+      <c r="AF90" s="10" t="n"/>
+      <c r="AG90" s="10" t="n"/>
+      <c r="AH90" s="10" t="n"/>
+      <c r="AI90" s="10" t="n"/>
+      <c r="AJ90" s="10" t="n"/>
+      <c r="AK90" s="11" t="n"/>
+    </row>
+    <row r="92" ht="19.5" customHeight="1">
+      <c r="B92" s="40" t="inlineStr">
         <is>
           <t>レスポンス（成功）</t>
         </is>
       </c>
     </row>
-    <row r="88" ht="409" customHeight="1">
-      <c r="C88" s="19" t="inlineStr">
+    <row r="93" ht="409" customHeight="1">
+      <c r="C93" s="19" t="inlineStr">
         <is>
           <t>{
   "data": [
@@ -8304,6 +8812,7 @@
       "haitatsu_yubin_no": "1500001",
       "haitatsu": "東京都渋谷区神宮前1-1-1 渋谷マンション101",
       "hanbaiten_id": 501,
+      "hanbaiten_code": "HB501",
       "hanbaiten_name": "渋谷販売店",
       "dokusya_shubetsu": 1,
       "shiharai_hoho": 1,
@@ -8329,6 +8838,7 @@
       "haitatsu_yubin_no": "1500002",
       "haitatsu": "東京都渋谷区神宮前2-2-2",
       "hanbaiten_id": 502,
+      "hanbaiten_code": "HB502",
       "hanbaiten_name": "原宿販売店",
       "dokusya_shubetsu": 2,
       "shiharai_hoho": 6,
@@ -8347,50 +8857,50 @@
 }</t>
         </is>
       </c>
-      <c r="D88" s="10" t="n"/>
-      <c r="E88" s="10" t="n"/>
-      <c r="F88" s="10" t="n"/>
-      <c r="G88" s="10" t="n"/>
-      <c r="H88" s="10" t="n"/>
-      <c r="I88" s="10" t="n"/>
-      <c r="J88" s="10" t="n"/>
-      <c r="K88" s="10" t="n"/>
-      <c r="L88" s="10" t="n"/>
-      <c r="M88" s="10" t="n"/>
-      <c r="N88" s="10" t="n"/>
-      <c r="O88" s="10" t="n"/>
-      <c r="P88" s="10" t="n"/>
-      <c r="Q88" s="10" t="n"/>
-      <c r="R88" s="10" t="n"/>
-      <c r="S88" s="10" t="n"/>
-      <c r="T88" s="10" t="n"/>
-      <c r="U88" s="10" t="n"/>
-      <c r="V88" s="10" t="n"/>
-      <c r="W88" s="10" t="n"/>
-      <c r="X88" s="10" t="n"/>
-      <c r="Y88" s="10" t="n"/>
-      <c r="Z88" s="10" t="n"/>
-      <c r="AA88" s="10" t="n"/>
-      <c r="AB88" s="10" t="n"/>
-      <c r="AC88" s="10" t="n"/>
-      <c r="AD88" s="10" t="n"/>
-      <c r="AE88" s="10" t="n"/>
-      <c r="AF88" s="10" t="n"/>
-      <c r="AG88" s="10" t="n"/>
-      <c r="AH88" s="10" t="n"/>
-      <c r="AI88" s="10" t="n"/>
-      <c r="AJ88" s="10" t="n"/>
-      <c r="AK88" s="11" t="n"/>
-    </row>
-    <row r="90" ht="19.5" customHeight="1">
-      <c r="B90" s="40" t="inlineStr">
+      <c r="D93" s="10" t="n"/>
+      <c r="E93" s="10" t="n"/>
+      <c r="F93" s="10" t="n"/>
+      <c r="G93" s="10" t="n"/>
+      <c r="H93" s="10" t="n"/>
+      <c r="I93" s="10" t="n"/>
+      <c r="J93" s="10" t="n"/>
+      <c r="K93" s="10" t="n"/>
+      <c r="L93" s="10" t="n"/>
+      <c r="M93" s="10" t="n"/>
+      <c r="N93" s="10" t="n"/>
+      <c r="O93" s="10" t="n"/>
+      <c r="P93" s="10" t="n"/>
+      <c r="Q93" s="10" t="n"/>
+      <c r="R93" s="10" t="n"/>
+      <c r="S93" s="10" t="n"/>
+      <c r="T93" s="10" t="n"/>
+      <c r="U93" s="10" t="n"/>
+      <c r="V93" s="10" t="n"/>
+      <c r="W93" s="10" t="n"/>
+      <c r="X93" s="10" t="n"/>
+      <c r="Y93" s="10" t="n"/>
+      <c r="Z93" s="10" t="n"/>
+      <c r="AA93" s="10" t="n"/>
+      <c r="AB93" s="10" t="n"/>
+      <c r="AC93" s="10" t="n"/>
+      <c r="AD93" s="10" t="n"/>
+      <c r="AE93" s="10" t="n"/>
+      <c r="AF93" s="10" t="n"/>
+      <c r="AG93" s="10" t="n"/>
+      <c r="AH93" s="10" t="n"/>
+      <c r="AI93" s="10" t="n"/>
+      <c r="AJ93" s="10" t="n"/>
+      <c r="AK93" s="11" t="n"/>
+    </row>
+    <row r="95" ht="19.5" customHeight="1">
+      <c r="B95" s="40" t="inlineStr">
         <is>
           <t>レスポンス（失敗 400 Validation Error（メール形式エラー））</t>
         </is>
       </c>
     </row>
-    <row r="91" ht="126" customHeight="1">
-      <c r="C91" s="19" t="inlineStr">
+    <row r="96" ht="126" customHeight="1">
+      <c r="C96" s="19" t="inlineStr">
         <is>
           <t>{
   "error_code": "VALIDATION_ERROR",
@@ -8401,50 +8911,50 @@
 }</t>
         </is>
       </c>
-      <c r="D91" s="10" t="n"/>
-      <c r="E91" s="10" t="n"/>
-      <c r="F91" s="10" t="n"/>
-      <c r="G91" s="10" t="n"/>
-      <c r="H91" s="10" t="n"/>
-      <c r="I91" s="10" t="n"/>
-      <c r="J91" s="10" t="n"/>
-      <c r="K91" s="10" t="n"/>
-      <c r="L91" s="10" t="n"/>
-      <c r="M91" s="10" t="n"/>
-      <c r="N91" s="10" t="n"/>
-      <c r="O91" s="10" t="n"/>
-      <c r="P91" s="10" t="n"/>
-      <c r="Q91" s="10" t="n"/>
-      <c r="R91" s="10" t="n"/>
-      <c r="S91" s="10" t="n"/>
-      <c r="T91" s="10" t="n"/>
-      <c r="U91" s="10" t="n"/>
-      <c r="V91" s="10" t="n"/>
-      <c r="W91" s="10" t="n"/>
-      <c r="X91" s="10" t="n"/>
-      <c r="Y91" s="10" t="n"/>
-      <c r="Z91" s="10" t="n"/>
-      <c r="AA91" s="10" t="n"/>
-      <c r="AB91" s="10" t="n"/>
-      <c r="AC91" s="10" t="n"/>
-      <c r="AD91" s="10" t="n"/>
-      <c r="AE91" s="10" t="n"/>
-      <c r="AF91" s="10" t="n"/>
-      <c r="AG91" s="10" t="n"/>
-      <c r="AH91" s="10" t="n"/>
-      <c r="AI91" s="10" t="n"/>
-      <c r="AJ91" s="10" t="n"/>
-      <c r="AK91" s="11" t="n"/>
-    </row>
-    <row r="93" ht="19.5" customHeight="1">
-      <c r="B93" s="40" t="inlineStr">
+      <c r="D96" s="10" t="n"/>
+      <c r="E96" s="10" t="n"/>
+      <c r="F96" s="10" t="n"/>
+      <c r="G96" s="10" t="n"/>
+      <c r="H96" s="10" t="n"/>
+      <c r="I96" s="10" t="n"/>
+      <c r="J96" s="10" t="n"/>
+      <c r="K96" s="10" t="n"/>
+      <c r="L96" s="10" t="n"/>
+      <c r="M96" s="10" t="n"/>
+      <c r="N96" s="10" t="n"/>
+      <c r="O96" s="10" t="n"/>
+      <c r="P96" s="10" t="n"/>
+      <c r="Q96" s="10" t="n"/>
+      <c r="R96" s="10" t="n"/>
+      <c r="S96" s="10" t="n"/>
+      <c r="T96" s="10" t="n"/>
+      <c r="U96" s="10" t="n"/>
+      <c r="V96" s="10" t="n"/>
+      <c r="W96" s="10" t="n"/>
+      <c r="X96" s="10" t="n"/>
+      <c r="Y96" s="10" t="n"/>
+      <c r="Z96" s="10" t="n"/>
+      <c r="AA96" s="10" t="n"/>
+      <c r="AB96" s="10" t="n"/>
+      <c r="AC96" s="10" t="n"/>
+      <c r="AD96" s="10" t="n"/>
+      <c r="AE96" s="10" t="n"/>
+      <c r="AF96" s="10" t="n"/>
+      <c r="AG96" s="10" t="n"/>
+      <c r="AH96" s="10" t="n"/>
+      <c r="AI96" s="10" t="n"/>
+      <c r="AJ96" s="10" t="n"/>
+      <c r="AK96" s="11" t="n"/>
+    </row>
+    <row r="98" ht="19.5" customHeight="1">
+      <c r="B98" s="40" t="inlineStr">
         <is>
           <t>レスポンス（失敗 401 Unauthorized）</t>
         </is>
       </c>
     </row>
-    <row r="94" ht="72" customHeight="1">
-      <c r="C94" s="19" t="inlineStr">
+    <row r="99" ht="72" customHeight="1">
+      <c r="C99" s="19" t="inlineStr">
         <is>
           <t>{
   "error_code": "UNAUTHORIZED",
@@ -8452,50 +8962,50 @@
 }</t>
         </is>
       </c>
-      <c r="D94" s="10" t="n"/>
-      <c r="E94" s="10" t="n"/>
-      <c r="F94" s="10" t="n"/>
-      <c r="G94" s="10" t="n"/>
-      <c r="H94" s="10" t="n"/>
-      <c r="I94" s="10" t="n"/>
-      <c r="J94" s="10" t="n"/>
-      <c r="K94" s="10" t="n"/>
-      <c r="L94" s="10" t="n"/>
-      <c r="M94" s="10" t="n"/>
-      <c r="N94" s="10" t="n"/>
-      <c r="O94" s="10" t="n"/>
-      <c r="P94" s="10" t="n"/>
-      <c r="Q94" s="10" t="n"/>
-      <c r="R94" s="10" t="n"/>
-      <c r="S94" s="10" t="n"/>
-      <c r="T94" s="10" t="n"/>
-      <c r="U94" s="10" t="n"/>
-      <c r="V94" s="10" t="n"/>
-      <c r="W94" s="10" t="n"/>
-      <c r="X94" s="10" t="n"/>
-      <c r="Y94" s="10" t="n"/>
-      <c r="Z94" s="10" t="n"/>
-      <c r="AA94" s="10" t="n"/>
-      <c r="AB94" s="10" t="n"/>
-      <c r="AC94" s="10" t="n"/>
-      <c r="AD94" s="10" t="n"/>
-      <c r="AE94" s="10" t="n"/>
-      <c r="AF94" s="10" t="n"/>
-      <c r="AG94" s="10" t="n"/>
-      <c r="AH94" s="10" t="n"/>
-      <c r="AI94" s="10" t="n"/>
-      <c r="AJ94" s="10" t="n"/>
-      <c r="AK94" s="11" t="n"/>
-    </row>
-    <row r="96" ht="19.5" customHeight="1">
-      <c r="B96" s="40" t="inlineStr">
+      <c r="D99" s="10" t="n"/>
+      <c r="E99" s="10" t="n"/>
+      <c r="F99" s="10" t="n"/>
+      <c r="G99" s="10" t="n"/>
+      <c r="H99" s="10" t="n"/>
+      <c r="I99" s="10" t="n"/>
+      <c r="J99" s="10" t="n"/>
+      <c r="K99" s="10" t="n"/>
+      <c r="L99" s="10" t="n"/>
+      <c r="M99" s="10" t="n"/>
+      <c r="N99" s="10" t="n"/>
+      <c r="O99" s="10" t="n"/>
+      <c r="P99" s="10" t="n"/>
+      <c r="Q99" s="10" t="n"/>
+      <c r="R99" s="10" t="n"/>
+      <c r="S99" s="10" t="n"/>
+      <c r="T99" s="10" t="n"/>
+      <c r="U99" s="10" t="n"/>
+      <c r="V99" s="10" t="n"/>
+      <c r="W99" s="10" t="n"/>
+      <c r="X99" s="10" t="n"/>
+      <c r="Y99" s="10" t="n"/>
+      <c r="Z99" s="10" t="n"/>
+      <c r="AA99" s="10" t="n"/>
+      <c r="AB99" s="10" t="n"/>
+      <c r="AC99" s="10" t="n"/>
+      <c r="AD99" s="10" t="n"/>
+      <c r="AE99" s="10" t="n"/>
+      <c r="AF99" s="10" t="n"/>
+      <c r="AG99" s="10" t="n"/>
+      <c r="AH99" s="10" t="n"/>
+      <c r="AI99" s="10" t="n"/>
+      <c r="AJ99" s="10" t="n"/>
+      <c r="AK99" s="11" t="n"/>
+    </row>
+    <row r="101" ht="19.5" customHeight="1">
+      <c r="B101" s="40" t="inlineStr">
         <is>
           <t>レスポンス（失敗 403 Forbidden）</t>
         </is>
       </c>
     </row>
-    <row r="97" ht="72" customHeight="1">
-      <c r="C97" s="19" t="inlineStr">
+    <row r="102" ht="72" customHeight="1">
+      <c r="C102" s="19" t="inlineStr">
         <is>
           <t>{
   "error_code": "FORBIDDEN",
@@ -8503,50 +9013,50 @@
 }</t>
         </is>
       </c>
-      <c r="D97" s="10" t="n"/>
-      <c r="E97" s="10" t="n"/>
-      <c r="F97" s="10" t="n"/>
-      <c r="G97" s="10" t="n"/>
-      <c r="H97" s="10" t="n"/>
-      <c r="I97" s="10" t="n"/>
-      <c r="J97" s="10" t="n"/>
-      <c r="K97" s="10" t="n"/>
-      <c r="L97" s="10" t="n"/>
-      <c r="M97" s="10" t="n"/>
-      <c r="N97" s="10" t="n"/>
-      <c r="O97" s="10" t="n"/>
-      <c r="P97" s="10" t="n"/>
-      <c r="Q97" s="10" t="n"/>
-      <c r="R97" s="10" t="n"/>
-      <c r="S97" s="10" t="n"/>
-      <c r="T97" s="10" t="n"/>
-      <c r="U97" s="10" t="n"/>
-      <c r="V97" s="10" t="n"/>
-      <c r="W97" s="10" t="n"/>
-      <c r="X97" s="10" t="n"/>
-      <c r="Y97" s="10" t="n"/>
-      <c r="Z97" s="10" t="n"/>
-      <c r="AA97" s="10" t="n"/>
-      <c r="AB97" s="10" t="n"/>
-      <c r="AC97" s="10" t="n"/>
-      <c r="AD97" s="10" t="n"/>
-      <c r="AE97" s="10" t="n"/>
-      <c r="AF97" s="10" t="n"/>
-      <c r="AG97" s="10" t="n"/>
-      <c r="AH97" s="10" t="n"/>
-      <c r="AI97" s="10" t="n"/>
-      <c r="AJ97" s="10" t="n"/>
-      <c r="AK97" s="11" t="n"/>
-    </row>
-    <row r="99" ht="19.5" customHeight="1">
-      <c r="B99" s="40" t="inlineStr">
+      <c r="D102" s="10" t="n"/>
+      <c r="E102" s="10" t="n"/>
+      <c r="F102" s="10" t="n"/>
+      <c r="G102" s="10" t="n"/>
+      <c r="H102" s="10" t="n"/>
+      <c r="I102" s="10" t="n"/>
+      <c r="J102" s="10" t="n"/>
+      <c r="K102" s="10" t="n"/>
+      <c r="L102" s="10" t="n"/>
+      <c r="M102" s="10" t="n"/>
+      <c r="N102" s="10" t="n"/>
+      <c r="O102" s="10" t="n"/>
+      <c r="P102" s="10" t="n"/>
+      <c r="Q102" s="10" t="n"/>
+      <c r="R102" s="10" t="n"/>
+      <c r="S102" s="10" t="n"/>
+      <c r="T102" s="10" t="n"/>
+      <c r="U102" s="10" t="n"/>
+      <c r="V102" s="10" t="n"/>
+      <c r="W102" s="10" t="n"/>
+      <c r="X102" s="10" t="n"/>
+      <c r="Y102" s="10" t="n"/>
+      <c r="Z102" s="10" t="n"/>
+      <c r="AA102" s="10" t="n"/>
+      <c r="AB102" s="10" t="n"/>
+      <c r="AC102" s="10" t="n"/>
+      <c r="AD102" s="10" t="n"/>
+      <c r="AE102" s="10" t="n"/>
+      <c r="AF102" s="10" t="n"/>
+      <c r="AG102" s="10" t="n"/>
+      <c r="AH102" s="10" t="n"/>
+      <c r="AI102" s="10" t="n"/>
+      <c r="AJ102" s="10" t="n"/>
+      <c r="AK102" s="11" t="n"/>
+    </row>
+    <row r="104" ht="19.5" customHeight="1">
+      <c r="B104" s="40" t="inlineStr">
         <is>
           <t>レスポンス（失敗 500 Internal Server Error）</t>
         </is>
       </c>
     </row>
-    <row r="100" ht="72" customHeight="1">
-      <c r="C100" s="19" t="inlineStr">
+    <row r="105" ht="72" customHeight="1">
+      <c r="C105" s="19" t="inlineStr">
         <is>
           <t>{
   "error_code": "INTERNAL_SERVER_ERROR",
@@ -8554,450 +9064,478 @@
 }</t>
         </is>
       </c>
-      <c r="D100" s="10" t="n"/>
-      <c r="E100" s="10" t="n"/>
-      <c r="F100" s="10" t="n"/>
-      <c r="G100" s="10" t="n"/>
-      <c r="H100" s="10" t="n"/>
-      <c r="I100" s="10" t="n"/>
-      <c r="J100" s="10" t="n"/>
-      <c r="K100" s="10" t="n"/>
-      <c r="L100" s="10" t="n"/>
-      <c r="M100" s="10" t="n"/>
-      <c r="N100" s="10" t="n"/>
-      <c r="O100" s="10" t="n"/>
-      <c r="P100" s="10" t="n"/>
-      <c r="Q100" s="10" t="n"/>
-      <c r="R100" s="10" t="n"/>
-      <c r="S100" s="10" t="n"/>
-      <c r="T100" s="10" t="n"/>
-      <c r="U100" s="10" t="n"/>
-      <c r="V100" s="10" t="n"/>
-      <c r="W100" s="10" t="n"/>
-      <c r="X100" s="10" t="n"/>
-      <c r="Y100" s="10" t="n"/>
-      <c r="Z100" s="10" t="n"/>
-      <c r="AA100" s="10" t="n"/>
-      <c r="AB100" s="10" t="n"/>
-      <c r="AC100" s="10" t="n"/>
-      <c r="AD100" s="10" t="n"/>
-      <c r="AE100" s="10" t="n"/>
-      <c r="AF100" s="10" t="n"/>
-      <c r="AG100" s="10" t="n"/>
-      <c r="AH100" s="10" t="n"/>
-      <c r="AI100" s="10" t="n"/>
-      <c r="AJ100" s="10" t="n"/>
-      <c r="AK100" s="11" t="n"/>
-    </row>
-    <row r="102" ht="19.5" customHeight="1"/>
-    <row r="103" ht="19.5" customHeight="1">
-      <c r="A103" s="27" t="inlineStr">
+      <c r="D105" s="10" t="n"/>
+      <c r="E105" s="10" t="n"/>
+      <c r="F105" s="10" t="n"/>
+      <c r="G105" s="10" t="n"/>
+      <c r="H105" s="10" t="n"/>
+      <c r="I105" s="10" t="n"/>
+      <c r="J105" s="10" t="n"/>
+      <c r="K105" s="10" t="n"/>
+      <c r="L105" s="10" t="n"/>
+      <c r="M105" s="10" t="n"/>
+      <c r="N105" s="10" t="n"/>
+      <c r="O105" s="10" t="n"/>
+      <c r="P105" s="10" t="n"/>
+      <c r="Q105" s="10" t="n"/>
+      <c r="R105" s="10" t="n"/>
+      <c r="S105" s="10" t="n"/>
+      <c r="T105" s="10" t="n"/>
+      <c r="U105" s="10" t="n"/>
+      <c r="V105" s="10" t="n"/>
+      <c r="W105" s="10" t="n"/>
+      <c r="X105" s="10" t="n"/>
+      <c r="Y105" s="10" t="n"/>
+      <c r="Z105" s="10" t="n"/>
+      <c r="AA105" s="10" t="n"/>
+      <c r="AB105" s="10" t="n"/>
+      <c r="AC105" s="10" t="n"/>
+      <c r="AD105" s="10" t="n"/>
+      <c r="AE105" s="10" t="n"/>
+      <c r="AF105" s="10" t="n"/>
+      <c r="AG105" s="10" t="n"/>
+      <c r="AH105" s="10" t="n"/>
+      <c r="AI105" s="10" t="n"/>
+      <c r="AJ105" s="10" t="n"/>
+      <c r="AK105" s="11" t="n"/>
+    </row>
+    <row r="107" ht="19.5" customHeight="1"/>
+    <row r="108" ht="19.5" customHeight="1">
+      <c r="A108" s="27" t="inlineStr">
         <is>
           <t>4. 処理手順</t>
         </is>
       </c>
     </row>
-    <row r="104" ht="18" customHeight="1">
-      <c r="B104" s="27" t="inlineStr">
+    <row r="109" ht="18" customHeight="1">
+      <c r="B109" s="27" t="inlineStr">
         <is>
           <t>4.1 リクエストのバリデーション</t>
         </is>
       </c>
     </row>
-    <row r="105" ht="18" customHeight="1">
-      <c r="C105" s="41" t="inlineStr">
+    <row r="110" ht="18" customHeight="1">
+      <c r="C110" s="41" t="inlineStr">
         <is>
           <t>クエリパラメータの検証：</t>
-        </is>
-      </c>
-    </row>
-    <row r="106" ht="18" customHeight="1">
-      <c r="D106" s="41" t="inlineStr">
-        <is>
-          <t>kanri_shiten_id / shiten_id / hanbaiten_id：数値型チェック</t>
-        </is>
-      </c>
-    </row>
-    <row r="107" ht="18" customHeight="1">
-      <c r="D107" s="41" t="inlineStr">
-        <is>
-          <t>kumiaiin_code：最大20文字</t>
-        </is>
-      </c>
-    </row>
-    <row r="108" ht="36" customHeight="1">
-      <c r="D108" s="41" t="inlineStr">
-        <is>
-          <t>jastem_toriatsukai_tenpo_code：最大3文字（物理カラム `bank_branch_code` に対する部分一致）</t>
-        </is>
-      </c>
-    </row>
-    <row r="109" ht="36" customHeight="1">
-      <c r="D109" s="41" t="inlineStr">
-        <is>
-          <t>jastem_tenpo_name：最大100文字（物理カラム `bank_branch_name` に対する部分一致）</t>
-        </is>
-      </c>
-    </row>
-    <row r="110" ht="18" customHeight="1">
-      <c r="D110" s="41" t="inlineStr">
-        <is>
-          <t>full_name / full_name_kana：最大100文字</t>
         </is>
       </c>
     </row>
     <row r="111" ht="18" customHeight="1">
       <c r="D111" s="41" t="inlineStr">
         <is>
-          <t>haitatsu：最大200文字</t>
+          <t>kanri_shiten_id / shiten_id / hanbaiten_id：数値型チェック</t>
         </is>
       </c>
     </row>
     <row r="112" ht="18" customHeight="1">
       <c r="D112" s="41" t="inlineStr">
         <is>
-          <t>renrakusaki_1：最大15文字</t>
+          <t>kumiaiin_code：最大20文字</t>
         </is>
       </c>
     </row>
     <row r="113" ht="36" customHeight="1">
       <c r="D113" s="41" t="inlineStr">
         <is>
-          <t>email：最大100文字、メール形式チェック（不正の場合、`VALIDATION_ERROR` + `errors[]` に `正しいメール形式を入力してください。` を含める）</t>
+          <t>bank_branch：最大100文字（物理カラム `bank_branch_code` / `bank_branch_name` に対する OR 部分一致）</t>
         </is>
       </c>
     </row>
     <row r="114" ht="18" customHeight="1">
       <c r="D114" s="41" t="inlineStr">
         <is>
-          <t>seikyu_kaishi_month：最大6文字</t>
-        </is>
-      </c>
-    </row>
-    <row r="115" ht="36" customHeight="1">
+          <t>full_name / full_name_kana：最大100文字</t>
+        </is>
+      </c>
+    </row>
+    <row r="115" ht="18" customHeight="1">
       <c r="D115" s="41" t="inlineStr">
         <is>
-          <t>shoki_dokusya_kaishi_date_from / shoki_dokusya_kaishi_date_to：有効な日付形式（YYYY/MM/DD）、両方指定時 `from ≦ to`</t>
-        </is>
-      </c>
-    </row>
-    <row r="116" ht="36" customHeight="1">
+          <t>haitatsu：最大200文字</t>
+        </is>
+      </c>
+    </row>
+    <row r="116" ht="18" customHeight="1">
       <c r="D116" s="41" t="inlineStr">
         <is>
-          <t>dokusya_chushi_date_from / dokusya_chushi_date_to：有効な日付形式（YYYY/MM/DD）、両方指定時 `from ≦ to`</t>
+          <t>renrakusaki：最大15文字</t>
         </is>
       </c>
     </row>
     <row r="117" ht="36" customHeight="1">
       <c r="D117" s="41" t="inlineStr">
         <is>
-          <t>joho_henko_tekiyo_date_from / joho_henko_tekiyo_date_to：有効な日付形式（YYYY/MM/DD）、両方指定時 `from ≦ to`</t>
+          <t>email：最大100文字、メール形式チェック（不正の場合、`VALIDATION_ERROR` + `errors[]` に `正しいメール形式を入力してください。` を含める）</t>
         </is>
       </c>
     </row>
     <row r="118" ht="18" customHeight="1">
       <c r="D118" s="41" t="inlineStr">
         <is>
-          <t>dokusya_shubetsu：1〜3 または未指定</t>
+          <t>yubin_kubun：m_code YUBIN_KUBUN（0:空 / 1:郵送）の値（完全一致）</t>
         </is>
       </c>
     </row>
     <row r="119" ht="18" customHeight="1">
       <c r="D119" s="41" t="inlineStr">
         <is>
-          <t>shiharai_hoho：1〜6, 9 または未指定</t>
+          <t>tanka_id：整数（完全一致）</t>
         </is>
       </c>
     </row>
     <row r="120" ht="18" customHeight="1">
       <c r="D120" s="41" t="inlineStr">
         <is>
-          <t>tetsuzuki_shurui：0 または 1 または未指定</t>
-        </is>
-      </c>
-    </row>
-    <row r="121" ht="18" customHeight="1">
+          <t>biko：最大500文字（部分一致）</t>
+        </is>
+      </c>
+    </row>
+    <row r="121" ht="36" customHeight="1">
       <c r="D121" s="41" t="inlineStr">
         <is>
-          <t>denshi_shonin_status：0〜2 または未指定</t>
-        </is>
-      </c>
-    </row>
-    <row r="122" ht="18" customHeight="1">
+          <t>seikyu_kaishi_month_from / seikyu_kaishi_month_to：YYYYMM形式（半角数字6桁）、両方指定時 `from ≦ to`</t>
+        </is>
+      </c>
+    </row>
+    <row r="122" ht="36" customHeight="1">
       <c r="D122" s="41" t="inlineStr">
         <is>
-          <t>page：1以上</t>
-        </is>
-      </c>
-    </row>
-    <row r="123" ht="18" customHeight="1">
+          <t>shoki_dokusya_kaishi_date_from / shoki_dokusya_kaishi_date_to：有効な日付形式（YYYY/MM/DD）、両方指定時 `from ≦ to`</t>
+        </is>
+      </c>
+    </row>
+    <row r="123" ht="36" customHeight="1">
       <c r="D123" s="41" t="inlineStr">
         <is>
-          <t>per_page：1〜100</t>
-        </is>
-      </c>
-    </row>
-    <row r="124" ht="54" customHeight="1">
+          <t>dokusya_chushi_date_from / dokusya_chushi_date_to：有効な日付形式（YYYY/MM/DD）、両方指定時 `from ≦ to`</t>
+        </is>
+      </c>
+    </row>
+    <row r="124" ht="36" customHeight="1">
       <c r="D124" s="41" t="inlineStr">
         <is>
-          <t>sort_by：許可カラム一覧に含まれるか確認（kanri_shiten_id, shiten_id, kumiaiin_code, hanbaiten_id, shoki_dokusya_kaishi_date, dokusya_chushi_date, updated_at）</t>
+          <t>joho_henko_tekiyo_date_from / joho_henko_tekiyo_date_to：有効な日付形式（YYYY/MM/DD）、両方指定時 `from ≦ to`</t>
         </is>
       </c>
     </row>
     <row r="125" ht="18" customHeight="1">
       <c r="D125" s="41" t="inlineStr">
         <is>
+          <t>dokusya_shubetsu：1〜3 または未指定</t>
+        </is>
+      </c>
+    </row>
+    <row r="126" ht="18" customHeight="1">
+      <c r="D126" s="41" t="inlineStr">
+        <is>
+          <t>shiharai_hoho：1〜6, 9 または未指定</t>
+        </is>
+      </c>
+    </row>
+    <row r="127" ht="18" customHeight="1">
+      <c r="D127" s="41" t="inlineStr">
+        <is>
+          <t>tetsuzuki_shurui：0 または 1 または未指定</t>
+        </is>
+      </c>
+    </row>
+    <row r="128" ht="18" customHeight="1">
+      <c r="D128" s="41" t="inlineStr">
+        <is>
+          <t>denshi_shonin_status：0〜2 または未指定</t>
+        </is>
+      </c>
+    </row>
+    <row r="129" ht="18" customHeight="1">
+      <c r="D129" s="41" t="inlineStr">
+        <is>
+          <t>page：1以上</t>
+        </is>
+      </c>
+    </row>
+    <row r="130" ht="18" customHeight="1">
+      <c r="D130" s="41" t="inlineStr">
+        <is>
+          <t>per_page：1〜100</t>
+        </is>
+      </c>
+    </row>
+    <row r="131" ht="72" customHeight="1">
+      <c r="D131" s="41" t="inlineStr">
+        <is>
+          <t>sort_by：許可カラム一覧に含まれるか確認（kanri_shiten_id, shiten_id, kumiaiin_code, hanbaiten_id, hanbaiten_code, shoki_dokusya_kaishi_date, dokusya_chushi_date, updated_at）</t>
+        </is>
+      </c>
+    </row>
+    <row r="132" ht="18" customHeight="1">
+      <c r="D132" s="41" t="inlineStr">
+        <is>
           <t>sort_order：`asc` または `desc`</t>
         </is>
       </c>
     </row>
-    <row r="126" ht="36" customHeight="1">
-      <c r="C126" s="41" t="inlineStr">
+    <row r="133" ht="36" customHeight="1">
+      <c r="C133" s="41" t="inlineStr">
         <is>
           <t>デフォルト値を設定する（page=1, per_page=20, sort_by=updated_at, sort_order=desc）</t>
         </is>
       </c>
     </row>
-    <row r="127" ht="36" customHeight="1">
-      <c r="C127" s="41" t="inlineStr">
+    <row r="134" ht="36" customHeight="1">
+      <c r="C134" s="41" t="inlineStr">
         <is>
           <t>不正なパラメータの場合：HTTP 400 (`BAD_REQUEST`) または HTTP 400 (`VALIDATION_ERROR`)</t>
         </is>
       </c>
     </row>
-    <row r="128" ht="18" customHeight="1">
-      <c r="B128" s="27" t="inlineStr">
+    <row r="135" ht="18" customHeight="1">
+      <c r="B135" s="27" t="inlineStr">
         <is>
           <t>4.2 認証・認可チェック</t>
         </is>
       </c>
     </row>
-    <row r="129" ht="18" customHeight="1">
-      <c r="C129" s="41" t="inlineStr">
+    <row r="136" ht="18" customHeight="1">
+      <c r="C136" s="41" t="inlineStr">
         <is>
           <t>認証情報を検証する（HTTP-only Cookieセッション）。</t>
         </is>
       </c>
     </row>
-    <row r="130" ht="18" customHeight="1">
-      <c r="C130" s="41" t="inlineStr">
+    <row r="137" ht="18" customHeight="1">
+      <c r="C137" s="41" t="inlineStr">
         <is>
           <t>未認証の場合：HTTP 401 (`UNAUTHORIZED`)</t>
         </is>
       </c>
     </row>
-    <row r="131" ht="18" customHeight="1">
-      <c r="C131" s="41" t="inlineStr">
+    <row r="138" ht="18" customHeight="1">
+      <c r="C138" s="41" t="inlineStr">
         <is>
           <t>必要権限: `dokusya.view`</t>
         </is>
       </c>
     </row>
-    <row r="132" ht="18" customHeight="1">
-      <c r="C132" s="41" t="inlineStr">
+    <row r="139" ht="18" customHeight="1">
+      <c r="C139" s="41" t="inlineStr">
         <is>
           <t>該当権限保持ロール: CHUOKAI / JA_HONTEN / JA_KANRI_SHITEN</t>
         </is>
       </c>
     </row>
-    <row r="133" ht="18" customHeight="1">
-      <c r="C133" s="41" t="inlineStr">
+    <row r="140" ht="18" customHeight="1">
+      <c r="C140" s="41" t="inlineStr">
         <is>
           <t>権限不足の場合：HTTP 403 (`FORBIDDEN`)</t>
-        </is>
-      </c>
-    </row>
-    <row r="134" ht="18" customHeight="1">
-      <c r="C134" s="41" t="inlineStr">
-        <is>
-          <t>DataScope:</t>
-        </is>
-      </c>
-    </row>
-    <row r="135" ht="54" customHeight="1">
-      <c r="D135" s="41" t="inlineStr">
-        <is>
-          <t>`CHUOKAI`：自中央会管轄JAの購読者のみ参照可能（`d.ja_id IN (SELECT ja_id FROM m_ja WHERE chuokai_id = :user_chuokai_id)`）</t>
-        </is>
-      </c>
-    </row>
-    <row r="136" ht="18" customHeight="1">
-      <c r="D136" s="41" t="inlineStr">
-        <is>
-          <t>`JA_HONTEN`：自JAの購読者のみ参照可能（`d.ja_id = :user_ja_id`）</t>
-        </is>
-      </c>
-    </row>
-    <row r="137" ht="54" customHeight="1">
-      <c r="D137" s="41" t="inlineStr">
-        <is>
-          <t>`JA_KANRI_SHITEN`：自管理支店の購読者のみ参照可能（`d.ja_id = :user_ja_id AND d.kanri_shiten_id = :user_kanri_shiten_id`）</t>
-        </is>
-      </c>
-    </row>
-    <row r="138" ht="36" customHeight="1">
-      <c r="C138" s="41" t="inlineStr">
-        <is>
-          <t>DataScope違反（他JA・他管理支店のレコードへのアクセス）の場合：HTTP 403 (`DATA_SCOPE_VIOLATION`)</t>
-        </is>
-      </c>
-    </row>
-    <row r="139" ht="18" customHeight="1">
-      <c r="B139" s="27" t="inlineStr">
-        <is>
-          <t>4.3 データ取得条件の設定</t>
-        </is>
-      </c>
-    </row>
-    <row r="140" ht="36" customHeight="1">
-      <c r="C140" s="41" t="inlineStr">
-        <is>
-          <t>ログインユーザーのスコープ（role_code, ja_id, kanri_shiten_id, chuokai_id）を取得する。</t>
         </is>
       </c>
     </row>
     <row r="141" ht="18" customHeight="1">
       <c r="C141" s="41" t="inlineStr">
         <is>
+          <t>DataScope:</t>
+        </is>
+      </c>
+    </row>
+    <row r="142" ht="54" customHeight="1">
+      <c r="D142" s="41" t="inlineStr">
+        <is>
+          <t>`CHUOKAI`：自中央会管轄JAの購読者のみ参照可能（`d.ja_id IN (SELECT ja_id FROM m_ja WHERE chuokai_id = :user_chuokai_id)`）</t>
+        </is>
+      </c>
+    </row>
+    <row r="143" ht="18" customHeight="1">
+      <c r="D143" s="41" t="inlineStr">
+        <is>
+          <t>`JA_HONTEN`：自JAの購読者のみ参照可能（`d.ja_id = :user_ja_id`）</t>
+        </is>
+      </c>
+    </row>
+    <row r="144" ht="54" customHeight="1">
+      <c r="D144" s="41" t="inlineStr">
+        <is>
+          <t>`JA_KANRI_SHITEN`：自管理支店の購読者のみ参照可能（`d.ja_id = :user_ja_id AND d.kanri_shiten_id = :user_kanri_shiten_id`）</t>
+        </is>
+      </c>
+    </row>
+    <row r="145" ht="36" customHeight="1">
+      <c r="C145" s="41" t="inlineStr">
+        <is>
+          <t>DataScope違反（他JA・他管理支店のレコードへのアクセス）の場合：HTTP 403 (`DATA_SCOPE_VIOLATION`)</t>
+        </is>
+      </c>
+    </row>
+    <row r="146" ht="18" customHeight="1">
+      <c r="B146" s="27" t="inlineStr">
+        <is>
+          <t>4.3 データ取得条件の設定</t>
+        </is>
+      </c>
+    </row>
+    <row r="147" ht="36" customHeight="1">
+      <c r="C147" s="41" t="inlineStr">
+        <is>
+          <t>ログインユーザーのスコープ（role_code, ja_id, kanri_shiten_id, chuokai_id）を取得する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="148" ht="18" customHeight="1">
+      <c r="C148" s="41" t="inlineStr">
+        <is>
           <t>DataScope を role_code により適用する（4.2 参照）。</t>
         </is>
       </c>
     </row>
-    <row r="142" ht="18" customHeight="1">
-      <c r="C142" s="41" t="inlineStr">
+    <row r="149" ht="18" customHeight="1">
+      <c r="C149" s="41" t="inlineStr">
         <is>
           <t>検索条件を追加する：</t>
         </is>
       </c>
     </row>
-    <row r="143" ht="36" customHeight="1">
-      <c r="D143" s="41" t="inlineStr">
+    <row r="150" ht="36" customHeight="1">
+      <c r="D150" s="41" t="inlineStr">
         <is>
           <t>kanri_shiten_id 指定時：`d.kanri_shiten_id = :kanri_shiten_id`</t>
         </is>
       </c>
     </row>
-    <row r="144" ht="18" customHeight="1">
-      <c r="D144" s="41" t="inlineStr">
+    <row r="151" ht="18" customHeight="1">
+      <c r="D151" s="41" t="inlineStr">
         <is>
           <t>shiten_id 指定時：`d.shiten_id = :shiten_id`</t>
         </is>
       </c>
     </row>
-    <row r="145" ht="36" customHeight="1">
-      <c r="D145" s="41" t="inlineStr">
+    <row r="152" ht="36" customHeight="1">
+      <c r="D152" s="41" t="inlineStr">
         <is>
           <t>kumiaiin_code 指定時：`d.kumiaiin_code ILIKE '%' || :kumiaiin_code || '%'`</t>
         </is>
       </c>
     </row>
-    <row r="146" ht="54" customHeight="1">
-      <c r="D146" s="41" t="inlineStr">
-        <is>
-          <t>jastem_toriatsukai_tenpo_code 指定時：`d.bank_branch_code ILIKE '%' || :jastem_toriatsukai_tenpo_code || '%'` ※物理カラムは `bank_branch_code`（レガシー名）</t>
-        </is>
-      </c>
-    </row>
-    <row r="147" ht="54" customHeight="1">
-      <c r="D147" s="41" t="inlineStr">
-        <is>
-          <t>jastem_tenpo_name 指定時：`d.bank_branch_name ILIKE '%' || :jastem_tenpo_name || '%'` ※物理カラムは `bank_branch_name`（レガシー名）</t>
-        </is>
-      </c>
-    </row>
-    <row r="148" ht="90" customHeight="1">
-      <c r="D148" s="41" t="inlineStr">
+    <row r="153" ht="72" customHeight="1">
+      <c r="D153" s="41" t="inlineStr">
+        <is>
+          <t>bank_branch 指定時：`(d.bank_branch_code ILIKE '%' || :bank_branch || '%' OR d.bank_branch_name ILIKE '%' || :bank_branch || '%')` ※物理カラムは `bank_branch_code` / `bank_branch_name`（レガシー名）</t>
+        </is>
+      </c>
+    </row>
+    <row r="154" ht="90" customHeight="1">
+      <c r="D154" s="41" t="inlineStr">
         <is>
           <t>full_name 指定時：`(d.shimei_sei ILIKE '%' || :full_name || '%' OR d.shimei_mei ILIKE '%' || :full_name || '%' OR d.haitatsu_shimei_sei ILIKE '%' || :full_name || '%' OR d.haitatsu_shimei_mei ILIKE '%' || :full_name || '%')`（購読者氏名＋配達先氏名の各カラムに OR 部分一致）</t>
         </is>
       </c>
     </row>
-    <row r="149" ht="90" customHeight="1">
-      <c r="D149" s="41" t="inlineStr">
+    <row r="155" ht="90" customHeight="1">
+      <c r="D155" s="41" t="inlineStr">
         <is>
           <t>full_name_kana 指定時：`(d.shimei_kana_sei ILIKE '%' || :full_name_kana || '%' OR d.shimei_kana_mei ILIKE ... OR d.haitatsu_shimei_kana_sei ILIKE ... OR d.haitatsu_shimei_kana_mei ILIKE ...)`（購読者かな氏名＋配達先かな氏名の各カラムに OR 部分一致）</t>
         </is>
       </c>
     </row>
-    <row r="150" ht="72" customHeight="1">
-      <c r="D150" s="41" t="inlineStr">
-        <is>
-          <t>renrakusaki_1 指定時：`(d.renrakusaki_1 ILIKE '%' || :renrakusaki_1 || '%' OR d.haitatsu_renrakusaki_1 ILIKE '%' || :renrakusaki_1 || '%')`（連絡先１＋配達先連絡先１に OR 部分一致）</t>
-        </is>
-      </c>
-    </row>
-    <row r="151" ht="90" customHeight="1">
-      <c r="D151" s="41" t="inlineStr">
+    <row r="156" ht="108" customHeight="1">
+      <c r="D156" s="41" t="inlineStr">
+        <is>
+          <t>renrakusaki 指定時：`(d.renrakusaki_1 ILIKE '%' || :renrakusaki || '%' OR d.haitatsu_renrakusaki_1 ILIKE '%' || :renrakusaki || '%' OR d.renrakusaki_2 ILIKE '%' || :renrakusaki || '%' OR d.haitatsu_renrakusaki_2 ILIKE '%' || :renrakusaki || '%')`（購読者連絡先1/2＋配達先連絡先1/2に OR 部分一致）</t>
+        </is>
+      </c>
+    </row>
+    <row r="157" ht="90" customHeight="1">
+      <c r="D157" s="41" t="inlineStr">
         <is>
           <t>haitatsu 指定時：配達先住所4項目（`haitatsu_todofuken_code` / `haitatsu_shikuchoson` / `haitatsu_chome_banchi` / `haitatsu_tatemono_mei`）＋購読者住所4項目（`todofuken_code` / `shikuchoson` / `chome_banchi` / `tatemono_mei`）の各カラムに OR 部分一致</t>
         </is>
       </c>
     </row>
-    <row r="152" ht="18" customHeight="1">
-      <c r="D152" s="41" t="inlineStr">
+    <row r="158" ht="18" customHeight="1">
+      <c r="D158" s="41" t="inlineStr">
         <is>
           <t>hanbaiten_id 指定時：`d.hanbaiten_id = :hanbaiten_id`</t>
         </is>
       </c>
     </row>
-    <row r="153" ht="18" customHeight="1">
-      <c r="D153" s="41" t="inlineStr">
+    <row r="159" ht="18" customHeight="1">
+      <c r="D159" s="41" t="inlineStr">
         <is>
           <t>email 指定時：部分一致</t>
         </is>
       </c>
     </row>
-    <row r="154" ht="18" customHeight="1">
-      <c r="D154" s="41" t="inlineStr">
-        <is>
-          <t>seikyu_kaishi_month 指定時：部分一致</t>
-        </is>
-      </c>
-    </row>
-    <row r="155" ht="36" customHeight="1">
-      <c r="D155" s="41" t="inlineStr">
+    <row r="160" ht="36" customHeight="1">
+      <c r="D160" s="41" t="inlineStr">
+        <is>
+          <t>yubin_kubun 指定時：`d.yubin_kubun = :yubin_kubun`（完全一致）</t>
+        </is>
+      </c>
+    </row>
+    <row r="161" ht="18" customHeight="1">
+      <c r="D161" s="41" t="inlineStr">
+        <is>
+          <t>tanka_id 指定時：`d.tanka_id = :tanka_id`（完全一致）</t>
+        </is>
+      </c>
+    </row>
+    <row r="162" ht="18" customHeight="1">
+      <c r="D162" s="41" t="inlineStr">
+        <is>
+          <t>biko 指定時：`d.biko ILIKE '%' || :biko || '%'`（部分一致）</t>
+        </is>
+      </c>
+    </row>
+    <row r="163" ht="72" customHeight="1">
+      <c r="D163" s="41" t="inlineStr">
+        <is>
+          <t>seikyu_kaishi_month_from / seikyu_kaishi_month_to 指定時：YYYYMM の範囲検索（未設定＝空文字の購読者は除外）。from 指定時 `d.seikyu_kaishi_month &gt;= :seikyu_from`、to 指定時 `d.seikyu_kaishi_month &lt;= :seikyu_to`（6桁固定のため辞書順比較が数値順と一致）</t>
+        </is>
+      </c>
+    </row>
+    <row r="164" ht="36" customHeight="1">
+      <c r="D164" s="41" t="inlineStr">
         <is>
           <t>shoki_dokusya_kaishi_date_from 指定時：`d.shoki_dokusya_kaishi_date &gt;= :shoki_dokusya_kaishi_date_from`</t>
         </is>
       </c>
     </row>
-    <row r="156" ht="36" customHeight="1">
-      <c r="D156" s="41" t="inlineStr">
+    <row r="165" ht="36" customHeight="1">
+      <c r="D165" s="41" t="inlineStr">
         <is>
           <t>shoki_dokusya_kaishi_date_to 指定時：`d.shoki_dokusya_kaishi_date &lt;= :shoki_dokusya_kaishi_date_to`</t>
         </is>
       </c>
     </row>
-    <row r="157" ht="36" customHeight="1">
-      <c r="D157" s="41" t="inlineStr">
+    <row r="166" ht="36" customHeight="1">
+      <c r="D166" s="41" t="inlineStr">
         <is>
           <t>dokusya_chushi_date_from 指定時：`d.dokusya_chushi_date &gt;= :dokusya_chushi_date_from`</t>
         </is>
       </c>
     </row>
-    <row r="158" ht="36" customHeight="1">
-      <c r="D158" s="41" t="inlineStr">
+    <row r="167" ht="36" customHeight="1">
+      <c r="D167" s="41" t="inlineStr">
         <is>
           <t>dokusya_chushi_date_to 指定時：`d.dokusya_chushi_date &lt;= :dokusya_chushi_date_to`</t>
         </is>
       </c>
     </row>
-    <row r="159" ht="36" customHeight="1">
-      <c r="D159" s="41" t="inlineStr">
+    <row r="168" ht="36" customHeight="1">
+      <c r="D168" s="41" t="inlineStr">
         <is>
           <t>dokusya_shubetsu / shiharai_hoho / tetsuzuki_shurui / denshi_shonin_status 指定時：それぞれ等価条件</t>
         </is>
       </c>
     </row>
-    <row r="160" ht="90" customHeight="1">
-      <c r="D160" s="41" t="inlineStr">
+    <row r="169" ht="90" customHeight="1">
+      <c r="D169" s="41" t="inlineStr">
         <is>
           <t>active_tanka_flg 指定時：`true`=参照購読料単価が有効(active_flg=TRUE)の購読者のみ、`false`=失効(active_flg=FALSE)の購読者のみ抽出（省略時は絞り込まない）。`tanka_id` は m_tanka の PK のため INNER JOIN で行数は増えない（0/1件）。JOIN 条件の active_flg はパラメータ（`:activeTankaFlg`）でバインドする。</t>
         </is>
       </c>
     </row>
-    <row r="161" ht="90" customHeight="1">
-      <c r="C161" s="42" t="inlineStr">
+    <row r="170" ht="90" customHeight="1">
+      <c r="C170" s="42" t="inlineStr">
         <is>
           <t xml:space="preserve">    INNER JOIN m_tanka mti
       ON mti.tanka_id = d.tanka_id
@@ -9006,71 +9544,71 @@
      AND mti.active_flg = FALSE</t>
         </is>
       </c>
-      <c r="D161" s="10" t="n"/>
-      <c r="E161" s="10" t="n"/>
-      <c r="F161" s="10" t="n"/>
-      <c r="G161" s="10" t="n"/>
-      <c r="H161" s="10" t="n"/>
-      <c r="I161" s="10" t="n"/>
-      <c r="J161" s="10" t="n"/>
-      <c r="K161" s="10" t="n"/>
-      <c r="L161" s="10" t="n"/>
-      <c r="M161" s="10" t="n"/>
-      <c r="N161" s="10" t="n"/>
-      <c r="O161" s="10" t="n"/>
-      <c r="P161" s="10" t="n"/>
-      <c r="Q161" s="10" t="n"/>
-      <c r="R161" s="10" t="n"/>
-      <c r="S161" s="10" t="n"/>
-      <c r="T161" s="10" t="n"/>
-      <c r="U161" s="10" t="n"/>
-      <c r="V161" s="10" t="n"/>
-      <c r="W161" s="10" t="n"/>
-      <c r="X161" s="10" t="n"/>
-      <c r="Y161" s="10" t="n"/>
-      <c r="Z161" s="10" t="n"/>
-      <c r="AA161" s="10" t="n"/>
-      <c r="AB161" s="10" t="n"/>
-      <c r="AC161" s="10" t="n"/>
-      <c r="AD161" s="10" t="n"/>
-      <c r="AE161" s="10" t="n"/>
-      <c r="AF161" s="10" t="n"/>
-      <c r="AG161" s="10" t="n"/>
-      <c r="AH161" s="10" t="n"/>
-      <c r="AI161" s="10" t="n"/>
-      <c r="AJ161" s="10" t="n"/>
-      <c r="AK161" s="11" t="n"/>
-    </row>
-    <row r="162" ht="36" customHeight="1">
-      <c r="C162" s="41" t="inlineStr">
+      <c r="D170" s="10" t="n"/>
+      <c r="E170" s="10" t="n"/>
+      <c r="F170" s="10" t="n"/>
+      <c r="G170" s="10" t="n"/>
+      <c r="H170" s="10" t="n"/>
+      <c r="I170" s="10" t="n"/>
+      <c r="J170" s="10" t="n"/>
+      <c r="K170" s="10" t="n"/>
+      <c r="L170" s="10" t="n"/>
+      <c r="M170" s="10" t="n"/>
+      <c r="N170" s="10" t="n"/>
+      <c r="O170" s="10" t="n"/>
+      <c r="P170" s="10" t="n"/>
+      <c r="Q170" s="10" t="n"/>
+      <c r="R170" s="10" t="n"/>
+      <c r="S170" s="10" t="n"/>
+      <c r="T170" s="10" t="n"/>
+      <c r="U170" s="10" t="n"/>
+      <c r="V170" s="10" t="n"/>
+      <c r="W170" s="10" t="n"/>
+      <c r="X170" s="10" t="n"/>
+      <c r="Y170" s="10" t="n"/>
+      <c r="Z170" s="10" t="n"/>
+      <c r="AA170" s="10" t="n"/>
+      <c r="AB170" s="10" t="n"/>
+      <c r="AC170" s="10" t="n"/>
+      <c r="AD170" s="10" t="n"/>
+      <c r="AE170" s="10" t="n"/>
+      <c r="AF170" s="10" t="n"/>
+      <c r="AG170" s="10" t="n"/>
+      <c r="AH170" s="10" t="n"/>
+      <c r="AI170" s="10" t="n"/>
+      <c r="AJ170" s="10" t="n"/>
+      <c r="AK170" s="11" t="n"/>
+    </row>
+    <row r="171" ht="36" customHeight="1">
+      <c r="C171" s="41" t="inlineStr">
         <is>
           <t>適用日（joho_henko_tekiyo_date_from / joho_henko_tekiyo_date_to）の処理：</t>
         </is>
       </c>
     </row>
-    <row r="163" ht="36" customHeight="1">
-      <c r="D163" s="41" t="inlineStr">
+    <row r="172" ht="36" customHeight="1">
+      <c r="D172" s="41" t="inlineStr">
         <is>
           <t>両方空欄の場合：購読者履歴の最新データフラグ（saishin_data_flg=TRUE）のレコードを抽出</t>
         </is>
       </c>
     </row>
-    <row r="164" ht="54" customHeight="1">
-      <c r="D164" s="41" t="inlineStr">
+    <row r="173" ht="54" customHeight="1">
+      <c r="D173" s="41" t="inlineStr">
         <is>
           <t>いずれか入力されている場合：購読者履歴テーブル（`t_dokusya_rireki`）の変更適用日が `[from, to]` の範囲内のレコードを抽出（from のみ指定 → `&gt;= from`、to のみ指定 → `&lt;= to`、両方 → 範囲内）</t>
         </is>
       </c>
     </row>
-    <row r="165" ht="18" customHeight="1">
-      <c r="B165" s="27" t="inlineStr">
+    <row r="174" ht="18" customHeight="1">
+      <c r="B174" s="27" t="inlineStr">
         <is>
           <t>4.4 データ件数の取得</t>
         </is>
       </c>
     </row>
-    <row r="166" ht="342" customHeight="1">
-      <c r="C166" s="42" t="inlineStr">
+    <row r="175" ht="342" customHeight="1">
+      <c r="C175" s="42" t="inlineStr">
         <is>
           <t>SELECT COUNT(*)
 FROM t_dokusya d
@@ -9093,50 +9631,50 @@
   /* ... 他の検索条件は省略 */</t>
         </is>
       </c>
-      <c r="D166" s="10" t="n"/>
-      <c r="E166" s="10" t="n"/>
-      <c r="F166" s="10" t="n"/>
-      <c r="G166" s="10" t="n"/>
-      <c r="H166" s="10" t="n"/>
-      <c r="I166" s="10" t="n"/>
-      <c r="J166" s="10" t="n"/>
-      <c r="K166" s="10" t="n"/>
-      <c r="L166" s="10" t="n"/>
-      <c r="M166" s="10" t="n"/>
-      <c r="N166" s="10" t="n"/>
-      <c r="O166" s="10" t="n"/>
-      <c r="P166" s="10" t="n"/>
-      <c r="Q166" s="10" t="n"/>
-      <c r="R166" s="10" t="n"/>
-      <c r="S166" s="10" t="n"/>
-      <c r="T166" s="10" t="n"/>
-      <c r="U166" s="10" t="n"/>
-      <c r="V166" s="10" t="n"/>
-      <c r="W166" s="10" t="n"/>
-      <c r="X166" s="10" t="n"/>
-      <c r="Y166" s="10" t="n"/>
-      <c r="Z166" s="10" t="n"/>
-      <c r="AA166" s="10" t="n"/>
-      <c r="AB166" s="10" t="n"/>
-      <c r="AC166" s="10" t="n"/>
-      <c r="AD166" s="10" t="n"/>
-      <c r="AE166" s="10" t="n"/>
-      <c r="AF166" s="10" t="n"/>
-      <c r="AG166" s="10" t="n"/>
-      <c r="AH166" s="10" t="n"/>
-      <c r="AI166" s="10" t="n"/>
-      <c r="AJ166" s="10" t="n"/>
-      <c r="AK166" s="11" t="n"/>
-    </row>
-    <row r="167" ht="18" customHeight="1">
-      <c r="B167" s="27" t="inlineStr">
+      <c r="D175" s="10" t="n"/>
+      <c r="E175" s="10" t="n"/>
+      <c r="F175" s="10" t="n"/>
+      <c r="G175" s="10" t="n"/>
+      <c r="H175" s="10" t="n"/>
+      <c r="I175" s="10" t="n"/>
+      <c r="J175" s="10" t="n"/>
+      <c r="K175" s="10" t="n"/>
+      <c r="L175" s="10" t="n"/>
+      <c r="M175" s="10" t="n"/>
+      <c r="N175" s="10" t="n"/>
+      <c r="O175" s="10" t="n"/>
+      <c r="P175" s="10" t="n"/>
+      <c r="Q175" s="10" t="n"/>
+      <c r="R175" s="10" t="n"/>
+      <c r="S175" s="10" t="n"/>
+      <c r="T175" s="10" t="n"/>
+      <c r="U175" s="10" t="n"/>
+      <c r="V175" s="10" t="n"/>
+      <c r="W175" s="10" t="n"/>
+      <c r="X175" s="10" t="n"/>
+      <c r="Y175" s="10" t="n"/>
+      <c r="Z175" s="10" t="n"/>
+      <c r="AA175" s="10" t="n"/>
+      <c r="AB175" s="10" t="n"/>
+      <c r="AC175" s="10" t="n"/>
+      <c r="AD175" s="10" t="n"/>
+      <c r="AE175" s="10" t="n"/>
+      <c r="AF175" s="10" t="n"/>
+      <c r="AG175" s="10" t="n"/>
+      <c r="AH175" s="10" t="n"/>
+      <c r="AI175" s="10" t="n"/>
+      <c r="AJ175" s="10" t="n"/>
+      <c r="AK175" s="11" t="n"/>
+    </row>
+    <row r="176" ht="18" customHeight="1">
+      <c r="B176" s="27" t="inlineStr">
         <is>
           <t>4.5 データ取得</t>
         </is>
       </c>
     </row>
-    <row r="168" ht="409" customHeight="1">
-      <c r="C168" s="42" t="inlineStr">
+    <row r="177" ht="409" customHeight="1">
+      <c r="C177" s="42" t="inlineStr">
         <is>
           <t>SELECT d.dokusya_id, d.ja_id,
        d.kanri_shiten_id, ks.kanri_shiten_name,
@@ -9149,7 +9687,7 @@
        (d.haitatsu_shimei_sei || ' ' || d.haitatsu_shimei_mei) AS haitatsu_full_name,
        d.haitatsu_yubin_no,
        (COALESCE(t.todofuken_name, '') || d.haitatsu_shikuchoson || d.haitatsu_chome_banchi || d.haitatsu_tatemono_mei) AS haitatsu,
-       d.hanbaiten_id, h.hanbaiten_name,
+       d.hanbaiten_id, h.hanbaiten_code, h.hanbaiten_name,
        d.dokusya_shubetsu, d.shiharai_hoho, d.denshi_shonin_status,
        d.shoki_dokusya_kaishi_date, d.dokusya_chushi_date,
        /* is_read_only: 電子版クレジットカード決済者（dokusya_shubetsu=2 AND shiharai_hoho=6）または併読者（dokusya_shubetsu=3） */
@@ -9168,92 +9706,92 @@
 LIMIT :per_page OFFSET (:page - 1) * :per_page</t>
         </is>
       </c>
-      <c r="D168" s="10" t="n"/>
-      <c r="E168" s="10" t="n"/>
-      <c r="F168" s="10" t="n"/>
-      <c r="G168" s="10" t="n"/>
-      <c r="H168" s="10" t="n"/>
-      <c r="I168" s="10" t="n"/>
-      <c r="J168" s="10" t="n"/>
-      <c r="K168" s="10" t="n"/>
-      <c r="L168" s="10" t="n"/>
-      <c r="M168" s="10" t="n"/>
-      <c r="N168" s="10" t="n"/>
-      <c r="O168" s="10" t="n"/>
-      <c r="P168" s="10" t="n"/>
-      <c r="Q168" s="10" t="n"/>
-      <c r="R168" s="10" t="n"/>
-      <c r="S168" s="10" t="n"/>
-      <c r="T168" s="10" t="n"/>
-      <c r="U168" s="10" t="n"/>
-      <c r="V168" s="10" t="n"/>
-      <c r="W168" s="10" t="n"/>
-      <c r="X168" s="10" t="n"/>
-      <c r="Y168" s="10" t="n"/>
-      <c r="Z168" s="10" t="n"/>
-      <c r="AA168" s="10" t="n"/>
-      <c r="AB168" s="10" t="n"/>
-      <c r="AC168" s="10" t="n"/>
-      <c r="AD168" s="10" t="n"/>
-      <c r="AE168" s="10" t="n"/>
-      <c r="AF168" s="10" t="n"/>
-      <c r="AG168" s="10" t="n"/>
-      <c r="AH168" s="10" t="n"/>
-      <c r="AI168" s="10" t="n"/>
-      <c r="AJ168" s="10" t="n"/>
-      <c r="AK168" s="11" t="n"/>
-    </row>
-    <row r="169" ht="72" customHeight="1">
-      <c r="C169" s="41" t="inlineStr">
+      <c r="D177" s="10" t="n"/>
+      <c r="E177" s="10" t="n"/>
+      <c r="F177" s="10" t="n"/>
+      <c r="G177" s="10" t="n"/>
+      <c r="H177" s="10" t="n"/>
+      <c r="I177" s="10" t="n"/>
+      <c r="J177" s="10" t="n"/>
+      <c r="K177" s="10" t="n"/>
+      <c r="L177" s="10" t="n"/>
+      <c r="M177" s="10" t="n"/>
+      <c r="N177" s="10" t="n"/>
+      <c r="O177" s="10" t="n"/>
+      <c r="P177" s="10" t="n"/>
+      <c r="Q177" s="10" t="n"/>
+      <c r="R177" s="10" t="n"/>
+      <c r="S177" s="10" t="n"/>
+      <c r="T177" s="10" t="n"/>
+      <c r="U177" s="10" t="n"/>
+      <c r="V177" s="10" t="n"/>
+      <c r="W177" s="10" t="n"/>
+      <c r="X177" s="10" t="n"/>
+      <c r="Y177" s="10" t="n"/>
+      <c r="Z177" s="10" t="n"/>
+      <c r="AA177" s="10" t="n"/>
+      <c r="AB177" s="10" t="n"/>
+      <c r="AC177" s="10" t="n"/>
+      <c r="AD177" s="10" t="n"/>
+      <c r="AE177" s="10" t="n"/>
+      <c r="AF177" s="10" t="n"/>
+      <c r="AG177" s="10" t="n"/>
+      <c r="AH177" s="10" t="n"/>
+      <c r="AI177" s="10" t="n"/>
+      <c r="AJ177" s="10" t="n"/>
+      <c r="AK177" s="11" t="n"/>
+    </row>
+    <row r="178" ht="72" customHeight="1">
+      <c r="C178" s="41" t="inlineStr">
         <is>
           <t>適用日（joho_henko_tekiyo_date_from / joho_henko_tekiyo_date_to）が入力されている場合は、`t_dokusya_rireki` から該当範囲内の履歴レコードを取得する（履歴テーブルへの JOIN または CTE で実装）。両方空欄の場合は `saishin_data_flg = TRUE` のレコードを使用する。</t>
         </is>
       </c>
     </row>
-    <row r="170" ht="18" customHeight="1">
-      <c r="B170" s="27" t="inlineStr">
+    <row r="179" ht="18" customHeight="1">
+      <c r="B179" s="27" t="inlineStr">
         <is>
           <t>4.6 レスポンス生成</t>
         </is>
       </c>
     </row>
-    <row r="171" ht="18" customHeight="1">
-      <c r="C171" s="41" t="inlineStr">
+    <row r="180" ht="18" customHeight="1">
+      <c r="C180" s="41" t="inlineStr">
         <is>
           <t>取得結果を data 配列として返却する。</t>
         </is>
       </c>
     </row>
-    <row r="172" ht="36" customHeight="1">
-      <c r="C172" s="41" t="inlineStr">
+    <row r="181" ht="36" customHeight="1">
+      <c r="C181" s="41" t="inlineStr">
         <is>
           <t>`meta` オブジェクトにページネーション情報（total / page / per_page / total_pages）を含める。</t>
         </is>
       </c>
     </row>
-    <row r="173" ht="36" customHeight="1">
-      <c r="C173" s="41" t="inlineStr">
+    <row r="182" ht="36" customHeight="1">
+      <c r="C182" s="41" t="inlineStr">
         <is>
           <t>`is_read_only` フラグは BE 側で算出し、FE 側で「編集」「削除」ボタンの活性制御に使用する。HTTP 200。</t>
         </is>
       </c>
     </row>
-    <row r="174" ht="18" customHeight="1">
-      <c r="B174" s="27" t="inlineStr">
+    <row r="183" ht="18" customHeight="1">
+      <c r="B183" s="27" t="inlineStr">
         <is>
           <t>4.7 例外処理</t>
         </is>
       </c>
     </row>
-    <row r="175" ht="18" customHeight="1">
-      <c r="C175" s="41" t="inlineStr">
+    <row r="184" ht="18" customHeight="1">
+      <c r="C184" s="41" t="inlineStr">
         <is>
           <t>DB接続エラー等の場合：HTTP 500 (`INTERNAL_SERVER_ERROR`)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="505">
+  <mergeCells count="542">
     <mergeCell ref="Y46:AB46"/>
     <mergeCell ref="AF65:AK65"/>
     <mergeCell ref="T24:X24"/>
@@ -9261,30 +9799,23 @@
     <mergeCell ref="Y48:AB48"/>
     <mergeCell ref="Q78:S78"/>
     <mergeCell ref="M72:P72"/>
-    <mergeCell ref="T53:X53"/>
     <mergeCell ref="Y41:AB41"/>
     <mergeCell ref="Q80:S80"/>
     <mergeCell ref="D62:L62"/>
     <mergeCell ref="T68:X68"/>
-    <mergeCell ref="D56:L56"/>
-    <mergeCell ref="T55:X55"/>
     <mergeCell ref="M59:P59"/>
     <mergeCell ref="Y43:AB43"/>
     <mergeCell ref="B8:I8"/>
-    <mergeCell ref="C100:AK100"/>
     <mergeCell ref="J1:P1"/>
     <mergeCell ref="AH2:AK3"/>
     <mergeCell ref="D64:L64"/>
-    <mergeCell ref="C94:AK94"/>
     <mergeCell ref="M82:P82"/>
-    <mergeCell ref="C142:AK142"/>
     <mergeCell ref="B10:I10"/>
+    <mergeCell ref="AF84:AK84"/>
     <mergeCell ref="AF22:AK22"/>
-    <mergeCell ref="C129:AK129"/>
     <mergeCell ref="Q25:S25"/>
-    <mergeCell ref="M54:P54"/>
     <mergeCell ref="D155:AK155"/>
-    <mergeCell ref="D149:AK149"/>
+    <mergeCell ref="AF86:AK86"/>
     <mergeCell ref="Q77:S77"/>
     <mergeCell ref="D124:AK124"/>
     <mergeCell ref="C22:L22"/>
@@ -9293,9 +9824,9 @@
     <mergeCell ref="D151:AK151"/>
     <mergeCell ref="T37:X37"/>
     <mergeCell ref="Y25:AB25"/>
-    <mergeCell ref="B165:AK165"/>
+    <mergeCell ref="D126:AK126"/>
+    <mergeCell ref="M85:P85"/>
     <mergeCell ref="Y36:AB36"/>
-    <mergeCell ref="C131:AK131"/>
     <mergeCell ref="AC39:AE39"/>
     <mergeCell ref="T38:X38"/>
     <mergeCell ref="D75:L75"/>
@@ -9305,36 +9836,38 @@
     <mergeCell ref="Q22:S22"/>
     <mergeCell ref="Q46:S46"/>
     <mergeCell ref="Y66:AE66"/>
-    <mergeCell ref="C88:AK88"/>
-    <mergeCell ref="Y53:AE53"/>
-    <mergeCell ref="C126:AK126"/>
+    <mergeCell ref="D129:AK129"/>
     <mergeCell ref="AF41:AK41"/>
     <mergeCell ref="Q61:S61"/>
+    <mergeCell ref="Q86:S86"/>
     <mergeCell ref="AF35:AK35"/>
     <mergeCell ref="C33:L33"/>
     <mergeCell ref="Q48:S48"/>
     <mergeCell ref="B14:I18"/>
     <mergeCell ref="Y68:AE68"/>
     <mergeCell ref="T74:X74"/>
-    <mergeCell ref="Y55:AE55"/>
     <mergeCell ref="AF81:AK81"/>
-    <mergeCell ref="B87:I87"/>
     <mergeCell ref="T40:X40"/>
     <mergeCell ref="C35:L35"/>
     <mergeCell ref="T76:X76"/>
+    <mergeCell ref="Y51:AB51"/>
     <mergeCell ref="T69:X69"/>
     <mergeCell ref="D65:L65"/>
     <mergeCell ref="M27:P27"/>
     <mergeCell ref="AF25:AK25"/>
     <mergeCell ref="Q35:S35"/>
+    <mergeCell ref="C145:AK145"/>
     <mergeCell ref="T45:X45"/>
     <mergeCell ref="A5:AK5"/>
     <mergeCell ref="Y33:AB33"/>
     <mergeCell ref="AF30:AK30"/>
     <mergeCell ref="Q34:S34"/>
     <mergeCell ref="C28:L28"/>
+    <mergeCell ref="D165:AK165"/>
     <mergeCell ref="AC25:AE25"/>
     <mergeCell ref="D152:AK152"/>
+    <mergeCell ref="T87:X87"/>
+    <mergeCell ref="B179:AK179"/>
     <mergeCell ref="B11:I11"/>
     <mergeCell ref="Q49:S49"/>
     <mergeCell ref="Q36:S36"/>
@@ -9345,11 +9878,12 @@
     <mergeCell ref="AF31:AK31"/>
     <mergeCell ref="B174:AK174"/>
     <mergeCell ref="C134:AK134"/>
+    <mergeCell ref="T51:X51"/>
     <mergeCell ref="T26:X26"/>
     <mergeCell ref="Y39:AB39"/>
     <mergeCell ref="Y74:AE74"/>
+    <mergeCell ref="D85:L85"/>
     <mergeCell ref="AF56:AK56"/>
-    <mergeCell ref="C54:L54"/>
     <mergeCell ref="AF43:AK43"/>
     <mergeCell ref="Y67:AE67"/>
     <mergeCell ref="AH1:AK1"/>
@@ -9357,26 +9891,27 @@
     <mergeCell ref="M75:P75"/>
     <mergeCell ref="M40:P40"/>
     <mergeCell ref="Q62:S62"/>
+    <mergeCell ref="B95:I95"/>
+    <mergeCell ref="C56:L56"/>
+    <mergeCell ref="B89:I89"/>
     <mergeCell ref="Y69:AE69"/>
     <mergeCell ref="D80:L80"/>
     <mergeCell ref="D120:AK120"/>
     <mergeCell ref="C43:L43"/>
-    <mergeCell ref="Q54:S54"/>
+    <mergeCell ref="A108:AK108"/>
     <mergeCell ref="J16:M16"/>
-    <mergeCell ref="D145:AK145"/>
     <mergeCell ref="AF57:AK57"/>
     <mergeCell ref="D163:AK163"/>
     <mergeCell ref="Q64:S64"/>
     <mergeCell ref="T77:X77"/>
-    <mergeCell ref="D147:AK147"/>
     <mergeCell ref="M41:P41"/>
-    <mergeCell ref="B167:AK167"/>
-    <mergeCell ref="B90:I90"/>
     <mergeCell ref="M24:P24"/>
     <mergeCell ref="T35:X35"/>
     <mergeCell ref="Y23:AB23"/>
     <mergeCell ref="M66:P66"/>
     <mergeCell ref="D58:L58"/>
+    <mergeCell ref="Y87:AE87"/>
+    <mergeCell ref="C147:AK147"/>
     <mergeCell ref="AF75:AK75"/>
     <mergeCell ref="Q57:S57"/>
     <mergeCell ref="AF28:AK28"/>
@@ -9384,26 +9919,29 @@
     <mergeCell ref="T61:X61"/>
     <mergeCell ref="Y82:AE82"/>
     <mergeCell ref="D158:AK158"/>
+    <mergeCell ref="C148:AK148"/>
     <mergeCell ref="AF39:AK39"/>
     <mergeCell ref="C44:L44"/>
     <mergeCell ref="AF70:AK70"/>
-    <mergeCell ref="D108:AK108"/>
     <mergeCell ref="C31:L31"/>
     <mergeCell ref="AC28:AE28"/>
     <mergeCell ref="M30:P30"/>
+    <mergeCell ref="D84:L84"/>
     <mergeCell ref="D160:AK160"/>
     <mergeCell ref="Y22:AB22"/>
+    <mergeCell ref="Q52:S52"/>
+    <mergeCell ref="B109:AK109"/>
     <mergeCell ref="Q39:S39"/>
     <mergeCell ref="M46:P46"/>
     <mergeCell ref="M37:P37"/>
     <mergeCell ref="AC30:AE30"/>
+    <mergeCell ref="D86:L86"/>
     <mergeCell ref="M61:P61"/>
     <mergeCell ref="AC23:AE23"/>
+    <mergeCell ref="C102:AK102"/>
     <mergeCell ref="Y77:AE77"/>
     <mergeCell ref="J18:M18"/>
-    <mergeCell ref="C79:C82"/>
-    <mergeCell ref="B96:I96"/>
-    <mergeCell ref="C166:AK166"/>
+    <mergeCell ref="C57:L57"/>
     <mergeCell ref="D121:AK121"/>
     <mergeCell ref="J17:M17"/>
     <mergeCell ref="C49:L49"/>
@@ -9411,24 +9949,33 @@
     <mergeCell ref="C141:AK141"/>
     <mergeCell ref="D113:AK113"/>
     <mergeCell ref="M43:P43"/>
+    <mergeCell ref="D173:AK173"/>
     <mergeCell ref="AF23:AK23"/>
+    <mergeCell ref="AF50:AK50"/>
     <mergeCell ref="Q70:S70"/>
+    <mergeCell ref="B98:I98"/>
     <mergeCell ref="Y72:AE72"/>
-    <mergeCell ref="D148:AK148"/>
     <mergeCell ref="C42:L42"/>
     <mergeCell ref="D115:AK115"/>
-    <mergeCell ref="B139:AK139"/>
+    <mergeCell ref="AF52:AK52"/>
+    <mergeCell ref="B183:AK183"/>
+    <mergeCell ref="T84:X84"/>
     <mergeCell ref="T22:X22"/>
     <mergeCell ref="AF34:AK34"/>
     <mergeCell ref="T75:X75"/>
     <mergeCell ref="M25:P25"/>
     <mergeCell ref="AF49:AK49"/>
+    <mergeCell ref="T86:X86"/>
+    <mergeCell ref="Q83:S83"/>
+    <mergeCell ref="D166:AK166"/>
     <mergeCell ref="M33:P33"/>
     <mergeCell ref="Q58:S58"/>
     <mergeCell ref="AF78:AK78"/>
     <mergeCell ref="Y65:AE65"/>
     <mergeCell ref="D76:L76"/>
     <mergeCell ref="C39:L39"/>
+    <mergeCell ref="Q85:S85"/>
+    <mergeCell ref="D168:AK168"/>
     <mergeCell ref="AF44:AK44"/>
     <mergeCell ref="Q60:S60"/>
     <mergeCell ref="M62:P62"/>
@@ -9437,41 +9984,49 @@
     <mergeCell ref="AF80:AK80"/>
     <mergeCell ref="D118:AK118"/>
     <mergeCell ref="AC29:AE29"/>
-    <mergeCell ref="AF55:AK55"/>
+    <mergeCell ref="D167:AK167"/>
+    <mergeCell ref="D161:AK161"/>
     <mergeCell ref="AC44:AE44"/>
+    <mergeCell ref="M87:P87"/>
     <mergeCell ref="AC31:AE31"/>
-    <mergeCell ref="C168:AK168"/>
+    <mergeCell ref="D169:AK169"/>
     <mergeCell ref="M64:P64"/>
+    <mergeCell ref="C180:AK180"/>
     <mergeCell ref="AF71:AK71"/>
+    <mergeCell ref="M51:P51"/>
+    <mergeCell ref="D131:AK131"/>
+    <mergeCell ref="C50:L50"/>
     <mergeCell ref="C25:L25"/>
     <mergeCell ref="AF37:AK37"/>
+    <mergeCell ref="C182:AK182"/>
     <mergeCell ref="AF24:AK24"/>
     <mergeCell ref="AF73:AK73"/>
     <mergeCell ref="Q71:S71"/>
-    <mergeCell ref="C169:AK169"/>
     <mergeCell ref="M65:P65"/>
     <mergeCell ref="Y78:AE78"/>
     <mergeCell ref="T46:X46"/>
     <mergeCell ref="AF66:AK66"/>
     <mergeCell ref="D116:AK116"/>
-    <mergeCell ref="AF53:AK53"/>
     <mergeCell ref="Q73:S73"/>
     <mergeCell ref="Y80:AE80"/>
     <mergeCell ref="Y49:AB49"/>
     <mergeCell ref="T48:X48"/>
     <mergeCell ref="AF68:AK68"/>
+    <mergeCell ref="C96:AK96"/>
     <mergeCell ref="A20:AK20"/>
     <mergeCell ref="AF42:AK42"/>
-    <mergeCell ref="C78:L78"/>
+    <mergeCell ref="Q84:S84"/>
+    <mergeCell ref="D142:AK142"/>
     <mergeCell ref="M34:P34"/>
-    <mergeCell ref="C162:AK162"/>
+    <mergeCell ref="M83:P83"/>
     <mergeCell ref="AF79:AK79"/>
     <mergeCell ref="M49:P49"/>
     <mergeCell ref="M39:P39"/>
     <mergeCell ref="D144:AK144"/>
+    <mergeCell ref="C93:AK93"/>
     <mergeCell ref="Y30:AB30"/>
     <mergeCell ref="D119:AK119"/>
-    <mergeCell ref="A51:AK51"/>
+    <mergeCell ref="AC52:AE52"/>
     <mergeCell ref="T41:X41"/>
     <mergeCell ref="M78:P78"/>
     <mergeCell ref="V1:Y1"/>
@@ -9482,37 +10037,45 @@
     <mergeCell ref="AC32:AE32"/>
     <mergeCell ref="AC37:AE37"/>
     <mergeCell ref="T43:X43"/>
+    <mergeCell ref="B135:AK135"/>
     <mergeCell ref="Y31:AB31"/>
     <mergeCell ref="AC47:AE47"/>
     <mergeCell ref="T36:X36"/>
-    <mergeCell ref="D57:L57"/>
     <mergeCell ref="AF63:AK63"/>
     <mergeCell ref="Q79:S79"/>
     <mergeCell ref="Y61:AE61"/>
-    <mergeCell ref="D137:AK137"/>
     <mergeCell ref="AF74:AK74"/>
     <mergeCell ref="C175:AK175"/>
     <mergeCell ref="Q81:S81"/>
-    <mergeCell ref="C53:L53"/>
+    <mergeCell ref="D130:AK130"/>
     <mergeCell ref="T25:X25"/>
     <mergeCell ref="M58:P58"/>
+    <mergeCell ref="AC50:AE50"/>
     <mergeCell ref="D117:AK117"/>
     <mergeCell ref="AF76:AK76"/>
     <mergeCell ref="Q74:S74"/>
     <mergeCell ref="T62:X62"/>
+    <mergeCell ref="D132:AK132"/>
+    <mergeCell ref="B146:AK146"/>
     <mergeCell ref="Q76:S76"/>
     <mergeCell ref="AC27:AE27"/>
+    <mergeCell ref="C137:AK137"/>
     <mergeCell ref="T64:X64"/>
     <mergeCell ref="Y44:AB44"/>
+    <mergeCell ref="C90:AK90"/>
     <mergeCell ref="D60:L60"/>
+    <mergeCell ref="C139:AK139"/>
     <mergeCell ref="Q28:S28"/>
+    <mergeCell ref="M84:P84"/>
     <mergeCell ref="M22:P22"/>
     <mergeCell ref="C138:AK138"/>
-    <mergeCell ref="C132:AK132"/>
+    <mergeCell ref="A54:AK54"/>
     <mergeCell ref="Y59:AE59"/>
+    <mergeCell ref="M86:P86"/>
     <mergeCell ref="M42:P42"/>
     <mergeCell ref="M80:P80"/>
     <mergeCell ref="T67:X67"/>
+    <mergeCell ref="AF87:AK87"/>
     <mergeCell ref="J11:AK11"/>
     <mergeCell ref="Y28:AB28"/>
     <mergeCell ref="Q29:S29"/>
@@ -9525,30 +10088,30 @@
     <mergeCell ref="Q31:S31"/>
     <mergeCell ref="AC38:AE38"/>
     <mergeCell ref="Y32:AB32"/>
+    <mergeCell ref="D78:L78"/>
     <mergeCell ref="J12:AK12"/>
     <mergeCell ref="AC46:AE46"/>
     <mergeCell ref="Y47:AB47"/>
     <mergeCell ref="AC40:AE40"/>
     <mergeCell ref="D71:L71"/>
     <mergeCell ref="C34:L34"/>
-    <mergeCell ref="C85:AK85"/>
     <mergeCell ref="Y62:AE62"/>
     <mergeCell ref="D73:L73"/>
     <mergeCell ref="C133:AK133"/>
     <mergeCell ref="M70:P70"/>
-    <mergeCell ref="C127:AK127"/>
-    <mergeCell ref="Y54:AE54"/>
     <mergeCell ref="M35:P35"/>
     <mergeCell ref="AC41:AE41"/>
     <mergeCell ref="Y64:AE64"/>
     <mergeCell ref="J2:P3"/>
     <mergeCell ref="AF77:AK77"/>
+    <mergeCell ref="Y50:AB50"/>
+    <mergeCell ref="C178:AK178"/>
     <mergeCell ref="M74:P74"/>
     <mergeCell ref="T34:X34"/>
     <mergeCell ref="Q42:S42"/>
     <mergeCell ref="T72:X72"/>
     <mergeCell ref="T28:X28"/>
-    <mergeCell ref="D135:AK135"/>
+    <mergeCell ref="Y52:AB52"/>
     <mergeCell ref="T30:X30"/>
     <mergeCell ref="T57:X57"/>
     <mergeCell ref="AC43:AE43"/>
@@ -9560,7 +10123,6 @@
     <mergeCell ref="B12:I12"/>
     <mergeCell ref="Q44:S44"/>
     <mergeCell ref="T58:X58"/>
-    <mergeCell ref="T54:X54"/>
     <mergeCell ref="Y75:AE75"/>
     <mergeCell ref="Y42:AB42"/>
     <mergeCell ref="AF32:AK32"/>
@@ -9569,8 +10131,10 @@
     <mergeCell ref="C24:L24"/>
     <mergeCell ref="AD2:AG3"/>
     <mergeCell ref="B13:I13"/>
+    <mergeCell ref="T83:X83"/>
     <mergeCell ref="D153:AK153"/>
     <mergeCell ref="Q45:S45"/>
+    <mergeCell ref="C99:AK99"/>
     <mergeCell ref="Q32:S32"/>
     <mergeCell ref="C26:L26"/>
     <mergeCell ref="AC48:AE48"/>
@@ -9578,65 +10142,68 @@
     <mergeCell ref="J13:AK13"/>
     <mergeCell ref="AF27:AK27"/>
     <mergeCell ref="Q47:S47"/>
-    <mergeCell ref="B104:AK104"/>
+    <mergeCell ref="T85:X85"/>
     <mergeCell ref="T60:X60"/>
-    <mergeCell ref="C130:AK130"/>
     <mergeCell ref="D81:L81"/>
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="M36:P36"/>
+    <mergeCell ref="C52:L52"/>
     <mergeCell ref="Q63:S63"/>
-    <mergeCell ref="C161:AK161"/>
+    <mergeCell ref="Q50:S50"/>
     <mergeCell ref="Y70:AE70"/>
+    <mergeCell ref="C136:AK136"/>
     <mergeCell ref="Y57:AE57"/>
     <mergeCell ref="T42:X42"/>
     <mergeCell ref="AF45:AK45"/>
-    <mergeCell ref="B93:I93"/>
     <mergeCell ref="D143:AK143"/>
     <mergeCell ref="C37:L37"/>
     <mergeCell ref="T78:X78"/>
-    <mergeCell ref="B170:AK170"/>
     <mergeCell ref="T65:X65"/>
     <mergeCell ref="Q27:S27"/>
     <mergeCell ref="Q2:U3"/>
+    <mergeCell ref="T50:X50"/>
     <mergeCell ref="T44:X44"/>
     <mergeCell ref="T80:X80"/>
     <mergeCell ref="J8:AK8"/>
-    <mergeCell ref="D55:L55"/>
+    <mergeCell ref="B101:I101"/>
     <mergeCell ref="AF40:AK40"/>
     <mergeCell ref="T79:X79"/>
     <mergeCell ref="D67:L67"/>
     <mergeCell ref="T73:X73"/>
     <mergeCell ref="J10:AK10"/>
+    <mergeCell ref="Y83:AE83"/>
     <mergeCell ref="D159:AK159"/>
     <mergeCell ref="C105:AK105"/>
     <mergeCell ref="D69:L69"/>
     <mergeCell ref="M31:P31"/>
+    <mergeCell ref="Y85:AE85"/>
     <mergeCell ref="Y60:AE60"/>
-    <mergeCell ref="C55:C77"/>
+    <mergeCell ref="B104:I104"/>
     <mergeCell ref="N16:AK16"/>
     <mergeCell ref="D154:AK154"/>
-    <mergeCell ref="Q55:S55"/>
+    <mergeCell ref="C149:AK149"/>
     <mergeCell ref="Y37:AB37"/>
     <mergeCell ref="C27:L27"/>
     <mergeCell ref="Q38:S38"/>
     <mergeCell ref="AC24:AE24"/>
+    <mergeCell ref="D162:AK162"/>
     <mergeCell ref="M26:P26"/>
     <mergeCell ref="D156:AK156"/>
-    <mergeCell ref="D106:AK106"/>
+    <mergeCell ref="B176:AK176"/>
     <mergeCell ref="Q40:S40"/>
     <mergeCell ref="AC26:AE26"/>
+    <mergeCell ref="D87:L87"/>
     <mergeCell ref="D157:AK157"/>
     <mergeCell ref="J14:M14"/>
     <mergeCell ref="AF47:AK47"/>
     <mergeCell ref="Y71:AE71"/>
+    <mergeCell ref="M52:P52"/>
+    <mergeCell ref="C45:L45"/>
     <mergeCell ref="D82:L82"/>
-    <mergeCell ref="C45:L45"/>
     <mergeCell ref="Y58:AE58"/>
-    <mergeCell ref="D109:AK109"/>
+    <mergeCell ref="C177:AK177"/>
     <mergeCell ref="AF46:AK46"/>
     <mergeCell ref="Q66:S66"/>
-    <mergeCell ref="B99:I99"/>
-    <mergeCell ref="Q53:S53"/>
     <mergeCell ref="Y73:AE73"/>
     <mergeCell ref="J15:M15"/>
     <mergeCell ref="C47:L47"/>
@@ -9644,17 +10211,20 @@
     <mergeCell ref="T70:X70"/>
     <mergeCell ref="AF61:AK61"/>
     <mergeCell ref="D111:AK111"/>
+    <mergeCell ref="B92:I92"/>
     <mergeCell ref="AF48:AK48"/>
     <mergeCell ref="Q68:S68"/>
     <mergeCell ref="C40:L40"/>
     <mergeCell ref="T81:X81"/>
-    <mergeCell ref="C91:AK91"/>
+    <mergeCell ref="C51:L51"/>
     <mergeCell ref="D150:AK150"/>
     <mergeCell ref="M28:P28"/>
     <mergeCell ref="D77:L77"/>
     <mergeCell ref="Q72:S72"/>
+    <mergeCell ref="Y84:AE84"/>
     <mergeCell ref="M57:P57"/>
     <mergeCell ref="M32:P32"/>
+    <mergeCell ref="Y86:AE86"/>
     <mergeCell ref="N18:AK18"/>
     <mergeCell ref="M29:P29"/>
     <mergeCell ref="M23:P23"/>
@@ -9665,13 +10235,12 @@
     <mergeCell ref="D164:AK164"/>
     <mergeCell ref="Y38:AB38"/>
     <mergeCell ref="T71:X71"/>
-    <mergeCell ref="B128:AK128"/>
     <mergeCell ref="Y24:AB24"/>
     <mergeCell ref="Q41:S41"/>
+    <mergeCell ref="D172:AK172"/>
     <mergeCell ref="Q1:U1"/>
     <mergeCell ref="AF36:AK36"/>
     <mergeCell ref="Q56:S56"/>
-    <mergeCell ref="A103:AK103"/>
     <mergeCell ref="Q43:S43"/>
     <mergeCell ref="T66:X66"/>
     <mergeCell ref="B9:I9"/>
@@ -9683,6 +10252,7 @@
     <mergeCell ref="M45:P45"/>
     <mergeCell ref="AF69:AK69"/>
     <mergeCell ref="Q67:S67"/>
+    <mergeCell ref="C170:AK170"/>
     <mergeCell ref="D125:AK125"/>
     <mergeCell ref="C48:L48"/>
     <mergeCell ref="AF62:AK62"/>
@@ -9691,23 +10261,29 @@
     <mergeCell ref="Q69:S69"/>
     <mergeCell ref="N14:AK14"/>
     <mergeCell ref="Y76:AE76"/>
+    <mergeCell ref="D127:AK127"/>
+    <mergeCell ref="C84:C87"/>
     <mergeCell ref="AF64:AK64"/>
     <mergeCell ref="D114:AK114"/>
+    <mergeCell ref="AF51:AK51"/>
     <mergeCell ref="AC22:AE22"/>
     <mergeCell ref="Y63:AE63"/>
     <mergeCell ref="M44:P44"/>
+    <mergeCell ref="AC51:AE51"/>
     <mergeCell ref="AF38:AK38"/>
     <mergeCell ref="M79:P79"/>
+    <mergeCell ref="C58:C82"/>
     <mergeCell ref="M73:P73"/>
     <mergeCell ref="M60:P60"/>
+    <mergeCell ref="Q87:S87"/>
     <mergeCell ref="A2:I3"/>
     <mergeCell ref="D63:L63"/>
     <mergeCell ref="Y26:AB26"/>
     <mergeCell ref="AF33:AK33"/>
     <mergeCell ref="AF82:AK82"/>
     <mergeCell ref="Q24:S24"/>
-    <mergeCell ref="D107:AK107"/>
     <mergeCell ref="C36:L36"/>
+    <mergeCell ref="Q51:S51"/>
     <mergeCell ref="Q82:S82"/>
     <mergeCell ref="AC33:AE33"/>
     <mergeCell ref="T39:X39"/>
@@ -9717,46 +10293,45 @@
     <mergeCell ref="AC35:AE35"/>
     <mergeCell ref="M63:P63"/>
     <mergeCell ref="T47:X47"/>
-    <mergeCell ref="M53:P53"/>
     <mergeCell ref="AC34:AE34"/>
-    <mergeCell ref="C172:AK172"/>
+    <mergeCell ref="M50:P50"/>
     <mergeCell ref="M68:P68"/>
-    <mergeCell ref="M55:P55"/>
+    <mergeCell ref="C184:AK184"/>
     <mergeCell ref="C171:AK171"/>
     <mergeCell ref="M67:P67"/>
     <mergeCell ref="M48:P48"/>
     <mergeCell ref="AF72:AK72"/>
     <mergeCell ref="Q75:S75"/>
-    <mergeCell ref="C173:AK173"/>
     <mergeCell ref="N15:AK15"/>
+    <mergeCell ref="D128:AK128"/>
     <mergeCell ref="M69:P69"/>
     <mergeCell ref="T23:X23"/>
+    <mergeCell ref="T52:X52"/>
     <mergeCell ref="Y40:AB40"/>
     <mergeCell ref="M81:P81"/>
     <mergeCell ref="V2:Y3"/>
     <mergeCell ref="T27:X27"/>
-    <mergeCell ref="AF54:AK54"/>
     <mergeCell ref="B7:I7"/>
     <mergeCell ref="Q26:S26"/>
     <mergeCell ref="T49:X49"/>
-    <mergeCell ref="D146:AK146"/>
     <mergeCell ref="M38:P38"/>
     <mergeCell ref="M76:P76"/>
+    <mergeCell ref="AF83:AK83"/>
     <mergeCell ref="AF58:AK58"/>
     <mergeCell ref="Q65:S65"/>
-    <mergeCell ref="C97:AK97"/>
+    <mergeCell ref="AF85:AK85"/>
     <mergeCell ref="D123:AK123"/>
+    <mergeCell ref="C83:L83"/>
     <mergeCell ref="AF60:AK60"/>
-    <mergeCell ref="D110:AK110"/>
     <mergeCell ref="D74:L74"/>
     <mergeCell ref="D68:L68"/>
     <mergeCell ref="AC49:AE49"/>
     <mergeCell ref="AC36:AE36"/>
     <mergeCell ref="Y35:AB35"/>
     <mergeCell ref="D59:L59"/>
-    <mergeCell ref="B84:I84"/>
     <mergeCell ref="Q37:S37"/>
-    <mergeCell ref="D136:AK136"/>
+    <mergeCell ref="C110:AK110"/>
+    <mergeCell ref="C181:AK181"/>
     <mergeCell ref="M77:P77"/>
     <mergeCell ref="AF29:AK29"/>
   </mergeCells>
@@ -9923,7 +10498,7 @@
       <c r="Y2" s="22" t="n"/>
       <c r="Z2" s="20" t="inlineStr">
         <is>
-          <t>Nguyen Duyen Manh</t>
+          <t>Tran Duc Tuyen</t>
         </is>
       </c>
       <c r="AA2" s="21" t="n"/>
@@ -9931,7 +10506,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/07/17</t>
+          <t>2026/07/24</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -9939,7 +10514,7 @@
       <c r="AG2" s="22" t="n"/>
       <c r="AH2" s="20" t="inlineStr">
         <is>
-          <t>Nguyen Duyen Manh</t>
+          <t>Tran Duc Tuyen</t>
         </is>
       </c>
       <c r="AI2" s="21" t="n"/>
@@ -12109,7 +12684,7 @@
       <c r="Y2" s="22" t="n"/>
       <c r="Z2" s="20" t="inlineStr">
         <is>
-          <t>Nguyen Duyen Manh</t>
+          <t>Tran Duc Tuyen</t>
         </is>
       </c>
       <c r="AA2" s="21" t="n"/>
@@ -12117,7 +12692,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/07/17</t>
+          <t>2026/07/24</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -12125,7 +12700,7 @@
       <c r="AG2" s="22" t="n"/>
       <c r="AH2" s="20" t="inlineStr">
         <is>
-          <t>Nguyen Duyen Manh</t>
+          <t>Tran Duc Tuyen</t>
         </is>
       </c>
       <c r="AI2" s="21" t="n"/>
@@ -13397,7 +13972,7 @@
       <c r="AE39" s="11" t="n"/>
       <c r="AF39" s="19" t="inlineStr">
         <is>
-          <t>hanbaiten_id</t>
+          <t>hanbaiten_code</t>
         </is>
       </c>
       <c r="AG39" s="10" t="n"/>
@@ -14126,7 +14701,7 @@
     <row r="87" ht="54" customHeight="1">
       <c r="C87" s="41" t="inlineStr">
         <is>
-          <t>ヘッダー行（検索結果テーブルと一致、15 列）：`ID, 管理支店, 組合員コード, 購読者名, 手続種類, 購読種別, 連絡先１, 配達先氏名, 配達先郵便, 配達先住所, 販売店コード, 販売店名, 支払方法, 購読開始日, 購読中止日`</t>
+          <t>ヘッダー行（検索結果テーブルと一致、16 列）：`ID, 管理支店, 組合員コード, 購読者名, 手続種類, 購読種別, 連絡先１, 配送先連絡先１, 配達先氏名, 配達先郵便, 配達先住所, 販売店コード, 販売店名, 支払方法, 購読開始日, 購読中止日`</t>
         </is>
       </c>
     </row>
@@ -14721,7 +15296,7 @@
       <c r="Y2" s="22" t="n"/>
       <c r="Z2" s="20" t="inlineStr">
         <is>
-          <t>Nguyen Duyen Manh</t>
+          <t>Tran Duc Tuyen</t>
         </is>
       </c>
       <c r="AA2" s="21" t="n"/>
@@ -14729,7 +15304,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/07/17</t>
+          <t>2026/07/24</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -14737,7 +15312,7 @@
       <c r="AG2" s="22" t="n"/>
       <c r="AH2" s="20" t="inlineStr">
         <is>
-          <t>Nguyen Duyen Manh</t>
+          <t>Tran Duc Tuyen</t>
         </is>
       </c>
       <c r="AI2" s="21" t="n"/>
@@ -14853,7 +15428,7 @@
       <c r="I8" s="11" t="n"/>
       <c r="J8" s="19" t="inlineStr">
         <is>
-          <t>一覧の「購読を停止する」ボタンから、購読中止日（解約予定日）だけを指定して解約予約行を1件挿入する専用API。購読中止日は予約時点で master（t_dokusya.dokusya_chushi_date）へ即時反映し、一覧（SCR-014）・詳細（SCR-011）に直ちに表示する。解約の確定（解約フラグ・購読状態の反映）は到来日バッチ（Phase 2）が行う。予約行を取消すると master の購読中止日は自動で null へ戻る。</t>
+          <t>一覧の「購読中止」ボタンから、購読中止日（解約予定日）だけを指定して解約予約行を1件挿入する専用API。購読中止日は予約時点で master（t_dokusya.dokusya_chushi_date）へ即時反映し、一覧（SCR-014）・詳細（SCR-011）に直ちに表示する。解約の確定（解約フラグ・購読状態の反映）は到来日バッチ（Phase 2）が行う。予約行を取消すると master の購読中止日は自動で null へ戻る。</t>
         </is>
       </c>
       <c r="K8" s="10" t="n"/>

--- a/docs/design/ACSMS-SCR-014/【日本農業新聞様】VTIジャパン_クラウド版購読者管理システム_API設計書_購読者明細検索画面_V1.0.xlsx
+++ b/docs/design/ACSMS-SCR-014/【日本農業新聞様】VTIジャパン_クラウド版購読者管理システム_API設計書_購読者明細検索画面_V1.0.xlsx
@@ -1354,7 +1354,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG10"/>
+  <dimension ref="A1:AG11"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="4.25" customWidth="1" min="1" max="1"/>
@@ -1986,78 +1986,144 @@
       <c r="AF10" s="10" t="n"/>
       <c r="AG10" s="11" t="n"/>
     </row>
+    <row r="11" ht="19.5" customHeight="1">
+      <c r="A11" s="17" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="11" t="n"/>
+      <c r="C11" s="18" t="inlineStr">
+        <is>
+          <t>2026/08/03</t>
+        </is>
+      </c>
+      <c r="D11" s="10" t="n"/>
+      <c r="E11" s="10" t="n"/>
+      <c r="F11" s="10" t="n"/>
+      <c r="G11" s="11" t="n"/>
+      <c r="H11" s="17" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="I11" s="10" t="n"/>
+      <c r="J11" s="11" t="n"/>
+      <c r="K11" s="17" t="inlineStr">
+        <is>
+          <t>Tran Duc Tuyen</t>
+        </is>
+      </c>
+      <c r="L11" s="10" t="n"/>
+      <c r="M11" s="10" t="n"/>
+      <c r="N11" s="10" t="n"/>
+      <c r="O11" s="10" t="n"/>
+      <c r="P11" s="10" t="n"/>
+      <c r="Q11" s="11" t="n"/>
+      <c r="R11" s="19" t="inlineStr">
+        <is>
+          <t>顧客要件 2026-08 反映（電子版の解約予約を変更・取消できるようにする）：&lt;br&gt;1. ACSMS-API-014-004 を「解約予約」専用から **解約予約 / 予約変更 / 予約取消** の3操作を兼ねるエンドポイントへ拡張。`dokusya_chushi_date` に **空文字**を許容し、電子版では予約取消を意味する。&lt;br&gt;2. 電子版（dokusya_shubetsu=2）は既存予約があっても 400 にせず受け付ける。旧予約行を取消（赤伝）してから、日付ありなら新予約を append する。紙版は従来どおり二重解約を 400 で拒否（変更・取消は履歴画面の取消経由）。&lt;br&gt;3. 到来日バッチが確定させた実解約行（kaiyaku_flg=true）に対する変更・取消は種別を問わず 400（`解約が確定済みのため変更できません。…`）。復帰は再購読（SCR-011）。&lt;br&gt;4. 予約変更・予約取消のいずれも同一トランザクション内で電子版へ `cancel` を push する。変更は新しい `cancel_ym`、取消は `cancel_ym` 空文字（電子版APIに解約取消の処理区分が無いため・顧客判断 2026-08）。push 失敗時は全ロールバック。&lt;br&gt;5. 応答 `message` を操作で出し分け：新規予約・予約変更＝`購読停止を予約しました。` / 予約取消＝`購読中止を取り消しました。`&lt;br&gt;6. 一覧のポップアップは予約中でも開き、予約中の終了月を復元表示する（クリアして確定＝取消）。</t>
+        </is>
+      </c>
+      <c r="S11" s="10" t="n"/>
+      <c r="T11" s="10" t="n"/>
+      <c r="U11" s="10" t="n"/>
+      <c r="V11" s="11" t="n"/>
+      <c r="W11" s="17" t="inlineStr">
+        <is>
+          <t>Nguyen Huy Dat</t>
+        </is>
+      </c>
+      <c r="X11" s="10" t="n"/>
+      <c r="Y11" s="10" t="n"/>
+      <c r="Z11" s="10" t="n"/>
+      <c r="AA11" s="11" t="n"/>
+      <c r="AB11" s="17" t="inlineStr">
+        <is>
+          <t>Nguyen Huy Dat</t>
+        </is>
+      </c>
+      <c r="AC11" s="10" t="n"/>
+      <c r="AD11" s="10" t="n"/>
+      <c r="AE11" s="10" t="n"/>
+      <c r="AF11" s="10" t="n"/>
+      <c r="AG11" s="11" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="70">
-    <mergeCell ref="R1:V1"/>
+  <mergeCells count="77">
     <mergeCell ref="R8:V8"/>
     <mergeCell ref="AB1:AG1"/>
-    <mergeCell ref="C6:G6"/>
+    <mergeCell ref="C5:G5"/>
+    <mergeCell ref="R10:V10"/>
+    <mergeCell ref="H2:J2"/>
+    <mergeCell ref="W5:AA5"/>
+    <mergeCell ref="H11:J11"/>
+    <mergeCell ref="C4:G4"/>
+    <mergeCell ref="R7:V7"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="H3:J3"/>
+    <mergeCell ref="AB10:AG10"/>
+    <mergeCell ref="W7:AA7"/>
+    <mergeCell ref="H5:J5"/>
+    <mergeCell ref="AB3:AG3"/>
+    <mergeCell ref="K1:Q1"/>
+    <mergeCell ref="C7:G7"/>
+    <mergeCell ref="W8:AA8"/>
+    <mergeCell ref="AB5:AG5"/>
+    <mergeCell ref="W2:AA2"/>
     <mergeCell ref="A9:B9"/>
+    <mergeCell ref="AB4:AG4"/>
+    <mergeCell ref="R1:V1"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="R4:V4"/>
+    <mergeCell ref="H7:J7"/>
+    <mergeCell ref="K10:Q10"/>
+    <mergeCell ref="K6:Q6"/>
+    <mergeCell ref="K3:Q3"/>
+    <mergeCell ref="AB8:AG8"/>
+    <mergeCell ref="K9:Q9"/>
+    <mergeCell ref="K5:Q5"/>
+    <mergeCell ref="R3:V3"/>
+    <mergeCell ref="K11:Q11"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="H4:J4"/>
+    <mergeCell ref="K8:Q8"/>
+    <mergeCell ref="R9:V9"/>
+    <mergeCell ref="R5:V5"/>
+    <mergeCell ref="W4:AA4"/>
+    <mergeCell ref="H6:J6"/>
     <mergeCell ref="W10:AA10"/>
-    <mergeCell ref="R5:V5"/>
-    <mergeCell ref="W6:AA6"/>
-    <mergeCell ref="AB9:AG9"/>
-    <mergeCell ref="C5:G5"/>
+    <mergeCell ref="R11:V11"/>
     <mergeCell ref="K7:Q7"/>
     <mergeCell ref="A1:B1"/>
-    <mergeCell ref="H2:J2"/>
-    <mergeCell ref="W5:AA5"/>
-    <mergeCell ref="R4:V4"/>
-    <mergeCell ref="R10:V10"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="H7:J7"/>
-    <mergeCell ref="K10:Q10"/>
-    <mergeCell ref="AB2:AG2"/>
-    <mergeCell ref="C4:G4"/>
-    <mergeCell ref="R7:V7"/>
-    <mergeCell ref="K4:Q4"/>
-    <mergeCell ref="K6:Q6"/>
-    <mergeCell ref="A7:B7"/>
     <mergeCell ref="R6:V6"/>
     <mergeCell ref="C10:G10"/>
-    <mergeCell ref="C1:G1"/>
-    <mergeCell ref="K3:Q3"/>
-    <mergeCell ref="W4:AA4"/>
-    <mergeCell ref="W1:AA1"/>
     <mergeCell ref="W3:AA3"/>
-    <mergeCell ref="H3:J3"/>
-    <mergeCell ref="AB8:AG8"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="C9:G9"/>
-    <mergeCell ref="K9:Q9"/>
     <mergeCell ref="AB7:AG7"/>
-    <mergeCell ref="K5:Q5"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="AB10:AG10"/>
-    <mergeCell ref="W7:AA7"/>
     <mergeCell ref="C2:G2"/>
-    <mergeCell ref="H5:J5"/>
     <mergeCell ref="A5:B5"/>
     <mergeCell ref="H8:J8"/>
-    <mergeCell ref="R3:V3"/>
-    <mergeCell ref="AB3:AG3"/>
-    <mergeCell ref="A8:B8"/>
-    <mergeCell ref="C8:G8"/>
-    <mergeCell ref="K1:Q1"/>
-    <mergeCell ref="AB6:AG6"/>
+    <mergeCell ref="C11:G11"/>
     <mergeCell ref="H1:J1"/>
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="W9:AA9"/>
-    <mergeCell ref="C7:G7"/>
     <mergeCell ref="H10:J10"/>
-    <mergeCell ref="W8:AA8"/>
-    <mergeCell ref="AB5:AG5"/>
-    <mergeCell ref="W2:AA2"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="H4:J4"/>
     <mergeCell ref="R2:V2"/>
     <mergeCell ref="H9:J9"/>
-    <mergeCell ref="K8:Q8"/>
-    <mergeCell ref="AB4:AG4"/>
+    <mergeCell ref="C6:G6"/>
+    <mergeCell ref="W6:AA6"/>
+    <mergeCell ref="AB9:AG9"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="AB2:AG2"/>
+    <mergeCell ref="AB11:AG11"/>
+    <mergeCell ref="K4:Q4"/>
+    <mergeCell ref="C1:G1"/>
+    <mergeCell ref="W1:AA1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="C8:G8"/>
+    <mergeCell ref="AB6:AG6"/>
+    <mergeCell ref="W11:AA11"/>
     <mergeCell ref="K2:Q2"/>
-    <mergeCell ref="R9:V9"/>
     <mergeCell ref="C3:G3"/>
-    <mergeCell ref="H6:J6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2222,7 +2288,7 @@
       <c r="Y2" s="22" t="n"/>
       <c r="Z2" s="20" t="inlineStr">
         <is>
-          <t>Tran Duc Tuyen</t>
+          <t>Nguyen Duyen Manh</t>
         </is>
       </c>
       <c r="AA2" s="21" t="n"/>
@@ -2230,7 +2296,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/07/24</t>
+          <t>2026/08/03</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -2238,7 +2304,7 @@
       <c r="AG2" s="22" t="n"/>
       <c r="AH2" s="20" t="inlineStr">
         <is>
-          <t>Tran Duc Tuyen</t>
+          <t>Nguyen Duyen Manh</t>
         </is>
       </c>
       <c r="AI2" s="21" t="n"/>
@@ -2738,7 +2804,7 @@
       <c r="Y2" s="22" t="n"/>
       <c r="Z2" s="20" t="inlineStr">
         <is>
-          <t>Tran Duc Tuyen</t>
+          <t>Nguyen Duyen Manh</t>
         </is>
       </c>
       <c r="AA2" s="21" t="n"/>
@@ -2746,7 +2812,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/07/24</t>
+          <t>2026/08/03</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -2754,7 +2820,7 @@
       <c r="AG2" s="22" t="n"/>
       <c r="AH2" s="20" t="inlineStr">
         <is>
-          <t>Tran Duc Tuyen</t>
+          <t>Nguyen Duyen Manh</t>
         </is>
       </c>
       <c r="AI2" s="21" t="n"/>
@@ -3724,7 +3790,7 @@
       <c r="Y2" s="22" t="n"/>
       <c r="Z2" s="20" t="inlineStr">
         <is>
-          <t>Tran Duc Tuyen</t>
+          <t>Nguyen Duyen Manh</t>
         </is>
       </c>
       <c r="AA2" s="21" t="n"/>
@@ -3732,7 +3798,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/07/24</t>
+          <t>2026/08/03</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -3740,7 +3806,7 @@
       <c r="AG2" s="22" t="n"/>
       <c r="AH2" s="20" t="inlineStr">
         <is>
-          <t>Tran Duc Tuyen</t>
+          <t>Nguyen Duyen Manh</t>
         </is>
       </c>
       <c r="AI2" s="21" t="n"/>
@@ -4035,7 +4101,7 @@
       <c r="I9" s="11" t="n"/>
       <c r="J9" s="19" t="inlineStr">
         <is>
-          <t>Stop Dokusya（購読停止・解約予約）</t>
+          <t>Stop Dokusya（購読中止・解約予約 / 予約変更 / 予約取消）</t>
         </is>
       </c>
       <c r="K9" s="10" t="n"/>
@@ -4048,7 +4114,7 @@
       <c r="R9" s="11" t="n"/>
       <c r="S9" s="19" t="inlineStr">
         <is>
-          <t>一覧の「購読中止」ボタンから、購読中止日（解約予定日）だけを指定して解約予約行を1件挿入する専用API。購読中止日は予約時点で master（t_dokusya.dokusya_chushi_date）へ即時反映し、一覧（SCR-014）・詳細（SCR-011）に直ちに表示する。解約の確定（解約フラグ・購読状態の反映）は到来日バッチ（Phase 2）が行う。予約行を取消すると master の購読中止日は自動で null へ戻る。</t>
+          <t>一覧の「購読中止」ボタンから、購読中止日（解約予定日）だけを指定して解約予約行を1件挿入する専用API。購読中止日は予約時点で master（t_dokusya.dokusya_chushi_date）へ即時反映し、一覧（SCR-014）・詳細（SCR-011）に直ちに表示する。解約の確定（解約フラグ・購読状態の反映）は到来日バッチ（Phase 2）が行う。予約行を取消すると master の購読中止日は自動で null へ戻る。&lt;br&gt;電子版（dokusya_shubetsu=2）は同一エンドポイントで **予約変更**（別の日付を送る）と **予約取消**（空文字を送る）も受け付ける。どちらも旧予約行を取消（赤伝）してから処理し、電子版へ `cancel` を push する。</t>
         </is>
       </c>
       <c r="T9" s="10" t="n"/>
@@ -4285,7 +4351,7 @@
       <c r="Y2" s="22" t="n"/>
       <c r="Z2" s="20" t="inlineStr">
         <is>
-          <t>Tran Duc Tuyen</t>
+          <t>Nguyen Duyen Manh</t>
         </is>
       </c>
       <c r="AA2" s="21" t="n"/>
@@ -4293,7 +4359,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/07/24</t>
+          <t>2026/08/03</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -4301,7 +4367,7 @@
       <c r="AG2" s="22" t="n"/>
       <c r="AH2" s="20" t="inlineStr">
         <is>
-          <t>Tran Duc Tuyen</t>
+          <t>Nguyen Duyen Manh</t>
         </is>
       </c>
       <c r="AI2" s="21" t="n"/>
@@ -10498,7 +10564,7 @@
       <c r="Y2" s="22" t="n"/>
       <c r="Z2" s="20" t="inlineStr">
         <is>
-          <t>Tran Duc Tuyen</t>
+          <t>Nguyen Duyen Manh</t>
         </is>
       </c>
       <c r="AA2" s="21" t="n"/>
@@ -10506,7 +10572,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/07/24</t>
+          <t>2026/08/03</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -10514,7 +10580,7 @@
       <c r="AG2" s="22" t="n"/>
       <c r="AH2" s="20" t="inlineStr">
         <is>
-          <t>Tran Duc Tuyen</t>
+          <t>Nguyen Duyen Manh</t>
         </is>
       </c>
       <c r="AI2" s="21" t="n"/>
@@ -12684,7 +12750,7 @@
       <c r="Y2" s="22" t="n"/>
       <c r="Z2" s="20" t="inlineStr">
         <is>
-          <t>Tran Duc Tuyen</t>
+          <t>Nguyen Duyen Manh</t>
         </is>
       </c>
       <c r="AA2" s="21" t="n"/>
@@ -12692,7 +12758,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/07/24</t>
+          <t>2026/08/03</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -12700,7 +12766,7 @@
       <c r="AG2" s="22" t="n"/>
       <c r="AH2" s="20" t="inlineStr">
         <is>
-          <t>Tran Duc Tuyen</t>
+          <t>Nguyen Duyen Manh</t>
         </is>
       </c>
       <c r="AI2" s="21" t="n"/>
@@ -15143,7 +15209,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK86"/>
+  <dimension ref="A1:AK101"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="4.25" customWidth="1" min="1" max="1"/>
@@ -15296,7 +15362,7 @@
       <c r="Y2" s="22" t="n"/>
       <c r="Z2" s="20" t="inlineStr">
         <is>
-          <t>Tran Duc Tuyen</t>
+          <t>Nguyen Duyen Manh</t>
         </is>
       </c>
       <c r="AA2" s="21" t="n"/>
@@ -15304,7 +15370,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/07/24</t>
+          <t>2026/08/03</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -15312,7 +15378,7 @@
       <c r="AG2" s="22" t="n"/>
       <c r="AH2" s="20" t="inlineStr">
         <is>
-          <t>Tran Duc Tuyen</t>
+          <t>Nguyen Duyen Manh</t>
         </is>
       </c>
       <c r="AI2" s="21" t="n"/>
@@ -15382,7 +15448,7 @@
       <c r="I7" s="11" t="n"/>
       <c r="J7" s="19" t="inlineStr">
         <is>
-          <t>Stop Dokusya（購読停止・解約予約）</t>
+          <t>Stop Dokusya（購読中止・解約予約 / 予約変更 / 予約取消）</t>
         </is>
       </c>
       <c r="K7" s="10" t="n"/>
@@ -15413,7 +15479,7 @@
       <c r="AJ7" s="10" t="n"/>
       <c r="AK7" s="11" t="n"/>
     </row>
-    <row r="8" ht="54" customHeight="1">
+    <row r="8" ht="72" customHeight="1">
       <c r="B8" s="33" t="inlineStr">
         <is>
           <t>概要</t>
@@ -15428,7 +15494,7 @@
       <c r="I8" s="11" t="n"/>
       <c r="J8" s="19" t="inlineStr">
         <is>
-          <t>一覧の「購読中止」ボタンから、購読中止日（解約予定日）だけを指定して解約予約行を1件挿入する専用API。購読中止日は予約時点で master（t_dokusya.dokusya_chushi_date）へ即時反映し、一覧（SCR-014）・詳細（SCR-011）に直ちに表示する。解約の確定（解約フラグ・購読状態の反映）は到来日バッチ（Phase 2）が行う。予約行を取消すると master の購読中止日は自動で null へ戻る。</t>
+          <t>一覧の「購読中止」ボタンから、購読中止日（解約予定日）だけを指定して解約予約行を1件挿入する専用API。購読中止日は予約時点で master（t_dokusya.dokusya_chushi_date）へ即時反映し、一覧（SCR-014）・詳細（SCR-011）に直ちに表示する。解約の確定（解約フラグ・購読状態の反映）は到来日バッチ（Phase 2）が行う。予約行を取消すると master の購読中止日は自動で null へ戻る。&lt;br&gt;電子版（dokusya_shubetsu=2）は同一エンドポイントで **予約変更**（別の日付を送る）と **予約取消**（空文字を送る）も受け付ける。どちらも旧予約行を取消（赤伝）してから処理し、電子版へ `cancel` を push する。</t>
         </is>
       </c>
       <c r="K8" s="10" t="n"/>
@@ -15566,7 +15632,7 @@
       <c r="I11" s="11" t="n"/>
       <c r="J11" s="19" t="inlineStr">
         <is>
-          <t>dokusya_chushi_date（YYYY-MM-DD）</t>
+          <t>dokusya_chushi_date（YYYY-MM-DD、または空文字＝予約取消）</t>
         </is>
       </c>
       <c r="K11" s="10" t="n"/>
@@ -15710,7 +15776,7 @@
       <c r="M14" s="11" t="n"/>
       <c r="N14" s="19" t="inlineStr">
         <is>
-          <t>購読停止を予約しました</t>
+          <t>購読停止を予約しました／購読中止を取り消しました</t>
         </is>
       </c>
       <c r="O14" s="10" t="n"/>
@@ -16110,7 +16176,7 @@
       <c r="AJ25" s="10" t="n"/>
       <c r="AK25" s="11" t="n"/>
     </row>
-    <row r="26" ht="36" customHeight="1">
+    <row r="26" ht="54" customHeight="1">
       <c r="B26" s="31" t="n">
         <v>2</v>
       </c>
@@ -16161,7 +16227,7 @@
       <c r="AE26" s="11" t="n"/>
       <c r="AF26" s="19" t="inlineStr">
         <is>
-          <t>購読中止日（解約予定日）。紙版はカレンダー選択日、電子版は選択した終了月の月末日。フォーマットは `YYYY-MM-DD`。</t>
+          <t>購読中止日（解約予定日）。紙版はカレンダー選択日、電子版は選択した終了月の月末日。フォーマットは `YYYY-MM-DD`。&lt;br&gt;**空文字 `""` = 解約予約の取消**（電子版のみ。紙版に送ると 400）。</t>
         </is>
       </c>
       <c r="AG26" s="10" t="n"/>
@@ -16305,7 +16371,7 @@
       <c r="AJ31" s="10" t="n"/>
       <c r="AK31" s="11" t="n"/>
     </row>
-    <row r="32" ht="18" customHeight="1">
+    <row r="32" ht="36" customHeight="1">
       <c r="B32" s="31" t="n">
         <v>2</v>
       </c>
@@ -16356,7 +16422,7 @@
       <c r="AE32" s="11" t="n"/>
       <c r="AF32" s="19" t="inlineStr">
         <is>
-          <t>「購読停止を予約しました。」</t>
+          <t>「購読停止を予約しました。」（新規予約・予約変更）／「購読中止を取り消しました。」（予約取消）</t>
         </is>
       </c>
       <c r="AG32" s="10" t="n"/>
@@ -16580,7 +16646,7 @@
     <row r="46" ht="19.5" customHeight="1">
       <c r="B46" s="40" t="inlineStr">
         <is>
-          <t>レスポンス（失敗 400 Validation Error（二重解約））</t>
+          <t>レスポンス（失敗 400 Validation Error（紙版：二重解約））</t>
         </is>
       </c>
     </row>
@@ -16634,16 +16700,19 @@
     <row r="49" ht="19.5" customHeight="1">
       <c r="B49" s="40" t="inlineStr">
         <is>
-          <t>レスポンス（失敗 403 Dokusya Read Only）</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" ht="72" customHeight="1">
+          <t>レスポンス（失敗 400 Validation Error（解約確定済み））</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="126" customHeight="1">
       <c r="C50" s="19" t="inlineStr">
         <is>
           <t>{
-  "error_code": "DOKUSYA_READ_ONLY",
-  "message": "この購読者は編集・削除できません。（電子版クレジットカード決済者・併読者は読み取り専用）"
+  "error_code": "VALIDATION_ERROR",
+  "message": "入力値が不正です",
+  "errors": [
+    { "field": "dokusya_chushi_date", "message": "解約が確定済みのため変更できません。再購読は購読者編集画面から行ってください。" }
+  ]
 }</t>
         </is>
       </c>
@@ -16685,16 +16754,19 @@
     <row r="52" ht="19.5" customHeight="1">
       <c r="B52" s="40" t="inlineStr">
         <is>
-          <t>レスポンス（失敗 404 Not Found）</t>
-        </is>
-      </c>
-    </row>
-    <row r="53" ht="72" customHeight="1">
+          <t>レスポンス（失敗 400 Validation Error（予約が無いのに取消を送った））</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="126" customHeight="1">
       <c r="C53" s="19" t="inlineStr">
         <is>
           <t>{
-  "error_code": "NOT_FOUND",
-  "message": "指定された購読者が見つかりません。"
+  "error_code": "VALIDATION_ERROR",
+  "message": "入力値が不正です",
+  "errors": [
+    { "field": "dokusya_chushi_date", "message": "解約予約がありません。画面を再読み込みしてください。" }
+  ]
 }</t>
         </is>
       </c>
@@ -16733,267 +16805,433 @@
       <c r="AJ53" s="10" t="n"/>
       <c r="AK53" s="11" t="n"/>
     </row>
-    <row r="55" ht="19.5" customHeight="1"/>
-    <row r="56" ht="19.5" customHeight="1">
-      <c r="A56" s="27" t="inlineStr">
+    <row r="55" ht="19.5" customHeight="1">
+      <c r="B55" s="40" t="inlineStr">
+        <is>
+          <t>レスポンス（失敗 403 Dokusya Read Only）</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="72" customHeight="1">
+      <c r="C56" s="19" t="inlineStr">
+        <is>
+          <t>{
+  "error_code": "DOKUSYA_READ_ONLY",
+  "message": "この購読者は編集・削除できません。（電子版クレジットカード決済者・併読者は読み取り専用）"
+}</t>
+        </is>
+      </c>
+      <c r="D56" s="10" t="n"/>
+      <c r="E56" s="10" t="n"/>
+      <c r="F56" s="10" t="n"/>
+      <c r="G56" s="10" t="n"/>
+      <c r="H56" s="10" t="n"/>
+      <c r="I56" s="10" t="n"/>
+      <c r="J56" s="10" t="n"/>
+      <c r="K56" s="10" t="n"/>
+      <c r="L56" s="10" t="n"/>
+      <c r="M56" s="10" t="n"/>
+      <c r="N56" s="10" t="n"/>
+      <c r="O56" s="10" t="n"/>
+      <c r="P56" s="10" t="n"/>
+      <c r="Q56" s="10" t="n"/>
+      <c r="R56" s="10" t="n"/>
+      <c r="S56" s="10" t="n"/>
+      <c r="T56" s="10" t="n"/>
+      <c r="U56" s="10" t="n"/>
+      <c r="V56" s="10" t="n"/>
+      <c r="W56" s="10" t="n"/>
+      <c r="X56" s="10" t="n"/>
+      <c r="Y56" s="10" t="n"/>
+      <c r="Z56" s="10" t="n"/>
+      <c r="AA56" s="10" t="n"/>
+      <c r="AB56" s="10" t="n"/>
+      <c r="AC56" s="10" t="n"/>
+      <c r="AD56" s="10" t="n"/>
+      <c r="AE56" s="10" t="n"/>
+      <c r="AF56" s="10" t="n"/>
+      <c r="AG56" s="10" t="n"/>
+      <c r="AH56" s="10" t="n"/>
+      <c r="AI56" s="10" t="n"/>
+      <c r="AJ56" s="10" t="n"/>
+      <c r="AK56" s="11" t="n"/>
+    </row>
+    <row r="58" ht="19.5" customHeight="1">
+      <c r="B58" s="40" t="inlineStr">
+        <is>
+          <t>レスポンス（失敗 404 Not Found）</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="72" customHeight="1">
+      <c r="C59" s="19" t="inlineStr">
+        <is>
+          <t>{
+  "error_code": "NOT_FOUND",
+  "message": "指定された購読者が見つかりません。"
+}</t>
+        </is>
+      </c>
+      <c r="D59" s="10" t="n"/>
+      <c r="E59" s="10" t="n"/>
+      <c r="F59" s="10" t="n"/>
+      <c r="G59" s="10" t="n"/>
+      <c r="H59" s="10" t="n"/>
+      <c r="I59" s="10" t="n"/>
+      <c r="J59" s="10" t="n"/>
+      <c r="K59" s="10" t="n"/>
+      <c r="L59" s="10" t="n"/>
+      <c r="M59" s="10" t="n"/>
+      <c r="N59" s="10" t="n"/>
+      <c r="O59" s="10" t="n"/>
+      <c r="P59" s="10" t="n"/>
+      <c r="Q59" s="10" t="n"/>
+      <c r="R59" s="10" t="n"/>
+      <c r="S59" s="10" t="n"/>
+      <c r="T59" s="10" t="n"/>
+      <c r="U59" s="10" t="n"/>
+      <c r="V59" s="10" t="n"/>
+      <c r="W59" s="10" t="n"/>
+      <c r="X59" s="10" t="n"/>
+      <c r="Y59" s="10" t="n"/>
+      <c r="Z59" s="10" t="n"/>
+      <c r="AA59" s="10" t="n"/>
+      <c r="AB59" s="10" t="n"/>
+      <c r="AC59" s="10" t="n"/>
+      <c r="AD59" s="10" t="n"/>
+      <c r="AE59" s="10" t="n"/>
+      <c r="AF59" s="10" t="n"/>
+      <c r="AG59" s="10" t="n"/>
+      <c r="AH59" s="10" t="n"/>
+      <c r="AI59" s="10" t="n"/>
+      <c r="AJ59" s="10" t="n"/>
+      <c r="AK59" s="11" t="n"/>
+    </row>
+    <row r="61" ht="19.5" customHeight="1"/>
+    <row r="62" ht="19.5" customHeight="1">
+      <c r="A62" s="27" t="inlineStr">
         <is>
           <t>4. 処理手順</t>
         </is>
       </c>
     </row>
-    <row r="57" ht="54" customHeight="1">
-      <c r="B57" s="42" t="inlineStr">
+    <row r="63" ht="54" customHeight="1">
+      <c r="B63" s="42" t="inlineStr">
         <is>
           <t>※ 解約予約行の挿入 と 操作ログ記録 は単一トランザクション内で実行する。
 いずれかが失敗した場合は全てロールバックすること。
 例外処理中のエラーログ（log_type=3）はトランザクション外で別途記録する。</t>
         </is>
       </c>
-      <c r="C57" s="10" t="n"/>
-      <c r="D57" s="10" t="n"/>
-      <c r="E57" s="10" t="n"/>
-      <c r="F57" s="10" t="n"/>
-      <c r="G57" s="10" t="n"/>
-      <c r="H57" s="10" t="n"/>
-      <c r="I57" s="10" t="n"/>
-      <c r="J57" s="10" t="n"/>
-      <c r="K57" s="10" t="n"/>
-      <c r="L57" s="10" t="n"/>
-      <c r="M57" s="10" t="n"/>
-      <c r="N57" s="10" t="n"/>
-      <c r="O57" s="10" t="n"/>
-      <c r="P57" s="10" t="n"/>
-      <c r="Q57" s="10" t="n"/>
-      <c r="R57" s="10" t="n"/>
-      <c r="S57" s="10" t="n"/>
-      <c r="T57" s="10" t="n"/>
-      <c r="U57" s="10" t="n"/>
-      <c r="V57" s="10" t="n"/>
-      <c r="W57" s="10" t="n"/>
-      <c r="X57" s="10" t="n"/>
-      <c r="Y57" s="10" t="n"/>
-      <c r="Z57" s="10" t="n"/>
-      <c r="AA57" s="10" t="n"/>
-      <c r="AB57" s="10" t="n"/>
-      <c r="AC57" s="10" t="n"/>
-      <c r="AD57" s="10" t="n"/>
-      <c r="AE57" s="10" t="n"/>
-      <c r="AF57" s="10" t="n"/>
-      <c r="AG57" s="10" t="n"/>
-      <c r="AH57" s="10" t="n"/>
-      <c r="AI57" s="10" t="n"/>
-      <c r="AJ57" s="10" t="n"/>
-      <c r="AK57" s="11" t="n"/>
-    </row>
-    <row r="58" ht="18" customHeight="1">
-      <c r="B58" s="27" t="inlineStr">
+      <c r="C63" s="10" t="n"/>
+      <c r="D63" s="10" t="n"/>
+      <c r="E63" s="10" t="n"/>
+      <c r="F63" s="10" t="n"/>
+      <c r="G63" s="10" t="n"/>
+      <c r="H63" s="10" t="n"/>
+      <c r="I63" s="10" t="n"/>
+      <c r="J63" s="10" t="n"/>
+      <c r="K63" s="10" t="n"/>
+      <c r="L63" s="10" t="n"/>
+      <c r="M63" s="10" t="n"/>
+      <c r="N63" s="10" t="n"/>
+      <c r="O63" s="10" t="n"/>
+      <c r="P63" s="10" t="n"/>
+      <c r="Q63" s="10" t="n"/>
+      <c r="R63" s="10" t="n"/>
+      <c r="S63" s="10" t="n"/>
+      <c r="T63" s="10" t="n"/>
+      <c r="U63" s="10" t="n"/>
+      <c r="V63" s="10" t="n"/>
+      <c r="W63" s="10" t="n"/>
+      <c r="X63" s="10" t="n"/>
+      <c r="Y63" s="10" t="n"/>
+      <c r="Z63" s="10" t="n"/>
+      <c r="AA63" s="10" t="n"/>
+      <c r="AB63" s="10" t="n"/>
+      <c r="AC63" s="10" t="n"/>
+      <c r="AD63" s="10" t="n"/>
+      <c r="AE63" s="10" t="n"/>
+      <c r="AF63" s="10" t="n"/>
+      <c r="AG63" s="10" t="n"/>
+      <c r="AH63" s="10" t="n"/>
+      <c r="AI63" s="10" t="n"/>
+      <c r="AJ63" s="10" t="n"/>
+      <c r="AK63" s="11" t="n"/>
+    </row>
+    <row r="64" ht="18" customHeight="1">
+      <c r="B64" s="27" t="inlineStr">
         <is>
           <t>4.1 リクエストのバリデーション</t>
         </is>
       </c>
     </row>
-    <row r="59" ht="18" customHeight="1">
-      <c r="C59" s="41" t="inlineStr">
+    <row r="65" ht="18" customHeight="1">
+      <c r="C65" s="41" t="inlineStr">
         <is>
           <t>パスパラメータ：dokusya_id の数値型チェック・必須チェック。</t>
         </is>
       </c>
     </row>
-    <row r="60" ht="36" customHeight="1">
-      <c r="C60" s="41" t="inlineStr">
-        <is>
-          <t>ボディ：dokusya_chushi_date の必須チェック・`YYYY-MM-DD` フォーマットチェック。</t>
-        </is>
-      </c>
-    </row>
-    <row r="61" ht="36" customHeight="1">
-      <c r="C61" s="41" t="inlineStr">
+    <row r="66" ht="36" customHeight="1">
+      <c r="C66" s="41" t="inlineStr">
+        <is>
+          <t>ボディ：dokusya_chushi_date の型チェック・`YYYY-MM-DD` フォーマットチェック（空文字は許容＝予約取消。「空文字を送ってよいか」は 4.4 で購読種別ごとに判定する）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="36" customHeight="1">
+      <c r="C67" s="41" t="inlineStr">
         <is>
           <t>不正な場合：HTTP 400（`BAD_REQUEST` / `VALIDATION_ERROR`）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="62" ht="18" customHeight="1">
-      <c r="B62" s="27" t="inlineStr">
-        <is>
-          <t>4.2 認証・認可チェック</t>
-        </is>
-      </c>
-    </row>
-    <row r="63" ht="36" customHeight="1">
-      <c r="C63" s="41" t="inlineStr">
-        <is>
-          <t>認証情報を検証する（HTTP-only Cookieセッション）。未認証：HTTP 401（`UNAUTHORIZED`）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="64" ht="18" customHeight="1">
-      <c r="C64" s="41" t="inlineStr">
-        <is>
-          <t>必要権限: `dokusya.update`。権限不足：HTTP 403（`FORBIDDEN`）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="65" ht="36" customHeight="1">
-      <c r="C65" s="41" t="inlineStr">
-        <is>
-          <t>DataScope（削除と同じ境界）：CHUOKAI=自中央会管轄JA / JA_HONTEN=自JA / JA_KANRI_SHITEN=自管理支店。範囲外は 404 でマスク。</t>
-        </is>
-      </c>
-    </row>
-    <row r="66" ht="18" customHeight="1">
-      <c r="B66" s="27" t="inlineStr">
-        <is>
-          <t>4.3 読み取り専用判定</t>
-        </is>
-      </c>
-    </row>
-    <row r="67" ht="54" customHeight="1">
-      <c r="C67" s="41" t="inlineStr">
-        <is>
-          <t>併読（dokusya_shubetsu=3）または 電子版クレカ決済者（dokusya_shubetsu=2 かつ shiharai_hoho=6）は編集不可 → HTTP 403（`DOKUSYA_READ_ONLY`）。</t>
         </is>
       </c>
     </row>
     <row r="68" ht="18" customHeight="1">
       <c r="B68" s="27" t="inlineStr">
         <is>
-          <t>4.4 停止（解約予約）バリデーション</t>
+          <t>4.2 認証・認可チェック</t>
         </is>
       </c>
     </row>
     <row r="69" ht="36" customHeight="1">
       <c r="C69" s="41" t="inlineStr">
         <is>
-          <t>二重解約ガード：有効な解約予約（購読中止日が入った取消されていない履歴行）が既にある場合は 400（`VALIDATION_ERROR` / 既に解約予約されています…）。</t>
+          <t>認証情報を検証する（HTTP-only Cookieセッション）。未認証：HTTP 401（`UNAUTHORIZED`）。</t>
         </is>
       </c>
     </row>
     <row r="70" ht="18" customHeight="1">
       <c r="C70" s="41" t="inlineStr">
         <is>
-          <t>紙版（dokusya_shubetsu=1）：</t>
-        </is>
-      </c>
-    </row>
-    <row r="71" ht="18" customHeight="1">
-      <c r="D71" s="41" t="inlineStr">
-        <is>
-          <t>解約予定日 &gt;= 購読開始日</t>
+          <t>必要権限: `dokusya.update`。権限不足：HTTP 403（`FORBIDDEN`）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="36" customHeight="1">
+      <c r="C71" s="41" t="inlineStr">
+        <is>
+          <t>DataScope（削除と同じ境界）：CHUOKAI=自中央会管轄JA / JA_HONTEN=自JA / JA_KANRI_SHITEN=自管理支店。範囲外は 404 でマスク。</t>
         </is>
       </c>
     </row>
     <row r="72" ht="18" customHeight="1">
-      <c r="D72" s="41" t="inlineStr">
-        <is>
-          <t>解約予定日 &gt; 本日（未来日のみ）</t>
-        </is>
-      </c>
-    </row>
-    <row r="73" ht="18" customHeight="1">
-      <c r="D73" s="41" t="inlineStr">
-        <is>
-          <t>解約予定日 &gt; 最終変更適用日（履歴 MAX joho・同日不可）</t>
+      <c r="B72" s="27" t="inlineStr">
+        <is>
+          <t>4.3 読み取り専用判定</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="54" customHeight="1">
+      <c r="C73" s="41" t="inlineStr">
+        <is>
+          <t>併読（dokusya_shubetsu=3）または 電子版クレカ決済者（dokusya_shubetsu=2 かつ shiharai_hoho=6）は編集不可 → HTTP 403（`DOKUSYA_READ_ONLY`）。</t>
         </is>
       </c>
     </row>
     <row r="74" ht="18" customHeight="1">
-      <c r="C74" s="41" t="inlineStr">
-        <is>
-          <t>電子版（dokusya_shubetsu=2）：</t>
-        </is>
-      </c>
-    </row>
-    <row r="75" ht="36" customHeight="1">
-      <c r="D75" s="41" t="inlineStr">
-        <is>
-          <t>請求開始月（seikyu_kaishi_month）が未設定なら停止不可（`この読者料金の徴収はまだ開始されていません。`）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="76" ht="36" customHeight="1">
-      <c r="D76" s="41" t="inlineStr">
-        <is>
-          <t>選択月（中止日の YYYYMM）は 請求開始月以降 かつ 当月以降。中止日は選択月の月末日（FE が丸めて送る）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="77" ht="18" customHeight="1">
-      <c r="B77" s="27" t="inlineStr">
-        <is>
-          <t>4.5 解約予約行の挿入</t>
-        </is>
-      </c>
-    </row>
-    <row r="78" ht="90" customHeight="1">
-      <c r="C78" s="41" t="inlineStr">
-        <is>
-          <t>Phase 1 の予約行を1件挿入する（`insertScheduledKaiyaku`）。最小限のみ override：`部数=0`・`zougen_hokoku_flg=true`・`中止日`・`適用日=中止日`・`kaiyaku_flg=false`・`saishin_data_flg=false`・`shinki_flg=false`・`torikeshi_flg=false`。その他項目は直前行から継承。</t>
-        </is>
-      </c>
-    </row>
-    <row r="79" ht="18" customHeight="1">
-      <c r="C79" s="41" t="inlineStr">
-        <is>
-          <t>未来日予約のため当日時点で t_dokusya は未反映（到来日バッチが確定）。</t>
+      <c r="B74" s="27" t="inlineStr">
+        <is>
+          <t>4.4 停止（解約予約 / 予約変更 / 予約取消）バリデーション</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="54" customHeight="1">
+      <c r="C75" s="41" t="inlineStr">
+        <is>
+          <t>**確定済みガード（種別共通）**：その行が `kaiyaku_flg=true`（到来日バッチが確定させた実解約行）なら 400（`解約が確定済みのため変更できません。…`）。以降の復帰は再購読（SCR-011）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="18" customHeight="1">
+      <c r="C76" s="41" t="inlineStr">
+        <is>
+          <t>**紙版（dokusya_shubetsu=1）**：</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="36" customHeight="1">
+      <c r="D77" s="41" t="inlineStr">
+        <is>
+          <t>空文字（取消）は受け付けない → 400（`購読中止日を入力してください。`）。変更・取消は履歴画面の取消（赤伝）が既存導線。</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="36" customHeight="1">
+      <c r="D78" s="41" t="inlineStr">
+        <is>
+          <t>予約が既にある場合は 400（`既に解約予約されています。変更する場合は履歴画面で解約を取消してください。`）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="36" customHeight="1">
+      <c r="D79" s="41" t="inlineStr">
+        <is>
+          <t>日付：解約予定日 &gt;= 購読開始日 ／ 解約予定日 &gt; 本日（未来日のみ）／ 解約予定日 &gt; 最終変更適用日（履歴 MAX joho・同日不可）。</t>
         </is>
       </c>
     </row>
     <row r="80" ht="18" customHeight="1">
-      <c r="B80" s="27" t="inlineStr">
-        <is>
-          <t>4.6 操作ログ記録</t>
-        </is>
-      </c>
-    </row>
-    <row r="81" ht="54" customHeight="1">
-      <c r="C81" s="41" t="inlineStr">
-        <is>
-          <t>`log_type=1`（USER_OPERATION）、`gamen_name='購読者明細検索画面 (ACSMS-SCR-014)'`、`operation='UPDATE'`、`target_table='t_dokusya'` で記録する（主DMLと同一トランザクション）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="82" ht="18" customHeight="1">
-      <c r="B82" s="27" t="inlineStr">
-        <is>
-          <t>4.7 レスポンス生成</t>
+      <c r="C80" s="41" t="inlineStr">
+        <is>
+          <t>**電子版（dokusya_shubetsu=2）**：</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="36" customHeight="1">
+      <c r="D81" s="41" t="inlineStr">
+        <is>
+          <t>空文字（取消）で予約が無い場合は 400（`解約予約がありません。画面を再読み込みしてください。`）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="54" customHeight="1">
+      <c r="D82" s="41" t="inlineStr">
+        <is>
+          <t>空文字以外のとき：請求開始月（seikyu_kaishi_month）が未設定なら停止不可（`この読者料金の徴収はまだ開始されていません。`）。選択月（中止日の YYYYMM）は 請求開始月以降 かつ 当月以降。中止日は選択月の月末日（FE が丸めて送る）。</t>
         </is>
       </c>
     </row>
     <row r="83" ht="36" customHeight="1">
-      <c r="C83" s="41" t="inlineStr">
-        <is>
-          <t>更新後の購読者詳細（ACSMS-API-011-001 と同型）を `data` に、`message: '購読停止を予約しました。'` を返す。HTTP 200。</t>
+      <c r="D83" s="41" t="inlineStr">
+        <is>
+          <t>予約が既にあっても拒否しない（＝予約変更・予約取消を受け付ける）。電子版は履歴画面の取消が購読種別で禁止されており、本エンドポイントが唯一の変更・取消導線であるため。</t>
         </is>
       </c>
     </row>
     <row r="84" ht="18" customHeight="1">
       <c r="B84" s="27" t="inlineStr">
         <is>
+          <t>4.5 解約予約行の挿入 / 旧予約の取消</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="72" customHeight="1">
+      <c r="C85" s="41" t="inlineStr">
+        <is>
+          <t>**旧予約の取消（予約変更・予約取消のみ）**：対象行に `torikeshi_flg=true` を立て、打ち消し行を append する（両行とも `torikeshi_flg=true`）。取消理由は両行の備考へ記録。残る `torikeshi_flg=false` 行で master を再計算するため、master の購読中止日は自動的に null へ戻る。</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="90" customHeight="1">
+      <c r="C86" s="41" t="inlineStr">
+        <is>
+          <t>**新予約の挿入（新規予約・予約変更のみ）**：Phase 1 の予約行を1件挿入する（`insertScheduledKaiyaku`）。最小限のみ override：`部数=0`・`zougen_hokoku_flg=true`・`中止日`・`適用日=中止日`・`kaiyaku_flg=false`・`saishin_data_flg=false`・`shinki_flg=false`・`torikeshi_flg=false`。その他項目は直前行から継承。</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="36" customHeight="1">
+      <c r="C87" s="41" t="inlineStr">
+        <is>
+          <t>未来日予約のため当日時点で t_dokusya は未反映（到来日バッチが確定）。ただし購読中止日のみ予約時点で master へ反映する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="18" customHeight="1">
+      <c r="B88" s="27" t="inlineStr">
+        <is>
+          <t>4.5.1 電子版システムへの連携（push）</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="36" customHeight="1">
+      <c r="C89" s="41" t="inlineStr">
+        <is>
+          <t>対象（電子版・非クレカ・非キャンペーン単価・push 有効）の場合、同一トランザクション内で電子版 `updateUserInfo` に `action_kbn=cancel` を送る。</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="36" customHeight="1">
+      <c r="D90" s="41" t="inlineStr">
+        <is>
+          <t>新規予約・予約変更：`cancel_ym` = 購読中止日の `YYYYMM`。変更時は新しい月で再送し、電子版側の解約月を上書きさせる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="54" customHeight="1">
+      <c r="D91" s="41" t="inlineStr">
+        <is>
+          <t>予約取消：`cancel_ym` = 空文字。電子版APIの `action_kbn` は create/update/reread/cancel/approve/unapprove の6種のみで解約取消専用の処理区分が存在しないため、この形で送る（顧客判断 2026-08）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="36" customHeight="1">
+      <c r="C92" s="41" t="inlineStr">
+        <is>
+          <t>push が失敗した場合は例外を送出し、予約行・master・操作ログもろともロールバックする（同期 Saga）。クラウド側だけ取消済みという食い違いは発生しない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" ht="18" customHeight="1">
+      <c r="B93" s="27" t="inlineStr">
+        <is>
+          <t>4.6 操作ログ記録</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="54" customHeight="1">
+      <c r="C94" s="41" t="inlineStr">
+        <is>
+          <t>`log_type=1`（USER_OPERATION）、`gamen_name='購読者明細検索画面 (ACSMS-SCR-014)'`、`operation='UPDATE'`、`target_table='t_dokusya'` で記録する（主DMLと同一トランザクション）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="18" customHeight="1">
+      <c r="B95" s="27" t="inlineStr">
+        <is>
+          <t>4.7 レスポンス生成</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" ht="36" customHeight="1">
+      <c r="C96" s="41" t="inlineStr">
+        <is>
+          <t>更新後の購読者詳細（ACSMS-API-011-001 と同型）を `data` に、`message` を返す。HTTP 200。</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" ht="18" customHeight="1">
+      <c r="D97" s="41" t="inlineStr">
+        <is>
+          <t>新規予約・予約変更：`'購読停止を予約しました。'`</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" ht="18" customHeight="1">
+      <c r="D98" s="41" t="inlineStr">
+        <is>
+          <t>予約取消：`'購読中止を取り消しました。'`</t>
+        </is>
+      </c>
+    </row>
+    <row r="99" ht="18" customHeight="1">
+      <c r="B99" s="27" t="inlineStr">
+        <is>
           <t>4.8 例外処理</t>
         </is>
       </c>
     </row>
-    <row r="85" ht="18" customHeight="1">
-      <c r="C85" s="41" t="inlineStr">
+    <row r="100" ht="18" customHeight="1">
+      <c r="C100" s="41" t="inlineStr">
         <is>
           <t>DB エラー等の場合：HTTP 500（`INTERNAL_SERVER_ERROR`）。</t>
         </is>
       </c>
     </row>
-    <row r="86" ht="18" customHeight="1">
-      <c r="C86" s="41" t="inlineStr">
+    <row r="101" ht="18" customHeight="1">
+      <c r="C101" s="41" t="inlineStr">
         <is>
           <t>エラー発生時も操作ログを記録する（`log_type=3`、トランザクション外）。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="130">
+  <mergeCells count="143">
     <mergeCell ref="J11:AK11"/>
+    <mergeCell ref="D78:AK78"/>
+    <mergeCell ref="C66:AK66"/>
     <mergeCell ref="T24:X24"/>
     <mergeCell ref="C53:AK53"/>
-    <mergeCell ref="D71:AK71"/>
     <mergeCell ref="Q31:S31"/>
     <mergeCell ref="M32:P32"/>
     <mergeCell ref="N18:AK18"/>
@@ -17002,50 +17240,59 @@
     <mergeCell ref="J12:AK12"/>
     <mergeCell ref="N17:AK17"/>
     <mergeCell ref="J17:M17"/>
-    <mergeCell ref="D73:AK73"/>
+    <mergeCell ref="D82:AK82"/>
     <mergeCell ref="B8:I8"/>
     <mergeCell ref="N19:AK19"/>
     <mergeCell ref="J19:M19"/>
     <mergeCell ref="C85:AK85"/>
+    <mergeCell ref="C100:AK100"/>
     <mergeCell ref="J1:P1"/>
     <mergeCell ref="AH2:AK3"/>
     <mergeCell ref="Y24:AB24"/>
     <mergeCell ref="C65:AK65"/>
+    <mergeCell ref="C94:AK94"/>
     <mergeCell ref="C44:AK44"/>
     <mergeCell ref="Q1:U1"/>
+    <mergeCell ref="C75:AK75"/>
     <mergeCell ref="B10:I10"/>
+    <mergeCell ref="C80:AK80"/>
     <mergeCell ref="Q25:S25"/>
     <mergeCell ref="J2:P3"/>
+    <mergeCell ref="B63:AK63"/>
     <mergeCell ref="B9:I9"/>
     <mergeCell ref="T31:X31"/>
     <mergeCell ref="N20:AK20"/>
+    <mergeCell ref="D77:AK77"/>
     <mergeCell ref="M25:P25"/>
     <mergeCell ref="C70:AK70"/>
     <mergeCell ref="Y25:AB25"/>
-    <mergeCell ref="D75:AK75"/>
-    <mergeCell ref="B66:AK66"/>
     <mergeCell ref="C38:AK38"/>
     <mergeCell ref="T30:X30"/>
-    <mergeCell ref="D72:AK72"/>
-    <mergeCell ref="B77:AK77"/>
+    <mergeCell ref="B93:AK93"/>
     <mergeCell ref="C32:L32"/>
     <mergeCell ref="Z1:AC1"/>
     <mergeCell ref="B46:I46"/>
+    <mergeCell ref="C101:AK101"/>
     <mergeCell ref="N14:AK14"/>
     <mergeCell ref="B12:I12"/>
-    <mergeCell ref="C74:AK74"/>
+    <mergeCell ref="D98:AK98"/>
     <mergeCell ref="AF32:AK32"/>
     <mergeCell ref="C35:AK35"/>
     <mergeCell ref="Z2:AC3"/>
     <mergeCell ref="AF26:AK26"/>
     <mergeCell ref="C24:L24"/>
+    <mergeCell ref="D79:AK79"/>
     <mergeCell ref="AD2:AG3"/>
     <mergeCell ref="B13:I13"/>
     <mergeCell ref="Q32:S32"/>
     <mergeCell ref="C26:L26"/>
+    <mergeCell ref="D81:AK81"/>
     <mergeCell ref="Y30:AE30"/>
+    <mergeCell ref="D90:AK90"/>
+    <mergeCell ref="B64:AK64"/>
     <mergeCell ref="J13:AK13"/>
     <mergeCell ref="B14:I20"/>
+    <mergeCell ref="B95:AK95"/>
     <mergeCell ref="B49:I49"/>
     <mergeCell ref="C59:AK59"/>
     <mergeCell ref="C25:L25"/>
@@ -17056,70 +17303,73 @@
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="J20:M20"/>
     <mergeCell ref="Y31:AE31"/>
-    <mergeCell ref="C61:AK61"/>
-    <mergeCell ref="D76:AK76"/>
-    <mergeCell ref="C81:AK81"/>
-    <mergeCell ref="B58:AK58"/>
     <mergeCell ref="AF25:AK25"/>
     <mergeCell ref="J7:AK7"/>
-    <mergeCell ref="C78:AK78"/>
+    <mergeCell ref="C96:AK96"/>
     <mergeCell ref="T32:X32"/>
+    <mergeCell ref="C87:AK87"/>
     <mergeCell ref="A5:AK5"/>
     <mergeCell ref="AF30:AK30"/>
-    <mergeCell ref="B57:AK57"/>
     <mergeCell ref="AC25:AE25"/>
     <mergeCell ref="B11:I11"/>
+    <mergeCell ref="C89:AK89"/>
     <mergeCell ref="Q2:U3"/>
-    <mergeCell ref="C64:AK64"/>
     <mergeCell ref="C30:L30"/>
     <mergeCell ref="Q30:S30"/>
-    <mergeCell ref="C79:AK79"/>
+    <mergeCell ref="C73:AK73"/>
     <mergeCell ref="J8:AK8"/>
     <mergeCell ref="AF31:AK31"/>
-    <mergeCell ref="C63:AK63"/>
     <mergeCell ref="C41:AK41"/>
     <mergeCell ref="B84:AK84"/>
     <mergeCell ref="C50:AK50"/>
     <mergeCell ref="T26:X26"/>
     <mergeCell ref="J10:AK10"/>
     <mergeCell ref="N15:AK15"/>
+    <mergeCell ref="C56:AK56"/>
     <mergeCell ref="V1:Y1"/>
-    <mergeCell ref="B80:AK80"/>
     <mergeCell ref="J9:AK9"/>
     <mergeCell ref="B40:I40"/>
     <mergeCell ref="AH1:AK1"/>
     <mergeCell ref="M31:P31"/>
+    <mergeCell ref="B55:I55"/>
     <mergeCell ref="V2:Y3"/>
     <mergeCell ref="N16:AK16"/>
     <mergeCell ref="J16:M16"/>
-    <mergeCell ref="A56:AK56"/>
+    <mergeCell ref="B72:AK72"/>
     <mergeCell ref="C67:AK67"/>
+    <mergeCell ref="D91:AK91"/>
     <mergeCell ref="AC24:AE24"/>
     <mergeCell ref="B7:I7"/>
     <mergeCell ref="M26:P26"/>
     <mergeCell ref="Q26:S26"/>
     <mergeCell ref="M24:P24"/>
     <mergeCell ref="C69:AK69"/>
-    <mergeCell ref="C83:AK83"/>
     <mergeCell ref="AC26:AE26"/>
+    <mergeCell ref="C92:AK92"/>
     <mergeCell ref="A22:AK22"/>
     <mergeCell ref="B43:I43"/>
+    <mergeCell ref="B58:I58"/>
     <mergeCell ref="B52:I52"/>
     <mergeCell ref="Y32:AE32"/>
+    <mergeCell ref="A62:AK62"/>
+    <mergeCell ref="D83:AK83"/>
     <mergeCell ref="T25:X25"/>
-    <mergeCell ref="B82:AK82"/>
+    <mergeCell ref="B88:AK88"/>
     <mergeCell ref="A28:AK28"/>
     <mergeCell ref="J14:M14"/>
     <mergeCell ref="C47:AK47"/>
+    <mergeCell ref="B99:AK99"/>
+    <mergeCell ref="B74:AK74"/>
     <mergeCell ref="B68:AK68"/>
     <mergeCell ref="B34:I34"/>
     <mergeCell ref="B37:I37"/>
     <mergeCell ref="J15:M15"/>
     <mergeCell ref="AD1:AG1"/>
-    <mergeCell ref="C60:AK60"/>
     <mergeCell ref="C31:L31"/>
+    <mergeCell ref="C71:AK71"/>
+    <mergeCell ref="C76:AK76"/>
     <mergeCell ref="M30:P30"/>
-    <mergeCell ref="B62:AK62"/>
+    <mergeCell ref="D97:AK97"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/design/ACSMS-SCR-014/【日本農業新聞様】VTIジャパン_クラウド版購読者管理システム_API設計書_購読者明細検索画面_V1.0.xlsx
+++ b/docs/design/ACSMS-SCR-014/【日本農業新聞様】VTIジャパン_クラウド版購読者管理システム_API設計書_購読者明細検索画面_V1.0.xlsx
@@ -2296,7 +2296,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/08/03</t>
+          <t>2026/08/04</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -2812,7 +2812,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/08/03</t>
+          <t>2026/08/04</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -3798,7 +3798,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/08/03</t>
+          <t>2026/08/04</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -4198,7 +4198,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK184"/>
+  <dimension ref="A1:AK185"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="4.25" customWidth="1" min="1" max="1"/>
@@ -4359,7 +4359,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/08/03</t>
+          <t>2026/08/04</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -7992,7 +7992,7 @@
       <c r="X74" s="11" t="n"/>
       <c r="Y74" s="17" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>〇</t>
         </is>
       </c>
       <c r="Z74" s="10" t="n"/>
@@ -8003,7 +8003,7 @@
       <c r="AE74" s="11" t="n"/>
       <c r="AF74" s="19" t="inlineStr">
         <is>
-          <t>販売店ID</t>
+          <t>販売店ID※未設定(NULL)あり</t>
         </is>
       </c>
       <c r="AG74" s="10" t="n"/>
@@ -8440,7 +8440,7 @@
       <c r="AJ81" s="10" t="n"/>
       <c r="AK81" s="11" t="n"/>
     </row>
-    <row r="82" ht="36" customHeight="1">
+    <row r="82" ht="72" customHeight="1">
       <c r="B82" s="31" t="n">
         <v>24</v>
       </c>
@@ -8491,7 +8491,7 @@
       <c r="AE82" s="11" t="n"/>
       <c r="AF82" s="19" t="inlineStr">
         <is>
-          <t>編集・削除不可フラグ（true=電子版クレジットカード決済者または併読者）</t>
+          <t>編集・削除不可フラグ（true=電子版クレジットカード決済者または併読者）。※削除ボタンの活性判定はこれに加えて `dokusya_shubetsu = 1`（紙版）も必要（顧客要件2026-08）</t>
         </is>
       </c>
       <c r="AG82" s="10" t="n"/>
@@ -9842,22 +9842,29 @@
         </is>
       </c>
     </row>
-    <row r="183" ht="18" customHeight="1">
-      <c r="B183" s="27" t="inlineStr">
+    <row r="183" ht="36" customHeight="1">
+      <c r="C183" s="41" t="inlineStr">
+        <is>
+          <t>「削除」ボタンは `is_read_only` に加えて `dokusya_shubetsu = 1`（紙版）のときだけ活性にする（顧客要件2026-08）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="184" ht="18" customHeight="1">
+      <c r="B184" s="27" t="inlineStr">
         <is>
           <t>4.7 例外処理</t>
         </is>
       </c>
     </row>
-    <row r="184" ht="18" customHeight="1">
-      <c r="C184" s="41" t="inlineStr">
+    <row r="185" ht="18" customHeight="1">
+      <c r="C185" s="41" t="inlineStr">
         <is>
           <t>DB接続エラー等の場合：HTTP 500 (`INTERNAL_SERVER_ERROR`)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="542">
+  <mergeCells count="543">
     <mergeCell ref="Y46:AB46"/>
     <mergeCell ref="AF65:AK65"/>
     <mergeCell ref="T24:X24"/>
@@ -9920,6 +9927,7 @@
     <mergeCell ref="T69:X69"/>
     <mergeCell ref="D65:L65"/>
     <mergeCell ref="M27:P27"/>
+    <mergeCell ref="B184:AK184"/>
     <mergeCell ref="AF25:AK25"/>
     <mergeCell ref="Q35:S35"/>
     <mergeCell ref="C145:AK145"/>
@@ -10024,7 +10032,6 @@
     <mergeCell ref="C42:L42"/>
     <mergeCell ref="D115:AK115"/>
     <mergeCell ref="AF52:AK52"/>
-    <mergeCell ref="B183:AK183"/>
     <mergeCell ref="T84:X84"/>
     <mergeCell ref="T22:X22"/>
     <mergeCell ref="AF34:AK34"/>
@@ -10119,6 +10126,7 @@
     <mergeCell ref="AC50:AE50"/>
     <mergeCell ref="D117:AK117"/>
     <mergeCell ref="AF76:AK76"/>
+    <mergeCell ref="C185:AK185"/>
     <mergeCell ref="Q74:S74"/>
     <mergeCell ref="T62:X62"/>
     <mergeCell ref="D132:AK132"/>
@@ -10161,6 +10169,7 @@
     <mergeCell ref="AC40:AE40"/>
     <mergeCell ref="D71:L71"/>
     <mergeCell ref="C34:L34"/>
+    <mergeCell ref="C183:AK183"/>
     <mergeCell ref="Y62:AE62"/>
     <mergeCell ref="D73:L73"/>
     <mergeCell ref="C133:AK133"/>
@@ -10362,7 +10371,6 @@
     <mergeCell ref="AC34:AE34"/>
     <mergeCell ref="M50:P50"/>
     <mergeCell ref="M68:P68"/>
-    <mergeCell ref="C184:AK184"/>
     <mergeCell ref="C171:AK171"/>
     <mergeCell ref="M67:P67"/>
     <mergeCell ref="M48:P48"/>
@@ -10411,7 +10419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK93"/>
+  <dimension ref="A1:AK94"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="4.25" customWidth="1" min="1" max="1"/>
@@ -10572,7 +10580,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/08/03</t>
+          <t>2026/08/04</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -12154,26 +12162,33 @@
     <row r="79" ht="36" customHeight="1">
       <c r="C79" s="41" t="inlineStr">
         <is>
+          <t>**削除できるのは紙版のみ**（顧客要件2026-08）。`dokusya_shubetsu &lt;&gt; 1` の場合：HTTP 400 (`VALIDATION_ERROR`)</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="36" customHeight="1">
+      <c r="C80" s="41" t="inlineStr">
+        <is>
           <t>関連データの存在確認（将来の拡張に備えた整合性チェック）：関連テーブルに購読者IDが紐づくレコードが存在する場合、削除を拒否する。</t>
         </is>
       </c>
     </row>
-    <row r="80" ht="18" customHeight="1">
-      <c r="D80" s="41" t="inlineStr">
+    <row r="81" ht="18" customHeight="1">
+      <c r="D81" s="41" t="inlineStr">
         <is>
           <t>関連データが存在する場合：HTTP 409 (`CONFLICT`)</t>
         </is>
       </c>
     </row>
-    <row r="81" ht="18" customHeight="1">
-      <c r="B81" s="27" t="inlineStr">
+    <row r="82" ht="18" customHeight="1">
+      <c r="B82" s="27" t="inlineStr">
         <is>
           <t>4.4 論理削除の実行</t>
         </is>
       </c>
     </row>
-    <row r="82" ht="108" customHeight="1">
-      <c r="C82" s="42" t="inlineStr">
+    <row r="83" ht="108" customHeight="1">
+      <c r="C83" s="42" t="inlineStr">
         <is>
           <t>UPDATE t_dokusya
 SET deleted_at = NOW(),
@@ -12183,57 +12198,57 @@
   AND deleted_at IS NULL</t>
         </is>
       </c>
-      <c r="D82" s="10" t="n"/>
-      <c r="E82" s="10" t="n"/>
-      <c r="F82" s="10" t="n"/>
-      <c r="G82" s="10" t="n"/>
-      <c r="H82" s="10" t="n"/>
-      <c r="I82" s="10" t="n"/>
-      <c r="J82" s="10" t="n"/>
-      <c r="K82" s="10" t="n"/>
-      <c r="L82" s="10" t="n"/>
-      <c r="M82" s="10" t="n"/>
-      <c r="N82" s="10" t="n"/>
-      <c r="O82" s="10" t="n"/>
-      <c r="P82" s="10" t="n"/>
-      <c r="Q82" s="10" t="n"/>
-      <c r="R82" s="10" t="n"/>
-      <c r="S82" s="10" t="n"/>
-      <c r="T82" s="10" t="n"/>
-      <c r="U82" s="10" t="n"/>
-      <c r="V82" s="10" t="n"/>
-      <c r="W82" s="10" t="n"/>
-      <c r="X82" s="10" t="n"/>
-      <c r="Y82" s="10" t="n"/>
-      <c r="Z82" s="10" t="n"/>
-      <c r="AA82" s="10" t="n"/>
-      <c r="AB82" s="10" t="n"/>
-      <c r="AC82" s="10" t="n"/>
-      <c r="AD82" s="10" t="n"/>
-      <c r="AE82" s="10" t="n"/>
-      <c r="AF82" s="10" t="n"/>
-      <c r="AG82" s="10" t="n"/>
-      <c r="AH82" s="10" t="n"/>
-      <c r="AI82" s="10" t="n"/>
-      <c r="AJ82" s="10" t="n"/>
-      <c r="AK82" s="11" t="n"/>
-    </row>
-    <row r="83" ht="18" customHeight="1">
-      <c r="B83" s="27" t="inlineStr">
+      <c r="D83" s="10" t="n"/>
+      <c r="E83" s="10" t="n"/>
+      <c r="F83" s="10" t="n"/>
+      <c r="G83" s="10" t="n"/>
+      <c r="H83" s="10" t="n"/>
+      <c r="I83" s="10" t="n"/>
+      <c r="J83" s="10" t="n"/>
+      <c r="K83" s="10" t="n"/>
+      <c r="L83" s="10" t="n"/>
+      <c r="M83" s="10" t="n"/>
+      <c r="N83" s="10" t="n"/>
+      <c r="O83" s="10" t="n"/>
+      <c r="P83" s="10" t="n"/>
+      <c r="Q83" s="10" t="n"/>
+      <c r="R83" s="10" t="n"/>
+      <c r="S83" s="10" t="n"/>
+      <c r="T83" s="10" t="n"/>
+      <c r="U83" s="10" t="n"/>
+      <c r="V83" s="10" t="n"/>
+      <c r="W83" s="10" t="n"/>
+      <c r="X83" s="10" t="n"/>
+      <c r="Y83" s="10" t="n"/>
+      <c r="Z83" s="10" t="n"/>
+      <c r="AA83" s="10" t="n"/>
+      <c r="AB83" s="10" t="n"/>
+      <c r="AC83" s="10" t="n"/>
+      <c r="AD83" s="10" t="n"/>
+      <c r="AE83" s="10" t="n"/>
+      <c r="AF83" s="10" t="n"/>
+      <c r="AG83" s="10" t="n"/>
+      <c r="AH83" s="10" t="n"/>
+      <c r="AI83" s="10" t="n"/>
+      <c r="AJ83" s="10" t="n"/>
+      <c r="AK83" s="11" t="n"/>
+    </row>
+    <row r="84" ht="18" customHeight="1">
+      <c r="B84" s="27" t="inlineStr">
         <is>
           <t>4.5 操作ログ記録</t>
         </is>
       </c>
     </row>
-    <row r="84" ht="18" customHeight="1">
-      <c r="C84" s="41" t="inlineStr">
+    <row r="85" ht="18" customHeight="1">
+      <c r="C85" s="41" t="inlineStr">
         <is>
           <t>削除前データ（4.3 のSELECT結果）を `before_value` に格納する。</t>
         </is>
       </c>
     </row>
-    <row r="85" ht="144" customHeight="1">
-      <c r="C85" s="42" t="inlineStr">
+    <row r="86" ht="144" customHeight="1">
+      <c r="C86" s="42" t="inlineStr">
         <is>
           <t>INSERT INTO t_log (log_type, log_datetime, account_id, ja_id,
                    gamen_name, operation, result_status,
@@ -12243,61 +12258,6 @@
         '購読者明細検索画面 (ACSMS-SCR-014)', 'DELETE', 1,
         :dokusya_id, 't_dokusya', :before_value_json, '',
         :ip_address, :user_agent)</t>
-        </is>
-      </c>
-      <c r="D85" s="10" t="n"/>
-      <c r="E85" s="10" t="n"/>
-      <c r="F85" s="10" t="n"/>
-      <c r="G85" s="10" t="n"/>
-      <c r="H85" s="10" t="n"/>
-      <c r="I85" s="10" t="n"/>
-      <c r="J85" s="10" t="n"/>
-      <c r="K85" s="10" t="n"/>
-      <c r="L85" s="10" t="n"/>
-      <c r="M85" s="10" t="n"/>
-      <c r="N85" s="10" t="n"/>
-      <c r="O85" s="10" t="n"/>
-      <c r="P85" s="10" t="n"/>
-      <c r="Q85" s="10" t="n"/>
-      <c r="R85" s="10" t="n"/>
-      <c r="S85" s="10" t="n"/>
-      <c r="T85" s="10" t="n"/>
-      <c r="U85" s="10" t="n"/>
-      <c r="V85" s="10" t="n"/>
-      <c r="W85" s="10" t="n"/>
-      <c r="X85" s="10" t="n"/>
-      <c r="Y85" s="10" t="n"/>
-      <c r="Z85" s="10" t="n"/>
-      <c r="AA85" s="10" t="n"/>
-      <c r="AB85" s="10" t="n"/>
-      <c r="AC85" s="10" t="n"/>
-      <c r="AD85" s="10" t="n"/>
-      <c r="AE85" s="10" t="n"/>
-      <c r="AF85" s="10" t="n"/>
-      <c r="AG85" s="10" t="n"/>
-      <c r="AH85" s="10" t="n"/>
-      <c r="AI85" s="10" t="n"/>
-      <c r="AJ85" s="10" t="n"/>
-      <c r="AK85" s="11" t="n"/>
-    </row>
-    <row r="86" ht="288" customHeight="1">
-      <c r="C86" s="42" t="inlineStr">
-        <is>
-          <t>`before_value`：削除前のデータをJSON形式で格納する。
-`after_value`：DELETE のため空文字列を設定する。
-{
-  "dokusya_id": 1001,
-  "ja_id": 1,
-  "kanri_shiten_id": 10,
-  "shiten_id": 21,
-  "kumiaiin_code": "K000001",
-  "shimei_sei": "山田",
-  "shimei_mei": "太郎",
-  "dokusya_shubetsu": 1,
-  "shiharai_hoho": 1,
-  "hanbaiten_id": 501,
-  "tanka_id": 1
-}</t>
         </is>
       </c>
       <c r="D86" s="10" t="n"/>
@@ -12335,84 +12295,139 @@
       <c r="AJ86" s="10" t="n"/>
       <c r="AK86" s="11" t="n"/>
     </row>
-    <row r="87" ht="18" customHeight="1">
-      <c r="B87" s="27" t="inlineStr">
+    <row r="87" ht="288" customHeight="1">
+      <c r="C87" s="42" t="inlineStr">
+        <is>
+          <t>`before_value`：削除前のデータをJSON形式で格納する。
+`after_value`：DELETE のため空文字列を設定する。
+{
+  "dokusya_id": 1001,
+  "ja_id": 1,
+  "kanri_shiten_id": 10,
+  "shiten_id": 21,
+  "kumiaiin_code": "K000001",
+  "shimei_sei": "山田",
+  "shimei_mei": "太郎",
+  "dokusya_shubetsu": 1,
+  "shiharai_hoho": 1,
+  "hanbaiten_id": 501,
+  "tanka_id": 1
+}</t>
+        </is>
+      </c>
+      <c r="D87" s="10" t="n"/>
+      <c r="E87" s="10" t="n"/>
+      <c r="F87" s="10" t="n"/>
+      <c r="G87" s="10" t="n"/>
+      <c r="H87" s="10" t="n"/>
+      <c r="I87" s="10" t="n"/>
+      <c r="J87" s="10" t="n"/>
+      <c r="K87" s="10" t="n"/>
+      <c r="L87" s="10" t="n"/>
+      <c r="M87" s="10" t="n"/>
+      <c r="N87" s="10" t="n"/>
+      <c r="O87" s="10" t="n"/>
+      <c r="P87" s="10" t="n"/>
+      <c r="Q87" s="10" t="n"/>
+      <c r="R87" s="10" t="n"/>
+      <c r="S87" s="10" t="n"/>
+      <c r="T87" s="10" t="n"/>
+      <c r="U87" s="10" t="n"/>
+      <c r="V87" s="10" t="n"/>
+      <c r="W87" s="10" t="n"/>
+      <c r="X87" s="10" t="n"/>
+      <c r="Y87" s="10" t="n"/>
+      <c r="Z87" s="10" t="n"/>
+      <c r="AA87" s="10" t="n"/>
+      <c r="AB87" s="10" t="n"/>
+      <c r="AC87" s="10" t="n"/>
+      <c r="AD87" s="10" t="n"/>
+      <c r="AE87" s="10" t="n"/>
+      <c r="AF87" s="10" t="n"/>
+      <c r="AG87" s="10" t="n"/>
+      <c r="AH87" s="10" t="n"/>
+      <c r="AI87" s="10" t="n"/>
+      <c r="AJ87" s="10" t="n"/>
+      <c r="AK87" s="11" t="n"/>
+    </row>
+    <row r="88" ht="18" customHeight="1">
+      <c r="B88" s="27" t="inlineStr">
         <is>
           <t>4.6 レスポンス生成</t>
         </is>
       </c>
     </row>
-    <row r="88" ht="18" customHeight="1">
-      <c r="C88" s="41" t="inlineStr">
+    <row r="89" ht="18" customHeight="1">
+      <c r="C89" s="41" t="inlineStr">
         <is>
           <t>削除完了メッセージを返却する。HTTP 200。</t>
         </is>
       </c>
     </row>
-    <row r="89" ht="18" customHeight="1">
-      <c r="C89" s="42" t="inlineStr">
+    <row r="90" ht="18" customHeight="1">
+      <c r="C90" s="42" t="inlineStr">
         <is>
           <t>{ "message": "削除しました。" }</t>
         </is>
       </c>
-      <c r="D89" s="10" t="n"/>
-      <c r="E89" s="10" t="n"/>
-      <c r="F89" s="10" t="n"/>
-      <c r="G89" s="10" t="n"/>
-      <c r="H89" s="10" t="n"/>
-      <c r="I89" s="10" t="n"/>
-      <c r="J89" s="10" t="n"/>
-      <c r="K89" s="10" t="n"/>
-      <c r="L89" s="10" t="n"/>
-      <c r="M89" s="10" t="n"/>
-      <c r="N89" s="10" t="n"/>
-      <c r="O89" s="10" t="n"/>
-      <c r="P89" s="10" t="n"/>
-      <c r="Q89" s="10" t="n"/>
-      <c r="R89" s="10" t="n"/>
-      <c r="S89" s="10" t="n"/>
-      <c r="T89" s="10" t="n"/>
-      <c r="U89" s="10" t="n"/>
-      <c r="V89" s="10" t="n"/>
-      <c r="W89" s="10" t="n"/>
-      <c r="X89" s="10" t="n"/>
-      <c r="Y89" s="10" t="n"/>
-      <c r="Z89" s="10" t="n"/>
-      <c r="AA89" s="10" t="n"/>
-      <c r="AB89" s="10" t="n"/>
-      <c r="AC89" s="10" t="n"/>
-      <c r="AD89" s="10" t="n"/>
-      <c r="AE89" s="10" t="n"/>
-      <c r="AF89" s="10" t="n"/>
-      <c r="AG89" s="10" t="n"/>
-      <c r="AH89" s="10" t="n"/>
-      <c r="AI89" s="10" t="n"/>
-      <c r="AJ89" s="10" t="n"/>
-      <c r="AK89" s="11" t="n"/>
-    </row>
-    <row r="90" ht="18" customHeight="1">
-      <c r="B90" s="27" t="inlineStr">
+      <c r="D90" s="10" t="n"/>
+      <c r="E90" s="10" t="n"/>
+      <c r="F90" s="10" t="n"/>
+      <c r="G90" s="10" t="n"/>
+      <c r="H90" s="10" t="n"/>
+      <c r="I90" s="10" t="n"/>
+      <c r="J90" s="10" t="n"/>
+      <c r="K90" s="10" t="n"/>
+      <c r="L90" s="10" t="n"/>
+      <c r="M90" s="10" t="n"/>
+      <c r="N90" s="10" t="n"/>
+      <c r="O90" s="10" t="n"/>
+      <c r="P90" s="10" t="n"/>
+      <c r="Q90" s="10" t="n"/>
+      <c r="R90" s="10" t="n"/>
+      <c r="S90" s="10" t="n"/>
+      <c r="T90" s="10" t="n"/>
+      <c r="U90" s="10" t="n"/>
+      <c r="V90" s="10" t="n"/>
+      <c r="W90" s="10" t="n"/>
+      <c r="X90" s="10" t="n"/>
+      <c r="Y90" s="10" t="n"/>
+      <c r="Z90" s="10" t="n"/>
+      <c r="AA90" s="10" t="n"/>
+      <c r="AB90" s="10" t="n"/>
+      <c r="AC90" s="10" t="n"/>
+      <c r="AD90" s="10" t="n"/>
+      <c r="AE90" s="10" t="n"/>
+      <c r="AF90" s="10" t="n"/>
+      <c r="AG90" s="10" t="n"/>
+      <c r="AH90" s="10" t="n"/>
+      <c r="AI90" s="10" t="n"/>
+      <c r="AJ90" s="10" t="n"/>
+      <c r="AK90" s="11" t="n"/>
+    </row>
+    <row r="91" ht="18" customHeight="1">
+      <c r="B91" s="27" t="inlineStr">
         <is>
           <t>4.7 例外処理</t>
-        </is>
-      </c>
-    </row>
-    <row r="91" ht="18" customHeight="1">
-      <c r="C91" s="41" t="inlineStr">
-        <is>
-          <t>DB接続エラー等の場合：HTTP 500 (`INTERNAL_SERVER_ERROR`)</t>
         </is>
       </c>
     </row>
     <row r="92" ht="18" customHeight="1">
       <c r="C92" s="41" t="inlineStr">
         <is>
+          <t>DB接続エラー等の場合：HTTP 500 (`INTERNAL_SERVER_ERROR`)</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" ht="18" customHeight="1">
+      <c r="C93" s="41" t="inlineStr">
+        <is>
           <t>エラー発生時も操作ログを記録する（`log_type = 3`、トランザクション外で記録）。</t>
         </is>
       </c>
     </row>
-    <row r="93" ht="144" customHeight="1">
-      <c r="C93" s="42" t="inlineStr">
+    <row r="94" ht="144" customHeight="1">
+      <c r="C94" s="42" t="inlineStr">
         <is>
           <t>INSERT INTO t_log (log_type, log_datetime, account_id, ja_id,
                    gamen_name, operation, result_status,
@@ -12424,43 +12439,43 @@
         :ip_address, :user_agent)</t>
         </is>
       </c>
-      <c r="D93" s="10" t="n"/>
-      <c r="E93" s="10" t="n"/>
-      <c r="F93" s="10" t="n"/>
-      <c r="G93" s="10" t="n"/>
-      <c r="H93" s="10" t="n"/>
-      <c r="I93" s="10" t="n"/>
-      <c r="J93" s="10" t="n"/>
-      <c r="K93" s="10" t="n"/>
-      <c r="L93" s="10" t="n"/>
-      <c r="M93" s="10" t="n"/>
-      <c r="N93" s="10" t="n"/>
-      <c r="O93" s="10" t="n"/>
-      <c r="P93" s="10" t="n"/>
-      <c r="Q93" s="10" t="n"/>
-      <c r="R93" s="10" t="n"/>
-      <c r="S93" s="10" t="n"/>
-      <c r="T93" s="10" t="n"/>
-      <c r="U93" s="10" t="n"/>
-      <c r="V93" s="10" t="n"/>
-      <c r="W93" s="10" t="n"/>
-      <c r="X93" s="10" t="n"/>
-      <c r="Y93" s="10" t="n"/>
-      <c r="Z93" s="10" t="n"/>
-      <c r="AA93" s="10" t="n"/>
-      <c r="AB93" s="10" t="n"/>
-      <c r="AC93" s="10" t="n"/>
-      <c r="AD93" s="10" t="n"/>
-      <c r="AE93" s="10" t="n"/>
-      <c r="AF93" s="10" t="n"/>
-      <c r="AG93" s="10" t="n"/>
-      <c r="AH93" s="10" t="n"/>
-      <c r="AI93" s="10" t="n"/>
-      <c r="AJ93" s="10" t="n"/>
-      <c r="AK93" s="11" t="n"/>
+      <c r="D94" s="10" t="n"/>
+      <c r="E94" s="10" t="n"/>
+      <c r="F94" s="10" t="n"/>
+      <c r="G94" s="10" t="n"/>
+      <c r="H94" s="10" t="n"/>
+      <c r="I94" s="10" t="n"/>
+      <c r="J94" s="10" t="n"/>
+      <c r="K94" s="10" t="n"/>
+      <c r="L94" s="10" t="n"/>
+      <c r="M94" s="10" t="n"/>
+      <c r="N94" s="10" t="n"/>
+      <c r="O94" s="10" t="n"/>
+      <c r="P94" s="10" t="n"/>
+      <c r="Q94" s="10" t="n"/>
+      <c r="R94" s="10" t="n"/>
+      <c r="S94" s="10" t="n"/>
+      <c r="T94" s="10" t="n"/>
+      <c r="U94" s="10" t="n"/>
+      <c r="V94" s="10" t="n"/>
+      <c r="W94" s="10" t="n"/>
+      <c r="X94" s="10" t="n"/>
+      <c r="Y94" s="10" t="n"/>
+      <c r="Z94" s="10" t="n"/>
+      <c r="AA94" s="10" t="n"/>
+      <c r="AB94" s="10" t="n"/>
+      <c r="AC94" s="10" t="n"/>
+      <c r="AD94" s="10" t="n"/>
+      <c r="AE94" s="10" t="n"/>
+      <c r="AF94" s="10" t="n"/>
+      <c r="AG94" s="10" t="n"/>
+      <c r="AH94" s="10" t="n"/>
+      <c r="AI94" s="10" t="n"/>
+      <c r="AJ94" s="10" t="n"/>
+      <c r="AK94" s="11" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="125">
+  <mergeCells count="126">
     <mergeCell ref="J11:AK11"/>
     <mergeCell ref="Q29:S29"/>
     <mergeCell ref="C66:AK66"/>
@@ -12476,7 +12491,6 @@
     <mergeCell ref="N17:AK17"/>
     <mergeCell ref="J17:M17"/>
     <mergeCell ref="C45:AK45"/>
-    <mergeCell ref="B87:AK87"/>
     <mergeCell ref="B8:I8"/>
     <mergeCell ref="N19:AK19"/>
     <mergeCell ref="J19:M19"/>
@@ -12485,10 +12499,11 @@
     <mergeCell ref="AH2:AK3"/>
     <mergeCell ref="Y24:AB24"/>
     <mergeCell ref="C65:AK65"/>
+    <mergeCell ref="C94:AK94"/>
     <mergeCell ref="C75:AK75"/>
     <mergeCell ref="Q1:U1"/>
-    <mergeCell ref="C84:AK84"/>
     <mergeCell ref="B10:I10"/>
+    <mergeCell ref="C80:AK80"/>
     <mergeCell ref="Q25:S25"/>
     <mergeCell ref="J2:P3"/>
     <mergeCell ref="B63:AK63"/>
@@ -12497,6 +12512,7 @@
     <mergeCell ref="N20:AK20"/>
     <mergeCell ref="M25:P25"/>
     <mergeCell ref="C48:AK48"/>
+    <mergeCell ref="B91:AK91"/>
     <mergeCell ref="Y25:AB25"/>
     <mergeCell ref="D61:AK61"/>
     <mergeCell ref="T30:X30"/>
@@ -12509,11 +12525,11 @@
     <mergeCell ref="B12:I12"/>
     <mergeCell ref="C33:AK33"/>
     <mergeCell ref="C42:AK42"/>
-    <mergeCell ref="C88:AK88"/>
     <mergeCell ref="Z2:AC3"/>
     <mergeCell ref="C24:L24"/>
     <mergeCell ref="AD2:AG3"/>
     <mergeCell ref="B13:I13"/>
+    <mergeCell ref="D81:AK81"/>
     <mergeCell ref="Y30:AE30"/>
     <mergeCell ref="J13:AK13"/>
     <mergeCell ref="B14:I20"/>
@@ -12525,19 +12541,17 @@
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="J20:M20"/>
     <mergeCell ref="C39:AK39"/>
-    <mergeCell ref="B81:AK81"/>
     <mergeCell ref="B41:I41"/>
-    <mergeCell ref="B90:AK90"/>
     <mergeCell ref="B35:I35"/>
     <mergeCell ref="B50:I50"/>
     <mergeCell ref="B58:AK58"/>
     <mergeCell ref="AF25:AK25"/>
     <mergeCell ref="J7:AK7"/>
     <mergeCell ref="C78:AK78"/>
+    <mergeCell ref="C87:AK87"/>
     <mergeCell ref="A5:AK5"/>
     <mergeCell ref="AF30:AK30"/>
     <mergeCell ref="C62:AK62"/>
-    <mergeCell ref="C82:AK82"/>
     <mergeCell ref="AC25:AE25"/>
     <mergeCell ref="B11:I11"/>
     <mergeCell ref="C89:AK89"/>
@@ -12549,11 +12563,11 @@
     <mergeCell ref="C73:AK73"/>
     <mergeCell ref="J8:AK8"/>
     <mergeCell ref="C54:AK54"/>
+    <mergeCell ref="B84:AK84"/>
     <mergeCell ref="C93:AK93"/>
     <mergeCell ref="J10:AK10"/>
     <mergeCell ref="B38:I38"/>
     <mergeCell ref="N15:AK15"/>
-    <mergeCell ref="D80:AK80"/>
     <mergeCell ref="V1:Y1"/>
     <mergeCell ref="J9:AK9"/>
     <mergeCell ref="AH1:AK1"/>
@@ -12568,22 +12582,24 @@
     <mergeCell ref="B7:I7"/>
     <mergeCell ref="M24:P24"/>
     <mergeCell ref="C69:AK69"/>
+    <mergeCell ref="C83:AK83"/>
     <mergeCell ref="C92:AK92"/>
     <mergeCell ref="A22:AK22"/>
     <mergeCell ref="T25:X25"/>
+    <mergeCell ref="B88:AK88"/>
+    <mergeCell ref="B82:AK82"/>
     <mergeCell ref="J14:M14"/>
     <mergeCell ref="B44:I44"/>
     <mergeCell ref="B53:I53"/>
     <mergeCell ref="B74:AK74"/>
-    <mergeCell ref="B83:AK83"/>
     <mergeCell ref="C29:L29"/>
     <mergeCell ref="J15:M15"/>
     <mergeCell ref="AD1:AG1"/>
+    <mergeCell ref="C90:AK90"/>
     <mergeCell ref="C60:AK60"/>
     <mergeCell ref="C76:AK76"/>
     <mergeCell ref="M30:P30"/>
     <mergeCell ref="D70:AK70"/>
-    <mergeCell ref="C91:AK91"/>
     <mergeCell ref="B59:AK59"/>
     <mergeCell ref="AF29:AK29"/>
   </mergeCells>
@@ -12758,7 +12774,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/08/03</t>
+          <t>2026/08/04</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -15370,7 +15386,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/08/03</t>
+          <t>2026/08/04</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>

--- a/docs/design/ACSMS-SCR-014/【日本農業新聞様】VTIジャパン_クラウド版購読者管理システム_API設計書_購読者明細検索画面_V1.0.xlsx
+++ b/docs/design/ACSMS-SCR-014/【日本農業新聞様】VTIジャパン_クラウド版購読者管理システム_API設計書_購読者明細検索画面_V1.0.xlsx
@@ -1354,7 +1354,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG11"/>
+  <dimension ref="A1:AG13"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="4.25" customWidth="1" min="1" max="1"/>
@@ -2045,8 +2045,110 @@
       <c r="AF11" s="10" t="n"/>
       <c r="AG11" s="11" t="n"/>
     </row>
+    <row r="12" ht="19.5" customHeight="1">
+      <c r="A12" s="17" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="11" t="n"/>
+      <c r="C12" s="18" t="inlineStr">
+        <is>
+          <t>2026/08/06</t>
+        </is>
+      </c>
+      <c r="D12" s="10" t="n"/>
+      <c r="E12" s="10" t="n"/>
+      <c r="F12" s="10" t="n"/>
+      <c r="G12" s="11" t="n"/>
+      <c r="H12" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="I12" s="10" t="n"/>
+      <c r="J12" s="11" t="n"/>
+      <c r="K12" s="17" t="inlineStr">
+        <is>
+          <t>Tran Duc Tuyen</t>
+        </is>
+      </c>
+      <c r="L12" s="10" t="n"/>
+      <c r="M12" s="10" t="n"/>
+      <c r="N12" s="10" t="n"/>
+      <c r="O12" s="10" t="n"/>
+      <c r="P12" s="10" t="n"/>
+      <c r="Q12" s="11" t="n"/>
+      <c r="R12" s="19" t="inlineStr">
+        <is>
+          <t>実装との差分是正（記載漏れの補完）：ACSMS-API-014-001 のレスポンス `meta` に `total_busu`（検索条件に一致する購読者の購読部数合計・顧客要件2026-08 #56240）を追記。画面はページネーションの「全 N 件」の横に「全 M 部」と併記する。あわせて処理手順に §4.4.1 を新設し、適用日絞り込み時に `t_dokusya_rireki` を INNER JOIN すると購読者が履歴行数だけ重複して部数が水増しされるため、`DISTINCT dokusya_id` で畳んでから外側で合計する実装を明記した（件数側は `COUNT(DISTINCT)` のため影響を受けず、合計だけがずれる）</t>
+        </is>
+      </c>
+      <c r="S12" s="10" t="n"/>
+      <c r="T12" s="10" t="n"/>
+      <c r="U12" s="10" t="n"/>
+      <c r="V12" s="11" t="n"/>
+      <c r="W12" s="17" t="inlineStr"/>
+      <c r="X12" s="10" t="n"/>
+      <c r="Y12" s="10" t="n"/>
+      <c r="Z12" s="10" t="n"/>
+      <c r="AA12" s="11" t="n"/>
+      <c r="AB12" s="17" t="inlineStr"/>
+      <c r="AC12" s="10" t="n"/>
+      <c r="AD12" s="10" t="n"/>
+      <c r="AE12" s="10" t="n"/>
+      <c r="AF12" s="10" t="n"/>
+      <c r="AG12" s="11" t="n"/>
+    </row>
+    <row r="13" ht="19.5" customHeight="1">
+      <c r="A13" s="17" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="11" t="n"/>
+      <c r="C13" s="18" t="inlineStr">
+        <is>
+          <t>2026/08/15</t>
+        </is>
+      </c>
+      <c r="D13" s="10" t="n"/>
+      <c r="E13" s="10" t="n"/>
+      <c r="F13" s="10" t="n"/>
+      <c r="G13" s="11" t="n"/>
+      <c r="H13" s="17" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="I13" s="10" t="n"/>
+      <c r="J13" s="11" t="n"/>
+      <c r="K13" s="17" t="inlineStr">
+        <is>
+          <t>Tran Duc Tuyen</t>
+        </is>
+      </c>
+      <c r="L13" s="10" t="n"/>
+      <c r="M13" s="10" t="n"/>
+      <c r="N13" s="10" t="n"/>
+      <c r="O13" s="10" t="n"/>
+      <c r="P13" s="10" t="n"/>
+      <c r="Q13" s="11" t="n"/>
+      <c r="R13" s="19" t="inlineStr">
+        <is>
+          <t>実装との差分是正（スポットチェック）：&lt;br&gt;1. `is_read_only`（ACSMS-API-014-001 レスポンス・§4.5 SQL例）に3つ目の条件（電子版かつ電子版読者管理システム未連携 denshi_kaiin_id IS NULL かつ参照単価が非キャンペーン）が実装済みだが未記載だったため追記。§4.5 の SELECT 例に `m_tanka tk` の LEFT JOIN を追加（顧客要件2026-08追補・dokusya.mapper.ts / dokusya-search.service.ts 準拠）。&lt;br&gt;2. ACSMS-API-014-004 §4.5「新予約の挿入」の適用日(joho_henko_tekiyo_date)記載を是正：紙版=中止日そのまま、**電子版=中止日の翌日(+1日)**（顧客要件2026-08改訂・insertScheduledKaiyaku 実装準拠）。旧記載は両種別とも「適用日=中止日」としており誤り。&lt;br&gt;3. §4.3 active_tanka_flg の JOIN 条件 SQL 例が `active_flg = FALSE` に固定されていたが、直前の説明文どおりパラメータバインド（`:activeTankaFlg`）に修正（true/false/省略のトライステート挙動は実装済みで正しく記載されていた）。&lt;br&gt;4. §4.1 sort_by 許可カラム一覧（リクエストパラメータ表）に漏れていた `updated_at` を追記（処理手順4.1には元々記載あり・実装の allow-list と整合）</t>
+        </is>
+      </c>
+      <c r="S13" s="10" t="n"/>
+      <c r="T13" s="10" t="n"/>
+      <c r="U13" s="10" t="n"/>
+      <c r="V13" s="11" t="n"/>
+      <c r="W13" s="17" t="inlineStr"/>
+      <c r="X13" s="10" t="n"/>
+      <c r="Y13" s="10" t="n"/>
+      <c r="Z13" s="10" t="n"/>
+      <c r="AA13" s="11" t="n"/>
+      <c r="AB13" s="17" t="inlineStr"/>
+      <c r="AC13" s="10" t="n"/>
+      <c r="AD13" s="10" t="n"/>
+      <c r="AE13" s="10" t="n"/>
+      <c r="AF13" s="10" t="n"/>
+      <c r="AG13" s="11" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="77">
+  <mergeCells count="91">
     <mergeCell ref="R8:V8"/>
     <mergeCell ref="AB1:AG1"/>
     <mergeCell ref="C5:G5"/>
@@ -2076,9 +2178,12 @@
     <mergeCell ref="K10:Q10"/>
     <mergeCell ref="K6:Q6"/>
     <mergeCell ref="K3:Q3"/>
+    <mergeCell ref="AB13:AG13"/>
     <mergeCell ref="AB8:AG8"/>
     <mergeCell ref="K9:Q9"/>
     <mergeCell ref="K5:Q5"/>
+    <mergeCell ref="C12:G12"/>
+    <mergeCell ref="W12:AA12"/>
     <mergeCell ref="R3:V3"/>
     <mergeCell ref="K11:Q11"/>
     <mergeCell ref="A8:B8"/>
@@ -2093,11 +2198,15 @@
     <mergeCell ref="R11:V11"/>
     <mergeCell ref="K7:Q7"/>
     <mergeCell ref="A1:B1"/>
+    <mergeCell ref="R13:V13"/>
+    <mergeCell ref="AB12:AG12"/>
     <mergeCell ref="R6:V6"/>
     <mergeCell ref="C10:G10"/>
+    <mergeCell ref="H13:J13"/>
     <mergeCell ref="W3:AA3"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="C9:G9"/>
+    <mergeCell ref="A12:B12"/>
     <mergeCell ref="AB7:AG7"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="A5:B5"/>
@@ -2109,19 +2218,26 @@
     <mergeCell ref="H10:J10"/>
     <mergeCell ref="R2:V2"/>
     <mergeCell ref="H9:J9"/>
+    <mergeCell ref="K12:Q12"/>
+    <mergeCell ref="C13:G13"/>
+    <mergeCell ref="W13:AA13"/>
     <mergeCell ref="C6:G6"/>
     <mergeCell ref="W6:AA6"/>
     <mergeCell ref="AB9:AG9"/>
     <mergeCell ref="A6:B6"/>
     <mergeCell ref="AB2:AG2"/>
+    <mergeCell ref="K13:Q13"/>
     <mergeCell ref="AB11:AG11"/>
     <mergeCell ref="K4:Q4"/>
     <mergeCell ref="C1:G1"/>
     <mergeCell ref="W1:AA1"/>
+    <mergeCell ref="H12:J12"/>
+    <mergeCell ref="R12:V12"/>
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="C8:G8"/>
     <mergeCell ref="AB6:AG6"/>
     <mergeCell ref="W11:AA11"/>
+    <mergeCell ref="A13:B13"/>
     <mergeCell ref="K2:Q2"/>
     <mergeCell ref="C3:G3"/>
   </mergeCells>
@@ -2296,7 +2412,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/08/04</t>
+          <t>2026/08/17</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -2812,7 +2928,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/08/04</t>
+          <t>2026/08/17</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -3798,7 +3914,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/08/04</t>
+          <t>2026/08/17</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -4198,7 +4314,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK185"/>
+  <dimension ref="A1:AK187"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="4.25" customWidth="1" min="1" max="1"/>
@@ -4359,7 +4475,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/08/04</t>
+          <t>2026/08/17</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -6788,7 +6904,7 @@
       <c r="AE51" s="11" t="n"/>
       <c r="AF51" s="19" t="inlineStr">
         <is>
-          <t>ソートカラム（dokusya_id, kanri_shiten_id, shiten_id, kumiaiin_code, hanbaiten_id, hanbaiten_code, shoki_dokusya_kaishi_date, dokusya_chushi_date）。デフォルト: updated_at</t>
+          <t>ソートカラム（dokusya_id, kanri_shiten_id, shiten_id, kumiaiin_code, hanbaiten_id, hanbaiten_code, shoki_dokusya_kaishi_date, dokusya_chushi_date, updated_at）。デフォルト: updated_at</t>
         </is>
       </c>
       <c r="AG51" s="10" t="n"/>
@@ -8440,7 +8556,7 @@
       <c r="AJ81" s="10" t="n"/>
       <c r="AK81" s="11" t="n"/>
     </row>
-    <row r="82" ht="72" customHeight="1">
+    <row r="82" ht="180" customHeight="1">
       <c r="B82" s="31" t="n">
         <v>24</v>
       </c>
@@ -8491,7 +8607,7 @@
       <c r="AE82" s="11" t="n"/>
       <c r="AF82" s="19" t="inlineStr">
         <is>
-          <t>編集・削除不可フラグ（true=電子版クレジットカード決済者または併読者）。※削除ボタンの活性判定はこれに加えて `dokusya_shubetsu = 1`（紙版）も必要（顧客要件2026-08）</t>
+          <t>編集・削除不可フラグ。true となる条件は3つ（OR）：①併読(dokusya_shubetsu=3)、②電子版クレジットカード決済者(dokusya_shubetsu=2 かつ shiharai_hoho=6)、③電子版かつ電子版読者管理システム未連携(denshi_kaiin_id IS NULL)かつ参照単価がキャンペーン単価でない(campaign_flg=false、単価未割当時もfalse扱い)（顧客要件2026-08追補）。※削除ボタンの活性判定はこれに加えて `dokusya_shubetsu = 1`（紙版）も必要（顧客要件2026-08）</t>
         </is>
       </c>
       <c r="AG82" s="10" t="n"/>
@@ -8744,7 +8860,7 @@
       <c r="B87" s="31" t="n">
         <v>29</v>
       </c>
-      <c r="C87" s="39" t="n"/>
+      <c r="C87" s="38" t="n"/>
       <c r="D87" s="19" t="inlineStr">
         <is>
           <t>total_pages</t>
@@ -8800,64 +8916,124 @@
       <c r="AJ87" s="10" t="n"/>
       <c r="AK87" s="11" t="n"/>
     </row>
-    <row r="88" ht="19.5" customHeight="1"/>
-    <row r="89" ht="19.5" customHeight="1">
-      <c r="B89" s="40" t="inlineStr">
+    <row r="88" ht="72" customHeight="1">
+      <c r="B88" s="31" t="n">
+        <v>30</v>
+      </c>
+      <c r="C88" s="39" t="n"/>
+      <c r="D88" s="19" t="inlineStr">
+        <is>
+          <t>total_busu</t>
+        </is>
+      </c>
+      <c r="E88" s="10" t="n"/>
+      <c r="F88" s="10" t="n"/>
+      <c r="G88" s="10" t="n"/>
+      <c r="H88" s="10" t="n"/>
+      <c r="I88" s="10" t="n"/>
+      <c r="J88" s="10" t="n"/>
+      <c r="K88" s="10" t="n"/>
+      <c r="L88" s="11" t="n"/>
+      <c r="M88" s="17" t="inlineStr">
+        <is>
+          <t>Number</t>
+        </is>
+      </c>
+      <c r="N88" s="10" t="n"/>
+      <c r="O88" s="10" t="n"/>
+      <c r="P88" s="11" t="n"/>
+      <c r="Q88" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R88" s="10" t="n"/>
+      <c r="S88" s="11" t="n"/>
+      <c r="T88" s="17" t="inlineStr"/>
+      <c r="U88" s="10" t="n"/>
+      <c r="V88" s="10" t="n"/>
+      <c r="W88" s="10" t="n"/>
+      <c r="X88" s="11" t="n"/>
+      <c r="Y88" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z88" s="10" t="n"/>
+      <c r="AA88" s="10" t="n"/>
+      <c r="AB88" s="10" t="n"/>
+      <c r="AC88" s="10" t="n"/>
+      <c r="AD88" s="10" t="n"/>
+      <c r="AE88" s="11" t="n"/>
+      <c r="AF88" s="19" t="inlineStr">
+        <is>
+          <t>検索条件に一致する購読者の購読部数合計（顧客要件2026-08。画面はページネーションの「全 N 件」の横に「全 M 部」と併記する）。ページングの影響を受けず、件数と同じ絞り込みで全件を集計する</t>
+        </is>
+      </c>
+      <c r="AG88" s="10" t="n"/>
+      <c r="AH88" s="10" t="n"/>
+      <c r="AI88" s="10" t="n"/>
+      <c r="AJ88" s="10" t="n"/>
+      <c r="AK88" s="11" t="n"/>
+    </row>
+    <row r="89" ht="19.5" customHeight="1"/>
+    <row r="90" ht="19.5" customHeight="1">
+      <c r="B90" s="40" t="inlineStr">
         <is>
           <t>リクエスト</t>
         </is>
       </c>
     </row>
-    <row r="90" ht="18" customHeight="1">
-      <c r="C90" s="19" t="inlineStr">
+    <row r="91" ht="18" customHeight="1">
+      <c r="C91" s="19" t="inlineStr">
         <is>
           <t>GET /api/v1/dokusya?kanri_shiten_id=10&amp;shiten_id=21&amp;dokusya_shubetsu=1&amp;shoki_dokusya_kaishi_date_from=2024/01/01&amp;shoki_dokusya_kaishi_date_to=2024/12/31&amp;page=1&amp;per_page=20&amp;sort_by=updated_at&amp;sort_order=desc</t>
         </is>
       </c>
-      <c r="D90" s="10" t="n"/>
-      <c r="E90" s="10" t="n"/>
-      <c r="F90" s="10" t="n"/>
-      <c r="G90" s="10" t="n"/>
-      <c r="H90" s="10" t="n"/>
-      <c r="I90" s="10" t="n"/>
-      <c r="J90" s="10" t="n"/>
-      <c r="K90" s="10" t="n"/>
-      <c r="L90" s="10" t="n"/>
-      <c r="M90" s="10" t="n"/>
-      <c r="N90" s="10" t="n"/>
-      <c r="O90" s="10" t="n"/>
-      <c r="P90" s="10" t="n"/>
-      <c r="Q90" s="10" t="n"/>
-      <c r="R90" s="10" t="n"/>
-      <c r="S90" s="10" t="n"/>
-      <c r="T90" s="10" t="n"/>
-      <c r="U90" s="10" t="n"/>
-      <c r="V90" s="10" t="n"/>
-      <c r="W90" s="10" t="n"/>
-      <c r="X90" s="10" t="n"/>
-      <c r="Y90" s="10" t="n"/>
-      <c r="Z90" s="10" t="n"/>
-      <c r="AA90" s="10" t="n"/>
-      <c r="AB90" s="10" t="n"/>
-      <c r="AC90" s="10" t="n"/>
-      <c r="AD90" s="10" t="n"/>
-      <c r="AE90" s="10" t="n"/>
-      <c r="AF90" s="10" t="n"/>
-      <c r="AG90" s="10" t="n"/>
-      <c r="AH90" s="10" t="n"/>
-      <c r="AI90" s="10" t="n"/>
-      <c r="AJ90" s="10" t="n"/>
-      <c r="AK90" s="11" t="n"/>
-    </row>
-    <row r="92" ht="19.5" customHeight="1">
-      <c r="B92" s="40" t="inlineStr">
+      <c r="D91" s="10" t="n"/>
+      <c r="E91" s="10" t="n"/>
+      <c r="F91" s="10" t="n"/>
+      <c r="G91" s="10" t="n"/>
+      <c r="H91" s="10" t="n"/>
+      <c r="I91" s="10" t="n"/>
+      <c r="J91" s="10" t="n"/>
+      <c r="K91" s="10" t="n"/>
+      <c r="L91" s="10" t="n"/>
+      <c r="M91" s="10" t="n"/>
+      <c r="N91" s="10" t="n"/>
+      <c r="O91" s="10" t="n"/>
+      <c r="P91" s="10" t="n"/>
+      <c r="Q91" s="10" t="n"/>
+      <c r="R91" s="10" t="n"/>
+      <c r="S91" s="10" t="n"/>
+      <c r="T91" s="10" t="n"/>
+      <c r="U91" s="10" t="n"/>
+      <c r="V91" s="10" t="n"/>
+      <c r="W91" s="10" t="n"/>
+      <c r="X91" s="10" t="n"/>
+      <c r="Y91" s="10" t="n"/>
+      <c r="Z91" s="10" t="n"/>
+      <c r="AA91" s="10" t="n"/>
+      <c r="AB91" s="10" t="n"/>
+      <c r="AC91" s="10" t="n"/>
+      <c r="AD91" s="10" t="n"/>
+      <c r="AE91" s="10" t="n"/>
+      <c r="AF91" s="10" t="n"/>
+      <c r="AG91" s="10" t="n"/>
+      <c r="AH91" s="10" t="n"/>
+      <c r="AI91" s="10" t="n"/>
+      <c r="AJ91" s="10" t="n"/>
+      <c r="AK91" s="11" t="n"/>
+    </row>
+    <row r="93" ht="19.5" customHeight="1">
+      <c r="B93" s="40" t="inlineStr">
         <is>
           <t>レスポンス（成功）</t>
         </is>
       </c>
     </row>
-    <row r="93" ht="409" customHeight="1">
-      <c r="C93" s="19" t="inlineStr">
+    <row r="94" ht="409" customHeight="1">
+      <c r="C94" s="19" t="inlineStr">
         <is>
           <t>{
   "data": [
@@ -8918,55 +9094,56 @@
     "total": 250,
     "page": 1,
     "per_page": 20,
-    "total_pages": 13
+    "total_pages": 13,
+    "total_busu": 318
   }
 }</t>
         </is>
       </c>
-      <c r="D93" s="10" t="n"/>
-      <c r="E93" s="10" t="n"/>
-      <c r="F93" s="10" t="n"/>
-      <c r="G93" s="10" t="n"/>
-      <c r="H93" s="10" t="n"/>
-      <c r="I93" s="10" t="n"/>
-      <c r="J93" s="10" t="n"/>
-      <c r="K93" s="10" t="n"/>
-      <c r="L93" s="10" t="n"/>
-      <c r="M93" s="10" t="n"/>
-      <c r="N93" s="10" t="n"/>
-      <c r="O93" s="10" t="n"/>
-      <c r="P93" s="10" t="n"/>
-      <c r="Q93" s="10" t="n"/>
-      <c r="R93" s="10" t="n"/>
-      <c r="S93" s="10" t="n"/>
-      <c r="T93" s="10" t="n"/>
-      <c r="U93" s="10" t="n"/>
-      <c r="V93" s="10" t="n"/>
-      <c r="W93" s="10" t="n"/>
-      <c r="X93" s="10" t="n"/>
-      <c r="Y93" s="10" t="n"/>
-      <c r="Z93" s="10" t="n"/>
-      <c r="AA93" s="10" t="n"/>
-      <c r="AB93" s="10" t="n"/>
-      <c r="AC93" s="10" t="n"/>
-      <c r="AD93" s="10" t="n"/>
-      <c r="AE93" s="10" t="n"/>
-      <c r="AF93" s="10" t="n"/>
-      <c r="AG93" s="10" t="n"/>
-      <c r="AH93" s="10" t="n"/>
-      <c r="AI93" s="10" t="n"/>
-      <c r="AJ93" s="10" t="n"/>
-      <c r="AK93" s="11" t="n"/>
-    </row>
-    <row r="95" ht="19.5" customHeight="1">
-      <c r="B95" s="40" t="inlineStr">
+      <c r="D94" s="10" t="n"/>
+      <c r="E94" s="10" t="n"/>
+      <c r="F94" s="10" t="n"/>
+      <c r="G94" s="10" t="n"/>
+      <c r="H94" s="10" t="n"/>
+      <c r="I94" s="10" t="n"/>
+      <c r="J94" s="10" t="n"/>
+      <c r="K94" s="10" t="n"/>
+      <c r="L94" s="10" t="n"/>
+      <c r="M94" s="10" t="n"/>
+      <c r="N94" s="10" t="n"/>
+      <c r="O94" s="10" t="n"/>
+      <c r="P94" s="10" t="n"/>
+      <c r="Q94" s="10" t="n"/>
+      <c r="R94" s="10" t="n"/>
+      <c r="S94" s="10" t="n"/>
+      <c r="T94" s="10" t="n"/>
+      <c r="U94" s="10" t="n"/>
+      <c r="V94" s="10" t="n"/>
+      <c r="W94" s="10" t="n"/>
+      <c r="X94" s="10" t="n"/>
+      <c r="Y94" s="10" t="n"/>
+      <c r="Z94" s="10" t="n"/>
+      <c r="AA94" s="10" t="n"/>
+      <c r="AB94" s="10" t="n"/>
+      <c r="AC94" s="10" t="n"/>
+      <c r="AD94" s="10" t="n"/>
+      <c r="AE94" s="10" t="n"/>
+      <c r="AF94" s="10" t="n"/>
+      <c r="AG94" s="10" t="n"/>
+      <c r="AH94" s="10" t="n"/>
+      <c r="AI94" s="10" t="n"/>
+      <c r="AJ94" s="10" t="n"/>
+      <c r="AK94" s="11" t="n"/>
+    </row>
+    <row r="96" ht="19.5" customHeight="1">
+      <c r="B96" s="40" t="inlineStr">
         <is>
           <t>レスポンス（失敗 400 Validation Error（メール形式エラー））</t>
         </is>
       </c>
     </row>
-    <row r="96" ht="126" customHeight="1">
-      <c r="C96" s="19" t="inlineStr">
+    <row r="97" ht="126" customHeight="1">
+      <c r="C97" s="19" t="inlineStr">
         <is>
           <t>{
   "error_code": "VALIDATION_ERROR",
@@ -8977,50 +9154,50 @@
 }</t>
         </is>
       </c>
-      <c r="D96" s="10" t="n"/>
-      <c r="E96" s="10" t="n"/>
-      <c r="F96" s="10" t="n"/>
-      <c r="G96" s="10" t="n"/>
-      <c r="H96" s="10" t="n"/>
-      <c r="I96" s="10" t="n"/>
-      <c r="J96" s="10" t="n"/>
-      <c r="K96" s="10" t="n"/>
-      <c r="L96" s="10" t="n"/>
-      <c r="M96" s="10" t="n"/>
-      <c r="N96" s="10" t="n"/>
-      <c r="O96" s="10" t="n"/>
-      <c r="P96" s="10" t="n"/>
-      <c r="Q96" s="10" t="n"/>
-      <c r="R96" s="10" t="n"/>
-      <c r="S96" s="10" t="n"/>
-      <c r="T96" s="10" t="n"/>
-      <c r="U96" s="10" t="n"/>
-      <c r="V96" s="10" t="n"/>
-      <c r="W96" s="10" t="n"/>
-      <c r="X96" s="10" t="n"/>
-      <c r="Y96" s="10" t="n"/>
-      <c r="Z96" s="10" t="n"/>
-      <c r="AA96" s="10" t="n"/>
-      <c r="AB96" s="10" t="n"/>
-      <c r="AC96" s="10" t="n"/>
-      <c r="AD96" s="10" t="n"/>
-      <c r="AE96" s="10" t="n"/>
-      <c r="AF96" s="10" t="n"/>
-      <c r="AG96" s="10" t="n"/>
-      <c r="AH96" s="10" t="n"/>
-      <c r="AI96" s="10" t="n"/>
-      <c r="AJ96" s="10" t="n"/>
-      <c r="AK96" s="11" t="n"/>
-    </row>
-    <row r="98" ht="19.5" customHeight="1">
-      <c r="B98" s="40" t="inlineStr">
+      <c r="D97" s="10" t="n"/>
+      <c r="E97" s="10" t="n"/>
+      <c r="F97" s="10" t="n"/>
+      <c r="G97" s="10" t="n"/>
+      <c r="H97" s="10" t="n"/>
+      <c r="I97" s="10" t="n"/>
+      <c r="J97" s="10" t="n"/>
+      <c r="K97" s="10" t="n"/>
+      <c r="L97" s="10" t="n"/>
+      <c r="M97" s="10" t="n"/>
+      <c r="N97" s="10" t="n"/>
+      <c r="O97" s="10" t="n"/>
+      <c r="P97" s="10" t="n"/>
+      <c r="Q97" s="10" t="n"/>
+      <c r="R97" s="10" t="n"/>
+      <c r="S97" s="10" t="n"/>
+      <c r="T97" s="10" t="n"/>
+      <c r="U97" s="10" t="n"/>
+      <c r="V97" s="10" t="n"/>
+      <c r="W97" s="10" t="n"/>
+      <c r="X97" s="10" t="n"/>
+      <c r="Y97" s="10" t="n"/>
+      <c r="Z97" s="10" t="n"/>
+      <c r="AA97" s="10" t="n"/>
+      <c r="AB97" s="10" t="n"/>
+      <c r="AC97" s="10" t="n"/>
+      <c r="AD97" s="10" t="n"/>
+      <c r="AE97" s="10" t="n"/>
+      <c r="AF97" s="10" t="n"/>
+      <c r="AG97" s="10" t="n"/>
+      <c r="AH97" s="10" t="n"/>
+      <c r="AI97" s="10" t="n"/>
+      <c r="AJ97" s="10" t="n"/>
+      <c r="AK97" s="11" t="n"/>
+    </row>
+    <row r="99" ht="19.5" customHeight="1">
+      <c r="B99" s="40" t="inlineStr">
         <is>
           <t>レスポンス（失敗 401 Unauthorized）</t>
         </is>
       </c>
     </row>
-    <row r="99" ht="72" customHeight="1">
-      <c r="C99" s="19" t="inlineStr">
+    <row r="100" ht="72" customHeight="1">
+      <c r="C100" s="19" t="inlineStr">
         <is>
           <t>{
   "error_code": "UNAUTHORIZED",
@@ -9028,50 +9205,50 @@
 }</t>
         </is>
       </c>
-      <c r="D99" s="10" t="n"/>
-      <c r="E99" s="10" t="n"/>
-      <c r="F99" s="10" t="n"/>
-      <c r="G99" s="10" t="n"/>
-      <c r="H99" s="10" t="n"/>
-      <c r="I99" s="10" t="n"/>
-      <c r="J99" s="10" t="n"/>
-      <c r="K99" s="10" t="n"/>
-      <c r="L99" s="10" t="n"/>
-      <c r="M99" s="10" t="n"/>
-      <c r="N99" s="10" t="n"/>
-      <c r="O99" s="10" t="n"/>
-      <c r="P99" s="10" t="n"/>
-      <c r="Q99" s="10" t="n"/>
-      <c r="R99" s="10" t="n"/>
-      <c r="S99" s="10" t="n"/>
-      <c r="T99" s="10" t="n"/>
-      <c r="U99" s="10" t="n"/>
-      <c r="V99" s="10" t="n"/>
-      <c r="W99" s="10" t="n"/>
-      <c r="X99" s="10" t="n"/>
-      <c r="Y99" s="10" t="n"/>
-      <c r="Z99" s="10" t="n"/>
-      <c r="AA99" s="10" t="n"/>
-      <c r="AB99" s="10" t="n"/>
-      <c r="AC99" s="10" t="n"/>
-      <c r="AD99" s="10" t="n"/>
-      <c r="AE99" s="10" t="n"/>
-      <c r="AF99" s="10" t="n"/>
-      <c r="AG99" s="10" t="n"/>
-      <c r="AH99" s="10" t="n"/>
-      <c r="AI99" s="10" t="n"/>
-      <c r="AJ99" s="10" t="n"/>
-      <c r="AK99" s="11" t="n"/>
-    </row>
-    <row r="101" ht="19.5" customHeight="1">
-      <c r="B101" s="40" t="inlineStr">
+      <c r="D100" s="10" t="n"/>
+      <c r="E100" s="10" t="n"/>
+      <c r="F100" s="10" t="n"/>
+      <c r="G100" s="10" t="n"/>
+      <c r="H100" s="10" t="n"/>
+      <c r="I100" s="10" t="n"/>
+      <c r="J100" s="10" t="n"/>
+      <c r="K100" s="10" t="n"/>
+      <c r="L100" s="10" t="n"/>
+      <c r="M100" s="10" t="n"/>
+      <c r="N100" s="10" t="n"/>
+      <c r="O100" s="10" t="n"/>
+      <c r="P100" s="10" t="n"/>
+      <c r="Q100" s="10" t="n"/>
+      <c r="R100" s="10" t="n"/>
+      <c r="S100" s="10" t="n"/>
+      <c r="T100" s="10" t="n"/>
+      <c r="U100" s="10" t="n"/>
+      <c r="V100" s="10" t="n"/>
+      <c r="W100" s="10" t="n"/>
+      <c r="X100" s="10" t="n"/>
+      <c r="Y100" s="10" t="n"/>
+      <c r="Z100" s="10" t="n"/>
+      <c r="AA100" s="10" t="n"/>
+      <c r="AB100" s="10" t="n"/>
+      <c r="AC100" s="10" t="n"/>
+      <c r="AD100" s="10" t="n"/>
+      <c r="AE100" s="10" t="n"/>
+      <c r="AF100" s="10" t="n"/>
+      <c r="AG100" s="10" t="n"/>
+      <c r="AH100" s="10" t="n"/>
+      <c r="AI100" s="10" t="n"/>
+      <c r="AJ100" s="10" t="n"/>
+      <c r="AK100" s="11" t="n"/>
+    </row>
+    <row r="102" ht="19.5" customHeight="1">
+      <c r="B102" s="40" t="inlineStr">
         <is>
           <t>レスポンス（失敗 403 Forbidden）</t>
         </is>
       </c>
     </row>
-    <row r="102" ht="72" customHeight="1">
-      <c r="C102" s="19" t="inlineStr">
+    <row r="103" ht="72" customHeight="1">
+      <c r="C103" s="19" t="inlineStr">
         <is>
           <t>{
   "error_code": "FORBIDDEN",
@@ -9079,50 +9256,50 @@
 }</t>
         </is>
       </c>
-      <c r="D102" s="10" t="n"/>
-      <c r="E102" s="10" t="n"/>
-      <c r="F102" s="10" t="n"/>
-      <c r="G102" s="10" t="n"/>
-      <c r="H102" s="10" t="n"/>
-      <c r="I102" s="10" t="n"/>
-      <c r="J102" s="10" t="n"/>
-      <c r="K102" s="10" t="n"/>
-      <c r="L102" s="10" t="n"/>
-      <c r="M102" s="10" t="n"/>
-      <c r="N102" s="10" t="n"/>
-      <c r="O102" s="10" t="n"/>
-      <c r="P102" s="10" t="n"/>
-      <c r="Q102" s="10" t="n"/>
-      <c r="R102" s="10" t="n"/>
-      <c r="S102" s="10" t="n"/>
-      <c r="T102" s="10" t="n"/>
-      <c r="U102" s="10" t="n"/>
-      <c r="V102" s="10" t="n"/>
-      <c r="W102" s="10" t="n"/>
-      <c r="X102" s="10" t="n"/>
-      <c r="Y102" s="10" t="n"/>
-      <c r="Z102" s="10" t="n"/>
-      <c r="AA102" s="10" t="n"/>
-      <c r="AB102" s="10" t="n"/>
-      <c r="AC102" s="10" t="n"/>
-      <c r="AD102" s="10" t="n"/>
-      <c r="AE102" s="10" t="n"/>
-      <c r="AF102" s="10" t="n"/>
-      <c r="AG102" s="10" t="n"/>
-      <c r="AH102" s="10" t="n"/>
-      <c r="AI102" s="10" t="n"/>
-      <c r="AJ102" s="10" t="n"/>
-      <c r="AK102" s="11" t="n"/>
-    </row>
-    <row r="104" ht="19.5" customHeight="1">
-      <c r="B104" s="40" t="inlineStr">
+      <c r="D103" s="10" t="n"/>
+      <c r="E103" s="10" t="n"/>
+      <c r="F103" s="10" t="n"/>
+      <c r="G103" s="10" t="n"/>
+      <c r="H103" s="10" t="n"/>
+      <c r="I103" s="10" t="n"/>
+      <c r="J103" s="10" t="n"/>
+      <c r="K103" s="10" t="n"/>
+      <c r="L103" s="10" t="n"/>
+      <c r="M103" s="10" t="n"/>
+      <c r="N103" s="10" t="n"/>
+      <c r="O103" s="10" t="n"/>
+      <c r="P103" s="10" t="n"/>
+      <c r="Q103" s="10" t="n"/>
+      <c r="R103" s="10" t="n"/>
+      <c r="S103" s="10" t="n"/>
+      <c r="T103" s="10" t="n"/>
+      <c r="U103" s="10" t="n"/>
+      <c r="V103" s="10" t="n"/>
+      <c r="W103" s="10" t="n"/>
+      <c r="X103" s="10" t="n"/>
+      <c r="Y103" s="10" t="n"/>
+      <c r="Z103" s="10" t="n"/>
+      <c r="AA103" s="10" t="n"/>
+      <c r="AB103" s="10" t="n"/>
+      <c r="AC103" s="10" t="n"/>
+      <c r="AD103" s="10" t="n"/>
+      <c r="AE103" s="10" t="n"/>
+      <c r="AF103" s="10" t="n"/>
+      <c r="AG103" s="10" t="n"/>
+      <c r="AH103" s="10" t="n"/>
+      <c r="AI103" s="10" t="n"/>
+      <c r="AJ103" s="10" t="n"/>
+      <c r="AK103" s="11" t="n"/>
+    </row>
+    <row r="105" ht="19.5" customHeight="1">
+      <c r="B105" s="40" t="inlineStr">
         <is>
           <t>レスポンス（失敗 500 Internal Server Error）</t>
         </is>
       </c>
     </row>
-    <row r="105" ht="72" customHeight="1">
-      <c r="C105" s="19" t="inlineStr">
+    <row r="106" ht="72" customHeight="1">
+      <c r="C106" s="19" t="inlineStr">
         <is>
           <t>{
   "error_code": "INTERNAL_SERVER_ERROR",
@@ -9130,551 +9307,551 @@
 }</t>
         </is>
       </c>
-      <c r="D105" s="10" t="n"/>
-      <c r="E105" s="10" t="n"/>
-      <c r="F105" s="10" t="n"/>
-      <c r="G105" s="10" t="n"/>
-      <c r="H105" s="10" t="n"/>
-      <c r="I105" s="10" t="n"/>
-      <c r="J105" s="10" t="n"/>
-      <c r="K105" s="10" t="n"/>
-      <c r="L105" s="10" t="n"/>
-      <c r="M105" s="10" t="n"/>
-      <c r="N105" s="10" t="n"/>
-      <c r="O105" s="10" t="n"/>
-      <c r="P105" s="10" t="n"/>
-      <c r="Q105" s="10" t="n"/>
-      <c r="R105" s="10" t="n"/>
-      <c r="S105" s="10" t="n"/>
-      <c r="T105" s="10" t="n"/>
-      <c r="U105" s="10" t="n"/>
-      <c r="V105" s="10" t="n"/>
-      <c r="W105" s="10" t="n"/>
-      <c r="X105" s="10" t="n"/>
-      <c r="Y105" s="10" t="n"/>
-      <c r="Z105" s="10" t="n"/>
-      <c r="AA105" s="10" t="n"/>
-      <c r="AB105" s="10" t="n"/>
-      <c r="AC105" s="10" t="n"/>
-      <c r="AD105" s="10" t="n"/>
-      <c r="AE105" s="10" t="n"/>
-      <c r="AF105" s="10" t="n"/>
-      <c r="AG105" s="10" t="n"/>
-      <c r="AH105" s="10" t="n"/>
-      <c r="AI105" s="10" t="n"/>
-      <c r="AJ105" s="10" t="n"/>
-      <c r="AK105" s="11" t="n"/>
-    </row>
-    <row r="107" ht="19.5" customHeight="1"/>
-    <row r="108" ht="19.5" customHeight="1">
-      <c r="A108" s="27" t="inlineStr">
+      <c r="D106" s="10" t="n"/>
+      <c r="E106" s="10" t="n"/>
+      <c r="F106" s="10" t="n"/>
+      <c r="G106" s="10" t="n"/>
+      <c r="H106" s="10" t="n"/>
+      <c r="I106" s="10" t="n"/>
+      <c r="J106" s="10" t="n"/>
+      <c r="K106" s="10" t="n"/>
+      <c r="L106" s="10" t="n"/>
+      <c r="M106" s="10" t="n"/>
+      <c r="N106" s="10" t="n"/>
+      <c r="O106" s="10" t="n"/>
+      <c r="P106" s="10" t="n"/>
+      <c r="Q106" s="10" t="n"/>
+      <c r="R106" s="10" t="n"/>
+      <c r="S106" s="10" t="n"/>
+      <c r="T106" s="10" t="n"/>
+      <c r="U106" s="10" t="n"/>
+      <c r="V106" s="10" t="n"/>
+      <c r="W106" s="10" t="n"/>
+      <c r="X106" s="10" t="n"/>
+      <c r="Y106" s="10" t="n"/>
+      <c r="Z106" s="10" t="n"/>
+      <c r="AA106" s="10" t="n"/>
+      <c r="AB106" s="10" t="n"/>
+      <c r="AC106" s="10" t="n"/>
+      <c r="AD106" s="10" t="n"/>
+      <c r="AE106" s="10" t="n"/>
+      <c r="AF106" s="10" t="n"/>
+      <c r="AG106" s="10" t="n"/>
+      <c r="AH106" s="10" t="n"/>
+      <c r="AI106" s="10" t="n"/>
+      <c r="AJ106" s="10" t="n"/>
+      <c r="AK106" s="11" t="n"/>
+    </row>
+    <row r="108" ht="19.5" customHeight="1"/>
+    <row r="109" ht="19.5" customHeight="1">
+      <c r="A109" s="27" t="inlineStr">
         <is>
           <t>4. 処理手順</t>
         </is>
       </c>
     </row>
-    <row r="109" ht="18" customHeight="1">
-      <c r="B109" s="27" t="inlineStr">
+    <row r="110" ht="18" customHeight="1">
+      <c r="B110" s="27" t="inlineStr">
         <is>
           <t>4.1 リクエストのバリデーション</t>
         </is>
       </c>
     </row>
-    <row r="110" ht="18" customHeight="1">
-      <c r="C110" s="41" t="inlineStr">
+    <row r="111" ht="18" customHeight="1">
+      <c r="C111" s="41" t="inlineStr">
         <is>
           <t>クエリパラメータの検証：</t>
-        </is>
-      </c>
-    </row>
-    <row r="111" ht="18" customHeight="1">
-      <c r="D111" s="41" t="inlineStr">
-        <is>
-          <t>kanri_shiten_id / shiten_id / hanbaiten_id：数値型チェック</t>
         </is>
       </c>
     </row>
     <row r="112" ht="18" customHeight="1">
       <c r="D112" s="41" t="inlineStr">
         <is>
+          <t>kanri_shiten_id / shiten_id / hanbaiten_id：数値型チェック</t>
+        </is>
+      </c>
+    </row>
+    <row r="113" ht="18" customHeight="1">
+      <c r="D113" s="41" t="inlineStr">
+        <is>
           <t>kumiaiin_code：最大20文字</t>
         </is>
       </c>
     </row>
-    <row r="113" ht="36" customHeight="1">
-      <c r="D113" s="41" t="inlineStr">
+    <row r="114" ht="36" customHeight="1">
+      <c r="D114" s="41" t="inlineStr">
         <is>
           <t>bank_branch：最大100文字（物理カラム `bank_branch_code` / `bank_branch_name` に対する OR 部分一致）</t>
-        </is>
-      </c>
-    </row>
-    <row r="114" ht="18" customHeight="1">
-      <c r="D114" s="41" t="inlineStr">
-        <is>
-          <t>full_name / full_name_kana：最大100文字</t>
         </is>
       </c>
     </row>
     <row r="115" ht="18" customHeight="1">
       <c r="D115" s="41" t="inlineStr">
         <is>
-          <t>haitatsu：最大200文字</t>
+          <t>full_name / full_name_kana：最大100文字</t>
         </is>
       </c>
     </row>
     <row r="116" ht="18" customHeight="1">
       <c r="D116" s="41" t="inlineStr">
         <is>
+          <t>haitatsu：最大200文字</t>
+        </is>
+      </c>
+    </row>
+    <row r="117" ht="18" customHeight="1">
+      <c r="D117" s="41" t="inlineStr">
+        <is>
           <t>renrakusaki：最大15文字</t>
         </is>
       </c>
     </row>
-    <row r="117" ht="36" customHeight="1">
-      <c r="D117" s="41" t="inlineStr">
+    <row r="118" ht="36" customHeight="1">
+      <c r="D118" s="41" t="inlineStr">
         <is>
           <t>email：最大100文字、メール形式チェック（不正の場合、`VALIDATION_ERROR` + `errors[]` に `正しいメール形式を入力してください。` を含める）</t>
-        </is>
-      </c>
-    </row>
-    <row r="118" ht="18" customHeight="1">
-      <c r="D118" s="41" t="inlineStr">
-        <is>
-          <t>yubin_kubun：m_code YUBIN_KUBUN（0:空 / 1:郵送）の値（完全一致）</t>
         </is>
       </c>
     </row>
     <row r="119" ht="18" customHeight="1">
       <c r="D119" s="41" t="inlineStr">
         <is>
-          <t>tanka_id：整数（完全一致）</t>
+          <t>yubin_kubun：m_code YUBIN_KUBUN（0:空 / 1:郵送）の値（完全一致）</t>
         </is>
       </c>
     </row>
     <row r="120" ht="18" customHeight="1">
       <c r="D120" s="41" t="inlineStr">
         <is>
+          <t>tanka_id：整数（完全一致）</t>
+        </is>
+      </c>
+    </row>
+    <row r="121" ht="18" customHeight="1">
+      <c r="D121" s="41" t="inlineStr">
+        <is>
           <t>biko：最大500文字（部分一致）</t>
-        </is>
-      </c>
-    </row>
-    <row r="121" ht="36" customHeight="1">
-      <c r="D121" s="41" t="inlineStr">
-        <is>
-          <t>seikyu_kaishi_month_from / seikyu_kaishi_month_to：YYYYMM形式（半角数字6桁）、両方指定時 `from ≦ to`</t>
         </is>
       </c>
     </row>
     <row r="122" ht="36" customHeight="1">
       <c r="D122" s="41" t="inlineStr">
         <is>
-          <t>shoki_dokusya_kaishi_date_from / shoki_dokusya_kaishi_date_to：有効な日付形式（YYYY/MM/DD）、両方指定時 `from ≦ to`</t>
+          <t>seikyu_kaishi_month_from / seikyu_kaishi_month_to：YYYYMM形式（半角数字6桁）、両方指定時 `from ≦ to`</t>
         </is>
       </c>
     </row>
     <row r="123" ht="36" customHeight="1">
       <c r="D123" s="41" t="inlineStr">
         <is>
-          <t>dokusya_chushi_date_from / dokusya_chushi_date_to：有効な日付形式（YYYY/MM/DD）、両方指定時 `from ≦ to`</t>
+          <t>shoki_dokusya_kaishi_date_from / shoki_dokusya_kaishi_date_to：有効な日付形式（YYYY/MM/DD）、両方指定時 `from ≦ to`</t>
         </is>
       </c>
     </row>
     <row r="124" ht="36" customHeight="1">
       <c r="D124" s="41" t="inlineStr">
         <is>
+          <t>dokusya_chushi_date_from / dokusya_chushi_date_to：有効な日付形式（YYYY/MM/DD）、両方指定時 `from ≦ to`</t>
+        </is>
+      </c>
+    </row>
+    <row r="125" ht="36" customHeight="1">
+      <c r="D125" s="41" t="inlineStr">
+        <is>
           <t>joho_henko_tekiyo_date_from / joho_henko_tekiyo_date_to：有効な日付形式（YYYY/MM/DD）、両方指定時 `from ≦ to`</t>
-        </is>
-      </c>
-    </row>
-    <row r="125" ht="18" customHeight="1">
-      <c r="D125" s="41" t="inlineStr">
-        <is>
-          <t>dokusya_shubetsu：1〜3 または未指定</t>
         </is>
       </c>
     </row>
     <row r="126" ht="18" customHeight="1">
       <c r="D126" s="41" t="inlineStr">
         <is>
-          <t>shiharai_hoho：1〜6, 9 または未指定</t>
+          <t>dokusya_shubetsu：1〜3 または未指定</t>
         </is>
       </c>
     </row>
     <row r="127" ht="18" customHeight="1">
       <c r="D127" s="41" t="inlineStr">
         <is>
-          <t>tetsuzuki_shurui：0 または 1 または未指定</t>
+          <t>shiharai_hoho：1〜6, 9 または未指定</t>
         </is>
       </c>
     </row>
     <row r="128" ht="18" customHeight="1">
       <c r="D128" s="41" t="inlineStr">
         <is>
-          <t>denshi_shonin_status：0〜2 または未指定</t>
+          <t>tetsuzuki_shurui：0 または 1 または未指定</t>
         </is>
       </c>
     </row>
     <row r="129" ht="18" customHeight="1">
       <c r="D129" s="41" t="inlineStr">
         <is>
-          <t>page：1以上</t>
+          <t>denshi_shonin_status：0〜2 または未指定</t>
         </is>
       </c>
     </row>
     <row r="130" ht="18" customHeight="1">
       <c r="D130" s="41" t="inlineStr">
         <is>
+          <t>page：1以上</t>
+        </is>
+      </c>
+    </row>
+    <row r="131" ht="18" customHeight="1">
+      <c r="D131" s="41" t="inlineStr">
+        <is>
           <t>per_page：1〜100</t>
         </is>
       </c>
     </row>
-    <row r="131" ht="72" customHeight="1">
-      <c r="D131" s="41" t="inlineStr">
+    <row r="132" ht="72" customHeight="1">
+      <c r="D132" s="41" t="inlineStr">
         <is>
           <t>sort_by：許可カラム一覧に含まれるか確認（kanri_shiten_id, shiten_id, kumiaiin_code, hanbaiten_id, hanbaiten_code, shoki_dokusya_kaishi_date, dokusya_chushi_date, updated_at）</t>
         </is>
       </c>
     </row>
-    <row r="132" ht="18" customHeight="1">
-      <c r="D132" s="41" t="inlineStr">
+    <row r="133" ht="18" customHeight="1">
+      <c r="D133" s="41" t="inlineStr">
         <is>
           <t>sort_order：`asc` または `desc`</t>
-        </is>
-      </c>
-    </row>
-    <row r="133" ht="36" customHeight="1">
-      <c r="C133" s="41" t="inlineStr">
-        <is>
-          <t>デフォルト値を設定する（page=1, per_page=20, sort_by=updated_at, sort_order=desc）</t>
         </is>
       </c>
     </row>
     <row r="134" ht="36" customHeight="1">
       <c r="C134" s="41" t="inlineStr">
         <is>
+          <t>デフォルト値を設定する（page=1, per_page=20, sort_by=updated_at, sort_order=desc）</t>
+        </is>
+      </c>
+    </row>
+    <row r="135" ht="36" customHeight="1">
+      <c r="C135" s="41" t="inlineStr">
+        <is>
           <t>不正なパラメータの場合：HTTP 400 (`BAD_REQUEST`) または HTTP 400 (`VALIDATION_ERROR`)</t>
         </is>
       </c>
     </row>
-    <row r="135" ht="18" customHeight="1">
-      <c r="B135" s="27" t="inlineStr">
+    <row r="136" ht="18" customHeight="1">
+      <c r="B136" s="27" t="inlineStr">
         <is>
           <t>4.2 認証・認可チェック</t>
-        </is>
-      </c>
-    </row>
-    <row r="136" ht="18" customHeight="1">
-      <c r="C136" s="41" t="inlineStr">
-        <is>
-          <t>認証情報を検証する（HTTP-only Cookieセッション）。</t>
         </is>
       </c>
     </row>
     <row r="137" ht="18" customHeight="1">
       <c r="C137" s="41" t="inlineStr">
         <is>
-          <t>未認証の場合：HTTP 401 (`UNAUTHORIZED`)</t>
+          <t>認証情報を検証する（HTTP-only Cookieセッション）。</t>
         </is>
       </c>
     </row>
     <row r="138" ht="18" customHeight="1">
       <c r="C138" s="41" t="inlineStr">
         <is>
-          <t>必要権限: `dokusya.view`</t>
+          <t>未認証の場合：HTTP 401 (`UNAUTHORIZED`)</t>
         </is>
       </c>
     </row>
     <row r="139" ht="18" customHeight="1">
       <c r="C139" s="41" t="inlineStr">
         <is>
-          <t>該当権限保持ロール: CHUOKAI / JA_HONTEN / JA_KANRI_SHITEN</t>
+          <t>必要権限: `dokusya.view`</t>
         </is>
       </c>
     </row>
     <row r="140" ht="18" customHeight="1">
       <c r="C140" s="41" t="inlineStr">
         <is>
-          <t>権限不足の場合：HTTP 403 (`FORBIDDEN`)</t>
+          <t>該当権限保持ロール: CHUOKAI / JA_HONTEN / JA_KANRI_SHITEN</t>
         </is>
       </c>
     </row>
     <row r="141" ht="18" customHeight="1">
       <c r="C141" s="41" t="inlineStr">
         <is>
+          <t>権限不足の場合：HTTP 403 (`FORBIDDEN`)</t>
+        </is>
+      </c>
+    </row>
+    <row r="142" ht="18" customHeight="1">
+      <c r="C142" s="41" t="inlineStr">
+        <is>
           <t>DataScope:</t>
         </is>
       </c>
     </row>
-    <row r="142" ht="54" customHeight="1">
-      <c r="D142" s="41" t="inlineStr">
+    <row r="143" ht="54" customHeight="1">
+      <c r="D143" s="41" t="inlineStr">
         <is>
           <t>`CHUOKAI`：自中央会管轄JAの購読者のみ参照可能（`d.ja_id IN (SELECT ja_id FROM m_ja WHERE chuokai_id = :user_chuokai_id)`）</t>
         </is>
       </c>
     </row>
-    <row r="143" ht="18" customHeight="1">
-      <c r="D143" s="41" t="inlineStr">
+    <row r="144" ht="18" customHeight="1">
+      <c r="D144" s="41" t="inlineStr">
         <is>
           <t>`JA_HONTEN`：自JAの購読者のみ参照可能（`d.ja_id = :user_ja_id`）</t>
         </is>
       </c>
     </row>
-    <row r="144" ht="54" customHeight="1">
-      <c r="D144" s="41" t="inlineStr">
+    <row r="145" ht="54" customHeight="1">
+      <c r="D145" s="41" t="inlineStr">
         <is>
           <t>`JA_KANRI_SHITEN`：自管理支店の購読者のみ参照可能（`d.ja_id = :user_ja_id AND d.kanri_shiten_id = :user_kanri_shiten_id`）</t>
         </is>
       </c>
     </row>
-    <row r="145" ht="36" customHeight="1">
-      <c r="C145" s="41" t="inlineStr">
+    <row r="146" ht="36" customHeight="1">
+      <c r="C146" s="41" t="inlineStr">
         <is>
           <t>DataScope違反（他JA・他管理支店のレコードへのアクセス）の場合：HTTP 403 (`DATA_SCOPE_VIOLATION`)</t>
         </is>
       </c>
     </row>
-    <row r="146" ht="18" customHeight="1">
-      <c r="B146" s="27" t="inlineStr">
+    <row r="147" ht="18" customHeight="1">
+      <c r="B147" s="27" t="inlineStr">
         <is>
           <t>4.3 データ取得条件の設定</t>
         </is>
       </c>
     </row>
-    <row r="147" ht="36" customHeight="1">
-      <c r="C147" s="41" t="inlineStr">
+    <row r="148" ht="36" customHeight="1">
+      <c r="C148" s="41" t="inlineStr">
         <is>
           <t>ログインユーザーのスコープ（role_code, ja_id, kanri_shiten_id, chuokai_id）を取得する。</t>
-        </is>
-      </c>
-    </row>
-    <row r="148" ht="18" customHeight="1">
-      <c r="C148" s="41" t="inlineStr">
-        <is>
-          <t>DataScope を role_code により適用する（4.2 参照）。</t>
         </is>
       </c>
     </row>
     <row r="149" ht="18" customHeight="1">
       <c r="C149" s="41" t="inlineStr">
         <is>
+          <t>DataScope を role_code により適用する（4.2 参照）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="150" ht="18" customHeight="1">
+      <c r="C150" s="41" t="inlineStr">
+        <is>
           <t>検索条件を追加する：</t>
         </is>
       </c>
     </row>
-    <row r="150" ht="36" customHeight="1">
-      <c r="D150" s="41" t="inlineStr">
+    <row r="151" ht="36" customHeight="1">
+      <c r="D151" s="41" t="inlineStr">
         <is>
           <t>kanri_shiten_id 指定時：`d.kanri_shiten_id = :kanri_shiten_id`</t>
         </is>
       </c>
     </row>
-    <row r="151" ht="18" customHeight="1">
-      <c r="D151" s="41" t="inlineStr">
+    <row r="152" ht="18" customHeight="1">
+      <c r="D152" s="41" t="inlineStr">
         <is>
           <t>shiten_id 指定時：`d.shiten_id = :shiten_id`</t>
         </is>
       </c>
     </row>
-    <row r="152" ht="36" customHeight="1">
-      <c r="D152" s="41" t="inlineStr">
+    <row r="153" ht="36" customHeight="1">
+      <c r="D153" s="41" t="inlineStr">
         <is>
           <t>kumiaiin_code 指定時：`d.kumiaiin_code ILIKE '%' || :kumiaiin_code || '%'`</t>
         </is>
       </c>
     </row>
-    <row r="153" ht="72" customHeight="1">
-      <c r="D153" s="41" t="inlineStr">
+    <row r="154" ht="72" customHeight="1">
+      <c r="D154" s="41" t="inlineStr">
         <is>
           <t>bank_branch 指定時：`(d.bank_branch_code ILIKE '%' || :bank_branch || '%' OR d.bank_branch_name ILIKE '%' || :bank_branch || '%')` ※物理カラムは `bank_branch_code` / `bank_branch_name`（レガシー名）</t>
-        </is>
-      </c>
-    </row>
-    <row r="154" ht="90" customHeight="1">
-      <c r="D154" s="41" t="inlineStr">
-        <is>
-          <t>full_name 指定時：`(d.shimei_sei ILIKE '%' || :full_name || '%' OR d.shimei_mei ILIKE '%' || :full_name || '%' OR d.haitatsu_shimei_sei ILIKE '%' || :full_name || '%' OR d.haitatsu_shimei_mei ILIKE '%' || :full_name || '%')`（購読者氏名＋配達先氏名の各カラムに OR 部分一致）</t>
         </is>
       </c>
     </row>
     <row r="155" ht="90" customHeight="1">
       <c r="D155" s="41" t="inlineStr">
         <is>
+          <t>full_name 指定時：`(d.shimei_sei ILIKE '%' || :full_name || '%' OR d.shimei_mei ILIKE '%' || :full_name || '%' OR d.haitatsu_shimei_sei ILIKE '%' || :full_name || '%' OR d.haitatsu_shimei_mei ILIKE '%' || :full_name || '%')`（購読者氏名＋配達先氏名の各カラムに OR 部分一致）</t>
+        </is>
+      </c>
+    </row>
+    <row r="156" ht="90" customHeight="1">
+      <c r="D156" s="41" t="inlineStr">
+        <is>
           <t>full_name_kana 指定時：`(d.shimei_kana_sei ILIKE '%' || :full_name_kana || '%' OR d.shimei_kana_mei ILIKE ... OR d.haitatsu_shimei_kana_sei ILIKE ... OR d.haitatsu_shimei_kana_mei ILIKE ...)`（購読者かな氏名＋配達先かな氏名の各カラムに OR 部分一致）</t>
         </is>
       </c>
     </row>
-    <row r="156" ht="108" customHeight="1">
-      <c r="D156" s="41" t="inlineStr">
+    <row r="157" ht="108" customHeight="1">
+      <c r="D157" s="41" t="inlineStr">
         <is>
           <t>renrakusaki 指定時：`(d.renrakusaki_1 ILIKE '%' || :renrakusaki || '%' OR d.haitatsu_renrakusaki_1 ILIKE '%' || :renrakusaki || '%' OR d.renrakusaki_2 ILIKE '%' || :renrakusaki || '%' OR d.haitatsu_renrakusaki_2 ILIKE '%' || :renrakusaki || '%')`（購読者連絡先1/2＋配達先連絡先1/2に OR 部分一致）</t>
         </is>
       </c>
     </row>
-    <row r="157" ht="90" customHeight="1">
-      <c r="D157" s="41" t="inlineStr">
+    <row r="158" ht="90" customHeight="1">
+      <c r="D158" s="41" t="inlineStr">
         <is>
           <t>haitatsu 指定時：配達先住所4項目（`haitatsu_todofuken_code` / `haitatsu_shikuchoson` / `haitatsu_chome_banchi` / `haitatsu_tatemono_mei`）＋購読者住所4項目（`todofuken_code` / `shikuchoson` / `chome_banchi` / `tatemono_mei`）の各カラムに OR 部分一致</t>
-        </is>
-      </c>
-    </row>
-    <row r="158" ht="18" customHeight="1">
-      <c r="D158" s="41" t="inlineStr">
-        <is>
-          <t>hanbaiten_id 指定時：`d.hanbaiten_id = :hanbaiten_id`</t>
         </is>
       </c>
     </row>
     <row r="159" ht="18" customHeight="1">
       <c r="D159" s="41" t="inlineStr">
         <is>
+          <t>hanbaiten_id 指定時：`d.hanbaiten_id = :hanbaiten_id`</t>
+        </is>
+      </c>
+    </row>
+    <row r="160" ht="18" customHeight="1">
+      <c r="D160" s="41" t="inlineStr">
+        <is>
           <t>email 指定時：部分一致</t>
         </is>
       </c>
     </row>
-    <row r="160" ht="36" customHeight="1">
-      <c r="D160" s="41" t="inlineStr">
+    <row r="161" ht="36" customHeight="1">
+      <c r="D161" s="41" t="inlineStr">
         <is>
           <t>yubin_kubun 指定時：`d.yubin_kubun = :yubin_kubun`（完全一致）</t>
-        </is>
-      </c>
-    </row>
-    <row r="161" ht="18" customHeight="1">
-      <c r="D161" s="41" t="inlineStr">
-        <is>
-          <t>tanka_id 指定時：`d.tanka_id = :tanka_id`（完全一致）</t>
         </is>
       </c>
     </row>
     <row r="162" ht="18" customHeight="1">
       <c r="D162" s="41" t="inlineStr">
         <is>
+          <t>tanka_id 指定時：`d.tanka_id = :tanka_id`（完全一致）</t>
+        </is>
+      </c>
+    </row>
+    <row r="163" ht="18" customHeight="1">
+      <c r="D163" s="41" t="inlineStr">
+        <is>
           <t>biko 指定時：`d.biko ILIKE '%' || :biko || '%'`（部分一致）</t>
         </is>
       </c>
     </row>
-    <row r="163" ht="72" customHeight="1">
-      <c r="D163" s="41" t="inlineStr">
+    <row r="164" ht="72" customHeight="1">
+      <c r="D164" s="41" t="inlineStr">
         <is>
           <t>seikyu_kaishi_month_from / seikyu_kaishi_month_to 指定時：YYYYMM の範囲検索（未設定＝空文字の購読者は除外）。from 指定時 `d.seikyu_kaishi_month &gt;= :seikyu_from`、to 指定時 `d.seikyu_kaishi_month &lt;= :seikyu_to`（6桁固定のため辞書順比較が数値順と一致）</t>
-        </is>
-      </c>
-    </row>
-    <row r="164" ht="36" customHeight="1">
-      <c r="D164" s="41" t="inlineStr">
-        <is>
-          <t>shoki_dokusya_kaishi_date_from 指定時：`d.shoki_dokusya_kaishi_date &gt;= :shoki_dokusya_kaishi_date_from`</t>
         </is>
       </c>
     </row>
     <row r="165" ht="36" customHeight="1">
       <c r="D165" s="41" t="inlineStr">
         <is>
-          <t>shoki_dokusya_kaishi_date_to 指定時：`d.shoki_dokusya_kaishi_date &lt;= :shoki_dokusya_kaishi_date_to`</t>
+          <t>shoki_dokusya_kaishi_date_from 指定時：`d.shoki_dokusya_kaishi_date &gt;= :shoki_dokusya_kaishi_date_from`</t>
         </is>
       </c>
     </row>
     <row r="166" ht="36" customHeight="1">
       <c r="D166" s="41" t="inlineStr">
         <is>
-          <t>dokusya_chushi_date_from 指定時：`d.dokusya_chushi_date &gt;= :dokusya_chushi_date_from`</t>
+          <t>shoki_dokusya_kaishi_date_to 指定時：`d.shoki_dokusya_kaishi_date &lt;= :shoki_dokusya_kaishi_date_to`</t>
         </is>
       </c>
     </row>
     <row r="167" ht="36" customHeight="1">
       <c r="D167" s="41" t="inlineStr">
         <is>
-          <t>dokusya_chushi_date_to 指定時：`d.dokusya_chushi_date &lt;= :dokusya_chushi_date_to`</t>
+          <t>dokusya_chushi_date_from 指定時：`d.dokusya_chushi_date &gt;= :dokusya_chushi_date_from`</t>
         </is>
       </c>
     </row>
     <row r="168" ht="36" customHeight="1">
       <c r="D168" s="41" t="inlineStr">
         <is>
+          <t>dokusya_chushi_date_to 指定時：`d.dokusya_chushi_date &lt;= :dokusya_chushi_date_to`</t>
+        </is>
+      </c>
+    </row>
+    <row r="169" ht="36" customHeight="1">
+      <c r="D169" s="41" t="inlineStr">
+        <is>
           <t>dokusya_shubetsu / shiharai_hoho / tetsuzuki_shurui / denshi_shonin_status 指定時：それぞれ等価条件</t>
         </is>
       </c>
     </row>
-    <row r="169" ht="90" customHeight="1">
-      <c r="D169" s="41" t="inlineStr">
+    <row r="170" ht="90" customHeight="1">
+      <c r="D170" s="41" t="inlineStr">
         <is>
           <t>active_tanka_flg 指定時：`true`=参照購読料単価が有効(active_flg=TRUE)の購読者のみ、`false`=失効(active_flg=FALSE)の購読者のみ抽出（省略時は絞り込まない）。`tanka_id` は m_tanka の PK のため INNER JOIN で行数は増えない（0/1件）。JOIN 条件の active_flg はパラメータ（`:activeTankaFlg`）でバインドする。</t>
         </is>
       </c>
     </row>
-    <row r="170" ht="90" customHeight="1">
-      <c r="C170" s="42" t="inlineStr">
+    <row r="171" ht="90" customHeight="1">
+      <c r="C171" s="42" t="inlineStr">
         <is>
           <t xml:space="preserve">    INNER JOIN m_tanka mti
       ON mti.tanka_id = d.tanka_id
      AND mti.tanka_type = 1
      AND mti.deleted_at IS NULL
-     AND mti.active_flg = FALSE</t>
-        </is>
-      </c>
-      <c r="D170" s="10" t="n"/>
-      <c r="E170" s="10" t="n"/>
-      <c r="F170" s="10" t="n"/>
-      <c r="G170" s="10" t="n"/>
-      <c r="H170" s="10" t="n"/>
-      <c r="I170" s="10" t="n"/>
-      <c r="J170" s="10" t="n"/>
-      <c r="K170" s="10" t="n"/>
-      <c r="L170" s="10" t="n"/>
-      <c r="M170" s="10" t="n"/>
-      <c r="N170" s="10" t="n"/>
-      <c r="O170" s="10" t="n"/>
-      <c r="P170" s="10" t="n"/>
-      <c r="Q170" s="10" t="n"/>
-      <c r="R170" s="10" t="n"/>
-      <c r="S170" s="10" t="n"/>
-      <c r="T170" s="10" t="n"/>
-      <c r="U170" s="10" t="n"/>
-      <c r="V170" s="10" t="n"/>
-      <c r="W170" s="10" t="n"/>
-      <c r="X170" s="10" t="n"/>
-      <c r="Y170" s="10" t="n"/>
-      <c r="Z170" s="10" t="n"/>
-      <c r="AA170" s="10" t="n"/>
-      <c r="AB170" s="10" t="n"/>
-      <c r="AC170" s="10" t="n"/>
-      <c r="AD170" s="10" t="n"/>
-      <c r="AE170" s="10" t="n"/>
-      <c r="AF170" s="10" t="n"/>
-      <c r="AG170" s="10" t="n"/>
-      <c r="AH170" s="10" t="n"/>
-      <c r="AI170" s="10" t="n"/>
-      <c r="AJ170" s="10" t="n"/>
-      <c r="AK170" s="11" t="n"/>
-    </row>
-    <row r="171" ht="36" customHeight="1">
-      <c r="C171" s="41" t="inlineStr">
+     AND mti.active_flg = :activeTankaFlg</t>
+        </is>
+      </c>
+      <c r="D171" s="10" t="n"/>
+      <c r="E171" s="10" t="n"/>
+      <c r="F171" s="10" t="n"/>
+      <c r="G171" s="10" t="n"/>
+      <c r="H171" s="10" t="n"/>
+      <c r="I171" s="10" t="n"/>
+      <c r="J171" s="10" t="n"/>
+      <c r="K171" s="10" t="n"/>
+      <c r="L171" s="10" t="n"/>
+      <c r="M171" s="10" t="n"/>
+      <c r="N171" s="10" t="n"/>
+      <c r="O171" s="10" t="n"/>
+      <c r="P171" s="10" t="n"/>
+      <c r="Q171" s="10" t="n"/>
+      <c r="R171" s="10" t="n"/>
+      <c r="S171" s="10" t="n"/>
+      <c r="T171" s="10" t="n"/>
+      <c r="U171" s="10" t="n"/>
+      <c r="V171" s="10" t="n"/>
+      <c r="W171" s="10" t="n"/>
+      <c r="X171" s="10" t="n"/>
+      <c r="Y171" s="10" t="n"/>
+      <c r="Z171" s="10" t="n"/>
+      <c r="AA171" s="10" t="n"/>
+      <c r="AB171" s="10" t="n"/>
+      <c r="AC171" s="10" t="n"/>
+      <c r="AD171" s="10" t="n"/>
+      <c r="AE171" s="10" t="n"/>
+      <c r="AF171" s="10" t="n"/>
+      <c r="AG171" s="10" t="n"/>
+      <c r="AH171" s="10" t="n"/>
+      <c r="AI171" s="10" t="n"/>
+      <c r="AJ171" s="10" t="n"/>
+      <c r="AK171" s="11" t="n"/>
+    </row>
+    <row r="172" ht="36" customHeight="1">
+      <c r="C172" s="41" t="inlineStr">
         <is>
           <t>適用日（joho_henko_tekiyo_date_from / joho_henko_tekiyo_date_to）の処理：</t>
         </is>
       </c>
     </row>
-    <row r="172" ht="36" customHeight="1">
-      <c r="D172" s="41" t="inlineStr">
+    <row r="173" ht="36" customHeight="1">
+      <c r="D173" s="41" t="inlineStr">
         <is>
           <t>両方空欄の場合：購読者履歴の最新データフラグ（saishin_data_flg=TRUE）のレコードを抽出</t>
         </is>
       </c>
     </row>
-    <row r="173" ht="54" customHeight="1">
-      <c r="D173" s="41" t="inlineStr">
+    <row r="174" ht="54" customHeight="1">
+      <c r="D174" s="41" t="inlineStr">
         <is>
           <t>いずれか入力されている場合：購読者履歴テーブル（`t_dokusya_rireki`）の変更適用日が `[from, to]` の範囲内のレコードを抽出（from のみ指定 → `&gt;= from`、to のみ指定 → `&lt;= to`、両方 → 範囲内）</t>
         </is>
       </c>
     </row>
-    <row r="174" ht="18" customHeight="1">
-      <c r="B174" s="27" t="inlineStr">
+    <row r="175" ht="18" customHeight="1">
+      <c r="B175" s="27" t="inlineStr">
         <is>
           <t>4.4 データ件数の取得</t>
         </is>
       </c>
     </row>
-    <row r="175" ht="342" customHeight="1">
-      <c r="C175" s="42" t="inlineStr">
+    <row r="176" ht="342" customHeight="1">
+      <c r="C176" s="42" t="inlineStr">
         <is>
           <t>SELECT COUNT(*)
 FROM t_dokusya d
@@ -9697,79 +9874,50 @@
   /* ... 他の検索条件は省略 */</t>
         </is>
       </c>
-      <c r="D175" s="10" t="n"/>
-      <c r="E175" s="10" t="n"/>
-      <c r="F175" s="10" t="n"/>
-      <c r="G175" s="10" t="n"/>
-      <c r="H175" s="10" t="n"/>
-      <c r="I175" s="10" t="n"/>
-      <c r="J175" s="10" t="n"/>
-      <c r="K175" s="10" t="n"/>
-      <c r="L175" s="10" t="n"/>
-      <c r="M175" s="10" t="n"/>
-      <c r="N175" s="10" t="n"/>
-      <c r="O175" s="10" t="n"/>
-      <c r="P175" s="10" t="n"/>
-      <c r="Q175" s="10" t="n"/>
-      <c r="R175" s="10" t="n"/>
-      <c r="S175" s="10" t="n"/>
-      <c r="T175" s="10" t="n"/>
-      <c r="U175" s="10" t="n"/>
-      <c r="V175" s="10" t="n"/>
-      <c r="W175" s="10" t="n"/>
-      <c r="X175" s="10" t="n"/>
-      <c r="Y175" s="10" t="n"/>
-      <c r="Z175" s="10" t="n"/>
-      <c r="AA175" s="10" t="n"/>
-      <c r="AB175" s="10" t="n"/>
-      <c r="AC175" s="10" t="n"/>
-      <c r="AD175" s="10" t="n"/>
-      <c r="AE175" s="10" t="n"/>
-      <c r="AF175" s="10" t="n"/>
-      <c r="AG175" s="10" t="n"/>
-      <c r="AH175" s="10" t="n"/>
-      <c r="AI175" s="10" t="n"/>
-      <c r="AJ175" s="10" t="n"/>
-      <c r="AK175" s="11" t="n"/>
-    </row>
-    <row r="176" ht="18" customHeight="1">
-      <c r="B176" s="27" t="inlineStr">
-        <is>
-          <t>4.5 データ取得</t>
-        </is>
-      </c>
-    </row>
-    <row r="177" ht="409" customHeight="1">
+      <c r="D176" s="10" t="n"/>
+      <c r="E176" s="10" t="n"/>
+      <c r="F176" s="10" t="n"/>
+      <c r="G176" s="10" t="n"/>
+      <c r="H176" s="10" t="n"/>
+      <c r="I176" s="10" t="n"/>
+      <c r="J176" s="10" t="n"/>
+      <c r="K176" s="10" t="n"/>
+      <c r="L176" s="10" t="n"/>
+      <c r="M176" s="10" t="n"/>
+      <c r="N176" s="10" t="n"/>
+      <c r="O176" s="10" t="n"/>
+      <c r="P176" s="10" t="n"/>
+      <c r="Q176" s="10" t="n"/>
+      <c r="R176" s="10" t="n"/>
+      <c r="S176" s="10" t="n"/>
+      <c r="T176" s="10" t="n"/>
+      <c r="U176" s="10" t="n"/>
+      <c r="V176" s="10" t="n"/>
+      <c r="W176" s="10" t="n"/>
+      <c r="X176" s="10" t="n"/>
+      <c r="Y176" s="10" t="n"/>
+      <c r="Z176" s="10" t="n"/>
+      <c r="AA176" s="10" t="n"/>
+      <c r="AB176" s="10" t="n"/>
+      <c r="AC176" s="10" t="n"/>
+      <c r="AD176" s="10" t="n"/>
+      <c r="AE176" s="10" t="n"/>
+      <c r="AF176" s="10" t="n"/>
+      <c r="AG176" s="10" t="n"/>
+      <c r="AH176" s="10" t="n"/>
+      <c r="AI176" s="10" t="n"/>
+      <c r="AJ176" s="10" t="n"/>
+      <c r="AK176" s="11" t="n"/>
+    </row>
+    <row r="177" ht="108" customHeight="1">
       <c r="C177" s="42" t="inlineStr">
         <is>
-          <t>SELECT d.dokusya_id, d.ja_id,
-       d.kanri_shiten_id, ks.kanri_shiten_name,
-       d.shiten_id, s.shiten_name,
-       d.kumiaiin_code,
-       (d.shimei_sei || ' ' || d.shimei_mei) AS full_name,
-       (d.shimei_kana_sei || ' ' || d.shimei_kana_mei) AS full_name_kana,
-       d.tetsuzuki_shurui,
-       d.renrakusaki_1, d.renrakusaki_2,
-       (d.haitatsu_shimei_sei || ' ' || d.haitatsu_shimei_mei) AS haitatsu_full_name,
-       d.haitatsu_yubin_no,
-       (COALESCE(t.todofuken_name, '') || d.haitatsu_shikuchoson || d.haitatsu_chome_banchi || d.haitatsu_tatemono_mei) AS haitatsu,
-       d.hanbaiten_id, h.hanbaiten_code, h.hanbaiten_name,
-       d.dokusya_shubetsu, d.shiharai_hoho, d.denshi_shonin_status,
-       d.shoki_dokusya_kaishi_date, d.dokusya_chushi_date,
-       /* is_read_only: 電子版クレジットカード決済者（dokusya_shubetsu=2 AND shiharai_hoho=6）または併読者（dokusya_shubetsu=3） */
-       (
-         (d.dokusya_shubetsu = 2 AND d.shiharai_hoho = 6)
-         OR d.dokusya_shubetsu = 3
-       ) AS is_read_only
-FROM t_dokusya d
-LEFT JOIN m_kanri_shiten ks ON ks.kanri_shiten_id = d.kanri_shiten_id AND ks.deleted_at IS NULL
-LEFT JOIN m_shiten s ON s.shiten_id = d.shiten_id AND s.deleted_at IS NULL
-LEFT JOIN m_hanbaiten h ON h.hanbaiten_id = d.hanbaiten_id AND h.deleted_at IS NULL
-LEFT JOIN m_todofuken t ON t.todofuken_code = d.haitatsu_todofuken_code
-WHERE d.deleted_at IS NULL
-  /* DataScope + 検索条件 は 4.4 と同じ */
-ORDER BY :sort_by :sort_order
-LIMIT :per_page OFFSET (:page - 1) * :per_page</t>
+          <t>SELECT COALESCE(SUM(t.dokusya_busu), 0)::int AS total_busu
+FROM (
+  SELECT DISTINCT d.dokusya_id, d.dokusya_busu
+  FROM t_dokusya d
+  /* 4.4 と同一の JOIN・DataScope・検索条件 */
+) t;</t>
         </is>
       </c>
       <c r="D177" s="10" t="n"/>
@@ -9807,64 +9955,150 @@
       <c r="AJ177" s="10" t="n"/>
       <c r="AK177" s="11" t="n"/>
     </row>
-    <row r="178" ht="72" customHeight="1">
-      <c r="C178" s="41" t="inlineStr">
+    <row r="178" ht="18" customHeight="1">
+      <c r="B178" s="27" t="inlineStr">
+        <is>
+          <t>4.5 データ取得</t>
+        </is>
+      </c>
+    </row>
+    <row r="179" ht="409" customHeight="1">
+      <c r="C179" s="42" t="inlineStr">
+        <is>
+          <t>SELECT d.dokusya_id, d.ja_id,
+       d.kanri_shiten_id, ks.kanri_shiten_name,
+       d.shiten_id, s.shiten_name,
+       d.kumiaiin_code,
+       (d.shimei_sei || ' ' || d.shimei_mei) AS full_name,
+       (d.shimei_kana_sei || ' ' || d.shimei_kana_mei) AS full_name_kana,
+       d.tetsuzuki_shurui,
+       d.renrakusaki_1, d.renrakusaki_2,
+       (d.haitatsu_shimei_sei || ' ' || d.haitatsu_shimei_mei) AS haitatsu_full_name,
+       d.haitatsu_yubin_no,
+       (COALESCE(t.todofuken_name, '') || d.haitatsu_shikuchoson || d.haitatsu_chome_banchi || d.haitatsu_tatemono_mei) AS haitatsu,
+       d.hanbaiten_id, h.hanbaiten_code, h.hanbaiten_name,
+       d.dokusya_shubetsu, d.shiharai_hoho, d.denshi_shonin_status,
+       d.shoki_dokusya_kaishi_date, d.dokusya_chushi_date,
+       /* is_read_only（顧客要件2026-08追補・3条件のOR）:
+          ①併読(dokusya_shubetsu=3)
+          ②電子版クレジットカード決済者(dokusya_shubetsu=2 AND shiharai_hoho=6)
+          ③電子版かつ電子版読者管理システム未連携(denshi_kaiin_id IS NULL)かつ
+            参照単価が非キャンペーン(COALESCE(tk.campaign_flg, false)=false。
+            単価未割当＝tk が LEFT JOIN で NULL のときも非キャンペーン扱い＝read-only側) */
+       (
+         d.dokusya_shubetsu = 3
+         OR (d.dokusya_shubetsu = 2 AND d.shiharai_hoho = 6)
+         OR (
+           d.dokusya_shubetsu = 2
+           AND d.denshi_kaiin_id IS NULL
+           AND COALESCE(tk.campaign_flg, false) = false
+         )
+       ) AS is_read_only
+FROM t_dokusya d
+LEFT JOIN m_kanri_shiten ks ON ks.kanri_shiten_id = d.kanri_shiten_id AND ks.deleted_at IS NULL
+LEFT JOIN m_shiten s ON s.shiten_id = d.shiten_id AND s.deleted_at IS NULL
+LEFT JOIN m_hanbaiten h ON h.hanbaiten_id = d.hanbaiten_id AND h.deleted_at IS NULL
+LEFT JOIN m_todofuken t ON t.todofuken_code = d.haitatsu_todofuken_code
+LEFT JOIN m_tanka tk ON tk.tanka_id = d.tanka_id AND tk.deleted_at IS NULL
+WHERE d.deleted_at IS NULL
+  /* DataScope + 検索条件 は 4.4 と同じ */
+ORDER BY :sort_by :sort_order
+LIMIT :per_page OFFSET (:page - 1) * :per_page</t>
+        </is>
+      </c>
+      <c r="D179" s="10" t="n"/>
+      <c r="E179" s="10" t="n"/>
+      <c r="F179" s="10" t="n"/>
+      <c r="G179" s="10" t="n"/>
+      <c r="H179" s="10" t="n"/>
+      <c r="I179" s="10" t="n"/>
+      <c r="J179" s="10" t="n"/>
+      <c r="K179" s="10" t="n"/>
+      <c r="L179" s="10" t="n"/>
+      <c r="M179" s="10" t="n"/>
+      <c r="N179" s="10" t="n"/>
+      <c r="O179" s="10" t="n"/>
+      <c r="P179" s="10" t="n"/>
+      <c r="Q179" s="10" t="n"/>
+      <c r="R179" s="10" t="n"/>
+      <c r="S179" s="10" t="n"/>
+      <c r="T179" s="10" t="n"/>
+      <c r="U179" s="10" t="n"/>
+      <c r="V179" s="10" t="n"/>
+      <c r="W179" s="10" t="n"/>
+      <c r="X179" s="10" t="n"/>
+      <c r="Y179" s="10" t="n"/>
+      <c r="Z179" s="10" t="n"/>
+      <c r="AA179" s="10" t="n"/>
+      <c r="AB179" s="10" t="n"/>
+      <c r="AC179" s="10" t="n"/>
+      <c r="AD179" s="10" t="n"/>
+      <c r="AE179" s="10" t="n"/>
+      <c r="AF179" s="10" t="n"/>
+      <c r="AG179" s="10" t="n"/>
+      <c r="AH179" s="10" t="n"/>
+      <c r="AI179" s="10" t="n"/>
+      <c r="AJ179" s="10" t="n"/>
+      <c r="AK179" s="11" t="n"/>
+    </row>
+    <row r="180" ht="72" customHeight="1">
+      <c r="C180" s="41" t="inlineStr">
         <is>
           <t>適用日（joho_henko_tekiyo_date_from / joho_henko_tekiyo_date_to）が入力されている場合は、`t_dokusya_rireki` から該当範囲内の履歴レコードを取得する（履歴テーブルへの JOIN または CTE で実装）。両方空欄の場合は `saishin_data_flg = TRUE` のレコードを使用する。</t>
         </is>
       </c>
     </row>
-    <row r="179" ht="18" customHeight="1">
-      <c r="B179" s="27" t="inlineStr">
+    <row r="181" ht="18" customHeight="1">
+      <c r="B181" s="27" t="inlineStr">
         <is>
           <t>4.6 レスポンス生成</t>
         </is>
       </c>
     </row>
-    <row r="180" ht="18" customHeight="1">
-      <c r="C180" s="41" t="inlineStr">
+    <row r="182" ht="18" customHeight="1">
+      <c r="C182" s="41" t="inlineStr">
         <is>
           <t>取得結果を data 配列として返却する。</t>
-        </is>
-      </c>
-    </row>
-    <row r="181" ht="36" customHeight="1">
-      <c r="C181" s="41" t="inlineStr">
-        <is>
-          <t>`meta` オブジェクトにページネーション情報（total / page / per_page / total_pages）を含める。</t>
-        </is>
-      </c>
-    </row>
-    <row r="182" ht="36" customHeight="1">
-      <c r="C182" s="41" t="inlineStr">
-        <is>
-          <t>`is_read_only` フラグは BE 側で算出し、FE 側で「編集」「削除」ボタンの活性制御に使用する。HTTP 200。</t>
         </is>
       </c>
     </row>
     <row r="183" ht="36" customHeight="1">
       <c r="C183" s="41" t="inlineStr">
         <is>
+          <t>`meta` オブジェクトにページネーション情報（total / page / per_page / total_pages）および購読部数合計（`total_busu`）を含める。</t>
+        </is>
+      </c>
+    </row>
+    <row r="184" ht="36" customHeight="1">
+      <c r="C184" s="41" t="inlineStr">
+        <is>
+          <t>`is_read_only` フラグは BE 側で算出し、FE 側で「編集」「削除」ボタンの活性制御に使用する。HTTP 200。</t>
+        </is>
+      </c>
+    </row>
+    <row r="185" ht="36" customHeight="1">
+      <c r="C185" s="41" t="inlineStr">
+        <is>
           <t>「削除」ボタンは `is_read_only` に加えて `dokusya_shubetsu = 1`（紙版）のときだけ活性にする（顧客要件2026-08）。</t>
         </is>
       </c>
     </row>
-    <row r="184" ht="18" customHeight="1">
-      <c r="B184" s="27" t="inlineStr">
+    <row r="186" ht="18" customHeight="1">
+      <c r="B186" s="27" t="inlineStr">
         <is>
           <t>4.7 例外処理</t>
         </is>
       </c>
     </row>
-    <row r="185" ht="18" customHeight="1">
-      <c r="C185" s="41" t="inlineStr">
+    <row r="187" ht="18" customHeight="1">
+      <c r="C187" s="41" t="inlineStr">
         <is>
           <t>DB接続エラー等の場合：HTTP 500 (`INTERNAL_SERVER_ERROR`)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="543">
+  <mergeCells count="550">
     <mergeCell ref="Y46:AB46"/>
     <mergeCell ref="AF65:AK65"/>
     <mergeCell ref="T24:X24"/>
@@ -9873,16 +10107,22 @@
     <mergeCell ref="Q78:S78"/>
     <mergeCell ref="M72:P72"/>
     <mergeCell ref="Y41:AB41"/>
+    <mergeCell ref="B181:AK181"/>
     <mergeCell ref="Q80:S80"/>
     <mergeCell ref="D62:L62"/>
     <mergeCell ref="T68:X68"/>
     <mergeCell ref="M59:P59"/>
+    <mergeCell ref="B147:AK147"/>
     <mergeCell ref="Y43:AB43"/>
     <mergeCell ref="B8:I8"/>
+    <mergeCell ref="C100:AK100"/>
     <mergeCell ref="J1:P1"/>
     <mergeCell ref="AH2:AK3"/>
     <mergeCell ref="D64:L64"/>
+    <mergeCell ref="C94:AK94"/>
+    <mergeCell ref="M88:P88"/>
     <mergeCell ref="M82:P82"/>
+    <mergeCell ref="C142:AK142"/>
     <mergeCell ref="B10:I10"/>
     <mergeCell ref="AF84:AK84"/>
     <mergeCell ref="AF22:AK22"/>
@@ -9925,12 +10165,11 @@
     <mergeCell ref="T76:X76"/>
     <mergeCell ref="Y51:AB51"/>
     <mergeCell ref="T69:X69"/>
+    <mergeCell ref="C150:AK150"/>
     <mergeCell ref="D65:L65"/>
     <mergeCell ref="M27:P27"/>
-    <mergeCell ref="B184:AK184"/>
     <mergeCell ref="AF25:AK25"/>
     <mergeCell ref="Q35:S35"/>
-    <mergeCell ref="C145:AK145"/>
     <mergeCell ref="T45:X45"/>
     <mergeCell ref="A5:AK5"/>
     <mergeCell ref="Y33:AB33"/>
@@ -9941,7 +10180,6 @@
     <mergeCell ref="AC25:AE25"/>
     <mergeCell ref="D152:AK152"/>
     <mergeCell ref="T87:X87"/>
-    <mergeCell ref="B179:AK179"/>
     <mergeCell ref="B11:I11"/>
     <mergeCell ref="Q49:S49"/>
     <mergeCell ref="Q36:S36"/>
@@ -9950,8 +10188,8 @@
     <mergeCell ref="C30:L30"/>
     <mergeCell ref="Q30:S30"/>
     <mergeCell ref="AF31:AK31"/>
-    <mergeCell ref="B174:AK174"/>
     <mergeCell ref="C134:AK134"/>
+    <mergeCell ref="T88:X88"/>
     <mergeCell ref="T51:X51"/>
     <mergeCell ref="T26:X26"/>
     <mergeCell ref="Y39:AB39"/>
@@ -9964,28 +10202,29 @@
     <mergeCell ref="C41:L41"/>
     <mergeCell ref="M75:P75"/>
     <mergeCell ref="M40:P40"/>
+    <mergeCell ref="D170:AK170"/>
     <mergeCell ref="Q62:S62"/>
-    <mergeCell ref="B95:I95"/>
     <mergeCell ref="C56:L56"/>
-    <mergeCell ref="B89:I89"/>
     <mergeCell ref="Y69:AE69"/>
     <mergeCell ref="D80:L80"/>
     <mergeCell ref="D120:AK120"/>
     <mergeCell ref="C43:L43"/>
-    <mergeCell ref="A108:AK108"/>
+    <mergeCell ref="D145:AK145"/>
     <mergeCell ref="J16:M16"/>
+    <mergeCell ref="C84:C88"/>
     <mergeCell ref="AF57:AK57"/>
     <mergeCell ref="D163:AK163"/>
     <mergeCell ref="Q64:S64"/>
     <mergeCell ref="T77:X77"/>
     <mergeCell ref="M41:P41"/>
+    <mergeCell ref="B90:I90"/>
     <mergeCell ref="M24:P24"/>
     <mergeCell ref="T35:X35"/>
     <mergeCell ref="Y23:AB23"/>
     <mergeCell ref="M66:P66"/>
+    <mergeCell ref="B175:AK175"/>
     <mergeCell ref="D58:L58"/>
     <mergeCell ref="Y87:AE87"/>
-    <mergeCell ref="C147:AK147"/>
     <mergeCell ref="AF75:AK75"/>
     <mergeCell ref="Q57:S57"/>
     <mergeCell ref="AF28:AK28"/>
@@ -10004,7 +10243,6 @@
     <mergeCell ref="D160:AK160"/>
     <mergeCell ref="Y22:AB22"/>
     <mergeCell ref="Q52:S52"/>
-    <mergeCell ref="B109:AK109"/>
     <mergeCell ref="Q39:S39"/>
     <mergeCell ref="M46:P46"/>
     <mergeCell ref="M37:P37"/>
@@ -10012,11 +10250,13 @@
     <mergeCell ref="D86:L86"/>
     <mergeCell ref="M61:P61"/>
     <mergeCell ref="AC23:AE23"/>
-    <mergeCell ref="C102:AK102"/>
     <mergeCell ref="Y77:AE77"/>
+    <mergeCell ref="C179:AK179"/>
     <mergeCell ref="J18:M18"/>
+    <mergeCell ref="B96:I96"/>
     <mergeCell ref="C57:L57"/>
     <mergeCell ref="D121:AK121"/>
+    <mergeCell ref="A109:AK109"/>
     <mergeCell ref="J17:M17"/>
     <mergeCell ref="C49:L49"/>
     <mergeCell ref="M56:P56"/>
@@ -10027,7 +10267,6 @@
     <mergeCell ref="AF23:AK23"/>
     <mergeCell ref="AF50:AK50"/>
     <mergeCell ref="Q70:S70"/>
-    <mergeCell ref="B98:I98"/>
     <mergeCell ref="Y72:AE72"/>
     <mergeCell ref="C42:L42"/>
     <mergeCell ref="D115:AK115"/>
@@ -10036,6 +10275,7 @@
     <mergeCell ref="T22:X22"/>
     <mergeCell ref="AF34:AK34"/>
     <mergeCell ref="T75:X75"/>
+    <mergeCell ref="Y88:AE88"/>
     <mergeCell ref="M25:P25"/>
     <mergeCell ref="AF49:AK49"/>
     <mergeCell ref="T86:X86"/>
@@ -10063,6 +10303,7 @@
     <mergeCell ref="M87:P87"/>
     <mergeCell ref="AC31:AE31"/>
     <mergeCell ref="D169:AK169"/>
+    <mergeCell ref="C103:AK103"/>
     <mergeCell ref="M64:P64"/>
     <mergeCell ref="C180:AK180"/>
     <mergeCell ref="AF71:AK71"/>
@@ -10085,18 +10326,16 @@
     <mergeCell ref="Y49:AB49"/>
     <mergeCell ref="T48:X48"/>
     <mergeCell ref="AF68:AK68"/>
-    <mergeCell ref="C96:AK96"/>
     <mergeCell ref="A20:AK20"/>
     <mergeCell ref="AF42:AK42"/>
     <mergeCell ref="Q84:S84"/>
-    <mergeCell ref="D142:AK142"/>
+    <mergeCell ref="C187:AK187"/>
     <mergeCell ref="M34:P34"/>
     <mergeCell ref="M83:P83"/>
     <mergeCell ref="AF79:AK79"/>
     <mergeCell ref="M49:P49"/>
     <mergeCell ref="M39:P39"/>
     <mergeCell ref="D144:AK144"/>
-    <mergeCell ref="C93:AK93"/>
     <mergeCell ref="Y30:AB30"/>
     <mergeCell ref="D119:AK119"/>
     <mergeCell ref="AC52:AE52"/>
@@ -10110,15 +10349,14 @@
     <mergeCell ref="AC32:AE32"/>
     <mergeCell ref="AC37:AE37"/>
     <mergeCell ref="T43:X43"/>
-    <mergeCell ref="B135:AK135"/>
     <mergeCell ref="Y31:AB31"/>
     <mergeCell ref="AC47:AE47"/>
     <mergeCell ref="T36:X36"/>
     <mergeCell ref="AF63:AK63"/>
     <mergeCell ref="Q79:S79"/>
+    <mergeCell ref="C111:AK111"/>
     <mergeCell ref="Y61:AE61"/>
     <mergeCell ref="AF74:AK74"/>
-    <mergeCell ref="C175:AK175"/>
     <mergeCell ref="Q81:S81"/>
     <mergeCell ref="D130:AK130"/>
     <mergeCell ref="T25:X25"/>
@@ -10130,15 +10368,14 @@
     <mergeCell ref="Q74:S74"/>
     <mergeCell ref="T62:X62"/>
     <mergeCell ref="D132:AK132"/>
-    <mergeCell ref="B146:AK146"/>
     <mergeCell ref="Q76:S76"/>
     <mergeCell ref="AC27:AE27"/>
     <mergeCell ref="C137:AK137"/>
     <mergeCell ref="T64:X64"/>
     <mergeCell ref="Y44:AB44"/>
-    <mergeCell ref="C90:AK90"/>
+    <mergeCell ref="C139:AK139"/>
     <mergeCell ref="D60:L60"/>
-    <mergeCell ref="C139:AK139"/>
+    <mergeCell ref="B110:AK110"/>
     <mergeCell ref="Q28:S28"/>
     <mergeCell ref="M84:P84"/>
     <mergeCell ref="M22:P22"/>
@@ -10161,6 +10398,7 @@
     <mergeCell ref="D122:AK122"/>
     <mergeCell ref="Q31:S31"/>
     <mergeCell ref="AC38:AE38"/>
+    <mergeCell ref="B136:AK136"/>
     <mergeCell ref="Y32:AB32"/>
     <mergeCell ref="D78:L78"/>
     <mergeCell ref="J12:AK12"/>
@@ -10172,15 +10410,14 @@
     <mergeCell ref="C183:AK183"/>
     <mergeCell ref="Y62:AE62"/>
     <mergeCell ref="D73:L73"/>
-    <mergeCell ref="C133:AK133"/>
     <mergeCell ref="M70:P70"/>
     <mergeCell ref="M35:P35"/>
     <mergeCell ref="AC41:AE41"/>
+    <mergeCell ref="C176:AK176"/>
     <mergeCell ref="Y64:AE64"/>
     <mergeCell ref="J2:P3"/>
     <mergeCell ref="AF77:AK77"/>
     <mergeCell ref="Y50:AB50"/>
-    <mergeCell ref="C178:AK178"/>
     <mergeCell ref="M74:P74"/>
     <mergeCell ref="T34:X34"/>
     <mergeCell ref="Q42:S42"/>
@@ -10201,6 +10438,7 @@
     <mergeCell ref="Y75:AE75"/>
     <mergeCell ref="Y42:AB42"/>
     <mergeCell ref="AF32:AK32"/>
+    <mergeCell ref="AF88:AK88"/>
     <mergeCell ref="Z2:AC3"/>
     <mergeCell ref="AF26:AK26"/>
     <mergeCell ref="C24:L24"/>
@@ -10209,7 +10447,6 @@
     <mergeCell ref="T83:X83"/>
     <mergeCell ref="D153:AK153"/>
     <mergeCell ref="Q45:S45"/>
-    <mergeCell ref="C99:AK99"/>
     <mergeCell ref="Q32:S32"/>
     <mergeCell ref="C26:L26"/>
     <mergeCell ref="AC48:AE48"/>
@@ -10226,10 +10463,10 @@
     <mergeCell ref="Q63:S63"/>
     <mergeCell ref="Q50:S50"/>
     <mergeCell ref="Y70:AE70"/>
-    <mergeCell ref="C136:AK136"/>
     <mergeCell ref="Y57:AE57"/>
     <mergeCell ref="T42:X42"/>
     <mergeCell ref="AF45:AK45"/>
+    <mergeCell ref="B93:I93"/>
     <mergeCell ref="D143:AK143"/>
     <mergeCell ref="C37:L37"/>
     <mergeCell ref="T78:X78"/>
@@ -10240,20 +10477,19 @@
     <mergeCell ref="T44:X44"/>
     <mergeCell ref="T80:X80"/>
     <mergeCell ref="J8:AK8"/>
-    <mergeCell ref="B101:I101"/>
+    <mergeCell ref="B186:AK186"/>
     <mergeCell ref="AF40:AK40"/>
     <mergeCell ref="T79:X79"/>
+    <mergeCell ref="C146:AK146"/>
     <mergeCell ref="D67:L67"/>
     <mergeCell ref="T73:X73"/>
     <mergeCell ref="J10:AK10"/>
     <mergeCell ref="Y83:AE83"/>
     <mergeCell ref="D159:AK159"/>
-    <mergeCell ref="C105:AK105"/>
     <mergeCell ref="D69:L69"/>
     <mergeCell ref="M31:P31"/>
     <mergeCell ref="Y85:AE85"/>
     <mergeCell ref="Y60:AE60"/>
-    <mergeCell ref="B104:I104"/>
     <mergeCell ref="N16:AK16"/>
     <mergeCell ref="D154:AK154"/>
     <mergeCell ref="C149:AK149"/>
@@ -10264,7 +10500,6 @@
     <mergeCell ref="D162:AK162"/>
     <mergeCell ref="M26:P26"/>
     <mergeCell ref="D156:AK156"/>
-    <mergeCell ref="B176:AK176"/>
     <mergeCell ref="Q40:S40"/>
     <mergeCell ref="AC26:AE26"/>
     <mergeCell ref="D87:L87"/>
@@ -10279,20 +10514,19 @@
     <mergeCell ref="C177:AK177"/>
     <mergeCell ref="AF46:AK46"/>
     <mergeCell ref="Q66:S66"/>
+    <mergeCell ref="B99:I99"/>
     <mergeCell ref="Y73:AE73"/>
     <mergeCell ref="J15:M15"/>
     <mergeCell ref="C47:L47"/>
     <mergeCell ref="AD1:AG1"/>
     <mergeCell ref="T70:X70"/>
     <mergeCell ref="AF61:AK61"/>
-    <mergeCell ref="D111:AK111"/>
-    <mergeCell ref="B92:I92"/>
     <mergeCell ref="AF48:AK48"/>
     <mergeCell ref="Q68:S68"/>
     <mergeCell ref="C40:L40"/>
     <mergeCell ref="T81:X81"/>
     <mergeCell ref="C51:L51"/>
-    <mergeCell ref="D150:AK150"/>
+    <mergeCell ref="C91:AK91"/>
     <mergeCell ref="M28:P28"/>
     <mergeCell ref="D77:L77"/>
     <mergeCell ref="Q72:S72"/>
@@ -10304,16 +10538,18 @@
     <mergeCell ref="M29:P29"/>
     <mergeCell ref="M23:P23"/>
     <mergeCell ref="D72:L72"/>
+    <mergeCell ref="B105:I105"/>
     <mergeCell ref="N17:AK17"/>
     <mergeCell ref="T63:X63"/>
     <mergeCell ref="M71:P71"/>
     <mergeCell ref="D164:AK164"/>
     <mergeCell ref="Y38:AB38"/>
+    <mergeCell ref="B178:AK178"/>
     <mergeCell ref="T71:X71"/>
     <mergeCell ref="Y24:AB24"/>
     <mergeCell ref="Q41:S41"/>
-    <mergeCell ref="D172:AK172"/>
     <mergeCell ref="Q1:U1"/>
+    <mergeCell ref="D88:L88"/>
     <mergeCell ref="AF36:AK36"/>
     <mergeCell ref="Q56:S56"/>
     <mergeCell ref="Q43:S43"/>
@@ -10322,22 +10558,22 @@
     <mergeCell ref="T31:X31"/>
     <mergeCell ref="Y79:AE79"/>
     <mergeCell ref="AF67:AK67"/>
+    <mergeCell ref="C106:AK106"/>
     <mergeCell ref="C46:L46"/>
     <mergeCell ref="Y81:AE81"/>
     <mergeCell ref="M45:P45"/>
     <mergeCell ref="AF69:AK69"/>
     <mergeCell ref="Q67:S67"/>
-    <mergeCell ref="C170:AK170"/>
     <mergeCell ref="D125:AK125"/>
     <mergeCell ref="C48:L48"/>
     <mergeCell ref="AF62:AK62"/>
     <mergeCell ref="D112:AK112"/>
     <mergeCell ref="M47:P47"/>
     <mergeCell ref="Q69:S69"/>
+    <mergeCell ref="B102:I102"/>
     <mergeCell ref="N14:AK14"/>
     <mergeCell ref="Y76:AE76"/>
     <mergeCell ref="D127:AK127"/>
-    <mergeCell ref="C84:C87"/>
     <mergeCell ref="AF64:AK64"/>
     <mergeCell ref="D114:AK114"/>
     <mergeCell ref="AF51:AK51"/>
@@ -10370,7 +10606,10 @@
     <mergeCell ref="T47:X47"/>
     <mergeCell ref="AC34:AE34"/>
     <mergeCell ref="M50:P50"/>
+    <mergeCell ref="C172:AK172"/>
+    <mergeCell ref="D133:AK133"/>
     <mergeCell ref="M68:P68"/>
+    <mergeCell ref="C184:AK184"/>
     <mergeCell ref="C171:AK171"/>
     <mergeCell ref="M67:P67"/>
     <mergeCell ref="M48:P48"/>
@@ -10385,7 +10624,9 @@
     <mergeCell ref="M81:P81"/>
     <mergeCell ref="V2:Y3"/>
     <mergeCell ref="T27:X27"/>
+    <mergeCell ref="C135:AK135"/>
     <mergeCell ref="B7:I7"/>
+    <mergeCell ref="Q88:S88"/>
     <mergeCell ref="Q26:S26"/>
     <mergeCell ref="T49:X49"/>
     <mergeCell ref="M38:P38"/>
@@ -10393,6 +10634,7 @@
     <mergeCell ref="AF83:AK83"/>
     <mergeCell ref="AF58:AK58"/>
     <mergeCell ref="Q65:S65"/>
+    <mergeCell ref="C97:AK97"/>
     <mergeCell ref="AF85:AK85"/>
     <mergeCell ref="D123:AK123"/>
     <mergeCell ref="C83:L83"/>
@@ -10401,11 +10643,10 @@
     <mergeCell ref="D68:L68"/>
     <mergeCell ref="AC49:AE49"/>
     <mergeCell ref="AC36:AE36"/>
+    <mergeCell ref="D174:AK174"/>
     <mergeCell ref="Y35:AB35"/>
     <mergeCell ref="D59:L59"/>
     <mergeCell ref="Q37:S37"/>
-    <mergeCell ref="C110:AK110"/>
-    <mergeCell ref="C181:AK181"/>
     <mergeCell ref="M77:P77"/>
     <mergeCell ref="AF29:AK29"/>
   </mergeCells>
@@ -10580,7 +10821,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/08/04</t>
+          <t>2026/08/17</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -12774,7 +13015,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/08/04</t>
+          <t>2026/08/17</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -15386,7 +15627,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/08/04</t>
+          <t>2026/08/17</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -17132,7 +17373,7 @@
     <row r="86" ht="90" customHeight="1">
       <c r="C86" s="41" t="inlineStr">
         <is>
-          <t>**新予約の挿入（新規予約・予約変更のみ）**：Phase 1 の予約行を1件挿入する（`insertScheduledKaiyaku`）。最小限のみ override：`部数=0`・`zougen_hokoku_flg=true`・`中止日`・`適用日=中止日`・`kaiyaku_flg=false`・`saishin_data_flg=false`・`shinki_flg=false`・`torikeshi_flg=false`。その他項目は直前行から継承。</t>
+          <t>**新予約の挿入（新規予約・予約変更のみ）**：Phase 1 の予約行を1件挿入する（`insertScheduledKaiyaku`）。最小限のみ override：`部数=0`・`zougen_hokoku_flg=true`・`dokusya_chushi_date=中止日`・`kaiyaku_flg=false`・`saishin_data_flg=false`・`shinki_flg=false`・`torikeshi_flg=false`。その他項目は直前行から継承。</t>
         </is>
       </c>
     </row>
